--- a/環保旅宿_Selenium結果.xlsx
+++ b/環保旅宿_Selenium結果.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026/12/28</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2028/01/06</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2028/12/28</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2028/12/11</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2028/09/16</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2028/09/03</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026/09/10</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2029/01/05</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2027/10/13</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026/10/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2028/06/25</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2028/12/17</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2027/12/10</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2029/01/18</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026/08/27</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2029/02/09</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026/11/16</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2028/06/15</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2027/04/14</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2028/02/13</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2028/10/12</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2027/05/12</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2028/09/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2028/01/06</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2027/12/20</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2029/03/02</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026/10/16</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026/12/10</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2027/06/02</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2028/09/16</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026/12/14</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026/12/14</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2028/07/17</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2028/12/11</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2028/05/28</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2028/03/13</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026/12/21</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2028/08/31</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026/08/10</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2028/09/08</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2027/05/22</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026/10/30</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2027/06/03</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2027/06/21</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2029/05/24</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2029/02/11</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2029/05/05</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2029/02/25</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2027/01/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2027/01/18</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2028/07/13</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2029/02/05</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2027/04/07</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2028/12/01</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2029/06/21</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2029/06/09</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026/11/05</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2029/04/19</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2027/07/09</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026/11/16</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7824,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2028/01/19</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7861,7 +7861,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2027/11/19</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2029/01/25</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2027/11/04</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2027/11/04</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2027/01/09</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8268,7 +8268,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2028/01/05</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2027/12/17</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2027/08/12</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2028/08/14</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2028/05/28</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2029/03/19</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2027/11/10</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2029/07/09</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2027/12/03</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2029/03/17</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2027/11/10</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2027/12/11</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2027/02/27</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2028/09/08</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2027/09/01</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9045,7 +9045,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2028/12/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2028/12/03</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2027/06/03</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2028/05/27</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2029/08/03</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2029/02/10</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026/12/05</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2028/03/09</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2029/04/12</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2027/11/06</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2027/02/16</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2028/08/24</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9600,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2029/05/10</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2029/01/07</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2029/01/22</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2028/10/12</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2029/01/18</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>

--- a/環保旅宿_Selenium結果.xlsx
+++ b/環保旅宿_Selenium結果.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G258"/>
+  <dimension ref="A1:G260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/12/28</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/01/06</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2027/11/28</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -2101,32 +2101,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>臺北花園大酒店</t>
+          <t>臺北旅人國際青年旅館</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路2段1號</t>
+          <t>新北市淡水區三民街22、22之1、22之2、22之3、22之4號</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(02)23143300#3151</t>
+          <t>(02)26258222</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026/08/30</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -2138,32 +2138,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>臺北旅人國際青年旅館</t>
+          <t>臺北時代寓所</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>新北市淡水區三民街22、22之1、22之2、22之3、22之4號</t>
+          <t>臺北市中正區林森南路7號1至14樓，7-1號1樓</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(02)26258222</t>
+          <t>(02)77521801</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2028/09/29</t>
         </is>
       </c>
     </row>
@@ -2175,22 +2175,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>臺北時代寓所</t>
+          <t>臺北新板希爾頓酒店</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>臺北市中正區林森南路7號1至14樓，7-1號1樓</t>
+          <t>新北市板橋區民權路88號、88號（2至31樓）90號</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(02)77521801</t>
+          <t>(02)29583000#7702</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2028/09/29</t>
+          <t>2028/03/31</t>
         </is>
       </c>
     </row>
@@ -2212,32 +2212,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>臺北新板希爾頓酒店</t>
+          <t>臺北萬豪酒店</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>新北市板橋區民權路88號、88號（2至31樓）90號</t>
+          <t>臺北市中山區樂群二路199號</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(02)29583000#7702</t>
+          <t>(02)21757999#1701</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2028/03/31</t>
+          <t>2028/12/07</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>臺北萬豪酒店</t>
+          <t>臺北遠東香格里拉</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2259,22 +2259,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>臺北市中山區樂群二路199號</t>
+          <t>臺北市大安區敦化南路二段201號</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(02)21757999#1701</t>
+          <t>(02)23788888#6608</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2028/12/07</t>
+          <t>2027/12/12</t>
         </is>
       </c>
     </row>
@@ -2286,22 +2286,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>臺北遠東香格里拉</t>
+          <t>臺東Deer  House民宿</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>臺北市大安區敦化南路二段201號</t>
+          <t>臺東縣鹿野鄉永安村1鄰永安路７１號</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(02)23788888#6608</t>
+          <t>(089)552224</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2027/12/12</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -2323,32 +2323,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>臺東Deer  House民宿</t>
+          <t>臺南大員皇冠假日酒店</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>臺東縣鹿野鄉永安村1鄰永安路７１號</t>
+          <t>臺南市安平區州平路289號</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(089)552224</t>
+          <t>(06)5121888#6002</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>臺南大員皇冠假日酒店</t>
+          <t>臺南大飯店</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2370,22 +2370,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>臺南市安平區州平路289號</t>
+          <t>臺南市中西區成功路1號</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(06)5121888#6002</t>
+          <t>(06)2289101#2012</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2028/01/09</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>臺南大飯店</t>
+          <t>臺南安平雅樂軒酒店</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2407,22 +2407,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>臺南市中西區成功路1號</t>
+          <t>臺南市安平區光州路108號2-12樓、光州路108之1號</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(06)2289101#2012</t>
+          <t>(06)3905000#8600</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>臺南安平雅樂軒酒店</t>
+          <t>臺南老爺行旅</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>臺南市安平區光州路108號2-12樓、光州路108之1號</t>
+          <t>臺南市東區中華東路一段368號1樓、6-10樓</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(06)3905000#8600</t>
+          <t>(06)2361680#301</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2028/12/18</t>
+          <t>2028/02/19</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>臺南老爺行旅</t>
+          <t>臺南遠東香格里拉</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>臺南市東區中華東路一段368號1樓、6-10樓</t>
+          <t>臺南市東區大學路西段89號</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(06)2361680#301</t>
+          <t>(06)7028888#6903</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2028/02/19</t>
+          <t>2026/12/30</t>
         </is>
       </c>
     </row>
@@ -2508,22 +2508,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>臺南遠東香格里拉</t>
+          <t>臺糖臺北會館</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>臺南市東區大學路西段89號</t>
+          <t>臺北市中正區中華路一段39號3至5樓</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(06)7028888#6903</t>
+          <t>(02)23885522#5001</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2027/03/10</t>
         </is>
       </c>
     </row>
@@ -2545,22 +2545,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>臺糖臺北會館</t>
+          <t>臺糖花蓮旅館</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路一段39號3至5樓</t>
+          <t>花蓮縣光復鄉大進村糖廠街19號</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(02)23885522#5001</t>
+          <t>(03)8704125#621</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2027/03/10</t>
+          <t>2027/03/21</t>
         </is>
       </c>
     </row>
@@ -2582,22 +2582,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>臺糖花蓮旅館</t>
+          <t>臺糖長榮酒店(臺南)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>花蓮縣光復鄉大進村糖廠街19號</t>
+          <t>臺南市東區中華東路三段336巷1號</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(03)8704125#621</t>
+          <t>(06)3378888</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2027/03/21</t>
+          <t>2026/11/28</t>
         </is>
       </c>
     </row>
@@ -2619,22 +2619,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>臺糖長榮酒店(臺南)</t>
+          <t>臺灣糖業股份有限公司池上牧野渡假村</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>臺南市東區中華東路三段336巷1號</t>
+          <t>臺東縣池上鄉新興村新興110號</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(06)3378888</t>
+          <t>(089)862736#1001</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2028/04/15</t>
         </is>
       </c>
     </row>
@@ -2656,32 +2656,32 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>臺灣糖業股份有限公司池上牧野渡假村</t>
+          <t>四季時光</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>臺東縣池上鄉新興村新興110號</t>
+          <t>南投縣魚池鄉頭社村平和巷103-11號</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(089)862736#1001</t>
+          <t>(0932)376767</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2028/04/15</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -2693,32 +2693,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>四季時光</t>
+          <t>巨蛋旅店</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉頭社村平和巷103-11號</t>
+          <t>高雄市鼓山區文忠路1號</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>(0932)376767</t>
+          <t>(07)5868388#0</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2028/10/07</t>
         </is>
       </c>
     </row>
@@ -2730,32 +2730,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>巨蛋旅店</t>
+          <t>打個蛋海旅民宿</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>高雄市鼓山區文忠路1號</t>
+          <t>臺東縣太麻里鄉金崙4鄰129號</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>(07)5868388#0</t>
+          <t>(089)771551</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2028/10/07</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>打個蛋海旅民宿</t>
+          <t>正好友生態環保旅店</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>臺東縣太麻里鄉金崙4鄰129號</t>
+          <t>屏東縣琉球鄉中山路153號</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(089)771551</t>
+          <t>(0886)12270</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2029/03/26</t>
         </is>
       </c>
     </row>
@@ -2804,32 +2804,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>正好友生態環保旅店</t>
+          <t>伊塔原旅臺東縣原住民文化會館</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>屏東縣琉球鄉中山路153號</t>
+          <t>臺東縣台東市中山路10號</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(0886)12270</t>
+          <t>(089)34060</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2029/03/26</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -2841,32 +2841,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>甲桂林商務旅館</t>
+          <t>兆品酒店</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>桃園市蘆竹區桃園街106號</t>
+          <t>嘉義市文化路257號B2-9F</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>03-3116799</t>
+          <t>(05)2292883#3130</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026/08/29</t>
+          <t>2028/03/30</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>伊塔原旅臺東縣原住民文化會館</t>
+          <t>好室民宿</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>臺東縣台東市中山路10號</t>
+          <t>臺東縣台東市中正路251巷9號</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(089)34060</t>
+          <t>(0905)583758</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/01/29</t>
         </is>
       </c>
     </row>
@@ -2915,32 +2915,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>兆品酒店</t>
+          <t>如一家精緻民宿</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>嘉義市文化路257號B2-9F</t>
+          <t>金門縣金城鎮珠浦北路35-1號</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(05)2292883#3130</t>
+          <t>(082)322167</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2028/03/30</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -2952,22 +2952,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>好室民宿</t>
+          <t>安樓文旅</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>基隆市</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>臺東縣台東市中正路251巷9號</t>
+          <t>基隆市仁愛區仁三路11-4</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(0905)583758</t>
+          <t>(02)24200220</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2027/01/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -2989,22 +2989,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>如一家精緻民宿</t>
+          <t>老公老婆友善民宿</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>金門縣金城鎮珠浦北路35-1號</t>
+          <t>宜蘭縣冬山鄉境安路345號</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(082)322167</t>
+          <t>(03) 9519013</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -3026,22 +3026,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>安樓文旅</t>
+          <t>老爺大酒店</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>基隆市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>基隆市仁愛區仁三路11-4</t>
+          <t>臺北市中山區中山北路2段37-1號</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(02)24200220</t>
+          <t>(02)25423299#359</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2029/07/09</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -3063,32 +3063,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>老公老婆友善民宿</t>
+          <t>西湖渡假大飯店</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>宜蘭縣冬山鄉境安路345號</t>
+          <t>苗栗縣三義鄉西湖村西湖11號</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(03) 9519013</t>
+          <t>(037)876699#1122</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026/12/28</t>
+          <t>2029/05/24</t>
         </is>
       </c>
     </row>
@@ -3100,32 +3100,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>老爺大酒店</t>
+          <t>亞昕福朋喜來登酒店</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路2段37-1號</t>
+          <t>新北市林口區文化三路一段1號、1號2樓、1號3樓</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(02)25423299#359</t>
+          <t>(02)77276961</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2028/09/25</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>西湖渡假大飯店</t>
+          <t>享沐時光</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3147,22 +3147,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>苗栗縣三義鄉西湖村西湖11號</t>
+          <t>苗栗縣苑裡鎮石鎮里錦山8-1,8-2號</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(037)876699#1122</t>
+          <t>(037)742878#124</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2029/05/24</t>
+          <t>2028/07/15</t>
         </is>
       </c>
     </row>
@@ -3174,32 +3174,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>亞昕福朋喜來登酒店</t>
+          <t>享豪大飯店</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段1號、1號2樓、1號3樓</t>
+          <t>新竹縣竹北市信義街7號</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(02)77276961</t>
+          <t>(03)6565501</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2028/09/25</t>
+          <t>2026/09/10</t>
         </is>
       </c>
     </row>
@@ -3211,22 +3211,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>享沐時光</t>
+          <t>和逸．高雄中山館</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮石鎮里錦山8-1,8-2號</t>
+          <t>高雄市前鎮區中山二路260號22-29樓</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(037)742878#124</t>
+          <t>(07)9756670</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2028/07/15</t>
+          <t>2028/09/10</t>
         </is>
       </c>
     </row>
@@ -3248,32 +3248,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>享豪大飯店</t>
+          <t>和逸·臺南西門館</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>新竹縣竹北市信義街7號</t>
+          <t>臺南市中西區西門路一段658之2號4樓至13樓</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>(03)6565501</t>
+          <t>(06)7026685</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026/09/10</t>
+          <t>2028/02/19</t>
         </is>
       </c>
     </row>
@@ -3285,22 +3285,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>和逸．高雄中山館</t>
+          <t>和逸飯店桃園青埔館</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>高雄市前鎮區中山二路260號22-29樓</t>
+          <t>桃園市中壢區春德路101號</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>(07)9756670</t>
+          <t>(03)2737692#2102</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2028/09/10</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -3322,32 +3322,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>和逸·臺南西門館</t>
+          <t>尚順君樂飯店</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>臺南市中西區西門路一段658之2號4樓至13樓</t>
+          <t>苗栗縣頭份市育樂街6號</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>(06)7026685</t>
+          <t>(037)539999#8611</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2028/02/19</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -3359,32 +3359,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>和逸飯店桃園青埔館</t>
+          <t>幸福蝸牛</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>桃園市中壢區春德路101號</t>
+          <t>宜蘭縣五結鄉利澤西路6號</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(03)2737692#2102</t>
+          <t>(03)9500047</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -3396,32 +3396,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>尚順君樂飯店</t>
+          <t>承萬尊爵渡假酒店</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>苗栗縣頭份市育樂街6號</t>
+          <t>南投縣埔里鎮樹人路131號</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(037)539999#8611</t>
+          <t>(049)2995757#6316</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2029/07/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -3433,22 +3433,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>幸福蝸牛</t>
+          <t>林口維多利亞民宿</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉利澤西路6號</t>
+          <t>桃園市蘆竹區坑子里14鄰八德二路280巷11號</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>(03)9500047</t>
+          <t>(0905)111918</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2029/08/24</t>
         </is>
       </c>
     </row>
@@ -3470,32 +3470,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>承萬尊爵渡假酒店</t>
+          <t>板橋凱撒大飯店</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>南投縣埔里鎮樹人路131號</t>
+          <t>新北市板橋區縣民大道二段8號</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>(049)2995757#6316</t>
+          <t>(02)29583000#7701</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2027/04/07</t>
+          <t>2029/02/12</t>
         </is>
       </c>
     </row>
@@ -3507,32 +3507,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>板橋凱撒大飯店</t>
+          <t>武陵國民賓館</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>新北市板橋區縣民大道二段8號</t>
+          <t>臺中市和平區平等里武陵路3-1號</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>(02)29583000#7701</t>
+          <t>(04)25901258#2103</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2029/02/12</t>
+          <t>2026/12/25</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>武陵國民賓館</t>
+          <t>武陵富野渡假村</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>臺中市和平區平等里武陵路3-1號</t>
+          <t>臺中市和平區武陵路3-16號</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>(04)25901258#2103</t>
+          <t>(04)25901399#8912</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026/12/25</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -3581,32 +3581,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>武陵富野渡假村</t>
+          <t>河那灣</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>臺中市和平區武陵路3-16號</t>
+          <t>桃園市復興區澤仁里3鄰溪口台41號</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(04)25901399#8912</t>
+          <t>(0919)235303</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2027/07/25</t>
         </is>
       </c>
     </row>
@@ -3618,22 +3618,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>河那灣</t>
+          <t>波西米亞民宿</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>桃園市復興區澤仁里3鄰溪口台41號</t>
+          <t>花蓮縣吉安鄉東昌村13鄰東海一街168號</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(0919)235303</t>
+          <t>(0385)31234</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2027/07/25</t>
+          <t>2029/01/06</t>
         </is>
       </c>
     </row>
@@ -3655,22 +3655,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>波西米亞民宿</t>
+          <t>泡泡森林民宿</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>花蓮縣吉安鄉東昌村13鄰東海一街168號</t>
+          <t>臺東縣台東市南一街40號</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(0385)31234</t>
+          <t>0986866545</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2029/01/06</t>
+          <t>2026/12/06</t>
         </is>
       </c>
     </row>
@@ -3692,22 +3692,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>泡泡森林民宿</t>
+          <t>泊寓</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>臺東縣台東市南一街40號</t>
+          <t>彰化縣鹿港鎮鹿興路57巷3號</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0986866545</t>
+          <t>(04)7115655#120</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026/12/06</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>泊寓</t>
+          <t>爸爸萬歲民宿</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮鹿興路57巷3號</t>
+          <t>花蓮縣花蓮市延平街68巷27號</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>(04)7115655#120</t>
+          <t>(0900)757520</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2027/01/10</t>
         </is>
       </c>
     </row>
@@ -3766,22 +3766,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>爸爸萬歲民宿</t>
+          <t>迎曦大飯店</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市延平街68巷27號</t>
+          <t>新竹市東區親仁里文化街10號2-10樓</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(0900)757520</t>
+          <t>(03)5347266#124</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2027/01/10</t>
+          <t>2028/04/28</t>
         </is>
       </c>
     </row>
@@ -3803,32 +3803,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>迎曦大飯店</t>
+          <t>金湖飯店</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>新竹市東區親仁里文化街10號2-10樓</t>
+          <t>金門縣金湖鎮太湖路二段218號</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>(03)5347266#124</t>
+          <t>(082)379666#160</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2028/04/28</t>
+          <t>2026/12/03</t>
         </is>
       </c>
     </row>
@@ -3840,22 +3840,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>金湖飯店</t>
+          <t>長榮文苑酒店(嘉義)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>金門縣金湖鎮太湖路二段218號</t>
+          <t>嘉義縣太保市東勢里故宮大道777號</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(082)379666#160</t>
+          <t>(05)3669988#2700</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026/12/03</t>
+          <t>2027/04/11</t>
         </is>
       </c>
     </row>
@@ -3877,22 +3877,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>長榮文苑酒店(嘉義)</t>
+          <t>長榮桂冠酒店(臺中)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>嘉義縣太保市東勢里故宮大道777號</t>
+          <t>臺中市西屯區臺灣大道二段666號</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(05)3669988#2700</t>
+          <t>(04)23242236#2700</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2027/04/11</t>
+          <t>2027/07/09</t>
         </is>
       </c>
     </row>
@@ -3914,22 +3914,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(臺中)</t>
+          <t>長榮桂冠酒店(臺北)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>臺中市西屯區臺灣大道二段666號</t>
+          <t>臺北市中山區松江路63號</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>(04)23242236#2700</t>
+          <t>(02)25019988#2701</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2027/07/09</t>
+          <t>2028/10/22</t>
         </is>
       </c>
     </row>
@@ -3951,32 +3951,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(臺北)</t>
+          <t>長榮桂冠酒店(基隆)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>基隆市</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>臺北市中山區松江路63號</t>
+          <t>基隆市中正區中正路62號之1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>(02)25019988#2701</t>
+          <t>(02)24279988</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2028/10/22</t>
+          <t>2028/05/22</t>
         </is>
       </c>
     </row>
@@ -3988,22 +3988,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(基隆)</t>
+          <t>長榮鳳凰酒店(礁溪)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>基隆市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>基隆市中正區中正路62號之1</t>
+          <t>宜蘭縣礁溪鄉健康路77號</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(02)24279988</t>
+          <t>(03)9100988#2335</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2028/05/22</t>
+          <t>2027/09/15</t>
         </is>
       </c>
     </row>
@@ -4025,32 +4025,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>長榮鳳凰酒店(礁溪)</t>
+          <t>阿里山東方明珠國際大飯店</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉健康路77號</t>
+          <t>嘉義縣中埔鄉社口村檨仔林23號</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>(03)9100988#2335</t>
+          <t>(05)2536999</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2027/09/15</t>
+          <t>2027/12/12</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>阿里山東方明珠國際大飯店</t>
+          <t>阿里山英迪格酒店</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4072,22 +4072,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>嘉義縣中埔鄉社口村檨仔林23號</t>
+          <t>嘉義縣番路鄉公田村2鄰龍頭20號2樓之1等10筆</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>(05)2536999</t>
+          <t>(05)2586800#121</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2027/12/12</t>
+          <t>2028/10/21</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>阿里山英迪格酒店</t>
+          <t>阿里山賓館（現代館）</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>嘉義縣番路鄉公田村2鄰龍頭20號2樓之1等10筆</t>
+          <t>嘉義縣阿里山鄉香林村西阿里山16-1號</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>(05)2586800#121</t>
+          <t>(05)2679996#5117</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2028/10/21</t>
+          <t>2027/06/19</t>
         </is>
       </c>
     </row>
@@ -4136,32 +4136,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>阿里山賓館（現代館）</t>
+          <t>阿爾卑斯莊園</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>嘉義縣阿里山鄉香林村西阿里山16-1號</t>
+          <t>宜蘭縣五結鄉協和村親河路二段88巷37號</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>(05)2679996#5117</t>
+          <t>(0905)787698</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2027/06/19</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2028/09/25</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2028/08/07</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2029/01/07</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/12/28</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/12/11</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/09/16</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/09/03</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/10/13</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/10/29</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/06/25</t>
         </is>
       </c>
     </row>
@@ -5172,22 +5172,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>海霞您的家</t>
+          <t>海福花園飯店</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>新北市貢寮區仁里里14鄰仁愛路38號</t>
+          <t>金門縣金沙鎮高陽路1號</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(09)35204895</t>
+          <t>(082)353888</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/09/01</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>海灣假日酒店</t>
+          <t>海霞您的家</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5219,22 +5219,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>新北市深坑區北深路3段265號</t>
+          <t>新北市貢寮區仁里里14鄰仁愛路38號</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>(02)77035880</t>
+          <t>(09)35204895</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>神隱國度民宿</t>
+          <t>海灣假日酒店</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5256,22 +5256,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>新北市瑞芳區崙頂路90號</t>
+          <t>新北市深坑區北深路3段265號</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(09)05788650</t>
+          <t>(02)77035880</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/12/17</t>
         </is>
       </c>
     </row>
@@ -5283,27 +5283,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>秧悦美地度假酒店</t>
+          <t>神隱國度民宿</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>花蓮縣吉安鄉干城村干城二街95-9號</t>
+          <t>新北市瑞芳區崙頂路90號</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(03)8129168#2701</t>
+          <t>(09)05788650</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5320,27 +5320,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>秘境41</t>
+          <t>秧悦美地度假酒店</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>桃園市大溪區興和里中央路41號</t>
+          <t>花蓮縣吉安鄉干城村干城二街95-9號</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>(03)3887111</t>
+          <t>(03)8129168#2701</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5357,22 +5357,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>秘境民宿</t>
+          <t>秘境41</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>屏東縣東港鎮屏東縣東港鎮水源路223號(新和段737-3地號)</t>
+          <t>桃園市大溪區興和里中央路41號</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>(08)8333345</t>
+          <t>(03)3887111</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5394,27 +5394,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>高雄中央公園英迪格酒店</t>
+          <t>秘境民宿</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>高雄市新興區中山一路4號</t>
+          <t>屏東縣東港鎮屏東縣東港鎮水源路223號(新和段737-3地號)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(07)2721555#301</t>
+          <t>(08)8333345</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>高雄洲際酒店</t>
+          <t>高雄中央公園英迪格酒店</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5441,22 +5441,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>高雄市前鎮區新光路33號 1樓、3~16樓</t>
+          <t>高雄市新興區中山一路4號</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>(07)2132006</t>
+          <t>(07)2721555#301</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/02/09</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/11/16</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/06/15</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>捷絲旅 臺南虎山館</t>
+          <t>康橋商旅臺南赤崁樓館</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5737,22 +5737,22 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>臺南市仁德區成功里5鄰文華路2段300號1~9樓，地下一、二樓</t>
+          <t>臺南市中西區赤崁里民權路二段97號1至8樓</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(06)2662218#8321</t>
+          <t>(06)2253377</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -5764,32 +5764,32 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>捷絲旅臺北三重館</t>
+          <t>康橋慢旅</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>新北市三重區三和路四段107-1號</t>
+          <t>臺南市中西區民生路二段416號</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(02)22806111#8304</t>
+          <t>(06)2805566</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -5801,32 +5801,32 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>捷絲旅西門町店</t>
+          <t>捷絲旅 臺南虎山館</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路一段41號5樓至9樓</t>
+          <t>臺南市仁德區成功里5鄰文華路2段300號1~9樓，地下一、二樓</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(02)25215000</t>
+          <t>(06)2662218#8321</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/02/13</t>
         </is>
       </c>
     </row>
@@ -5838,22 +5838,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>捷絲旅花蓮中正館</t>
+          <t>捷絲旅臺北三重館</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市主睦里14鄰中正路396號</t>
+          <t>新北市三重區三和路四段107-1號</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>(03)8900069#8104</t>
+          <t>(02)22806111#8304</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/10/12</t>
         </is>
       </c>
     </row>
@@ -5875,32 +5875,32 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>捷絲旅高雄中正館</t>
+          <t>捷絲旅西門町店</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>高雄市苓雅區中正一路134號</t>
+          <t>臺北市中正區中華路一段41號5樓至9樓</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>(07)9733587#8104</t>
+          <t>(02)25215000</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/05/12</t>
         </is>
       </c>
     </row>
@@ -5912,22 +5912,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>捷絲旅高雄站前館</t>
+          <t>捷絲旅花蓮中正館</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>高雄市新興區中山一路280號1至14樓</t>
+          <t>花蓮縣花蓮市主睦里14鄰中正路396號</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>(07)9733587#8104</t>
+          <t>(03)8900069#8104</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5949,22 +5949,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>捷絲旅臺大尊賢館</t>
+          <t>捷絲旅高雄中正館</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>臺北市大安區羅斯福路四段83號1-10樓</t>
+          <t>高雄市苓雅區中正一路134號</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(02)77355088</t>
+          <t>(07)9733587#8104</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>捷絲旅礁溪館</t>
+          <t>捷絲旅高雄站前館</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉德陽路24巷8號、10號</t>
+          <t>高雄市新興區中山一路280號1至14樓</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>(03)9102000#8104</t>
+          <t>(07)9733587#8104</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2027/01/07</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6023,22 +6023,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>清新溫泉飯店</t>
+          <t>捷絲旅臺大尊賢館</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>臺中市烏日區溫泉路2號</t>
+          <t>臺北市大安區羅斯福路四段83號1-10樓</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(04)23831088#7602</t>
+          <t>(02)77355088</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6060,22 +6060,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>統一谷關渡假村</t>
+          <t>捷絲旅礁溪館</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>臺中市和平區博愛里東關路一段188號</t>
+          <t>宜蘭縣礁溪鄉德陽路24巷8號、10號</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(04)25950000</t>
+          <t>(03)9102000#8104</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6097,27 +6097,27 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>統一渡假村</t>
+          <t>清新溫泉飯店</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>新竹縣關西鎮金山里34號</t>
+          <t>臺中市烏日區溫泉路2號</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(03)5478888</t>
+          <t>(04)23831088#7602</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6134,22 +6134,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>鹿港澄悅酒店</t>
+          <t>統一谷關渡假村</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮中正路598號1樓、5至8樓</t>
+          <t>臺中市和平區博愛里東關路一段188號</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(04)7785727</t>
+          <t>(04)25950000</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/01/06</t>
         </is>
       </c>
     </row>
@@ -6171,32 +6171,32 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>傑仕堡有氧酒店</t>
+          <t>統一渡假村</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>新北市板橋區縣民大道2段275號、275號2至17樓、277號2樓</t>
+          <t>新竹縣關西鎮金山里34號</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(02)77273000#54083</t>
+          <t>(03)5478888</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/12/20</t>
         </is>
       </c>
     </row>
@@ -6208,32 +6208,32 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>凱旋酒店</t>
+          <t>鹿港澄悅酒店</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>臺北市內湖區江南街55號3樓至9樓</t>
+          <t>彰化縣鹿港鎮中正路598號1樓、5至8樓</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>(02)87527888#6203</t>
+          <t>(04)7785727</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/03/02</t>
         </is>
       </c>
     </row>
@@ -6245,22 +6245,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>凱達大飯店</t>
+          <t>傑仕堡有氧酒店</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>臺北市萬華區艋舺大道167號1-26樓</t>
+          <t>新北市板橋區縣民大道2段275號、275號2至17樓、277號2樓</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>(02)23836789#6321</t>
+          <t>(02)77273000#54083</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/10/16</t>
         </is>
       </c>
     </row>
@@ -6282,22 +6282,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>凱撒大飯店</t>
+          <t>凱旋酒店</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁路6號</t>
+          <t>臺北市內湖區江南街55號3樓至9樓</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>(08)8861888</t>
+          <t>(02)87527888#6203</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6319,27 +6319,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>勝利127民宿</t>
+          <t>凱達大飯店</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>屏東縣屏東市勝利路127號</t>
+          <t>臺北市萬華區艋舺大道167號1-26樓</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>(08)7320099</t>
+          <t>(02)23836789#6321</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>勝利131民宿</t>
+          <t>凱撒大飯店</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6366,17 +6366,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>屏東縣屏東市勝利路131號</t>
+          <t>屏東縣恆春鎮墾丁路6號</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>(08)7320099</t>
+          <t>(08)8861888</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -6393,32 +6393,32 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>寒居酒店</t>
+          <t>勝利127民宿</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>臺北市中山區松江路116號1樓至9樓</t>
+          <t>屏東縣屏東市勝利路127號</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(02)66008000#8886</t>
+          <t>(08)7320099</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/12/14</t>
         </is>
       </c>
     </row>
@@ -6430,22 +6430,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>寒軒國際大飯店</t>
+          <t>勝利131民宿</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>高雄市苓雅區四維三路三十三號</t>
+          <t>屏東縣屏東市勝利路131號</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(0980)556224</t>
+          <t>(08)7320099</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/12/14</t>
         </is>
       </c>
     </row>
@@ -6467,32 +6467,32 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>富光大旅社</t>
+          <t>寒居酒店</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公園路19-7號</t>
+          <t>臺北市中山區松江路116號1樓至9樓</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(08)7345656</t>
+          <t>(02)66008000#8886</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/07/17</t>
         </is>
       </c>
     </row>
@@ -6504,32 +6504,32 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>富信大飯店</t>
+          <t>寒軒國際大飯店</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>新北市汐止區大同路一段152號</t>
+          <t>高雄市苓雅區四維三路三十三號</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(02)26416422#5112</t>
+          <t>(0980)556224</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/12/11</t>
         </is>
       </c>
     </row>
@@ -6541,32 +6541,32 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>尊爵大飯店</t>
+          <t>富光大旅社</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>桃園市桃園區莊敬路一段300號</t>
+          <t>屏東縣屏東市公園路19-7號</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(03)3169090#8502</t>
+          <t>(08)7345656</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/05/28</t>
         </is>
       </c>
     </row>
@@ -6578,32 +6578,32 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>尊爵天際大飯店</t>
+          <t>富信大飯店</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>桃園市蘆竹區南崁路一段108號</t>
+          <t>新北市汐止區大同路一段152號</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>(03)2228100#6081</t>
+          <t>(02)26416422#5112</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/03/13</t>
         </is>
       </c>
     </row>
@@ -6615,27 +6615,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>惠來谷關溫泉會館</t>
+          <t>尊爵大飯店</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>臺中市和平區東關路一段溫泉巷十號</t>
+          <t>桃園市桃園區莊敬路一段300號</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>(04)25951998#621</t>
+          <t>(03)3169090#8502</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -6652,22 +6652,22 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>提米好旅</t>
+          <t>尊爵天際大飯店</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>彰化縣彰化市成功路277號</t>
+          <t>桃園市蘆竹區南崁路一段108號</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>(04)7061086#9</t>
+          <t>(03)2228100#6081</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/08/31</t>
         </is>
       </c>
     </row>
@@ -6689,22 +6689,22 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>揚昊民宿</t>
+          <t>惠來谷關溫泉會館</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之6號</t>
+          <t>臺中市和平區東關路一段溫泉巷十號</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>(037)747711#9</t>
+          <t>(04)25951998#621</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6726,27 +6726,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>晶泉丰旅</t>
+          <t>提米好旅</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉溫泉路67號2至10樓</t>
+          <t>彰化縣彰化市成功路277號</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>(03)9100000#6105</t>
+          <t>(04)7061086#9</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -6763,22 +6763,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>智醫康寓</t>
+          <t>揚昊民宿</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>桃園市桃園區民生路107號1-3樓及7-20樓</t>
+          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之6號</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(03)3362575</t>
+          <t>(037)747711#9</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/09/08</t>
         </is>
       </c>
     </row>
@@ -6800,32 +6800,32 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>渴望會館</t>
+          <t>晶泉丰旅</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>桃園市龍潭區渴望路428號3-5樓</t>
+          <t>宜蘭縣礁溪鄉溫泉路67號2至10樓</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(03)4072999#7110</t>
+          <t>(03)9100000#6105</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/05/22</t>
         </is>
       </c>
     </row>
@@ -6837,32 +6837,32 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>然一酒店</t>
+          <t>智醫康寓</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>高雄市前鎮區中山二路199號</t>
+          <t>桃園市桃園區民生路107號1-3樓及7-20樓</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(07)9730186#1666</t>
+          <t>(03)3362575</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/10/30</t>
         </is>
       </c>
     </row>
@@ -6874,32 +6874,32 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>發現號特色民宿</t>
+          <t>渴望會館</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>屏東縣林邊鄉崎峰村裕後路90號</t>
+          <t>桃園市龍潭區渴望路428號3-5樓</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>(08)8750300</t>
+          <t>(03)4072999#7110</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -6911,22 +6911,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>華泰瑞苑</t>
+          <t>然一酒店</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮公園路101號</t>
+          <t>高雄市前鎮區中山二路199號</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>(08)8863666</t>
+          <t>(07)9730186#1666</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/06/03</t>
         </is>
       </c>
     </row>
@@ -6948,22 +6948,22 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>貳十二度行旅</t>
+          <t>發現號特色民宿</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>宜蘭縣蘇澳鎮信義路177號</t>
+          <t>屏東縣林邊鄉崎峰村裕後路90號</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>(03)9901888</t>
+          <t>(08)8750300</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -6985,32 +6985,32 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>陽明山天籟渡假酒店</t>
+          <t>華泰瑞苑</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>新北市金山區名流路1之6號、1之7號、1之9號、1之9號5樓及1之9號5樓之1至之8</t>
+          <t>屏東縣恆春鎮公園路101號</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>(02)24080400#1700</t>
+          <t>(08)8863666</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/06/21</t>
         </is>
       </c>
     </row>
@@ -7022,22 +7022,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>雅霖大飯店</t>
+          <t>貳十二度行旅</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市同和路100號</t>
+          <t>宜蘭縣蘇澳鎮信義路177號</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>(06)9261366</t>
+          <t>(03)9901888</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/05/24</t>
         </is>
       </c>
     </row>
@@ -7059,27 +7059,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>雲品溫泉酒店日月潭</t>
+          <t>陽明山天籟渡假酒店</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉水社村中正路23號</t>
+          <t>新北市金山區名流路1之6號、1之7號、1之9號、1之9號5樓及1之9號5樓之1至之8</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>(049)2212959</t>
+          <t>(02)24080400#1700</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -7096,22 +7096,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>雲頂國際商旅</t>
+          <t>雅霖大飯店</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>臺南市南區大同路二段530號</t>
+          <t>澎湖縣馬公市同和路100號</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>(06)2687766</t>
+          <t>(06)9261366</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -7133,32 +7133,32 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>圓山大飯店</t>
+          <t>雲品溫泉酒店日月潭</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路4段1巷1號</t>
+          <t>南投縣魚池鄉水社村中正路23號</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>(02)28861818#1007</t>
+          <t>(049)2212959</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/05/05</t>
         </is>
       </c>
     </row>
@@ -7170,22 +7170,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>奧斯卡去旅行民宿</t>
+          <t>雲頂國際商旅</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>臺東縣臺東市興安路一段167號</t>
+          <t>臺南市南區大同路二段530號</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>(0910)633944</t>
+          <t>(06)2687766</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/02/25</t>
         </is>
       </c>
     </row>
@@ -7207,32 +7207,32 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>奧斯卡民宿</t>
+          <t>圓山大飯店</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>臺東縣台東市興安路1段175號</t>
+          <t>臺北市中山區中山北路4段1巷1號</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>(0965)329000</t>
+          <t>(02)28861818#1007</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -7244,22 +7244,22 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>新竹安捷國際酒店</t>
+          <t>奧斯卡去旅行民宿</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>新竹縣竹北市復興三路二段168號14樓-18樓</t>
+          <t>臺東縣臺東市興安路一段167號</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>(03)6209777#660</t>
+          <t>(0910)633944</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -7281,22 +7281,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>新竹老爺大酒店</t>
+          <t>奧斯卡民宿</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>新竹市東區光復路一段227號</t>
+          <t>臺東縣台東市興安路1段175號</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>(03)5631285#204</t>
+          <t>(0965)329000</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>新竹喜來登大飯店</t>
+          <t>新竹安捷國際酒店</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7328,17 +7328,17 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>新竹縣竹北市光明六路東一段265號</t>
+          <t>新竹縣竹北市復興三路二段168號14樓-18樓</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>(03)6206126</t>
+          <t>(03)6209777#660</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>新竹福華大飯店</t>
+          <t>新竹老爺大酒店</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>新竹市中正路178號</t>
+          <t>新竹市東區光復路一段227號</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>(03)5282323#5303</t>
+          <t>(03)5631285#204</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7392,27 +7392,27 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>新南一二文創商行</t>
+          <t>新竹喜來登大飯店</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>桃園市大溪區中山路１２號</t>
+          <t>新竹縣竹北市光明六路東一段265號</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>(03)3884466</t>
+          <t>(03)6206126</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -7429,32 +7429,32 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>新悦花園酒店</t>
+          <t>新竹福華大飯店</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>嘉義市東區後湖里6鄰保順路69號</t>
+          <t>新竹市中正路178號</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>(05)2777266#5801</t>
+          <t>(03)5282323#5303</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/10/26</t>
         </is>
       </c>
     </row>
@@ -7466,32 +7466,32 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>溪頭福華渡假飯店-溪頭漢光樓</t>
+          <t>新南一二文創商行</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>南投縣鹿谷鄉森林巷11、12號</t>
+          <t>桃園市大溪區中山路１２號</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>(049)2612588#3005</t>
+          <t>(03)3884466</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/02/05</t>
         </is>
       </c>
     </row>
@@ -7503,32 +7503,32 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>溪邊小築民宿</t>
+          <t>新悦花園酒店</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>新北市瑞芳區祈堂路133號</t>
+          <t>嘉義市東區後湖里6鄰保順路69號</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>(02)24961191</t>
+          <t>(05)2777266#5801</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/04/07</t>
         </is>
       </c>
     </row>
@@ -7540,32 +7540,32 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>煙波大飯店臺南館</t>
+          <t>溪頭福華渡假飯店-溪頭漢光樓</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>臺南市中西區永福路1段269號1-12樓及地下一層至三層</t>
+          <t>南投縣鹿谷鄉森林巷11、12號</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>(06)2156000#1171</t>
+          <t>(049)2612588#3005</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/12/01</t>
         </is>
       </c>
     </row>
@@ -7577,32 +7577,32 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>煙波大飯店宜蘭館</t>
+          <t>溪邊小築民宿</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>宜蘭縣宜蘭市凱旋路135號 、135號2至9樓</t>
+          <t>新北市瑞芳區祈堂路133號</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>(09)9256899#1171</t>
+          <t>(02)24961191</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2029/05/06</t>
+          <t>2029/06/21</t>
         </is>
       </c>
     </row>
@@ -7614,22 +7614,22 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮太魯閣山闊館</t>
+          <t>煙波大飯店臺南館</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村草林10-7號</t>
+          <t>臺南市中西區永福路1段269號1-12樓及地下一層至三層</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>(03)8612000#1470</t>
+          <t>(06)2156000#1171</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/06/09</t>
         </is>
       </c>
     </row>
@@ -7651,22 +7651,22 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮太魯閣沁海館</t>
+          <t>煙波大飯店宜蘭館</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村6鄰草林10之6號</t>
+          <t>宜蘭縣宜蘭市凱旋路135號 、135號2至9樓</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>(03)8228835#1174</t>
+          <t>(09)9256899#1171</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2029/04/19</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮館</t>
+          <t>煙波大飯店花蓮太魯閣山闊館</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市民立里1鄰中美路142號</t>
+          <t>花蓮縣新城鄉順安村草林10-7號</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>(03)8228835#1174</t>
+          <t>(03)8612000#1470</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/11/05</t>
         </is>
       </c>
     </row>
@@ -7725,22 +7725,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>煙波花時間 宜蘭傳藝</t>
+          <t>煙波大飯店花蓮太魯閣沁海館</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉五濱路二段201號</t>
+          <t>花蓮縣新城鄉順安村6鄰草林10之6號</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>(03)9256899#1171</t>
+          <t>(03)8228835#1174</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>煙波花時間 花蓮</t>
+          <t>煙波大飯店花蓮館</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村草林10-5號2~6樓</t>
+          <t>花蓮縣花蓮市民立里1鄰中美路142號</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>(03)8612000#1470</t>
+          <t>(03)8228835#1174</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/04/19</t>
         </is>
       </c>
     </row>
@@ -7799,32 +7799,32 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>瑞穗天合國際觀光酒店</t>
+          <t>煙波花時間 宜蘭傳藝</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>花蓮縣瑞穗鄉溫泉路二段368號</t>
+          <t>宜蘭縣五結鄉五濱路二段201號</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>(03)8876000#3260</t>
+          <t>(03)9256899#1171</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/07/09</t>
         </is>
       </c>
     </row>
@@ -7836,32 +7836,32 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>裕元花園酒店</t>
+          <t>煙波花時間 花蓮</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>臺中市西屯區臺灣大道四段610號</t>
+          <t>花蓮縣新城鄉順安村草林10-5號2~6樓</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>(04)24655660#5030</t>
+          <t>(03)8612000#1470</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/11/16</t>
         </is>
       </c>
     </row>
@@ -7873,32 +7873,32 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>遇見民宿</t>
+          <t>瑞穗天合國際觀光酒店</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>屏東縣東港鎮水源路221號(新和段737-4地號)</t>
+          <t>花蓮縣瑞穗鄉溫泉路二段368號</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>(08)8333345</t>
+          <t>(03)8876000#3260</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/01/19</t>
         </is>
       </c>
     </row>
@@ -7910,27 +7910,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>頌華私墅肆區民宿</t>
+          <t>裕元花園酒店</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>澎湖縣湖西鄉許家村6鄰港子尾120之5號</t>
+          <t>臺中市西屯區臺灣大道四段610號</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>(06)9212953</t>
+          <t>(04)24655660#5030</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -7947,22 +7947,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>嘉仕特飯店</t>
+          <t>遇見民宿</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>桃園市桃園區中山路203號</t>
+          <t>屏東縣東港鎮水源路221號(新和段737-4地號)</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>(03)3343999</t>
+          <t>(08)8333345</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7984,32 +7984,32 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>嘉義富野渡假酒店</t>
+          <t>頌華私墅肆區民宿</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>嘉義縣民雄鄉三興村升學一街3、5、7、9、11、13、15、17、19、21、23、25、27號</t>
+          <t>澎湖縣湖西鄉許家村6鄰港子尾120之5號</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>(05)2721688</t>
+          <t>(06)9212953</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2028/08/12</t>
+          <t>2029/01/25</t>
         </is>
       </c>
     </row>
@@ -8021,22 +8021,22 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>嘉義智選假日酒店</t>
+          <t>嘉仕特飯店</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>嘉義市西區中興路69號B2至13層樓</t>
+          <t>桃園市桃園區中山路203號</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>(05)2335899#801</t>
+          <t>(03)3343999</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2027/11/24</t>
+          <t>2027/11/27</t>
         </is>
       </c>
     </row>
@@ -8058,32 +8058,32 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>嘉義福容voco酒店</t>
+          <t>嘉義富野渡假酒店</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>嘉義市西區世賢路一段789號B4-4樓、7樓、16樓-32樓</t>
+          <t>嘉義縣民雄鄉三興村升學一街3、5、7、9、11、13、15、17、19、21、23、25、27號</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>(05)232338971</t>
+          <t>(05)2721688</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2029/06/15</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8095,22 +8095,22 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>夢想森林親子民宿</t>
+          <t>嘉義智選假日酒店</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉三星鄉大德路二段613號</t>
+          <t>嘉義市西區中興路69號B2至13層樓</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>(03)9898113</t>
+          <t>(05)2335899#801</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/11/24</t>
         </is>
       </c>
     </row>
@@ -8132,32 +8132,32 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>榮美金鬱金香酒店</t>
+          <t>嘉義福容voco酒店</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>臺南市北區海安路三段50號</t>
+          <t>嘉義市西區世賢路一段789號B4-4樓、7樓、16樓-32樓</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>(06)2200800#6001</t>
+          <t>(05)232338971</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/06/15</t>
         </is>
       </c>
     </row>
@@ -8169,22 +8169,22 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>榮興金鬱金香酒店</t>
+          <t>夢想森林親子民宿</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>臺南市中西區民族路二段128號</t>
+          <t>宜蘭縣三星鄉三星鄉大德路二段613號</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>(06)2200800#6006</t>
+          <t>(03)9898113</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -8206,32 +8206,32 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>福美民宿</t>
+          <t>榮美金鬱金香酒店</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>臺東縣台東市精誠路241號</t>
+          <t>臺南市北區海安路三段50號</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>(089)328466</t>
+          <t>(06)2200800#6001</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/11/04</t>
         </is>
       </c>
     </row>
@@ -8243,32 +8243,32 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>福容大飯店 臺北二館</t>
+          <t>榮興金鬱金香酒店</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>新北市深坑區北深路三段236號</t>
+          <t>臺南市中西區民族路二段128號</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>(02)26620088#186</t>
+          <t>(06)2200800#6006</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/11/04</t>
         </is>
       </c>
     </row>
@@ -8280,27 +8280,27 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>福容大飯店 桃園</t>
+          <t>福美民宿</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>桃園市桃園區同安里大興西路一段200號</t>
+          <t>臺東縣台東市精誠路241號</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>(03)3265800#300</t>
+          <t>(089)328466</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -8317,27 +8317,27 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>福容大飯店 桃園機場捷運 A8</t>
+          <t>福容大飯店 臺北二館</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>桃園市龜山區復興一路2號3樓</t>
+          <t>新北市深坑區北深路三段236號</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>(03)3285688#8770</t>
+          <t>(02)26620088#186</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -8354,27 +8354,27 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>福容大飯店 高雄</t>
+          <t>福容大飯店 桃園</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區五福四路45號</t>
+          <t>桃園市桃園區同安里大興西路一段200號</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>(07)5317777#7782</t>
+          <t>(03)3265800#300</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -8391,32 +8391,32 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>福容大飯店 淡水漁人碼頭</t>
+          <t>福容大飯店 桃園機場捷運 A8</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>新北市淡水區觀海路83號</t>
+          <t>桃園市龜山區復興一路2號3樓</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>(02)2805 9958#8178</t>
+          <t>(03)3285688#8770</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2028/11/16</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -8428,22 +8428,22 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>福容大飯店　福隆</t>
+          <t>福容大飯店 高雄</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>新北市貢寮區福隆里福隆街41號</t>
+          <t>高雄市鹽埕區五福四路45號</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>(02)24992381</t>
+          <t>(07)5317777#7782</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/08/14</t>
         </is>
       </c>
     </row>
@@ -8465,32 +8465,32 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>福容大飯店 墾丁</t>
+          <t>福容大飯店 淡水漁人碼頭</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮船帆路1000號</t>
+          <t>新北市淡水區觀海路83號</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>(08)8856969#340</t>
+          <t>(02)2805 9958#8178</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/11/16</t>
         </is>
       </c>
     </row>
@@ -8502,22 +8502,22 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>福容大飯店 麗寶樂園</t>
+          <t>福容大飯店　福隆</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>臺中市后里區福容路88號</t>
+          <t>新北市貢寮區福隆里福隆街41號</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>(04)25571366#8343</t>
+          <t>(02)24992381</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -8539,22 +8539,22 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>福容大飯店花蓮</t>
+          <t>福容大飯店 墾丁</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市民生路51號</t>
+          <t>屏東縣恆春鎮船帆路1000號</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>(03)8239988#7507</t>
+          <t>(08)8856969#340</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/05/28</t>
         </is>
       </c>
     </row>
@@ -8576,22 +8576,22 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>福容徠旅 水里</t>
+          <t>福容大飯店 麗寶樂園</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>南投縣水里鄉東三街51號1樓至6樓</t>
+          <t>臺中市后里區福容路88號</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>(049)2771888#5560</t>
+          <t>(04)25571366#8343</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/03/19</t>
         </is>
       </c>
     </row>
@@ -8613,22 +8613,22 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>福容徠旅林口</t>
+          <t>福容大飯店花蓮</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>桃園市龜山區文二一街68號</t>
+          <t>花蓮縣花蓮市民生路51號</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>(03)3277388#300</t>
+          <t>(03)8239988#7507</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/11/10</t>
         </is>
       </c>
     </row>
@@ -8650,22 +8650,22 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>福容徠旅高雄</t>
+          <t>福容徠旅 水里</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>高雄市前金區永恆街3號6-14樓</t>
+          <t>南投縣水里鄉東三街51號1樓至6樓</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>(07)2156688#6309</t>
+          <t>(049)2771888#5560</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/07/09</t>
         </is>
       </c>
     </row>
@@ -8687,22 +8687,22 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>福華大飯店</t>
+          <t>福容徠旅林口</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>臺北市大安區仁愛路三段160號</t>
+          <t>桃園市龜山區文二一街68號</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>(02)27002323#2411</t>
+          <t>(03)3277388#300</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -8724,32 +8724,32 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>福華石門水庫渡假飯店</t>
+          <t>福容徠旅高雄</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>桃園市龍潭區民富街176號</t>
+          <t>高雄市前金區永恆街3號6-14樓</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>(03)4714888</t>
+          <t>(07)2156688#6309</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/03/17</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>福華國際文教會館</t>
+          <t>福華大飯店</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>臺北市大安區新生南路3段30號(住宿棟1樓及5樓至14樓)</t>
+          <t>臺北市大安區仁愛路三段160號</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>(02)77122323#2340</t>
+          <t>(02)27002323#2411</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/10/26</t>
         </is>
       </c>
     </row>
@@ -8798,32 +8798,32 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>福爾摩沙遊艇酒店</t>
+          <t>福華石門水庫渡假飯店</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>臺南市安平區王城里13鄰安平路988號1至10樓</t>
+          <t>桃園市龍潭區民富街176號</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>(06)3911313</t>
+          <t>(03)4714888</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/11/10</t>
         </is>
       </c>
     </row>
@@ -8835,32 +8835,32 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>綠意山莊民宿</t>
+          <t>福華國際文教會館</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之5號</t>
+          <t>臺北市大安區新生南路3段30號(住宿棟1樓及5樓至14樓)</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>(037)747711#9</t>
+          <t>(02)77122323#2340</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/12/11</t>
         </is>
       </c>
     </row>
@@ -8872,22 +8872,22 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>綠藤輕旅</t>
+          <t>福爾摩沙遊艇酒店</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>桃園市大園區中山南路二段673號</t>
+          <t>臺南市安平區王城里13鄰安平路988號1至10樓</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>(03)2873043</t>
+          <t>(06)3911313</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/02/27</t>
         </is>
       </c>
     </row>
@@ -8909,22 +8909,22 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>維悅酒店</t>
+          <t>綠意山莊民宿</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>臺南市安平區慶平路539號 1至5樓及地下1樓</t>
+          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之5號</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>(06)2950888#1125</t>
+          <t>(037)747711#9</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8946,22 +8946,22 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>臺中逢甲智選假日酒店</t>
+          <t>綠藤輕旅</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>臺中市西屯區福星北三街33巷28號</t>
+          <t>桃園市大園區中山南路二段673號</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>(04)27083911#6101</t>
+          <t>(03)2873043</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>臺邦商旅</t>
+          <t>維悅酒店</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8993,17 +8993,17 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>臺南市安平區永華二街199號</t>
+          <t>臺南市安平區慶平路539號 1至5樓及地下1樓</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>(06)2931800#8603</t>
+          <t>(06)2950888#1125</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>遠雄悅來大飯店</t>
+          <t>臺中逢甲智選假日酒店</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>花蓮縣壽豐鄉鹽寮村山嶺18號</t>
+          <t>臺中市西屯區福星北三街33巷28號</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>(03)8123900#8266</t>
+          <t>(04)27083911#6101</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9057,27 +9057,27 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>鳳山79 背包客</t>
+          <t>臺邦商旅</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>高雄市鳳山區黃埔新村東一巷79號</t>
+          <t>臺南市安平區永華二街199號</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>(07)5524545</t>
+          <t>(06)2931800#8603</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -9094,32 +9094,32 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>劍湖山渡假大飯店</t>
+          <t>遠雄悅來大飯店</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>雲林縣古坑鄉永光村大湖口67-8號</t>
+          <t>花蓮縣壽豐鄉鹽寮村山嶺18號</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>(05)5829900#7214</t>
+          <t>(03)8123900#8266</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/12/29</t>
         </is>
       </c>
     </row>
@@ -9131,32 +9131,32 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>澎湖福朋喜來登酒店</t>
+          <t>鳳山79 背包客</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市新店路197號</t>
+          <t>高雄市鳳山區黃埔新村東一巷79號</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>(06)9279955#3701</t>
+          <t>(07)5524545</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/12/03</t>
         </is>
       </c>
     </row>
@@ -9168,32 +9168,32 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>澎澄飯店</t>
+          <t>劍湖山渡假大飯店</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市同和路168號</t>
+          <t>雲林縣古坑鄉永光村大湖口67-8號</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>(06)9235678#2103</t>
+          <t>(05)5829900#7214</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/06/03</t>
         </is>
       </c>
     </row>
@@ -9205,32 +9205,32 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>緻麗伯爵酒店</t>
+          <t>澎湖福朋喜來登酒店</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>雲林縣斗六市中山路6號</t>
+          <t>澎湖縣馬公市新店路197號</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>(05)5341666#3</t>
+          <t>(06)9279955#3701</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/05/27</t>
         </is>
       </c>
     </row>
@@ -9242,27 +9242,27 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>緣羊軒民宿</t>
+          <t>澎澄飯店</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>臺東縣台東市南一街96號</t>
+          <t>澎湖縣馬公市同和路168號</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>089326400</t>
+          <t>(06)9235678#2103</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -9279,32 +9279,32 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺北</t>
+          <t>緻麗伯爵酒店</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
+          <t>雲林縣斗六市中山路6號</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>(02)29583000#7701</t>
+          <t>(05)5341666#3</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2028/03/31</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺東</t>
+          <t>緣羊軒民宿</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>臺東縣台東市新站路260號</t>
+          <t>臺東縣台東市南一街96號</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>(089)231188#7187</t>
+          <t>089326400</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2027/12/05</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9353,32 +9353,32 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>墾丁夏都沙灘酒店</t>
+          <t>趣淘漫旅-臺北</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁路451號</t>
+          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>(0910)371823</t>
+          <t>(02)29583000#7701</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/03/31</t>
         </is>
       </c>
     </row>
@@ -9390,22 +9390,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>墾丁福華渡假飯店</t>
+          <t>趣淘漫旅-臺東</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
+          <t>臺東縣台東市新站路260號</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>(08)8862324#2701</t>
+          <t>(089)231188#7187</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/12/05</t>
         </is>
       </c>
     </row>
@@ -9427,32 +9427,32 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>橘子民宿</t>
+          <t>墾丁夏都沙灘酒店</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
+          <t>屏東縣恆春鎮墾丁路451號</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>(0972)092658</t>
+          <t>(0910)371823</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/03/09</t>
         </is>
       </c>
     </row>
@@ -9464,32 +9464,32 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>翰品酒店 高雄</t>
+          <t>墾丁福華渡假飯店</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區大仁路43號</t>
+          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>(07)5614688#3110</t>
+          <t>(08)8862324#2701</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/04/12</t>
         </is>
       </c>
     </row>
@@ -9501,32 +9501,32 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>礁溪老爺酒店</t>
+          <t>橘子民宿</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
+          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>(03)9885211#8006</t>
+          <t>(0972)092658</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/11/06</t>
         </is>
       </c>
     </row>
@@ -9538,22 +9538,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>礁溪寒沐酒店</t>
+          <t>翰品酒店 高雄</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
+          <t>高雄市鹽埕區大仁路43號</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>(03)9058007</t>
+          <t>(07)5614688#3110</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/02/16</t>
         </is>
       </c>
     </row>
@@ -9575,32 +9575,32 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>禧榕軒大飯店</t>
+          <t>礁溪老爺酒店</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>臺南市北區成功路28號</t>
+          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>(06)2222788#2203</t>
+          <t>(03)9885211#8006</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/08/24</t>
         </is>
       </c>
     </row>
@@ -9612,32 +9612,32 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>薆悅酒店野柳渡假館一館</t>
+          <t>礁溪寒沐酒店</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>新北市萬里區野柳里港東路162號之2</t>
+          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>(02)77035770#623</t>
+          <t>(03)9058007</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -9649,32 +9649,32 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>藍水輕旅</t>
+          <t>禧榕軒大飯店</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>桃園市大園區高鐵南路一段126號</t>
+          <t>臺南市北區成功路28號</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>(03)2871855</t>
+          <t>(06)2222788#2203</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/05/10</t>
         </is>
       </c>
     </row>
@@ -9686,22 +9686,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>關子嶺富野溫泉會館</t>
+          <t>薆悅酒店野柳渡假館一館</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>臺南市白河區關子嶺28號</t>
+          <t>新北市萬里區野柳里港東路162號之2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>(06)6822288</t>
+          <t>(02)77035770#623</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -9723,22 +9723,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>麗格休閒飯店</t>
+          <t>藍水輕旅</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市商校街258.260.262號</t>
+          <t>桃園市大園區高鐵南路一段126號</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>(03)8349922</t>
+          <t>(03)2871855</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/11/23</t>
         </is>
       </c>
     </row>
@@ -9760,22 +9760,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>麗軒國際飯店</t>
+          <t>關子嶺富野溫泉會館</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市中美路99之1號</t>
+          <t>臺南市白河區關子嶺28號</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>(03)8246898</t>
+          <t>(06)6822288</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/07</t>
         </is>
       </c>
     </row>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>麗翔大飯店</t>
+          <t>麗格休閒飯店</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9807,12 +9807,12 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
+          <t>花蓮縣花蓮市商校街258.260.262號</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>(03)8323737</t>
+          <t>(03)8349922</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2028/01/12</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -9834,22 +9834,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>讀好民宿</t>
+          <t>麗軒國際飯店</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
+          <t>花蓮縣花蓮市中美路99之1號</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>(0920)023139</t>
+          <t>(03)8246898</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -9871,32 +9871,32 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>觀霧山莊</t>
+          <t>麗翔大飯店</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
+          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>(03)3343818</t>
+          <t>(03)8323737</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/01/12</t>
         </is>
       </c>
     </row>
@@ -9908,27 +9908,27 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>綉溪安平</t>
+          <t>讀好民宿</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>(06)3910988#3111</t>
+          <t>(0920)023139</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -9945,32 +9945,106 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
+          <t>觀霧山莊</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>苗栗縣</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>(03)3343818</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>銀級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>查無資料</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>綉溪安平</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>臺南市</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>(06)3910988#3111</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>銀級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>2028/10/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
           <t>鐡馬騎跡</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C260" t="inlineStr">
         <is>
           <t>屏東縣</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="D260" t="inlineStr">
         <is>
           <t>屏東縣東港鎮新學路50號</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E260" t="inlineStr">
         <is>
           <t>(0952)848898</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>銅級環保旅宿</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>查無資料</t>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>2029/01/18</t>
         </is>
       </c>
     </row>

--- a/環保旅宿_Selenium結果.xlsx
+++ b/環保旅宿_Selenium結果.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G260"/>
+  <dimension ref="A1:G261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,22 +843,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>大溪老城四季行館</t>
+          <t>大板根渡假酒店</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>桃園市大溪區中央路37號</t>
+          <t>新北市三峽區插角里79號</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(03)3881818</t>
+          <t>(02)26749228#3213</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2027/12/03</t>
+          <t>2029/08/24</t>
         </is>
       </c>
     </row>
@@ -880,22 +880,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>小古堡民宿</t>
+          <t>大溪老城四季行館</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>臺東縣台東市興安路一段165號</t>
+          <t>桃園市大溪區中央路37號</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(0910)633944</t>
+          <t>(03)3881818</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2027/01/28</t>
+          <t>2027/12/03</t>
         </is>
       </c>
     </row>
@@ -917,22 +917,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>小叮噹科學遊樂區生活大師會館</t>
+          <t>小古堡民宿</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>新竹縣新豐鄉松柏村康和路199號</t>
+          <t>臺東縣台東市興安路一段165號</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(03)5592132</t>
+          <t>(0910)633944</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2028/03/17</t>
+          <t>2027/01/28</t>
         </is>
       </c>
     </row>
@@ -954,22 +954,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>小巷內</t>
+          <t>小叮噹科學遊樂區生活大師會館</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>桃園市大溪區中央路52-3號</t>
+          <t>新竹縣新豐鄉松柏村康和路199號</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(03)3881052</t>
+          <t>(03)5592132</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2029/04/08</t>
+          <t>2028/03/17</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>小烏來山莊</t>
+          <t>小巷內</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>桃園市復興區義盛里1鄰宇內路99號</t>
+          <t>桃園市大溪區中央路52-3號</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(03)3821199</t>
+          <t>(03)3881052</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2029/04/08</t>
         </is>
       </c>
     </row>
@@ -1028,22 +1028,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>小琉球古拉克民宿</t>
+          <t>小烏來山莊</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>屏東縣琉球鄉本福村中山路61-20號</t>
+          <t>桃園市復興區義盛里1鄰宇內路99號</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(08)8612229</t>
+          <t>(03)3821199</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2029/03/04</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>山形閣</t>
+          <t>小琉球古拉克民宿</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉中山路二段187號</t>
+          <t>屏東縣琉球鄉本福村中山路61-20號</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(03)9872323</t>
+          <t>(08)8612229</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2027/06/02</t>
+          <t>2029/03/04</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>山慕民宿</t>
+          <t>山形閣</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉水社村中山路216號</t>
+          <t>宜蘭縣礁溪鄉中山路二段187號</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(0925)97162</t>
+          <t>(03)9872323</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2029/06/11</t>
+          <t>2027/06/02</t>
         </is>
       </c>
     </row>
@@ -1139,22 +1139,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>山鄰山林青年文旅</t>
+          <t>山慕民宿</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮大同路226.228號</t>
+          <t>南投縣魚池鄉水社村中山路216號</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(03)8887228</t>
+          <t>(0925)97162</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2027/11/10</t>
+          <t>2029/06/11</t>
         </is>
       </c>
     </row>
@@ -1176,32 +1176,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>仁義湖岸大酒店</t>
+          <t>山鄰山林青年文旅</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>嘉義縣番路鄉內甕村後坑仔35號</t>
+          <t>花蓮縣玉里鎮大同路226.228號</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(05)2769388</t>
+          <t>(03)8887228</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2028/08/31</t>
+          <t>2027/11/10</t>
         </is>
       </c>
     </row>
@@ -1213,32 +1213,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>今古安民宿</t>
+          <t>仁義湖岸大酒店</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市重慶路353巷30號</t>
+          <t>嘉義縣番路鄉內甕村後坑仔35號</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(03)8345555</t>
+          <t>(05)2769388</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2029/01/06</t>
+          <t>2028/08/31</t>
         </is>
       </c>
     </row>
@@ -1250,32 +1250,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>天成大飯店</t>
+          <t>今古安民宿</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>臺北市中正區忠孝西路一段43號</t>
+          <t>花蓮縣花蓮市重慶路353巷30號</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(02)23118905#3705</t>
+          <t>(03)8345555</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2027/03/07</t>
+          <t>2029/01/06</t>
         </is>
       </c>
     </row>
@@ -1287,22 +1287,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>太子文旅</t>
+          <t>天成大飯店</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>臺南市東區大學路2號(3，5-10F)</t>
+          <t>臺北市中正區忠孝西路一段43號</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(06)2095199#6103</t>
+          <t>(02)23118905#3705</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2029/07/08</t>
+          <t>2027/03/07</t>
         </is>
       </c>
     </row>
@@ -1324,32 +1324,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>太平⼭莊</t>
+          <t>太子文旅</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>宜蘭縣大同鄉太平村太平巷58之1號</t>
+          <t>臺南市東區大學路2號(3，5-10F)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(03)9545114#607</t>
+          <t>(06)2095199#6103</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2027/10/15</t>
+          <t>2029/07/08</t>
         </is>
       </c>
     </row>
@@ -1361,32 +1361,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>日日森旅二館</t>
+          <t>太平⼭莊</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>彰化縣田尾鄉民族路一段185巷11號</t>
+          <t>宜蘭縣大同鄉太平村太平巷58之1號</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(04)8221669</t>
+          <t>(03)9545114#607</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/10/15</t>
         </is>
       </c>
     </row>
@@ -1398,32 +1398,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>日月潭力麗溫德姆溫泉酒店</t>
+          <t>日日森旅二館</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉日月村中正路312號</t>
+          <t>彰化縣田尾鄉民族路一段185巷11號</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(049)2850085#8802</t>
+          <t>(04)8221669</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2029/01/01</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -1435,32 +1435,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>日玥居</t>
+          <t>日月潭力麗溫德姆溫泉酒店</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>金門縣金寧鄉南山19號</t>
+          <t>南投縣魚池鄉日月村中正路312號</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(0987)397327</t>
+          <t>(049)2850085#8802</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2029/01/01</t>
         </is>
       </c>
     </row>
@@ -1472,22 +1472,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>月光寶盒旅店</t>
+          <t>日玥居</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>高雄市鳳山區黃埔新村東一巷80號</t>
+          <t>金門縣金寧鄉南山19號</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(09)33631615</t>
+          <t>(0987)397327</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2026/11/28</t>
         </is>
       </c>
     </row>
@@ -1509,32 +1509,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>北投老爺酒店</t>
+          <t>月光寶盒旅店</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>臺北市北投區中和街2號</t>
+          <t>高雄市鳳山區黃埔新村東一巷80號</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(02)28966966#8878</t>
+          <t>(09)33631615</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2028/01/06</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>北投麗禧溫泉酒店</t>
+          <t>北投老爺酒店</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>臺北市北投區幽雅路30號</t>
+          <t>臺北市北投區中和街2號</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(02)28967799#738</t>
+          <t>(02)28966966#8878</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2028/04/13</t>
+          <t>2028/01/06</t>
         </is>
       </c>
     </row>
@@ -1583,32 +1583,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>臺中李方艾美酒店</t>
+          <t>北投麗禧溫泉酒店</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>臺中市中區建國路111號</t>
+          <t>臺北市北投區幽雅路30號</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(04)22240888#81002</t>
+          <t>(02)28967799#738</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2028/11/05</t>
+          <t>2028/04/13</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>臺中金典酒店</t>
+          <t>臺中李方艾美酒店</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1630,22 +1630,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>臺中市西區健行路1049號</t>
+          <t>臺中市中區建國路111號</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(04)23288000#6692</t>
+          <t>(04)22240888#81002</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2028/11/19</t>
+          <t>2028/11/05</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>臺中港酒店</t>
+          <t>臺中金典酒店</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1667,22 +1667,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>臺中市梧棲區大智路二段388號</t>
+          <t>臺中市西區健行路1049號</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>(04)37055888#6128</t>
+          <t>(04)23288000#6692</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2029/01/18</t>
+          <t>2028/11/19</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>臺中豐邑慕奇夕酒店</t>
+          <t>臺中港酒店</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1704,22 +1704,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>臺中市西屯區文心南六路288號、288號2樓、288號3樓(地上物3至17樓)</t>
+          <t>臺中市梧棲區大智路二段388號</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(04)36007009#7099</t>
+          <t>(04)37055888#6128</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2029/05/14</t>
+          <t>2029/01/18</t>
         </is>
       </c>
     </row>
@@ -1731,32 +1731,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>臺北W飯店</t>
+          <t>臺中豐邑慕奇夕酒店</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>臺北市信義區忠孝東路五段10號</t>
+          <t>臺中市西屯區文心南六路288號、288號2樓、288號3樓(地上物3至17樓)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(02)77038765</t>
+          <t>(04)36007009#7099</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2028/08/07</t>
+          <t>2029/05/14</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>臺北士林萬麗酒店</t>
+          <t>臺北W飯店</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>臺北市士林區中山北路五段470巷8號</t>
+          <t>臺北市信義區忠孝東路五段10號</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(02)88612389</t>
+          <t>(02)77038765</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2028/07/10</t>
+          <t>2028/08/07</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>臺北中山九昱希爾頓逸林酒店</t>
+          <t>臺北士林萬麗酒店</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1815,22 +1815,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路一段121巷1之1號, 121巷1號1樓至14樓</t>
+          <t>臺北市士林區中山北路五段470巷8號</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(02)66253281</t>
+          <t>(02)88612389</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2028/07/10</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>臺北中山雅樂軒酒店</t>
+          <t>臺北中山九昱希爾頓逸林酒店</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1852,22 +1852,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>臺北市中山區雙城街1號</t>
+          <t>臺北市中山區中山北路一段121巷1之1號, 121巷1號1樓至14樓</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(02)77439900</t>
+          <t>(02)66253281</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2028/11/13</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>臺北中山意舍酒店</t>
+          <t>臺北中山雅樂軒酒店</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路二段57之1號1至8樓</t>
+          <t>臺北市中山區雙城街1號</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(02)25652828</t>
+          <t>(02)77439900</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2028/09/17</t>
+          <t>2028/11/13</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>臺北六福萬怡酒店</t>
+          <t>臺北中山意舍酒店</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>臺北市南港區忠孝東路七段359號7至30樓</t>
+          <t>臺北市中山區中山北路二段57之1號1至8樓</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(02)66156565#5000</t>
+          <t>(02)25652828</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2029/04/09</t>
+          <t>2028/09/17</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>臺北艾麗酒店</t>
+          <t>臺北六福萬怡酒店</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1963,22 +1963,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>臺北市信義區松高路18號</t>
+          <t>臺北市南港區忠孝東路七段359號7至30樓</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>(02)66318031</t>
+          <t>(02)66156565#5000</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2029/04/08</t>
+          <t>2029/04/09</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>臺北西門町意舍酒店</t>
+          <t>臺北艾麗酒店</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2000,22 +2000,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>臺北市萬華區武昌街2段77號5樓至10樓</t>
+          <t>臺北市信義區松高路18號</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>(02)23755111#2100</t>
+          <t>(02)66318031</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2028/10/22</t>
+          <t>2029/04/08</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>臺北君品大酒店</t>
+          <t>臺北西門町意舍酒店</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>臺北市大同區承德路1段3號1樓、5樓~16樓及地下1樓、地下3樓</t>
+          <t>臺北市萬華區武昌街2段77號5樓至10樓</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>(02)21819999#3142</t>
+          <t>(02)23755111#2100</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/10/22</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>臺北松山意舍酒店</t>
+          <t>臺北君品大酒店</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2074,22 +2074,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>臺北市南港區市民大道7段8號17樓至21樓</t>
+          <t>臺北市大同區承德路1段3號1樓、5樓~16樓及地下1樓、地下3樓</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(02)26532828#2100</t>
+          <t>(02)21819999#3142</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -2101,32 +2101,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>臺北旅人國際青年旅館</t>
+          <t>臺北松山意舍酒店</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>新北市淡水區三民街22、22之1、22之2、22之3、22之4號</t>
+          <t>臺北市南港區市民大道7段8號17樓至21樓</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(02)26258222</t>
+          <t>(02)26532828#2100</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2027/11/28</t>
         </is>
       </c>
     </row>
@@ -2138,32 +2138,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>臺北時代寓所</t>
+          <t>臺北旅人國際青年旅館</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>臺北市中正區林森南路7號1至14樓，7-1號1樓</t>
+          <t>新北市淡水區三民街22、22之1、22之2、22之3、22之4號</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(02)77521801</t>
+          <t>(02)26258222</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2028/09/29</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -2175,22 +2175,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>臺北新板希爾頓酒店</t>
+          <t>臺北時代寓所</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>新北市板橋區民權路88號、88號（2至31樓）90號</t>
+          <t>臺北市中正區林森南路7號1至14樓，7-1號1樓</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(02)29583000#7702</t>
+          <t>(02)77521801</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2028/03/31</t>
+          <t>2028/09/29</t>
         </is>
       </c>
     </row>
@@ -2212,32 +2212,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>臺北萬豪酒店</t>
+          <t>臺北新板希爾頓酒店</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>臺北市中山區樂群二路199號</t>
+          <t>新北市板橋區民權路88號、88號（2至31樓）90號</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(02)21757999#1701</t>
+          <t>(02)29583000#7702</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2028/12/07</t>
+          <t>2028/03/31</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>臺北遠東香格里拉</t>
+          <t>臺北萬豪酒店</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2259,22 +2259,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>臺北市大安區敦化南路二段201號</t>
+          <t>臺北市中山區樂群二路199號</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(02)23788888#6608</t>
+          <t>(02)21757999#1701</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2027/12/12</t>
+          <t>2028/12/07</t>
         </is>
       </c>
     </row>
@@ -2286,22 +2286,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>臺東Deer  House民宿</t>
+          <t>臺北遠東香格里拉</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>臺東縣鹿野鄉永安村1鄰永安路７１號</t>
+          <t>臺北市大安區敦化南路二段201號</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(089)552224</t>
+          <t>(02)23788888#6608</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2027/12/12</t>
         </is>
       </c>
     </row>
@@ -2323,32 +2323,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>臺南大員皇冠假日酒店</t>
+          <t>臺東Deer  House民宿</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>臺南市安平區州平路289號</t>
+          <t>臺東縣鹿野鄉永安村1鄰永安路７１號</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(06)5121888#6002</t>
+          <t>(089)552224</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>臺南大飯店</t>
+          <t>臺南大員皇冠假日酒店</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2370,22 +2370,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>臺南市中西區成功路1號</t>
+          <t>臺南市安平區州平路289號</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(06)2289101#2012</t>
+          <t>(06)5121888#6002</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/01/09</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>臺南安平雅樂軒酒店</t>
+          <t>臺南大飯店</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2407,22 +2407,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>臺南市安平區光州路108號2-12樓、光州路108之1號</t>
+          <t>臺南市中西區成功路1號</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(06)3905000#8600</t>
+          <t>(06)2289101#2012</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>臺南老爺行旅</t>
+          <t>臺南安平雅樂軒酒店</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>臺南市東區中華東路一段368號1樓、6-10樓</t>
+          <t>臺南市安平區光州路108號2-12樓、光州路108之1號</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(06)2361680#301</t>
+          <t>(06)3905000#8600</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2028/02/19</t>
+          <t>2028/12/18</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>臺南遠東香格里拉</t>
+          <t>臺南老爺行旅</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>臺南市東區大學路西段89號</t>
+          <t>臺南市東區中華東路一段368號1樓、6-10樓</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(06)7028888#6903</t>
+          <t>(06)2361680#301</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2028/02/19</t>
         </is>
       </c>
     </row>
@@ -2508,22 +2508,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>臺糖臺北會館</t>
+          <t>臺南遠東香格里拉</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路一段39號3至5樓</t>
+          <t>臺南市東區大學路西段89號</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(02)23885522#5001</t>
+          <t>(06)7028888#6903</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2027/03/10</t>
+          <t>2026/12/30</t>
         </is>
       </c>
     </row>
@@ -2545,22 +2545,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>臺糖花蓮旅館</t>
+          <t>臺糖臺北會館</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>花蓮縣光復鄉大進村糖廠街19號</t>
+          <t>臺北市中正區中華路一段39號3至5樓</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(03)8704125#621</t>
+          <t>(02)23885522#5001</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2027/03/21</t>
+          <t>2027/03/10</t>
         </is>
       </c>
     </row>
@@ -2582,22 +2582,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>臺糖長榮酒店(臺南)</t>
+          <t>臺糖花蓮旅館</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>臺南市東區中華東路三段336巷1號</t>
+          <t>花蓮縣光復鄉大進村糖廠街19號</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(06)3378888</t>
+          <t>(03)8704125#621</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2027/03/21</t>
         </is>
       </c>
     </row>
@@ -2619,22 +2619,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>臺灣糖業股份有限公司池上牧野渡假村</t>
+          <t>臺糖長榮酒店(臺南)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>臺東縣池上鄉新興村新興110號</t>
+          <t>臺南市東區中華東路三段336巷1號</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(089)862736#1001</t>
+          <t>(06)3378888</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2028/04/15</t>
+          <t>2026/11/28</t>
         </is>
       </c>
     </row>
@@ -2656,32 +2656,32 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>四季時光</t>
+          <t>臺灣糖業股份有限公司池上牧野渡假村</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉頭社村平和巷103-11號</t>
+          <t>臺東縣池上鄉新興村新興110號</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(0932)376767</t>
+          <t>(089)862736#1001</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2028/04/15</t>
         </is>
       </c>
     </row>
@@ -2693,32 +2693,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>巨蛋旅店</t>
+          <t>四季時光</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>高雄市鼓山區文忠路1號</t>
+          <t>南投縣魚池鄉頭社村平和巷103-11號</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>(07)5868388#0</t>
+          <t>(0932)376767</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2028/10/07</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -2730,32 +2730,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>打個蛋海旅民宿</t>
+          <t>巨蛋旅店</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>臺東縣太麻里鄉金崙4鄰129號</t>
+          <t>高雄市鼓山區文忠路1號</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>(089)771551</t>
+          <t>(07)5868388#0</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2028/10/07</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>正好友生態環保旅店</t>
+          <t>打個蛋海旅民宿</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>屏東縣琉球鄉中山路153號</t>
+          <t>臺東縣太麻里鄉金崙4鄰129號</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(0886)12270</t>
+          <t>(089)771551</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2029/03/26</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -2804,32 +2804,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>伊塔原旅臺東縣原住民文化會館</t>
+          <t>正好友生態環保旅店</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>臺東縣台東市中山路10號</t>
+          <t>屏東縣琉球鄉中山路153號</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(089)34060</t>
+          <t>(0886)12270</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/03/26</t>
         </is>
       </c>
     </row>
@@ -2841,32 +2841,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>兆品酒店</t>
+          <t>伊塔原旅臺東縣原住民文化會館</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>嘉義市文化路257號B2-9F</t>
+          <t>臺東縣台東市中山路10號</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(05)2292883#3130</t>
+          <t>(089)34060</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2028/03/30</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -2878,32 +2878,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>好室民宿</t>
+          <t>兆品酒店</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>臺東縣台東市中正路251巷9號</t>
+          <t>嘉義市文化路257號B2-9F</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(0905)583758</t>
+          <t>(05)2292883#3130</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2027/01/29</t>
+          <t>2028/03/30</t>
         </is>
       </c>
     </row>
@@ -2915,22 +2915,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>如一家精緻民宿</t>
+          <t>好室民宿</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>金門縣金城鎮珠浦北路35-1號</t>
+          <t>臺東縣台東市中正路251巷9號</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(082)322167</t>
+          <t>(0905)583758</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2027/01/29</t>
         </is>
       </c>
     </row>
@@ -2952,22 +2952,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>安樓文旅</t>
+          <t>如一家精緻民宿</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>基隆市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>基隆市仁愛區仁三路11-4</t>
+          <t>金門縣金城鎮珠浦北路35-1號</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(02)24200220</t>
+          <t>(082)322167</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -2989,22 +2989,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>老公老婆友善民宿</t>
+          <t>安樓文旅</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>基隆市</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>宜蘭縣冬山鄉境安路345號</t>
+          <t>基隆市仁愛區仁三路11-4</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(03) 9519013</t>
+          <t>(02)24200220</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/07/09</t>
         </is>
       </c>
     </row>
@@ -3026,22 +3026,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>老爺大酒店</t>
+          <t>老公老婆友善民宿</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路2段37-1號</t>
+          <t>宜蘭縣冬山鄉境安路345號</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(02)25423299#359</t>
+          <t>(03) 9519013</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/12/28</t>
         </is>
       </c>
     </row>
@@ -3063,32 +3063,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>西湖渡假大飯店</t>
+          <t>老爺大酒店</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>苗栗縣三義鄉西湖村西湖11號</t>
+          <t>臺北市中山區中山北路2段37-1號</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(037)876699#1122</t>
+          <t>(02)25423299#359</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2029/05/24</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -3100,32 +3100,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>亞昕福朋喜來登酒店</t>
+          <t>西湖渡假大飯店</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段1號、1號2樓、1號3樓</t>
+          <t>苗栗縣三義鄉西湖村西湖11號</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(02)77276961</t>
+          <t>(037)876699#1122</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2028/09/25</t>
+          <t>2029/05/24</t>
         </is>
       </c>
     </row>
@@ -3137,22 +3137,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>享沐時光</t>
+          <t>亞昕福朋喜來登酒店</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮石鎮里錦山8-1,8-2號</t>
+          <t>新北市林口區文化三路一段1號、1號2樓、1號3樓</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(037)742878#124</t>
+          <t>(02)77276961</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2028/07/15</t>
+          <t>2028/09/25</t>
         </is>
       </c>
     </row>
@@ -3174,32 +3174,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>享豪大飯店</t>
+          <t>享沐時光</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>新竹縣竹北市信義街7號</t>
+          <t>苗栗縣苑裡鎮石鎮里錦山8-1,8-2號</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(03)6565501</t>
+          <t>(037)742878#124</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026/09/10</t>
+          <t>2028/07/15</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/07/29</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/04/07</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/09/25</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/08/07</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/07</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/07/20</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/05</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/12/10</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/18</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/04/14</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/09/29</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/01/07</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/12/10</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/06/02</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/09/16</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/12/21</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/08/13</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/11/27</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/02/11</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/01/29</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/01/18</t>
         </is>
       </c>
     </row>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/07/13</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/05/06</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/04/19</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/11/19</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/08/12</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/01/09</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/01/05</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/12/17</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/08/12</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/12/03</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/09/08</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/09/01</t>
         </is>
       </c>
     </row>
@@ -9205,32 +9205,32 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>澎湖福朋喜來登酒店</t>
+          <t>澄悅商旅</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市新店路197號</t>
+          <t>彰化縣鹿港鎮埔崙里中正路510巷1號</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>(06)9279955#3701</t>
+          <t>(04)7785727</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2028/05/27</t>
+          <t>2029/09/07</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>澎澄飯店</t>
+          <t>澎湖福朋喜來登酒店</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -9252,12 +9252,12 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市同和路168號</t>
+          <t>澎湖縣馬公市新店路197號</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>(06)9235678#2103</t>
+          <t>(06)9279955#3701</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/05/27</t>
         </is>
       </c>
     </row>
@@ -9279,32 +9279,32 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>緻麗伯爵酒店</t>
+          <t>澎澄飯店</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>雲林縣斗六市中山路6號</t>
+          <t>澎湖縣馬公市同和路168號</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>(05)5341666#3</t>
+          <t>(06)9235678#2103</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/08/03</t>
         </is>
       </c>
     </row>
@@ -9316,32 +9316,32 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>緣羊軒民宿</t>
+          <t>緻麗伯爵酒店</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>臺東縣台東市南一街96號</t>
+          <t>雲林縣斗六市中山路6號</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>089326400</t>
+          <t>(05)5341666#3</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/02/10</t>
         </is>
       </c>
     </row>
@@ -9353,32 +9353,32 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺北</t>
+          <t>緣羊軒民宿</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
+          <t>臺東縣台東市南一街96號</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>(02)29583000#7701</t>
+          <t>089326400</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2028/03/31</t>
+          <t>2026/12/05</t>
         </is>
       </c>
     </row>
@@ -9390,32 +9390,32 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺東</t>
+          <t>趣淘漫旅-臺北</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>臺東縣台東市新站路260號</t>
+          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>(089)231188#7187</t>
+          <t>(02)29583000#7701</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2027/12/05</t>
+          <t>2028/03/31</t>
         </is>
       </c>
     </row>
@@ -9427,32 +9427,32 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>墾丁夏都沙灘酒店</t>
+          <t>趣淘漫旅-臺東</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁路451號</t>
+          <t>臺東縣台東市新站路260號</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>(0910)371823</t>
+          <t>(089)231188#7187</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2028/03/09</t>
+          <t>2027/12/05</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>墾丁福華渡假飯店</t>
+          <t>墾丁夏都沙灘酒店</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -9474,22 +9474,22 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
+          <t>屏東縣恆春鎮墾丁路451號</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>(08)8862324#2701</t>
+          <t>(0910)371823</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2029/04/12</t>
+          <t>2028/03/09</t>
         </is>
       </c>
     </row>
@@ -9501,22 +9501,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>橘子民宿</t>
+          <t>墾丁福華渡假飯店</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
+          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>(0972)092658</t>
+          <t>(08)8862324#2701</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2027/11/06</t>
+          <t>2029/04/12</t>
         </is>
       </c>
     </row>
@@ -9538,32 +9538,32 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>翰品酒店 高雄</t>
+          <t>橘子民宿</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區大仁路43號</t>
+          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>(07)5614688#3110</t>
+          <t>(0972)092658</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2027/02/16</t>
+          <t>2027/11/06</t>
         </is>
       </c>
     </row>
@@ -9575,22 +9575,22 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>礁溪老爺酒店</t>
+          <t>翰品酒店 高雄</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
+          <t>高雄市鹽埕區大仁路43號</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>(03)9885211#8006</t>
+          <t>(07)5614688#3110</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2028/08/24</t>
+          <t>2027/02/16</t>
         </is>
       </c>
     </row>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>礁溪寒沐酒店</t>
+          <t>礁溪老爺酒店</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
+          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>(03)9058007</t>
+          <t>(03)9885211#8006</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2028/08/24</t>
         </is>
       </c>
     </row>
@@ -9649,32 +9649,32 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>禧榕軒大飯店</t>
+          <t>礁溪寒沐酒店</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>臺南市北區成功路28號</t>
+          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>(06)2222788#2203</t>
+          <t>(03)9058007</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2029/05/10</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -9686,32 +9686,32 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>薆悅酒店野柳渡假館一館</t>
+          <t>禧榕軒大飯店</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>新北市萬里區野柳里港東路162號之2</t>
+          <t>臺南市北區成功路28號</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>(02)77035770#623</t>
+          <t>(06)2222788#2203</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2029/05/10</t>
         </is>
       </c>
     </row>
@@ -9723,22 +9723,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>藍水輕旅</t>
+          <t>薆悅酒店野柳渡假館一館</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>桃園市大園區高鐵南路一段126號</t>
+          <t>新北市萬里區野柳里港東路162號之2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>(03)2871855</t>
+          <t>(02)77035770#623</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -9760,22 +9760,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>關子嶺富野溫泉會館</t>
+          <t>藍水輕旅</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>臺南市白河區關子嶺28號</t>
+          <t>桃園市大園區高鐵南路一段126號</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>(06)6822288</t>
+          <t>(03)2871855</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2029/01/07</t>
+          <t>2026/11/23</t>
         </is>
       </c>
     </row>
@@ -9797,22 +9797,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>麗格休閒飯店</t>
+          <t>關子嶺富野溫泉會館</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市商校街258.260.262號</t>
+          <t>臺南市白河區關子嶺28號</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>(03)8349922</t>
+          <t>(06)6822288</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2029/01/07</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>麗軒國際飯店</t>
+          <t>麗格休閒飯店</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市中美路99之1號</t>
+          <t>花蓮縣花蓮市商校街258.260.262號</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>(03)8246898</t>
+          <t>(03)8349922</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>麗翔大飯店</t>
+          <t>麗軒國際飯店</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
+          <t>花蓮縣花蓮市中美路99之1號</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>(03)8323737</t>
+          <t>(03)8246898</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2028/01/12</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -9908,22 +9908,22 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>讀好民宿</t>
+          <t>麗翔大飯店</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
+          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>(0920)023139</t>
+          <t>(03)8323737</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/01/12</t>
         </is>
       </c>
     </row>
@@ -9945,32 +9945,32 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>觀霧山莊</t>
+          <t>讀好民宿</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
+          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>(03)3343818</t>
+          <t>(0920)023139</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -9982,22 +9982,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>綉溪安平</t>
+          <t>觀霧山莊</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>(06)3910988#3111</t>
+          <t>(03)3343818</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2028/10/12</t>
+          <t>2029/01/22</t>
         </is>
       </c>
     </row>
@@ -10019,30 +10019,67 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
+          <t>綉溪安平</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>臺南市</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>(06)3910988#3111</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>銀級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>2028/10/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
           <t>鐡馬騎跡</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C261" t="inlineStr">
         <is>
           <t>屏東縣</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="D261" t="inlineStr">
         <is>
           <t>屏東縣東港鎮新學路50號</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="E261" t="inlineStr">
         <is>
           <t>(0952)848898</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>銅級環保旅宿</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
         <is>
           <t>2029/01/18</t>
         </is>

--- a/環保旅宿_Selenium結果.xlsx
+++ b/環保旅宿_Selenium結果.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G261"/>
+  <dimension ref="A1:G263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>臺中豐邑慕奇夕酒店</t>
+          <t>臺中萬楓酒店</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1741,22 +1741,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>臺中市西屯區文心南六路288號、288號2樓、288號3樓(地上物3至17樓)</t>
+          <t>臺中市西屯區環中路二段1155號、1149號2樓、1151號3至11樓(之1)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(04)36007009#7099</t>
+          <t>(04)36065188#2501</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2029/05/14</t>
+          <t>2029/09/09</t>
         </is>
       </c>
     </row>
@@ -1768,32 +1768,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>臺北W飯店</t>
+          <t>臺中豐邑慕奇夕酒店</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>臺北市信義區忠孝東路五段10號</t>
+          <t>臺中市西屯區文心南六路288號、288號2樓、288號3樓(地上物3至17樓)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(02)77038765</t>
+          <t>(04)36007009#7099</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2028/08/07</t>
+          <t>2029/05/14</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>臺北士林萬麗酒店</t>
+          <t>臺北W飯店</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>臺北市士林區中山北路五段470巷8號</t>
+          <t>臺北市信義區忠孝東路五段10號</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(02)88612389</t>
+          <t>(02)77038765</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2028/07/10</t>
+          <t>2028/08/07</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>臺北中山九昱希爾頓逸林酒店</t>
+          <t>臺北士林萬麗酒店</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1852,22 +1852,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路一段121巷1之1號, 121巷1號1樓至14樓</t>
+          <t>臺北市士林區中山北路五段470巷8號</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(02)66253281</t>
+          <t>(02)88612389</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2028/07/10</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>臺北中山雅樂軒酒店</t>
+          <t>臺北中山九昱希爾頓逸林酒店</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1889,22 +1889,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>臺北市中山區雙城街1號</t>
+          <t>臺北市中山區中山北路一段121巷1之1號, 121巷1號1樓至14樓</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(02)77439900</t>
+          <t>(02)66253281</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2028/11/13</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>臺北中山意舍酒店</t>
+          <t>臺北中山雅樂軒酒店</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路二段57之1號1至8樓</t>
+          <t>臺北市中山區雙城街1號</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(02)25652828</t>
+          <t>(02)77439900</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2028/09/17</t>
+          <t>2028/11/13</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>臺北六福萬怡酒店</t>
+          <t>臺北中山意舍酒店</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1963,12 +1963,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>臺北市南港區忠孝東路七段359號7至30樓</t>
+          <t>臺北市中山區中山北路二段57之1號1至8樓</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>(02)66156565#5000</t>
+          <t>(02)25652828</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2029/04/09</t>
+          <t>2028/09/17</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>臺北艾麗酒店</t>
+          <t>臺北六福萬怡酒店</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2000,22 +2000,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>臺北市信義區松高路18號</t>
+          <t>臺北市南港區忠孝東路七段359號7至30樓</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>(02)66318031</t>
+          <t>(02)66156565#5000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2029/04/08</t>
+          <t>2029/04/09</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>臺北西門町意舍酒店</t>
+          <t>臺北艾麗酒店</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>臺北市萬華區武昌街2段77號5樓至10樓</t>
+          <t>臺北市信義區松高路18號</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>(02)23755111#2100</t>
+          <t>(02)66318031</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2028/10/22</t>
+          <t>2029/04/08</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>臺北君品大酒店</t>
+          <t>臺北西門町意舍酒店</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2074,22 +2074,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>臺北市大同區承德路1段3號1樓、5樓~16樓及地下1樓、地下3樓</t>
+          <t>臺北市萬華區武昌街2段77號5樓至10樓</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(02)21819999#3142</t>
+          <t>(02)23755111#2100</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>2028/10/22</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>臺北松山意舍酒店</t>
+          <t>臺北君品大酒店</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2111,22 +2111,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>臺北市南港區市民大道7段8號17樓至21樓</t>
+          <t>臺北市大同區承德路1段3號1樓、5樓~16樓及地下1樓、地下3樓</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(02)26532828#2100</t>
+          <t>(02)21819999#3142</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2027/11/28</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -2138,32 +2138,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>臺北旅人國際青年旅館</t>
+          <t>臺北松山意舍酒店</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>新北市淡水區三民街22、22之1、22之2、22之3、22之4號</t>
+          <t>臺北市南港區市民大道7段8號17樓至21樓</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(02)26258222</t>
+          <t>(02)26532828#2100</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2027/11/28</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>臺北時代寓所</t>
+          <t>臺北旅人國際青年旅館</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>臺北市中正區林森南路7號1至14樓，7-1號1樓</t>
+          <t>新北市淡水區三民街22、22之1、22之2、22之3、22之4號</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(02)77521801</t>
+          <t>(02)26258222</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2028/09/29</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -2212,22 +2212,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>臺北新板希爾頓酒店</t>
+          <t>臺北時代寓所</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>新北市板橋區民權路88號、88號（2至31樓）90號</t>
+          <t>臺北市中正區林森南路7號1至14樓，7-1號1樓</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(02)29583000#7702</t>
+          <t>(02)77521801</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2028/03/31</t>
+          <t>2028/09/29</t>
         </is>
       </c>
     </row>
@@ -2249,32 +2249,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>臺北萬豪酒店</t>
+          <t>臺北新板希爾頓酒店</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>臺北市中山區樂群二路199號</t>
+          <t>新北市板橋區民權路88號、88號（2至31樓）90號</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(02)21757999#1701</t>
+          <t>(02)29583000#7702</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2028/12/07</t>
+          <t>2028/03/31</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>臺北遠東香格里拉</t>
+          <t>臺北萬豪酒店</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2296,22 +2296,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>臺北市大安區敦化南路二段201號</t>
+          <t>臺北市中山區樂群二路199號</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(02)23788888#6608</t>
+          <t>(02)21757999#1701</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2027/12/12</t>
+          <t>2028/12/07</t>
         </is>
       </c>
     </row>
@@ -2323,22 +2323,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>臺東Deer  House民宿</t>
+          <t>臺北遠東香格里拉</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>臺東縣鹿野鄉永安村1鄰永安路７１號</t>
+          <t>臺北市大安區敦化南路二段201號</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(089)552224</t>
+          <t>(02)23788888#6608</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2027/12/12</t>
         </is>
       </c>
     </row>
@@ -2360,32 +2360,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>臺南大員皇冠假日酒店</t>
+          <t>臺東Deer  House民宿</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>臺南市安平區州平路289號</t>
+          <t>臺東縣鹿野鄉永安村1鄰永安路７１號</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(06)5121888#6002</t>
+          <t>(089)552224</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2028/01/09</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>臺南大飯店</t>
+          <t>臺南大員皇冠假日酒店</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2407,22 +2407,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>臺南市中西區成功路1號</t>
+          <t>臺南市安平區州平路289號</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(06)2289101#2012</t>
+          <t>(06)5121888#6002</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2028/01/09</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>臺南安平雅樂軒酒店</t>
+          <t>臺南大飯店</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2444,22 +2444,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>臺南市安平區光州路108號2-12樓、光州路108之1號</t>
+          <t>臺南市中西區成功路1號</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(06)3905000#8600</t>
+          <t>(06)2289101#2012</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2028/12/18</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>臺南老爺行旅</t>
+          <t>臺南安平雅樂軒酒店</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>臺南市東區中華東路一段368號1樓、6-10樓</t>
+          <t>臺南市安平區光州路108號2-12樓、光州路108之1號</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(06)2361680#301</t>
+          <t>(06)3905000#8600</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2028/02/19</t>
+          <t>2028/12/18</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>臺南遠東香格里拉</t>
+          <t>臺南老爺行旅</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2518,22 +2518,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>臺南市東區大學路西段89號</t>
+          <t>臺南市東區中華東路一段368號1樓、6-10樓</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(06)7028888#6903</t>
+          <t>(06)2361680#301</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2028/02/19</t>
         </is>
       </c>
     </row>
@@ -2545,22 +2545,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>臺糖臺北會館</t>
+          <t>臺南遠東香格里拉</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路一段39號3至5樓</t>
+          <t>臺南市東區大學路西段89號</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(02)23885522#5001</t>
+          <t>(06)7028888#6903</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2027/03/10</t>
+          <t>2026/12/30</t>
         </is>
       </c>
     </row>
@@ -2582,22 +2582,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>臺糖花蓮旅館</t>
+          <t>臺糖臺北會館</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>花蓮縣光復鄉大進村糖廠街19號</t>
+          <t>臺北市中正區中華路一段39號3至5樓</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(03)8704125#621</t>
+          <t>(02)23885522#5001</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2027/03/21</t>
+          <t>2027/03/10</t>
         </is>
       </c>
     </row>
@@ -2619,22 +2619,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>臺糖長榮酒店(臺南)</t>
+          <t>臺糖花蓮旅館</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>臺南市東區中華東路三段336巷1號</t>
+          <t>花蓮縣光復鄉大進村糖廠街19號</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(06)3378888</t>
+          <t>(03)8704125#621</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2027/03/21</t>
         </is>
       </c>
     </row>
@@ -2656,22 +2656,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>臺灣糖業股份有限公司池上牧野渡假村</t>
+          <t>臺糖長榮酒店(臺南)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>臺東縣池上鄉新興村新興110號</t>
+          <t>臺南市東區中華東路三段336巷1號</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(089)862736#1001</t>
+          <t>(06)3378888</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2028/04/15</t>
+          <t>2026/11/28</t>
         </is>
       </c>
     </row>
@@ -2693,32 +2693,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>四季時光</t>
+          <t>臺灣糖業股份有限公司池上牧野渡假村</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉頭社村平和巷103-11號</t>
+          <t>臺東縣池上鄉新興村新興110號</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>(0932)376767</t>
+          <t>(089)862736#1001</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2028/04/15</t>
         </is>
       </c>
     </row>
@@ -2730,32 +2730,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>巨蛋旅店</t>
+          <t>四季時光</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>高雄市鼓山區文忠路1號</t>
+          <t>南投縣魚池鄉頭社村平和巷103-11號</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>(07)5868388#0</t>
+          <t>(0932)376767</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2028/10/07</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>打個蛋海旅民宿</t>
+          <t>巨蛋旅店</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>臺東縣太麻里鄉金崙4鄰129號</t>
+          <t>高雄市鼓山區文忠路1號</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(089)771551</t>
+          <t>(07)5868388#0</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2028/10/07</t>
         </is>
       </c>
     </row>
@@ -2804,32 +2804,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>正好友生態環保旅店</t>
+          <t>打個蛋海旅民宿</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>屏東縣琉球鄉中山路153號</t>
+          <t>臺東縣太麻里鄉金崙4鄰129號</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(0886)12270</t>
+          <t>(089)771551</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2029/03/26</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -2841,32 +2841,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>伊塔原旅臺東縣原住民文化會館</t>
+          <t>正好友生態環保旅店</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>臺東縣台東市中山路10號</t>
+          <t>屏東縣琉球鄉中山路153號</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(089)34060</t>
+          <t>(0886)12270</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/03/26</t>
         </is>
       </c>
     </row>
@@ -2878,32 +2878,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>兆品酒店</t>
+          <t>伊塔原旅臺東縣原住民文化會館</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>嘉義市文化路257號B2-9F</t>
+          <t>臺東縣台東市中山路10號</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(05)2292883#3130</t>
+          <t>(089)34060</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2028/03/30</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -2915,32 +2915,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>好室民宿</t>
+          <t>兆品酒店</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>臺東縣台東市中正路251巷9號</t>
+          <t>嘉義市文化路257號B2-9F</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(0905)583758</t>
+          <t>(05)2292883#3130</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2027/01/29</t>
+          <t>2028/03/30</t>
         </is>
       </c>
     </row>
@@ -2952,22 +2952,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>如一家精緻民宿</t>
+          <t>好室民宿</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>金門縣金城鎮珠浦北路35-1號</t>
+          <t>臺東縣台東市中正路251巷9號</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(082)322167</t>
+          <t>(0905)583758</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2027/01/29</t>
         </is>
       </c>
     </row>
@@ -2989,22 +2989,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>安樓文旅</t>
+          <t>如一家精緻民宿</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>基隆市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>基隆市仁愛區仁三路11-4</t>
+          <t>金門縣金城鎮珠浦北路35-1號</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(02)24200220</t>
+          <t>(082)322167</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2029/07/09</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -3026,22 +3026,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>老公老婆友善民宿</t>
+          <t>安樓文旅</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>基隆市</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>宜蘭縣冬山鄉境安路345號</t>
+          <t>基隆市仁愛區仁三路11-4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(03) 9519013</t>
+          <t>(02)24200220</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026/12/28</t>
+          <t>2029/07/09</t>
         </is>
       </c>
     </row>
@@ -3063,22 +3063,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>老爺大酒店</t>
+          <t>老公老婆友善民宿</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路2段37-1號</t>
+          <t>宜蘭縣冬山鄉境安路345號</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(02)25423299#359</t>
+          <t>(03) 9519013</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2026/12/28</t>
         </is>
       </c>
     </row>
@@ -3100,32 +3100,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>西湖渡假大飯店</t>
+          <t>老爺大酒店</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>苗栗縣三義鄉西湖村西湖11號</t>
+          <t>臺北市中山區中山北路2段37-1號</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(037)876699#1122</t>
+          <t>(02)25423299#359</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2029/05/24</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -3137,32 +3137,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>亞昕福朋喜來登酒店</t>
+          <t>西湖渡假大飯店</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段1號、1號2樓、1號3樓</t>
+          <t>苗栗縣三義鄉西湖村西湖11號</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(02)77276961</t>
+          <t>(037)876699#1122</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2028/09/25</t>
+          <t>2029/05/24</t>
         </is>
       </c>
     </row>
@@ -3174,22 +3174,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>享沐時光</t>
+          <t>亞昕福朋喜來登酒店</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮石鎮里錦山8-1,8-2號</t>
+          <t>新北市林口區文化三路一段1號、1號2樓、1號3樓</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(037)742878#124</t>
+          <t>(02)77276961</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2028/07/15</t>
+          <t>2028/09/25</t>
         </is>
       </c>
     </row>
@@ -3211,22 +3211,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>和逸．高雄中山館</t>
+          <t>享沐時光</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>高雄市前鎮區中山二路260號22-29樓</t>
+          <t>苗栗縣苑裡鎮石鎮里錦山8-1,8-2號</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(07)9756670</t>
+          <t>(037)742878#124</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2028/09/10</t>
+          <t>2028/07/15</t>
         </is>
       </c>
     </row>
@@ -3248,22 +3248,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>和逸·臺南西門館</t>
+          <t>和逸．高雄中山館</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>臺南市中西區西門路一段658之2號4樓至13樓</t>
+          <t>高雄市前鎮區中山二路260號22-29樓</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>(06)7026685</t>
+          <t>(07)9756670</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2028/02/19</t>
+          <t>2028/09/10</t>
         </is>
       </c>
     </row>
@@ -3285,22 +3285,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>和逸飯店桃園青埔館</t>
+          <t>和逸·臺南西門館</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>桃園市中壢區春德路101號</t>
+          <t>臺南市中西區西門路一段658之2號4樓至13樓</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>(03)2737692#2102</t>
+          <t>(06)7026685</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2028/02/19</t>
         </is>
       </c>
     </row>
@@ -3322,32 +3322,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>尚順君樂飯店</t>
+          <t>和逸飯店桃園青埔館</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>苗栗縣頭份市育樂街6號</t>
+          <t>桃園市中壢區春德路101號</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>(037)539999#8611</t>
+          <t>(03)2737692#2102</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2029/07/29</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -3359,22 +3359,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>幸福蝸牛</t>
+          <t>尚順君樂飯店</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉利澤西路6號</t>
+          <t>苗栗縣頭份市育樂街6號</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(03)9500047</t>
+          <t>(037)539999#8611</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2029/07/29</t>
         </is>
       </c>
     </row>
@@ -3396,32 +3396,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>承萬尊爵渡假酒店</t>
+          <t>幸福蝸牛</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>南投縣埔里鎮樹人路131號</t>
+          <t>宜蘭縣五結鄉利澤西路6號</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(049)2995757#6316</t>
+          <t>(03)9500047</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2027/04/07</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -3433,32 +3433,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>林口維多利亞民宿</t>
+          <t>承萬尊爵渡假酒店</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>桃園市蘆竹區坑子里14鄰八德二路280巷11號</t>
+          <t>南投縣埔里鎮樹人路131號</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>(0905)111918</t>
+          <t>(049)2995757#6316</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2029/08/24</t>
+          <t>2027/04/07</t>
         </is>
       </c>
     </row>
@@ -3470,32 +3470,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>板橋凱撒大飯店</t>
+          <t>林口維多利亞民宿</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>新北市板橋區縣民大道二段8號</t>
+          <t>桃園市蘆竹區坑子里14鄰八德二路280巷11號</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>(02)29583000#7701</t>
+          <t>(0905)111918</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2029/02/12</t>
+          <t>2029/08/24</t>
         </is>
       </c>
     </row>
@@ -3507,32 +3507,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>武陵國民賓館</t>
+          <t>板橋凱撒大飯店</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>臺中市和平區平等里武陵路3-1號</t>
+          <t>新北市板橋區縣民大道二段8號</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>(04)25901258#2103</t>
+          <t>(02)29583000#7701</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026/12/25</t>
+          <t>2029/02/12</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>武陵富野渡假村</t>
+          <t>武陵國民賓館</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>臺中市和平區武陵路3-16號</t>
+          <t>臺中市和平區平等里武陵路3-1號</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>(04)25901399#8912</t>
+          <t>(04)25901258#2103</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2026/12/25</t>
         </is>
       </c>
     </row>
@@ -3581,32 +3581,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>河那灣</t>
+          <t>武陵富野渡假村</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>桃園市復興區澤仁里3鄰溪口台41號</t>
+          <t>臺中市和平區武陵路3-16號</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(0919)235303</t>
+          <t>(04)25901399#8912</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2027/07/25</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -3618,22 +3618,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>波西米亞民宿</t>
+          <t>河那灣</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>花蓮縣吉安鄉東昌村13鄰東海一街168號</t>
+          <t>桃園市復興區澤仁里3鄰溪口台41號</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(0385)31234</t>
+          <t>(0919)235303</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2029/01/06</t>
+          <t>2027/07/25</t>
         </is>
       </c>
     </row>
@@ -3655,22 +3655,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>泡泡森林民宿</t>
+          <t>波西米亞民宿</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>臺東縣台東市南一街40號</t>
+          <t>花蓮縣吉安鄉東昌村13鄰東海一街168號</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0986866545</t>
+          <t>(0385)31234</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026/12/06</t>
+          <t>2029/01/06</t>
         </is>
       </c>
     </row>
@@ -3692,22 +3692,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>泊寓</t>
+          <t>泡泡森林民宿</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮鹿興路57巷3號</t>
+          <t>臺東縣台東市南一街40號</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(04)7115655#120</t>
+          <t>0986866545</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2026/12/06</t>
         </is>
       </c>
     </row>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>爸爸萬歲民宿</t>
+          <t>泊寓</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市延平街68巷27號</t>
+          <t>彰化縣鹿港鎮鹿興路57巷3號</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>(0900)757520</t>
+          <t>(04)7115655#120</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2027/01/10</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -3766,22 +3766,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>迎曦大飯店</t>
+          <t>爸爸萬歲民宿</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>新竹市東區親仁里文化街10號2-10樓</t>
+          <t>花蓮縣花蓮市延平街68巷27號</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(03)5347266#124</t>
+          <t>(0900)757520</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2028/04/28</t>
+          <t>2027/01/10</t>
         </is>
       </c>
     </row>
@@ -3803,32 +3803,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>金湖飯店</t>
+          <t>迎曦大飯店</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>金門縣金湖鎮太湖路二段218號</t>
+          <t>新竹市東區親仁里文化街10號2-10樓</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>(082)379666#160</t>
+          <t>(03)5347266#124</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026/12/03</t>
+          <t>2028/04/28</t>
         </is>
       </c>
     </row>
@@ -3840,22 +3840,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>長榮文苑酒店(嘉義)</t>
+          <t>金湖飯店</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>嘉義縣太保市東勢里故宮大道777號</t>
+          <t>金門縣金湖鎮太湖路二段218號</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(05)3669988#2700</t>
+          <t>(082)379666#160</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2027/04/11</t>
+          <t>2026/12/03</t>
         </is>
       </c>
     </row>
@@ -3877,22 +3877,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(臺中)</t>
+          <t>長榮文苑酒店(嘉義)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>臺中市西屯區臺灣大道二段666號</t>
+          <t>嘉義縣太保市東勢里故宮大道777號</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(04)23242236#2700</t>
+          <t>(05)3669988#2700</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2027/07/09</t>
+          <t>2027/04/11</t>
         </is>
       </c>
     </row>
@@ -3914,22 +3914,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(臺北)</t>
+          <t>長榮桂冠酒店(臺中)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>臺北市中山區松江路63號</t>
+          <t>臺中市西屯區臺灣大道二段666號</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>(02)25019988#2701</t>
+          <t>(04)23242236#2700</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2028/10/22</t>
+          <t>2027/07/09</t>
         </is>
       </c>
     </row>
@@ -3951,32 +3951,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(基隆)</t>
+          <t>長榮桂冠酒店(臺北)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>基隆市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>基隆市中正區中正路62號之1</t>
+          <t>臺北市中山區松江路63號</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>(02)24279988</t>
+          <t>(02)25019988#2701</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2028/05/22</t>
+          <t>2028/10/22</t>
         </is>
       </c>
     </row>
@@ -3988,22 +3988,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>長榮鳳凰酒店(礁溪)</t>
+          <t>長榮桂冠酒店(基隆)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>基隆市</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉健康路77號</t>
+          <t>基隆市中正區中正路62號之1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(03)9100988#2335</t>
+          <t>(02)24279988</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2027/09/15</t>
+          <t>2028/05/22</t>
         </is>
       </c>
     </row>
@@ -4025,32 +4025,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>阿里山東方明珠國際大飯店</t>
+          <t>長榮鳳凰酒店(礁溪)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>嘉義縣中埔鄉社口村檨仔林23號</t>
+          <t>宜蘭縣礁溪鄉健康路77號</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>(05)2536999</t>
+          <t>(03)9100988#2335</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2027/12/12</t>
+          <t>2027/09/15</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>阿里山英迪格酒店</t>
+          <t>阿里山東方明珠國際大飯店</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4072,22 +4072,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>嘉義縣番路鄉公田村2鄰龍頭20號2樓之1等10筆</t>
+          <t>嘉義縣中埔鄉社口村檨仔林23號</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>(05)2586800#121</t>
+          <t>(05)2536999</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2028/10/21</t>
+          <t>2027/12/12</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>阿里山賓館（現代館）</t>
+          <t>阿里山英迪格酒店</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>嘉義縣阿里山鄉香林村西阿里山16-1號</t>
+          <t>嘉義縣番路鄉公田村2鄰龍頭20號2樓之1等10筆</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>(05)2679996#5117</t>
+          <t>(05)2586800#121</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2027/06/19</t>
+          <t>2028/10/21</t>
         </is>
       </c>
     </row>
@@ -4136,32 +4136,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>阿爾卑斯莊園</t>
+          <t>阿里山賓館（現代館）</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉協和村親河路二段88巷37號</t>
+          <t>嘉義縣阿里山鄉香林村西阿里山16-1號</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>(0905)787698</t>
+          <t>(05)2679996#5117</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2029/09/02</t>
+          <t>2027/06/19</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>冠翔泉旅</t>
+          <t>阿爾卑斯莊園</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4183,22 +4183,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉仁愛路66巷6號</t>
+          <t>宜蘭縣五結鄉協和村親河路二段88巷37號</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>(03)9875599#119</t>
+          <t>(0905)787698</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2029/07/20</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -4210,22 +4210,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>南港老爺行旅</t>
+          <t>冠翔泉旅</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>臺北市南港區經貿二路196號、196號10樓至20樓</t>
+          <t>宜蘭縣礁溪鄉仁愛路66巷6號</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>(02)77500588</t>
+          <t>(03)9875599#119</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2028/11/27</t>
+          <t>2029/07/20</t>
         </is>
       </c>
     </row>
@@ -4247,32 +4247,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>城市商旅美麗島館(HOTEL PAPA WHALE)</t>
+          <t>南港老爺行旅</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>高雄市新興區民生一路328號1-7樓</t>
+          <t>臺北市南港區經貿二路196號、196號10樓至20樓</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>(07)2519888</t>
+          <t>(02)77500588</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2028/09/24</t>
+          <t>2028/11/27</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>城市商旅高雄真愛館</t>
+          <t>城市商旅美麗島館(HOTEL PAPA WHALE)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區大義街1號</t>
+          <t>高雄市新興區民生一路328號1-7樓</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>(07)5215116#9303</t>
+          <t>(07)2519888</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2028/09/25</t>
+          <t>2028/09/24</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>城市商旅駁二館</t>
+          <t>城市商旅高雄真愛館</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區公園二路83號1至11樓</t>
+          <t>高雄市鹽埕區大義街1號</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>(07)5322777</t>
+          <t>(07)5215116#9303</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>城市商旅德立莊博愛館</t>
+          <t>城市商旅駁二館</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4368,12 +4368,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>高雄市三民區博愛一路338號地上1至10樓</t>
+          <t>高雄市鹽埕區公園二路83號1至11樓</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>(07)3238777#9301</t>
+          <t>(07)5322777</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2028/08/07</t>
+          <t>2028/09/25</t>
         </is>
       </c>
     </row>
@@ -4395,32 +4395,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>星8藝宿</t>
+          <t>城市商旅德立莊博愛館</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉中山路三段192巷8號</t>
+          <t>高雄市三民區博愛一路338號地上1至10樓</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>(0932)495200</t>
+          <t>(07)3238777#9301</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2029/01/07</t>
+          <t>2028/08/07</t>
         </is>
       </c>
     </row>
@@ -4432,22 +4432,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>星漾商旅</t>
+          <t>星8藝宿</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>臺中市北區錦南街17號,錦新街30號4樓至9樓,錦新街32號4樓至9樓</t>
+          <t>宜蘭縣三星鄉中山路三段192巷8號</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>(04)22289008</t>
+          <t>(0932)495200</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2029/01/07</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>星漾商旅(中清館)</t>
+          <t>星漾商旅</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>臺中市北區中清路一段63號</t>
+          <t>臺中市北區錦南街17號,錦新街30號4樓至9樓,錦新街32號4樓至9樓</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>(04)22083888</t>
+          <t>(04)22289008</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4506,22 +4506,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>柳營尖山埤渡假村</t>
+          <t>星漾商旅(中清館)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>臺南市柳營區旭山里60號</t>
+          <t>臺中市北區中清路一段63號</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>(06)6233888#2100</t>
+          <t>(04)22083888</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2029/07/28</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -4543,32 +4543,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>美之旅商務飯店</t>
+          <t>柳營尖山埤渡假村</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>臺中市西區美村路一段269號1樓、2樓之1、2樓之2、3、4、5、6、7樓</t>
+          <t>臺南市柳營區旭山里60號</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>(04)23024330</t>
+          <t>(06)6233888#2100</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2029/04/07</t>
+          <t>2029/07/28</t>
         </is>
       </c>
     </row>
@@ -4580,32 +4580,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>美侖商旅</t>
+          <t>美之旅商務飯店</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>臺北市中山區吉林路49號1至8樓</t>
+          <t>臺中市西區美村路一段269號1樓、2樓之1、2樓之2、3、4、5、6、7樓</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>(02)25313535#878</t>
+          <t>(04)23024330</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2028/11/27</t>
+          <t>2029/04/07</t>
         </is>
       </c>
     </row>
@@ -4617,32 +4617,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>美墅館</t>
+          <t>美侖商旅</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>臺南市善化區昌隆里9鄰東勢寮131之8號</t>
+          <t>臺北市中山區吉林路49號1至8樓</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>(09)20656908</t>
+          <t>(02)25313535#878</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2028/11/27</t>
         </is>
       </c>
     </row>
@@ -4654,22 +4654,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>美綠民宿</t>
+          <t>美墅館</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>高雄市美濃區獅山里竹門14-2號</t>
+          <t>臺南市善化區昌隆里9鄰東勢寮131之8號</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>(07)6851111</t>
+          <t>(09)20656908</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2028/12/28</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -4691,22 +4691,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>夏堤民宿</t>
+          <t>美綠民宿</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>屏東縣琉球鄉上福村2鄰杉板路51巷2號</t>
+          <t>高雄市美濃區獅山里竹門14-2號</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>(08)8611155</t>
+          <t>(07)6851111</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2029/02/25</t>
+          <t>2028/12/28</t>
         </is>
       </c>
     </row>
@@ -4728,22 +4728,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>夏優旅居</t>
+          <t>夏堤民宿</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區新興街67號</t>
+          <t>屏東縣琉球鄉上福村2鄰杉板路51巷2號</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(07)5328885</t>
+          <t>(08)8611155</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2028/12/11</t>
+          <t>2029/02/25</t>
         </is>
       </c>
     </row>
@@ -4765,22 +4765,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>娜路彎花園酒店</t>
+          <t>夏優旅居</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>臺東縣台東市新興路77號</t>
+          <t>高雄市鹽埕區新興街67號</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(089)231111</t>
+          <t>(07)5328885</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2028/12/11</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>娜路彎會館</t>
+          <t>娜路彎花園酒店</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>臺東縣台東市中興路2段385號</t>
+          <t>臺東縣台東市新興路77號</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(089)235500</t>
+          <t>(089)231111</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>娜路彎銀河行館</t>
+          <t>娜路彎會館</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>臺東縣台東市豐興路88號</t>
+          <t>臺東縣台東市中興路2段385號</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(089)383366</t>
+          <t>(089)235500</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2028/09/16</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>娜路彎銀河酒店</t>
+          <t>娜路彎銀河行館</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4886,22 +4886,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>臺東縣台東市豐興路66號</t>
+          <t>臺東縣台東市豐興路88號</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(089)225000#8263</t>
+          <t>(089)383366</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2028/09/03</t>
+          <t>2028/09/16</t>
         </is>
       </c>
     </row>
@@ -4913,32 +4913,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>悅徠舘</t>
+          <t>娜路彎銀河酒店</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>桃園市龜山區興華三街18號2樓之1</t>
+          <t>臺東縣台東市豐興路66號</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(03)3280177</t>
+          <t>(089)225000#8263</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2028/09/03</t>
         </is>
       </c>
     </row>
@@ -4950,22 +4950,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>悅豪大飯店</t>
+          <t>悅徠舘</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>新竹市東區復興路22號</t>
+          <t>桃園市龜山區興華三街18號2樓之1</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(03)5267890</t>
+          <t>(03)3280177</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2029/07/20</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -4987,22 +4987,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>旅行邦尼</t>
+          <t>悅豪大飯店</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>新北市淡水區中山路87巷7號</t>
+          <t>新竹市東區復興路22號</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>(09)28824850</t>
+          <t>(03)5267890</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2029/01/05</t>
+          <t>2029/07/20</t>
         </is>
       </c>
     </row>
@@ -5024,22 +5024,22 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>旅悅國際青年旅館</t>
+          <t>旅行邦尼</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>高雄市前鎮區三多三路211號3樓及4樓</t>
+          <t>新北市淡水區中山路87巷7號</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(07)3359006</t>
+          <t>(09)28824850</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2027/10/13</t>
+          <t>2029/01/05</t>
         </is>
       </c>
     </row>
@@ -5061,32 +5061,32 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>桃園大溪笠復威斯汀度假酒店</t>
+          <t>旅悅國際青年旅館</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>桃園市大溪區日新路166號</t>
+          <t>高雄市前鎮區三多三路211號3樓及4樓</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(03)2725035</t>
+          <t>(07)3359006</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2027/10/13</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>桃園喜來登酒店</t>
+          <t>桃園大溪笠復威斯汀度假酒店</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>桃園市大園區大觀路777號</t>
+          <t>桃園市大溪區日新路166號</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(03)3850000#2605</t>
+          <t>(03)2725035</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026/10/29</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>泰安觀止溫泉會館</t>
+          <t>桃園喜來登酒店</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>苗栗縣泰安鄉錦水村圓墩58-7號</t>
+          <t>桃園市大園區大觀路777號</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(037)941951#527</t>
+          <t>(03)3850000#2605</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2028/06/25</t>
+          <t>2026/10/29</t>
         </is>
       </c>
     </row>
@@ -5172,32 +5172,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>海福花園飯店</t>
+          <t>泰安觀止溫泉會館</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>金門縣金沙鎮高陽路1號</t>
+          <t>苗栗縣泰安鄉錦水村圓墩58-7號</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(082)353888</t>
+          <t>(037)941951#527</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2029/09/01</t>
+          <t>2028/06/25</t>
         </is>
       </c>
     </row>
@@ -5209,22 +5209,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>海霞您的家</t>
+          <t>海福花園飯店</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>新北市貢寮區仁里里14鄰仁愛路38號</t>
+          <t>金門縣金沙鎮高陽路1號</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>(09)35204895</t>
+          <t>(082)353888</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2029/09/01</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>海灣假日酒店</t>
+          <t>海霞您的家</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5256,22 +5256,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>新北市深坑區北深路3段265號</t>
+          <t>新北市貢寮區仁里里14鄰仁愛路38號</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(02)77035880</t>
+          <t>(09)35204895</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2028/12/17</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>神隱國度民宿</t>
+          <t>海灣假日酒店</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5293,22 +5293,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>新北市瑞芳區崙頂路90號</t>
+          <t>新北市深坑區北深路3段265號</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(09)05788650</t>
+          <t>(02)77035880</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2028/12/17</t>
         </is>
       </c>
     </row>
@@ -5320,32 +5320,32 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>秧悦美地度假酒店</t>
+          <t>神隱國度民宿</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>花蓮縣吉安鄉干城村干城二街95-9號</t>
+          <t>新北市瑞芳區崙頂路90號</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>(03)8129168#2701</t>
+          <t>(09)05788650</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -5357,32 +5357,32 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>秘境41</t>
+          <t>秧悦美地度假酒店</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>桃園市大溪區興和里中央路41號</t>
+          <t>花蓮縣吉安鄉干城村干城二街95-9號</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>(03)3887111</t>
+          <t>(03)8129168#2701</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2027/12/10</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -5394,22 +5394,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>秘境民宿</t>
+          <t>秘境41</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>屏東縣東港鎮屏東縣東港鎮水源路223號(新和段737-3地號)</t>
+          <t>桃園市大溪區興和里中央路41號</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(08)8333345</t>
+          <t>(03)3887111</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2029/01/18</t>
+          <t>2027/12/10</t>
         </is>
       </c>
     </row>
@@ -5431,32 +5431,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>高雄中央公園英迪格酒店</t>
+          <t>秘境民宿</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>高雄市新興區中山一路4號</t>
+          <t>屏東縣東港鎮屏東縣東港鎮水源路223號(新和段737-3地號)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>(07)2721555#301</t>
+          <t>(08)8333345</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2029/01/18</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>高雄商旅</t>
+          <t>高雄中央公園英迪格酒店</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>高雄市新興區民族二路33號1、4~10樓；37號1、3~10樓</t>
+          <t>高雄市新興區中山一路4號</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>(09)19546590</t>
+          <t>(07)2721555#301</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>高雄富野渡假酒店</t>
+          <t>高雄商旅</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>高雄市前鎮區瑞田街99號</t>
+          <t>高雄市新興區民族二路33號1、4~10樓；37號1、3~10樓</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>(07)8215299#7102</t>
+          <t>(09)19546590</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2029/02/09</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>高雄圓山大飯店</t>
+          <t>高雄富野渡假酒店</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5552,22 +5552,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>高雄市鳥松區圓山路2號</t>
+          <t>高雄市前鎮區瑞田街99號</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>(07)3706007#519</t>
+          <t>(07)8215299#7102</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2029/02/09</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>高雄福華大飯店</t>
+          <t>高雄圓山大飯店</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>高雄市新興區七賢一路311號</t>
+          <t>高雄市鳥松區圓山路2號</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>(07)2307737</t>
+          <t>(07)3706007#519</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026/11/16</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>基拉耳景觀民宿</t>
+          <t>高雄福華大飯店</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>桃園市復興區溪口路16巷29號</t>
+          <t>高雄市新興區七賢一路311號</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>(02)23965188#594</t>
+          <t>(07)2307737</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2028/06/15</t>
+          <t>2026/11/16</t>
         </is>
       </c>
     </row>
@@ -5653,32 +5653,32 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>將捷金鬱金香酒店</t>
+          <t>國聯大飯店</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>新北市淡水區中正路1段2之1號(A區地上3至6層、B區地上1至5層、C區地下3層至地上3層)</t>
+          <t>臺北市大安區光復南路200號</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(02)26218555#2913</t>
+          <t>(02)27731515#184</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2027/04/14</t>
+          <t>2029/09/15</t>
         </is>
       </c>
     </row>
@@ -5690,22 +5690,22 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>康橋商旅-六合夜市七賢館</t>
+          <t>基拉耳景觀民宿</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>高雄市新興區同愛街28號1樓、30號</t>
+          <t>桃園市復興區溪口路16巷29號</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(07)288-5588</t>
+          <t>(02)23965188#594</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2028/06/15</t>
         </is>
       </c>
     </row>
@@ -5727,32 +5727,32 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>康橋商旅臺南赤崁樓館</t>
+          <t>將捷金鬱金香酒店</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>臺南市中西區赤崁里民權路二段97號1至8樓</t>
+          <t>新北市淡水區中正路1段2之1號(A區地上3至6層、B區地上1至5層、C區地下3層至地上3層)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(06)2253377</t>
+          <t>(02)26218555#2913</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2029/09/02</t>
+          <t>2027/04/14</t>
         </is>
       </c>
     </row>
@@ -5764,22 +5764,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>康橋慢旅</t>
+          <t>康橋商旅-六合夜市七賢館</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>臺南市中西區民生路二段416號</t>
+          <t>高雄市新興區同愛街28號1樓、30號</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(06)2805566</t>
+          <t>(07)288-5588</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2029/09/02</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>捷絲旅 臺南虎山館</t>
+          <t>康橋商旅臺南赤崁樓館</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5811,22 +5811,22 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>臺南市仁德區成功里5鄰文華路2段300號1~9樓，地下一、二樓</t>
+          <t>臺南市中西區赤崁里民權路二段97號1至8樓</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(06)2662218#8321</t>
+          <t>(06)2253377</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2028/02/13</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>捷絲旅臺北三重館</t>
+          <t>康橋慢旅</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>新北市三重區三和路四段107-1號</t>
+          <t>臺南市中西區民生路二段416號</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>(02)22806111#8304</t>
+          <t>(06)2805566</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2028/10/12</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -5875,32 +5875,32 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>捷絲旅西門町店</t>
+          <t>捷絲旅 臺南虎山館</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路一段41號5樓至9樓</t>
+          <t>臺南市仁德區成功里5鄰文華路2段300號1~9樓，地下一、二樓</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>(02)25215000</t>
+          <t>(06)2662218#8321</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2027/05/12</t>
+          <t>2028/02/13</t>
         </is>
       </c>
     </row>
@@ -5912,22 +5912,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>捷絲旅花蓮中正館</t>
+          <t>捷絲旅臺北三重館</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市主睦里14鄰中正路396號</t>
+          <t>新北市三重區三和路四段107-1號</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>(03)8900069#8104</t>
+          <t>(02)22806111#8304</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2028/10/12</t>
         </is>
       </c>
     </row>
@@ -5949,32 +5949,32 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>捷絲旅高雄中正館</t>
+          <t>捷絲旅西門町店</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>高雄市苓雅區中正一路134號</t>
+          <t>臺北市中正區中華路一段41號5樓至9樓</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(07)9733587#8104</t>
+          <t>(02)25215000</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>2027/05/12</t>
         </is>
       </c>
     </row>
@@ -5986,22 +5986,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>捷絲旅高雄站前館</t>
+          <t>捷絲旅花蓮中正館</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>高雄市新興區中山一路280號1至14樓</t>
+          <t>花蓮縣花蓮市主睦里14鄰中正路396號</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>(07)9733587#8104</t>
+          <t>(03)8900069#8104</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2028/09/29</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -6023,22 +6023,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>捷絲旅臺大尊賢館</t>
+          <t>捷絲旅高雄中正館</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>臺北市大安區羅斯福路四段83號1-10樓</t>
+          <t>高雄市苓雅區中正一路134號</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(02)77355088</t>
+          <t>(07)9733587#8104</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>捷絲旅礁溪館</t>
+          <t>捷絲旅高雄站前館</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉德陽路24巷8號、10號</t>
+          <t>高雄市新興區中山一路280號1至14樓</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(03)9102000#8104</t>
+          <t>(07)9733587#8104</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2027/01/07</t>
+          <t>2028/09/29</t>
         </is>
       </c>
     </row>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>清新溫泉飯店</t>
+          <t>捷絲旅臺大尊賢館</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>臺中市烏日區溫泉路2號</t>
+          <t>臺北市大安區羅斯福路四段83號1-10樓</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(04)23831088#7602</t>
+          <t>(02)77355088</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6134,22 +6134,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>統一谷關渡假村</t>
+          <t>捷絲旅礁溪館</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>臺中市和平區博愛里東關路一段188號</t>
+          <t>宜蘭縣礁溪鄉德陽路24巷8號、10號</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(04)25950000</t>
+          <t>(03)9102000#8104</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2028/01/06</t>
+          <t>2027/01/07</t>
         </is>
       </c>
     </row>
@@ -6171,32 +6171,32 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>統一渡假村</t>
+          <t>清新溫泉飯店</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>新竹縣關西鎮金山里34號</t>
+          <t>臺中市烏日區溫泉路2號</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(03)5478888</t>
+          <t>(04)23831088#7602</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2027/12/20</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -6208,22 +6208,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>鹿港澄悅酒店</t>
+          <t>統一谷關渡假村</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮中正路598號1樓、5至8樓</t>
+          <t>臺中市和平區博愛里東關路一段188號</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>(04)7785727</t>
+          <t>(04)25950000</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2029/03/02</t>
+          <t>2028/01/06</t>
         </is>
       </c>
     </row>
@@ -6245,32 +6245,32 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>傑仕堡有氧酒店</t>
+          <t>統一渡假村</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>新北市板橋區縣民大道2段275號、275號2至17樓、277號2樓</t>
+          <t>新竹縣關西鎮金山里34號</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>(02)77273000#54083</t>
+          <t>(03)5478888</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026/10/16</t>
+          <t>2027/12/20</t>
         </is>
       </c>
     </row>
@@ -6282,32 +6282,32 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>凱旋酒店</t>
+          <t>鹿港澄悅酒店</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>臺北市內湖區江南街55號3樓至9樓</t>
+          <t>彰化縣鹿港鎮中正路598號1樓、5至8樓</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>(02)87527888#6203</t>
+          <t>(04)7785727</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026/12/10</t>
+          <t>2029/03/02</t>
         </is>
       </c>
     </row>
@@ -6319,22 +6319,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>凱達大飯店</t>
+          <t>傑仕堡有氧酒店</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>臺北市萬華區艋舺大道167號1-26樓</t>
+          <t>新北市板橋區縣民大道2段275號、275號2至17樓、277號2樓</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>(02)23836789#6321</t>
+          <t>(02)77273000#54083</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2027/06/02</t>
+          <t>2026/10/16</t>
         </is>
       </c>
     </row>
@@ -6356,22 +6356,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>凱撒大飯店</t>
+          <t>凱旋酒店</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁路6號</t>
+          <t>臺北市內湖區江南街55號3樓至9樓</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>(08)8861888</t>
+          <t>(02)87527888#6203</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2028/09/16</t>
+          <t>2026/12/10</t>
         </is>
       </c>
     </row>
@@ -6393,32 +6393,32 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>勝利127民宿</t>
+          <t>凱達大飯店</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>屏東縣屏東市勝利路127號</t>
+          <t>臺北市萬華區艋舺大道167號1-26樓</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(08)7320099</t>
+          <t>(02)23836789#6321</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026/12/14</t>
+          <t>2027/06/02</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>勝利131民宿</t>
+          <t>凱撒大飯店</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6440,22 +6440,22 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>屏東縣屏東市勝利路131號</t>
+          <t>屏東縣恆春鎮墾丁路6號</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(08)7320099</t>
+          <t>(08)8861888</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026/12/14</t>
+          <t>2028/09/16</t>
         </is>
       </c>
     </row>
@@ -6467,32 +6467,32 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>寒居酒店</t>
+          <t>勝利127民宿</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>臺北市中山區松江路116號1樓至9樓</t>
+          <t>屏東縣屏東市勝利路127號</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(02)66008000#8886</t>
+          <t>(08)7320099</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2028/07/17</t>
+          <t>2026/12/14</t>
         </is>
       </c>
     </row>
@@ -6504,22 +6504,22 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>寒軒國際大飯店</t>
+          <t>勝利131民宿</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>高雄市苓雅區四維三路三十三號</t>
+          <t>屏東縣屏東市勝利路131號</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(0980)556224</t>
+          <t>(08)7320099</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2028/12/11</t>
+          <t>2026/12/14</t>
         </is>
       </c>
     </row>
@@ -6541,32 +6541,32 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>富光大旅社</t>
+          <t>寒居酒店</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公園路19-7號</t>
+          <t>臺北市中山區松江路116號1樓至9樓</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(08)7345656</t>
+          <t>(02)66008000#8886</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2028/05/28</t>
+          <t>2028/07/17</t>
         </is>
       </c>
     </row>
@@ -6578,32 +6578,32 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>富信大飯店</t>
+          <t>寒軒國際大飯店</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>新北市汐止區大同路一段152號</t>
+          <t>高雄市苓雅區四維三路三十三號</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>(02)26416422#5112</t>
+          <t>(0980)556224</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2028/03/13</t>
+          <t>2028/12/11</t>
         </is>
       </c>
     </row>
@@ -6615,32 +6615,32 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>尊爵大飯店</t>
+          <t>富光大旅社</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>桃園市桃園區莊敬路一段300號</t>
+          <t>屏東縣屏東市公園路19-7號</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>(03)3169090#8502</t>
+          <t>(08)7345656</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026/12/21</t>
+          <t>2028/05/28</t>
         </is>
       </c>
     </row>
@@ -6652,32 +6652,32 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>尊爵天際大飯店</t>
+          <t>富信大飯店</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>桃園市蘆竹區南崁路一段108號</t>
+          <t>新北市汐止區大同路一段152號</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>(03)2228100#6081</t>
+          <t>(02)26416422#5112</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2028/08/31</t>
+          <t>2028/03/13</t>
         </is>
       </c>
     </row>
@@ -6689,32 +6689,32 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>惠來谷關溫泉會館</t>
+          <t>尊爵大飯店</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>臺中市和平區東關路一段溫泉巷十號</t>
+          <t>桃園市桃園區莊敬路一段300號</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>(04)25951998#621</t>
+          <t>(03)3169090#8502</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2029/08/13</t>
+          <t>2026/12/21</t>
         </is>
       </c>
     </row>
@@ -6726,22 +6726,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>提米好旅</t>
+          <t>尊爵天際大飯店</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>彰化縣彰化市成功路277號</t>
+          <t>桃園市蘆竹區南崁路一段108號</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>(04)7061086#9</t>
+          <t>(03)2228100#6081</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>2028/08/31</t>
         </is>
       </c>
     </row>
@@ -6763,22 +6763,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>揚昊民宿</t>
+          <t>惠來谷關溫泉會館</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之6號</t>
+          <t>臺中市和平區東關路一段溫泉巷十號</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(037)747711#9</t>
+          <t>(04)25951998#621</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2028/09/08</t>
+          <t>2029/08/13</t>
         </is>
       </c>
     </row>
@@ -6800,32 +6800,32 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>晶泉丰旅</t>
+          <t>提米好旅</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉溫泉路67號2至10樓</t>
+          <t>彰化縣彰化市成功路277號</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(03)9100000#6105</t>
+          <t>(04)7061086#9</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2027/05/22</t>
+          <t>2027/11/27</t>
         </is>
       </c>
     </row>
@@ -6837,22 +6837,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>智醫康寓</t>
+          <t>揚昊民宿</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>桃園市桃園區民生路107號1-3樓及7-20樓</t>
+          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之6號</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(03)3362575</t>
+          <t>(037)747711#9</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026/10/30</t>
+          <t>2028/09/08</t>
         </is>
       </c>
     </row>
@@ -6874,32 +6874,32 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>渴望會館</t>
+          <t>晶泉丰旅</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>桃園市龍潭區渴望路428號3-5樓</t>
+          <t>宜蘭縣礁溪鄉溫泉路67號2至10樓</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>(03)4072999#7110</t>
+          <t>(03)9100000#6105</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2027/05/22</t>
         </is>
       </c>
     </row>
@@ -6911,32 +6911,32 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>然一酒店</t>
+          <t>智醫康寓</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>高雄市前鎮區中山二路199號</t>
+          <t>桃園市桃園區民生路107號1-3樓及7-20樓</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>(07)9730186#1666</t>
+          <t>(03)3362575</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2027/06/03</t>
+          <t>2026/10/30</t>
         </is>
       </c>
     </row>
@@ -6948,32 +6948,32 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>發現號特色民宿</t>
+          <t>渴望會館</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>屏東縣林邊鄉崎峰村裕後路90號</t>
+          <t>桃園市龍潭區渴望路428號3-5樓</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>(08)8750300</t>
+          <t>(03)4072999#7110</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -6985,22 +6985,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>華泰瑞苑</t>
+          <t>然一酒店</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮公園路101號</t>
+          <t>高雄市前鎮區中山二路199號</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>(08)8863666</t>
+          <t>(07)9730186#1666</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2027/06/21</t>
+          <t>2027/06/03</t>
         </is>
       </c>
     </row>
@@ -7022,22 +7022,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>貳十二度行旅</t>
+          <t>發現號特色民宿</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>宜蘭縣蘇澳鎮信義路177號</t>
+          <t>屏東縣林邊鄉崎峰村裕後路90號</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>(03)9901888</t>
+          <t>(08)8750300</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2029/05/24</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -7059,32 +7059,32 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>陽明山天籟渡假酒店</t>
+          <t>華泰瑞苑</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>新北市金山區名流路1之6號、1之7號、1之9號、1之9號5樓及1之9號5樓之1至之8</t>
+          <t>屏東縣恆春鎮公園路101號</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>(02)24080400#1700</t>
+          <t>(08)8863666</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2029/02/11</t>
+          <t>2027/06/21</t>
         </is>
       </c>
     </row>
@@ -7096,22 +7096,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>雅霖大飯店</t>
+          <t>貳十二度行旅</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市同和路100號</t>
+          <t>宜蘭縣蘇澳鎮信義路177號</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>(06)9261366</t>
+          <t>(03)9901888</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2029/05/24</t>
         </is>
       </c>
     </row>
@@ -7133,32 +7133,32 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>雲品溫泉酒店日月潭</t>
+          <t>陽明山天籟渡假酒店</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉水社村中正路23號</t>
+          <t>新北市金山區名流路1之6號、1之7號、1之9號、1之9號5樓及1之9號5樓之1至之8</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>(049)2212959</t>
+          <t>(02)24080400#1700</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2029/05/05</t>
+          <t>2029/02/11</t>
         </is>
       </c>
     </row>
@@ -7170,22 +7170,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>雲頂國際商旅</t>
+          <t>雅霖大飯店</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>臺南市南區大同路二段530號</t>
+          <t>澎湖縣馬公市同和路100號</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>(06)2687766</t>
+          <t>(06)9261366</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2029/02/25</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -7207,32 +7207,32 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>圓山大飯店</t>
+          <t>雲品溫泉酒店日月潭</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路4段1巷1號</t>
+          <t>南投縣魚池鄉水社村中正路23號</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>(02)28861818#1007</t>
+          <t>(049)2212959</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2029/05/05</t>
         </is>
       </c>
     </row>
@@ -7244,22 +7244,22 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>奧斯卡去旅行民宿</t>
+          <t>雲頂國際商旅</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>臺東縣臺東市興安路一段167號</t>
+          <t>臺南市南區大同路二段530號</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>(0910)633944</t>
+          <t>(06)2687766</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2027/01/29</t>
+          <t>2029/02/25</t>
         </is>
       </c>
     </row>
@@ -7281,32 +7281,32 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>奧斯卡民宿</t>
+          <t>圓山大飯店</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>臺東縣台東市興安路1段175號</t>
+          <t>臺北市中山區中山北路4段1巷1號</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>(0965)329000</t>
+          <t>(02)28861818#1007</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2027/01/18</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -7318,22 +7318,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>新竹安捷國際酒店</t>
+          <t>奧斯卡去旅行民宿</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>新竹縣竹北市復興三路二段168號14樓-18樓</t>
+          <t>臺東縣臺東市興安路一段167號</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>(03)6209777#660</t>
+          <t>(0910)633944</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2028/07/13</t>
+          <t>2027/01/29</t>
         </is>
       </c>
     </row>
@@ -7355,22 +7355,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>新竹老爺大酒店</t>
+          <t>奧斯卡民宿</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>新竹市東區光復路一段227號</t>
+          <t>臺東縣台東市興安路1段175號</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>(03)5631285#204</t>
+          <t>(0965)329000</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2027/01/18</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>新竹喜來登大飯店</t>
+          <t>新竹安捷國際酒店</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7402,22 +7402,22 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>新竹縣竹北市光明六路東一段265號</t>
+          <t>新竹縣竹北市復興三路二段168號14樓-18樓</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>(03)6206126</t>
+          <t>(03)6209777#660</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2028/07/13</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>新竹福華大飯店</t>
+          <t>新竹老爺大酒店</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>新竹市中正路178號</t>
+          <t>新竹市東區光復路一段227號</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>(03)5282323#5303</t>
+          <t>(03)5631285#204</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -7466,32 +7466,32 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>新南一二文創商行</t>
+          <t>新竹喜來登大飯店</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>桃園市大溪區中山路１２號</t>
+          <t>新竹縣竹北市光明六路東一段265號</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>(03)3884466</t>
+          <t>(03)6206126</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2029/02/05</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -7503,32 +7503,32 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>新悦花園酒店</t>
+          <t>新竹福華大飯店</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>嘉義市東區後湖里6鄰保順路69號</t>
+          <t>新竹市中正路178號</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>(05)2777266#5801</t>
+          <t>(03)5282323#5303</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2027/04/07</t>
+          <t>2026/10/26</t>
         </is>
       </c>
     </row>
@@ -7540,32 +7540,32 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>溪頭福華渡假飯店-溪頭漢光樓</t>
+          <t>新南一二文創商行</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>南投縣鹿谷鄉森林巷11、12號</t>
+          <t>桃園市大溪區中山路１２號</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>(049)2612588#3005</t>
+          <t>(03)3884466</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2028/12/01</t>
+          <t>2029/02/05</t>
         </is>
       </c>
     </row>
@@ -7577,32 +7577,32 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>溪邊小築民宿</t>
+          <t>新悦花園酒店</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>新北市瑞芳區祈堂路133號</t>
+          <t>嘉義市東區後湖里6鄰保順路69號</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>(02)24961191</t>
+          <t>(05)2777266#5801</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2029/06/21</t>
+          <t>2027/04/07</t>
         </is>
       </c>
     </row>
@@ -7614,32 +7614,32 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>煙波大飯店臺南館</t>
+          <t>溪頭福華渡假飯店-溪頭漢光樓</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>臺南市中西區永福路1段269號1-12樓及地下一層至三層</t>
+          <t>南投縣鹿谷鄉森林巷11、12號</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>(06)2156000#1171</t>
+          <t>(049)2612588#3005</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2029/06/09</t>
+          <t>2028/12/01</t>
         </is>
       </c>
     </row>
@@ -7651,32 +7651,32 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>煙波大飯店宜蘭館</t>
+          <t>溪邊小築民宿</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>宜蘭縣宜蘭市凱旋路135號 、135號2至9樓</t>
+          <t>新北市瑞芳區祈堂路133號</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>(09)9256899#1171</t>
+          <t>(02)24961191</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2029/05/06</t>
+          <t>2029/06/21</t>
         </is>
       </c>
     </row>
@@ -7688,22 +7688,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮太魯閣山闊館</t>
+          <t>煙波大飯店臺南館</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村草林10-7號</t>
+          <t>臺南市中西區永福路1段269號1-12樓及地下一層至三層</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>(03)8612000#1470</t>
+          <t>(06)2156000#1171</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026/11/05</t>
+          <t>2029/06/09</t>
         </is>
       </c>
     </row>
@@ -7725,22 +7725,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮太魯閣沁海館</t>
+          <t>煙波大飯店宜蘭館</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村6鄰草林10之6號</t>
+          <t>宜蘭縣宜蘭市凱旋路135號 、135號2至9樓</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>(03)8228835#1174</t>
+          <t>(09)9256899#1171</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2029/04/19</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮館</t>
+          <t>煙波大飯店花蓮太魯閣山闊館</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市民立里1鄰中美路142號</t>
+          <t>花蓮縣新城鄉順安村草林10-7號</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>(03)8228835#1174</t>
+          <t>(03)8612000#1470</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2029/04/19</t>
+          <t>2026/11/05</t>
         </is>
       </c>
     </row>
@@ -7799,22 +7799,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>煙波花時間 宜蘭傳藝</t>
+          <t>煙波大飯店花蓮太魯閣沁海館</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉五濱路二段201號</t>
+          <t>花蓮縣新城鄉順安村6鄰草林10之6號</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>(03)9256899#1171</t>
+          <t>(03)8228835#1174</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2027/07/09</t>
+          <t>2029/04/19</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>煙波花時間 花蓮</t>
+          <t>煙波大飯店花蓮館</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村草林10-5號2~6樓</t>
+          <t>花蓮縣花蓮市民立里1鄰中美路142號</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>(03)8612000#1470</t>
+          <t>(03)8228835#1174</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026/11/16</t>
+          <t>2029/04/19</t>
         </is>
       </c>
     </row>
@@ -7873,32 +7873,32 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>瑞穗天合國際觀光酒店</t>
+          <t>煙波花時間 宜蘭傳藝</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>花蓮縣瑞穗鄉溫泉路二段368號</t>
+          <t>宜蘭縣五結鄉五濱路二段201號</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>(03)8876000#3260</t>
+          <t>(03)9256899#1171</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2028/01/19</t>
+          <t>2027/07/09</t>
         </is>
       </c>
     </row>
@@ -7910,32 +7910,32 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>裕元花園酒店</t>
+          <t>煙波花時間 花蓮</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>臺中市西屯區臺灣大道四段610號</t>
+          <t>花蓮縣新城鄉順安村草林10-5號2~6樓</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>(04)24655660#5030</t>
+          <t>(03)8612000#1470</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2027/11/19</t>
+          <t>2026/11/16</t>
         </is>
       </c>
     </row>
@@ -7947,32 +7947,32 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>遇見民宿</t>
+          <t>瑞穗天合國際觀光酒店</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>屏東縣東港鎮水源路221號(新和段737-4地號)</t>
+          <t>花蓮縣瑞穗鄉溫泉路二段368號</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>(08)8333345</t>
+          <t>(03)8876000#3260</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2028/01/19</t>
         </is>
       </c>
     </row>
@@ -7984,32 +7984,32 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>頌華私墅肆區民宿</t>
+          <t>裕元花園酒店</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>澎湖縣湖西鄉許家村6鄰港子尾120之5號</t>
+          <t>臺中市西屯區臺灣大道四段610號</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>(06)9212953</t>
+          <t>(04)24655660#5030</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2029/01/25</t>
+          <t>2027/11/19</t>
         </is>
       </c>
     </row>
@@ -8021,22 +8021,22 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>嘉仕特飯店</t>
+          <t>遇見民宿</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>桃園市桃園區中山路203號</t>
+          <t>屏東縣東港鎮水源路221號(新和段737-4地號)</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>(03)3343999</t>
+          <t>(08)8333345</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -8058,32 +8058,32 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>嘉義富野渡假酒店</t>
+          <t>頌華私墅肆區民宿</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>嘉義縣民雄鄉三興村升學一街3、5、7、9、11、13、15、17、19、21、23、25、27號</t>
+          <t>澎湖縣湖西鄉許家村6鄰港子尾120之5號</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>(05)2721688</t>
+          <t>(06)9212953</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2028/08/12</t>
+          <t>2029/01/25</t>
         </is>
       </c>
     </row>
@@ -8095,22 +8095,22 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>嘉義智選假日酒店</t>
+          <t>嘉仕特飯店</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>嘉義市西區中興路69號B2至13層樓</t>
+          <t>桃園市桃園區中山路203號</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>(05)2335899#801</t>
+          <t>(03)3343999</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2027/11/24</t>
+          <t>2027/11/27</t>
         </is>
       </c>
     </row>
@@ -8132,32 +8132,32 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>嘉義福容voco酒店</t>
+          <t>嘉義富野渡假酒店</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>嘉義市西區世賢路一段789號B4-4樓、7樓、16樓-32樓</t>
+          <t>嘉義縣民雄鄉三興村升學一街3、5、7、9、11、13、15、17、19、21、23、25、27號</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>(05)232338971</t>
+          <t>(05)2721688</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2029/06/15</t>
+          <t>2028/08/12</t>
         </is>
       </c>
     </row>
@@ -8169,22 +8169,22 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>夢想森林親子民宿</t>
+          <t>嘉義智選假日酒店</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉三星鄉大德路二段613號</t>
+          <t>嘉義市西區中興路69號B2至13層樓</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>(03)9898113</t>
+          <t>(05)2335899#801</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2027/11/24</t>
         </is>
       </c>
     </row>
@@ -8206,32 +8206,32 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>榮美金鬱金香酒店</t>
+          <t>嘉義福容voco酒店</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>臺南市北區海安路三段50號</t>
+          <t>嘉義市西區世賢路一段789號B4-4樓、7樓、16樓-32樓</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>(06)2200800#6001</t>
+          <t>(05)232338971</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2027/11/04</t>
+          <t>2029/06/15</t>
         </is>
       </c>
     </row>
@@ -8243,22 +8243,22 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>榮興金鬱金香酒店</t>
+          <t>夢想森林親子民宿</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>臺南市中西區民族路二段128號</t>
+          <t>宜蘭縣三星鄉三星鄉大德路二段613號</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>(06)2200800#6006</t>
+          <t>(03)9898113</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2027/11/04</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -8280,32 +8280,32 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>福美民宿</t>
+          <t>榮美金鬱金香酒店</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>臺東縣台東市精誠路241號</t>
+          <t>臺南市北區海安路三段50號</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>(089)328466</t>
+          <t>(06)2200800#6001</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2027/01/09</t>
+          <t>2027/11/04</t>
         </is>
       </c>
     </row>
@@ -8317,32 +8317,32 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>福容大飯店 臺北二館</t>
+          <t>榮興金鬱金香酒店</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>新北市深坑區北深路三段236號</t>
+          <t>臺南市中西區民族路二段128號</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>(02)26620088#186</t>
+          <t>(06)2200800#6006</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2028/01/05</t>
+          <t>2027/11/04</t>
         </is>
       </c>
     </row>
@@ -8354,32 +8354,32 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>福容大飯店 桃園</t>
+          <t>福美民宿</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>桃園市桃園區同安里大興西路一段200號</t>
+          <t>臺東縣台東市精誠路241號</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>(03)3265800#300</t>
+          <t>(089)328466</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2027/12/17</t>
+          <t>2027/01/09</t>
         </is>
       </c>
     </row>
@@ -8391,32 +8391,32 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>福容大飯店 桃園機場捷運 A8</t>
+          <t>福容大飯店 臺北二館</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>桃園市龜山區復興一路2號3樓</t>
+          <t>新北市深坑區北深路三段236號</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>(03)3285688#8770</t>
+          <t>(02)26620088#186</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2027/08/12</t>
+          <t>2028/01/05</t>
         </is>
       </c>
     </row>
@@ -8428,32 +8428,32 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>福容大飯店 高雄</t>
+          <t>福容大飯店 桃園</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區五福四路45號</t>
+          <t>桃園市桃園區同安里大興西路一段200號</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>(07)5317777#7782</t>
+          <t>(03)3265800#300</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2028/08/14</t>
+          <t>2027/12/17</t>
         </is>
       </c>
     </row>
@@ -8465,32 +8465,32 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>福容大飯店 淡水漁人碼頭</t>
+          <t>福容大飯店 桃園機場捷運 A8</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>新北市淡水區觀海路83號</t>
+          <t>桃園市龜山區復興一路2號3樓</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>(02)2805 9958#8178</t>
+          <t>(03)3285688#8770</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2028/11/16</t>
+          <t>2027/08/12</t>
         </is>
       </c>
     </row>
@@ -8502,22 +8502,22 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>福容大飯店　福隆</t>
+          <t>福容大飯店 高雄</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>新北市貢寮區福隆里福隆街41號</t>
+          <t>高雄市鹽埕區五福四路45號</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>(02)24992381</t>
+          <t>(07)5317777#7782</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2028/08/14</t>
         </is>
       </c>
     </row>
@@ -8539,32 +8539,32 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>福容大飯店 墾丁</t>
+          <t>福容大飯店 淡水漁人碼頭</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮船帆路1000號</t>
+          <t>新北市淡水區觀海路83號</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>(08)8856969#340</t>
+          <t>(02)2805 9958#8178</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2028/05/28</t>
+          <t>2028/11/16</t>
         </is>
       </c>
     </row>
@@ -8576,22 +8576,22 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>福容大飯店 麗寶樂園</t>
+          <t>福容大飯店　福隆</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>臺中市后里區福容路88號</t>
+          <t>新北市貢寮區福隆里福隆街41號</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>(04)25571366#8343</t>
+          <t>(02)24992381</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2029/03/19</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -8613,22 +8613,22 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>福容大飯店花蓮</t>
+          <t>福容大飯店 墾丁</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市民生路51號</t>
+          <t>屏東縣恆春鎮船帆路1000號</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>(03)8239988#7507</t>
+          <t>(08)8856969#340</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2027/11/10</t>
+          <t>2028/05/28</t>
         </is>
       </c>
     </row>
@@ -8650,22 +8650,22 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>福容徠旅 水里</t>
+          <t>福容大飯店 麗寶樂園</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>南投縣水里鄉東三街51號1樓至6樓</t>
+          <t>臺中市后里區福容路88號</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>(049)2771888#5560</t>
+          <t>(04)25571366#8343</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2029/07/09</t>
+          <t>2029/03/19</t>
         </is>
       </c>
     </row>
@@ -8687,22 +8687,22 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>福容徠旅林口</t>
+          <t>福容大飯店花蓮</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>桃園市龜山區文二一街68號</t>
+          <t>花蓮縣花蓮市民生路51號</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>(03)3277388#300</t>
+          <t>(03)8239988#7507</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2027/12/03</t>
+          <t>2027/11/10</t>
         </is>
       </c>
     </row>
@@ -8724,22 +8724,22 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>福容徠旅高雄</t>
+          <t>福容徠旅 水里</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>高雄市前金區永恆街3號6-14樓</t>
+          <t>南投縣水里鄉東三街51號1樓至6樓</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>(07)2156688#6309</t>
+          <t>(049)2771888#5560</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2029/03/17</t>
+          <t>2029/07/09</t>
         </is>
       </c>
     </row>
@@ -8761,22 +8761,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>福華大飯店</t>
+          <t>福容徠旅林口</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>臺北市大安區仁愛路三段160號</t>
+          <t>桃園市龜山區文二一街68號</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>(02)27002323#2411</t>
+          <t>(03)3277388#300</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2027/12/03</t>
         </is>
       </c>
     </row>
@@ -8798,32 +8798,32 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>福華石門水庫渡假飯店</t>
+          <t>福容徠旅高雄</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>桃園市龍潭區民富街176號</t>
+          <t>高雄市前金區永恆街3號6-14樓</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>(03)4714888</t>
+          <t>(07)2156688#6309</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2027/11/10</t>
+          <t>2029/03/17</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>福華國際文教會館</t>
+          <t>福華大飯店</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>臺北市大安區新生南路3段30號(住宿棟1樓及5樓至14樓)</t>
+          <t>臺北市大安區仁愛路三段160號</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>(02)77122323#2340</t>
+          <t>(02)27002323#2411</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2027/12/11</t>
+          <t>2026/10/26</t>
         </is>
       </c>
     </row>
@@ -8872,32 +8872,32 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>福爾摩沙遊艇酒店</t>
+          <t>福華石門水庫渡假飯店</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>臺南市安平區王城里13鄰安平路988號1至10樓</t>
+          <t>桃園市龍潭區民富街176號</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>(06)3911313</t>
+          <t>(03)4714888</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2027/02/27</t>
+          <t>2027/11/10</t>
         </is>
       </c>
     </row>
@@ -8909,32 +8909,32 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>綠意山莊民宿</t>
+          <t>福華國際文教會館</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之5號</t>
+          <t>臺北市大安區新生南路3段30號(住宿棟1樓及5樓至14樓)</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>(037)747711#9</t>
+          <t>(02)77122323#2340</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2028/09/08</t>
+          <t>2027/12/11</t>
         </is>
       </c>
     </row>
@@ -8946,22 +8946,22 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>綠藤輕旅</t>
+          <t>福爾摩沙遊艇酒店</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>桃園市大園區中山南路二段673號</t>
+          <t>臺南市安平區王城里13鄰安平路988號1至10樓</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>(03)2873043</t>
+          <t>(06)3911313</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2027/02/27</t>
         </is>
       </c>
     </row>
@@ -8983,22 +8983,22 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>維悅酒店</t>
+          <t>綠意山莊民宿</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>臺南市安平區慶平路539號 1至5樓及地下1樓</t>
+          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之5號</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>(06)2950888#1125</t>
+          <t>(037)747711#9</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2027/09/01</t>
+          <t>2028/09/08</t>
         </is>
       </c>
     </row>
@@ -9020,22 +9020,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>臺中逢甲智選假日酒店</t>
+          <t>綠藤輕旅</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>臺中市西屯區福星北三街33巷28號</t>
+          <t>桃園市大園區中山南路二段673號</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>(04)27083911#6101</t>
+          <t>(03)2873043</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>臺邦商旅</t>
+          <t>維悅酒店</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -9067,22 +9067,22 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>臺南市安平區永華二街199號</t>
+          <t>臺南市安平區慶平路539號 1至5樓及地下1樓</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>(06)2931800#8603</t>
+          <t>(06)2950888#1125</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/09/01</t>
         </is>
       </c>
     </row>
@@ -9094,22 +9094,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>遠雄悅來大飯店</t>
+          <t>臺中逢甲智選假日酒店</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>花蓮縣壽豐鄉鹽寮村山嶺18號</t>
+          <t>臺中市西屯區福星北三街33巷28號</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>(03)8123900#8266</t>
+          <t>(04)27083911#6101</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2028/12/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9131,32 +9131,32 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>鳳山79 背包客</t>
+          <t>臺邦商旅</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>高雄市鳳山區黃埔新村東一巷79號</t>
+          <t>臺南市安平區永華二街199號</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>(07)5524545</t>
+          <t>(06)2931800#8603</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2028/12/03</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9168,32 +9168,32 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>劍湖山渡假大飯店</t>
+          <t>遠雄悅來大飯店</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>雲林縣古坑鄉永光村大湖口67-8號</t>
+          <t>花蓮縣壽豐鄉鹽寮村山嶺18號</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>(05)5829900#7214</t>
+          <t>(03)8123900#8266</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2027/06/03</t>
+          <t>2028/12/29</t>
         </is>
       </c>
     </row>
@@ -9205,22 +9205,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>澄悅商旅</t>
+          <t>鳳山79 背包客</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮埔崙里中正路510巷1號</t>
+          <t>高雄市鳳山區黃埔新村東一巷79號</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>(04)7785727</t>
+          <t>(07)5524545</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2029/09/07</t>
+          <t>2028/12/03</t>
         </is>
       </c>
     </row>
@@ -9242,32 +9242,32 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>澎湖福朋喜來登酒店</t>
+          <t>劍湖山渡假大飯店</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市新店路197號</t>
+          <t>雲林縣古坑鄉永光村大湖口67-8號</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>(06)9279955#3701</t>
+          <t>(05)5829900#7214</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2028/05/27</t>
+          <t>2027/06/03</t>
         </is>
       </c>
     </row>
@@ -9279,32 +9279,32 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>澎澄飯店</t>
+          <t>澄悅商旅</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市同和路168號</t>
+          <t>彰化縣鹿港鎮埔崙里中正路510巷1號</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>(06)9235678#2103</t>
+          <t>(04)7785727</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2029/08/03</t>
+          <t>2029/09/07</t>
         </is>
       </c>
     </row>
@@ -9316,32 +9316,32 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>緻麗伯爵酒店</t>
+          <t>澎湖福朋喜來登酒店</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>雲林縣斗六市中山路6號</t>
+          <t>澎湖縣馬公市新店路197號</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>(05)5341666#3</t>
+          <t>(06)9279955#3701</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2029/02/10</t>
+          <t>2028/05/27</t>
         </is>
       </c>
     </row>
@@ -9353,32 +9353,32 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>緣羊軒民宿</t>
+          <t>澎澄飯店</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>臺東縣台東市南一街96號</t>
+          <t>澎湖縣馬公市同和路168號</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>089326400</t>
+          <t>(06)9235678#2103</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026/12/05</t>
+          <t>2029/08/03</t>
         </is>
       </c>
     </row>
@@ -9390,32 +9390,32 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺北</t>
+          <t>緻麗伯爵酒店</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
+          <t>雲林縣斗六市中山路6號</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>(02)29583000#7701</t>
+          <t>(05)5341666#3</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2028/03/31</t>
+          <t>2029/02/10</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺東</t>
+          <t>緣羊軒民宿</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>臺東縣台東市新站路260號</t>
+          <t>臺東縣台東市南一街96號</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>(089)231188#7187</t>
+          <t>089326400</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2027/12/05</t>
+          <t>2026/12/05</t>
         </is>
       </c>
     </row>
@@ -9464,32 +9464,32 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>墾丁夏都沙灘酒店</t>
+          <t>趣淘漫旅-臺北</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁路451號</t>
+          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>(0910)371823</t>
+          <t>(02)29583000#7701</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2028/03/09</t>
+          <t>2028/03/31</t>
         </is>
       </c>
     </row>
@@ -9501,22 +9501,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>墾丁福華渡假飯店</t>
+          <t>趣淘漫旅-臺東</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
+          <t>臺東縣台東市新站路260號</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>(08)8862324#2701</t>
+          <t>(089)231188#7187</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2029/04/12</t>
+          <t>2027/12/05</t>
         </is>
       </c>
     </row>
@@ -9538,32 +9538,32 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>橘子民宿</t>
+          <t>墾丁夏都沙灘酒店</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
+          <t>屏東縣恆春鎮墾丁路451號</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>(0972)092658</t>
+          <t>(0910)371823</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2027/11/06</t>
+          <t>2028/03/09</t>
         </is>
       </c>
     </row>
@@ -9575,32 +9575,32 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>翰品酒店 高雄</t>
+          <t>墾丁福華渡假飯店</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區大仁路43號</t>
+          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>(07)5614688#3110</t>
+          <t>(08)8862324#2701</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2027/02/16</t>
+          <t>2029/04/12</t>
         </is>
       </c>
     </row>
@@ -9612,32 +9612,32 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>礁溪老爺酒店</t>
+          <t>橘子民宿</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
+          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>(03)9885211#8006</t>
+          <t>(0972)092658</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2028/08/24</t>
+          <t>2027/11/06</t>
         </is>
       </c>
     </row>
@@ -9649,22 +9649,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>礁溪寒沐酒店</t>
+          <t>翰品酒店 高雄</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
+          <t>高雄市鹽埕區大仁路43號</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>(03)9058007</t>
+          <t>(07)5614688#3110</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2027/02/16</t>
         </is>
       </c>
     </row>
@@ -9686,32 +9686,32 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>禧榕軒大飯店</t>
+          <t>礁溪老爺酒店</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>臺南市北區成功路28號</t>
+          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>(06)2222788#2203</t>
+          <t>(03)9885211#8006</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2029/05/10</t>
+          <t>2028/08/24</t>
         </is>
       </c>
     </row>
@@ -9723,32 +9723,32 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>薆悅酒店野柳渡假館一館</t>
+          <t>礁溪寒沐酒店</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>新北市萬里區野柳里港東路162號之2</t>
+          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>(02)77035770#623</t>
+          <t>(03)9058007</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -9760,32 +9760,32 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>藍水輕旅</t>
+          <t>禧榕軒大飯店</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>桃園市大園區高鐵南路一段126號</t>
+          <t>臺南市北區成功路28號</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>(03)2871855</t>
+          <t>(06)2222788#2203</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2029/05/10</t>
         </is>
       </c>
     </row>
@@ -9797,22 +9797,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>關子嶺富野溫泉會館</t>
+          <t>薆悅酒店野柳渡假館一館</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>臺南市白河區關子嶺28號</t>
+          <t>新北市萬里區野柳里港東路162號之2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>(06)6822288</t>
+          <t>(02)77035770#623</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2029/01/07</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -9834,22 +9834,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>麗格休閒飯店</t>
+          <t>藍水輕旅</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市商校街258.260.262號</t>
+          <t>桃園市大園區高鐵南路一段126號</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>(03)8349922</t>
+          <t>(03)2871855</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2026/11/23</t>
         </is>
       </c>
     </row>
@@ -9871,22 +9871,22 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>麗軒國際飯店</t>
+          <t>關子嶺富野溫泉會館</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市中美路99之1號</t>
+          <t>臺南市白河區關子嶺28號</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>(03)8246898</t>
+          <t>(06)6822288</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2029/01/07</t>
         </is>
       </c>
     </row>
@@ -9908,7 +9908,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>麗翔大飯店</t>
+          <t>麗格休閒飯店</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
+          <t>花蓮縣花蓮市商校街258.260.262號</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>(03)8323737</t>
+          <t>(03)8349922</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2028/01/12</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -9945,22 +9945,22 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>讀好民宿</t>
+          <t>麗軒國際飯店</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
+          <t>花蓮縣花蓮市中美路99之1號</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>(0920)023139</t>
+          <t>(03)8246898</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -9982,32 +9982,32 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>觀霧山莊</t>
+          <t>麗翔大飯店</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
+          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>(03)3343818</t>
+          <t>(03)8323737</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2029/01/22</t>
+          <t>2028/01/12</t>
         </is>
       </c>
     </row>
@@ -10019,32 +10019,32 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>綉溪安平</t>
+          <t>讀好民宿</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>(06)3910988#3111</t>
+          <t>(0920)023139</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2028/10/12</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -10056,30 +10056,104 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
+          <t>觀霧山莊</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>苗栗縣</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>(03)3343818</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>銀級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>2029/01/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>綉溪安平</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>臺南市</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>(06)3910988#3111</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>銀級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>2028/10/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
           <t>鐡馬騎跡</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
+      <c r="C263" t="inlineStr">
         <is>
           <t>屏東縣</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="D263" t="inlineStr">
         <is>
           <t>屏東縣東港鎮新學路50號</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="E263" t="inlineStr">
         <is>
           <t>(0952)848898</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>銅級環保旅宿</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
         <is>
           <t>2029/01/18</t>
         </is>

--- a/環保旅宿_Selenium結果.xlsx
+++ b/環保旅宿_Selenium結果.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G263"/>
+  <dimension ref="A1:G264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3470,32 +3470,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>林口維多利亞民宿</t>
+          <t>承億酒店</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>桃園市蘆竹區坑子里14鄰八德二路280巷11號</t>
+          <t>高雄市前鎮區林森四路189號</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>(0905)111918</t>
+          <t>(07)3332000#6870</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2029/08/24</t>
+          <t>2029/09/22</t>
         </is>
       </c>
     </row>
@@ -3507,32 +3507,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>板橋凱撒大飯店</t>
+          <t>林口維多利亞民宿</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>新北市板橋區縣民大道二段8號</t>
+          <t>桃園市蘆竹區坑子里14鄰八德二路280巷11號</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>(02)29583000#7701</t>
+          <t>(0905)111918</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2029/02/12</t>
+          <t>2029/08/24</t>
         </is>
       </c>
     </row>
@@ -3544,32 +3544,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>武陵國民賓館</t>
+          <t>板橋凱撒大飯店</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>臺中市和平區平等里武陵路3-1號</t>
+          <t>新北市板橋區縣民大道二段8號</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>(04)25901258#2103</t>
+          <t>(02)29583000#7701</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026/12/25</t>
+          <t>2029/02/12</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>武陵富野渡假村</t>
+          <t>武陵國民賓館</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>臺中市和平區武陵路3-16號</t>
+          <t>臺中市和平區平等里武陵路3-1號</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(04)25901399#8912</t>
+          <t>(04)25901258#2103</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2026/12/25</t>
         </is>
       </c>
     </row>
@@ -3618,32 +3618,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>河那灣</t>
+          <t>武陵富野渡假村</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>桃園市復興區澤仁里3鄰溪口台41號</t>
+          <t>臺中市和平區武陵路3-16號</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(0919)235303</t>
+          <t>(04)25901399#8912</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2027/07/25</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -3655,22 +3655,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>波西米亞民宿</t>
+          <t>河那灣</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>花蓮縣吉安鄉東昌村13鄰東海一街168號</t>
+          <t>桃園市復興區澤仁里3鄰溪口台41號</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(0385)31234</t>
+          <t>(0919)235303</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2029/01/06</t>
+          <t>2027/07/25</t>
         </is>
       </c>
     </row>
@@ -3692,22 +3692,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>泡泡森林民宿</t>
+          <t>波西米亞民宿</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>臺東縣台東市南一街40號</t>
+          <t>花蓮縣吉安鄉東昌村13鄰東海一街168號</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0986866545</t>
+          <t>(0385)31234</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026/12/06</t>
+          <t>2029/01/06</t>
         </is>
       </c>
     </row>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>泊寓</t>
+          <t>泡泡森林民宿</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮鹿興路57巷3號</t>
+          <t>臺東縣台東市南一街40號</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>(04)7115655#120</t>
+          <t>0986866545</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2026/12/06</t>
         </is>
       </c>
     </row>
@@ -3766,22 +3766,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>爸爸萬歲民宿</t>
+          <t>泊寓</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市延平街68巷27號</t>
+          <t>彰化縣鹿港鎮鹿興路57巷3號</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(0900)757520</t>
+          <t>(04)7115655#120</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2027/01/10</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -3803,22 +3803,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>迎曦大飯店</t>
+          <t>爸爸萬歲民宿</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>新竹市東區親仁里文化街10號2-10樓</t>
+          <t>花蓮縣花蓮市延平街68巷27號</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>(03)5347266#124</t>
+          <t>(0900)757520</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2028/04/28</t>
+          <t>2027/01/10</t>
         </is>
       </c>
     </row>
@@ -3840,32 +3840,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>金湖飯店</t>
+          <t>迎曦大飯店</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>金門縣金湖鎮太湖路二段218號</t>
+          <t>新竹市東區親仁里文化街10號2-10樓</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(082)379666#160</t>
+          <t>(03)5347266#124</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026/12/03</t>
+          <t>2028/04/28</t>
         </is>
       </c>
     </row>
@@ -3877,22 +3877,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>長榮文苑酒店(嘉義)</t>
+          <t>金湖飯店</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>嘉義縣太保市東勢里故宮大道777號</t>
+          <t>金門縣金湖鎮太湖路二段218號</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(05)3669988#2700</t>
+          <t>(082)379666#160</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2027/04/11</t>
+          <t>2026/12/03</t>
         </is>
       </c>
     </row>
@@ -3914,22 +3914,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(臺中)</t>
+          <t>長榮文苑酒店(嘉義)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>臺中市西屯區臺灣大道二段666號</t>
+          <t>嘉義縣太保市東勢里故宮大道777號</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>(04)23242236#2700</t>
+          <t>(05)3669988#2700</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2027/07/09</t>
+          <t>2027/04/11</t>
         </is>
       </c>
     </row>
@@ -3951,22 +3951,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(臺北)</t>
+          <t>長榮桂冠酒店(臺中)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>臺北市中山區松江路63號</t>
+          <t>臺中市西屯區臺灣大道二段666號</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>(02)25019988#2701</t>
+          <t>(04)23242236#2700</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2028/10/22</t>
+          <t>2027/07/09</t>
         </is>
       </c>
     </row>
@@ -3988,32 +3988,32 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(基隆)</t>
+          <t>長榮桂冠酒店(臺北)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>基隆市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>基隆市中正區中正路62號之1</t>
+          <t>臺北市中山區松江路63號</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(02)24279988</t>
+          <t>(02)25019988#2701</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2028/05/22</t>
+          <t>2028/10/22</t>
         </is>
       </c>
     </row>
@@ -4025,22 +4025,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>長榮鳳凰酒店(礁溪)</t>
+          <t>長榮桂冠酒店(基隆)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>基隆市</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉健康路77號</t>
+          <t>基隆市中正區中正路62號之1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>(03)9100988#2335</t>
+          <t>(02)24279988</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2027/09/15</t>
+          <t>2028/05/22</t>
         </is>
       </c>
     </row>
@@ -4062,32 +4062,32 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>阿里山東方明珠國際大飯店</t>
+          <t>長榮鳳凰酒店(礁溪)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>嘉義縣中埔鄉社口村檨仔林23號</t>
+          <t>宜蘭縣礁溪鄉健康路77號</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>(05)2536999</t>
+          <t>(03)9100988#2335</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2027/12/12</t>
+          <t>2027/09/15</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>阿里山英迪格酒店</t>
+          <t>阿里山東方明珠國際大飯店</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4109,22 +4109,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>嘉義縣番路鄉公田村2鄰龍頭20號2樓之1等10筆</t>
+          <t>嘉義縣中埔鄉社口村檨仔林23號</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>(05)2586800#121</t>
+          <t>(05)2536999</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2028/10/21</t>
+          <t>2027/12/12</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>阿里山賓館（現代館）</t>
+          <t>阿里山英迪格酒店</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>嘉義縣阿里山鄉香林村西阿里山16-1號</t>
+          <t>嘉義縣番路鄉公田村2鄰龍頭20號2樓之1等10筆</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>(05)2679996#5117</t>
+          <t>(05)2586800#121</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2027/06/19</t>
+          <t>2028/10/21</t>
         </is>
       </c>
     </row>
@@ -4173,32 +4173,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>阿爾卑斯莊園</t>
+          <t>阿里山賓館（現代館）</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉協和村親河路二段88巷37號</t>
+          <t>嘉義縣阿里山鄉香林村西阿里山16-1號</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>(0905)787698</t>
+          <t>(05)2679996#5117</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2029/09/02</t>
+          <t>2027/06/19</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>冠翔泉旅</t>
+          <t>阿爾卑斯莊園</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4220,22 +4220,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉仁愛路66巷6號</t>
+          <t>宜蘭縣五結鄉協和村親河路二段88巷37號</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>(03)9875599#119</t>
+          <t>(0905)787698</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2029/07/20</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -4247,22 +4247,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>南港老爺行旅</t>
+          <t>冠翔泉旅</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>臺北市南港區經貿二路196號、196號10樓至20樓</t>
+          <t>宜蘭縣礁溪鄉仁愛路66巷6號</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>(02)77500588</t>
+          <t>(03)9875599#119</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2028/11/27</t>
+          <t>2029/07/20</t>
         </is>
       </c>
     </row>
@@ -4284,32 +4284,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>城市商旅美麗島館(HOTEL PAPA WHALE)</t>
+          <t>南港老爺行旅</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>高雄市新興區民生一路328號1-7樓</t>
+          <t>臺北市南港區經貿二路196號、196號10樓至20樓</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>(07)2519888</t>
+          <t>(02)77500588</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2028/09/24</t>
+          <t>2028/11/27</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>城市商旅高雄真愛館</t>
+          <t>城市商旅美麗島館(HOTEL PAPA WHALE)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區大義街1號</t>
+          <t>高雄市新興區民生一路328號1-7樓</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>(07)5215116#9303</t>
+          <t>(07)2519888</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2028/09/25</t>
+          <t>2028/09/24</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>城市商旅駁二館</t>
+          <t>城市商旅高雄真愛館</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4368,12 +4368,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區公園二路83號1至11樓</t>
+          <t>高雄市鹽埕區大義街1號</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>(07)5322777</t>
+          <t>(07)5215116#9303</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>城市商旅德立莊博愛館</t>
+          <t>城市商旅駁二館</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>高雄市三民區博愛一路338號地上1至10樓</t>
+          <t>高雄市鹽埕區公園二路83號1至11樓</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>(07)3238777#9301</t>
+          <t>(07)5322777</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2028/08/07</t>
+          <t>2028/09/25</t>
         </is>
       </c>
     </row>
@@ -4432,32 +4432,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>星8藝宿</t>
+          <t>城市商旅德立莊博愛館</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉中山路三段192巷8號</t>
+          <t>高雄市三民區博愛一路338號地上1至10樓</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>(0932)495200</t>
+          <t>(07)3238777#9301</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2029/01/07</t>
+          <t>2028/08/07</t>
         </is>
       </c>
     </row>
@@ -4469,22 +4469,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>星漾商旅</t>
+          <t>星8藝宿</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>臺中市北區錦南街17號,錦新街30號4樓至9樓,錦新街32號4樓至9樓</t>
+          <t>宜蘭縣三星鄉中山路三段192巷8號</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>(04)22289008</t>
+          <t>(0932)495200</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2029/01/07</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>星漾商旅(中清館)</t>
+          <t>星漾商旅</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>臺中市北區中清路一段63號</t>
+          <t>臺中市北區錦南街17號,錦新街30號4樓至9樓,錦新街32號4樓至9樓</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>(04)22083888</t>
+          <t>(04)22289008</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4543,22 +4543,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>柳營尖山埤渡假村</t>
+          <t>星漾商旅(中清館)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>臺南市柳營區旭山里60號</t>
+          <t>臺中市北區中清路一段63號</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>(06)6233888#2100</t>
+          <t>(04)22083888</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2029/07/28</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -4580,32 +4580,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>美之旅商務飯店</t>
+          <t>柳營尖山埤渡假村</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>臺中市西區美村路一段269號1樓、2樓之1、2樓之2、3、4、5、6、7樓</t>
+          <t>臺南市柳營區旭山里60號</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>(04)23024330</t>
+          <t>(06)6233888#2100</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2029/04/07</t>
+          <t>2029/07/28</t>
         </is>
       </c>
     </row>
@@ -4617,32 +4617,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>美侖商旅</t>
+          <t>美之旅商務飯店</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>臺北市中山區吉林路49號1至8樓</t>
+          <t>臺中市西區美村路一段269號1樓、2樓之1、2樓之2、3、4、5、6、7樓</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>(02)25313535#878</t>
+          <t>(04)23024330</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2028/11/27</t>
+          <t>2029/04/07</t>
         </is>
       </c>
     </row>
@@ -4654,32 +4654,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>美墅館</t>
+          <t>美侖商旅</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>臺南市善化區昌隆里9鄰東勢寮131之8號</t>
+          <t>臺北市中山區吉林路49號1至8樓</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>(09)20656908</t>
+          <t>(02)25313535#878</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2028/11/27</t>
         </is>
       </c>
     </row>
@@ -4691,22 +4691,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>美綠民宿</t>
+          <t>美墅館</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>高雄市美濃區獅山里竹門14-2號</t>
+          <t>臺南市善化區昌隆里9鄰東勢寮131之8號</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>(07)6851111</t>
+          <t>(09)20656908</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2028/12/28</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -4728,22 +4728,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>夏堤民宿</t>
+          <t>美綠民宿</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>屏東縣琉球鄉上福村2鄰杉板路51巷2號</t>
+          <t>高雄市美濃區獅山里竹門14-2號</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(08)8611155</t>
+          <t>(07)6851111</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2029/02/25</t>
+          <t>2028/12/28</t>
         </is>
       </c>
     </row>
@@ -4765,22 +4765,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>夏優旅居</t>
+          <t>夏堤民宿</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區新興街67號</t>
+          <t>屏東縣琉球鄉上福村2鄰杉板路51巷2號</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(07)5328885</t>
+          <t>(08)8611155</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2028/12/11</t>
+          <t>2029/02/25</t>
         </is>
       </c>
     </row>
@@ -4802,22 +4802,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>娜路彎花園酒店</t>
+          <t>夏優旅居</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>臺東縣台東市新興路77號</t>
+          <t>高雄市鹽埕區新興街67號</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(089)231111</t>
+          <t>(07)5328885</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2028/12/11</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>娜路彎會館</t>
+          <t>娜路彎花園酒店</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>臺東縣台東市中興路2段385號</t>
+          <t>臺東縣台東市新興路77號</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(089)235500</t>
+          <t>(089)231111</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>娜路彎銀河行館</t>
+          <t>娜路彎會館</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>臺東縣台東市豐興路88號</t>
+          <t>臺東縣台東市中興路2段385號</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(089)383366</t>
+          <t>(089)235500</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2028/09/16</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>娜路彎銀河酒店</t>
+          <t>娜路彎銀河行館</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4923,22 +4923,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>臺東縣台東市豐興路66號</t>
+          <t>臺東縣台東市豐興路88號</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(089)225000#8263</t>
+          <t>(089)383366</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2028/09/03</t>
+          <t>2028/09/16</t>
         </is>
       </c>
     </row>
@@ -4950,32 +4950,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>悅徠舘</t>
+          <t>娜路彎銀河酒店</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>桃園市龜山區興華三街18號2樓之1</t>
+          <t>臺東縣台東市豐興路66號</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(03)3280177</t>
+          <t>(089)225000#8263</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2028/09/03</t>
         </is>
       </c>
     </row>
@@ -4987,22 +4987,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>悅豪大飯店</t>
+          <t>悅徠舘</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>新竹市東區復興路22號</t>
+          <t>桃園市龜山區興華三街18號2樓之1</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>(03)5267890</t>
+          <t>(03)3280177</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2029/07/20</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -5024,22 +5024,22 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>旅行邦尼</t>
+          <t>悅豪大飯店</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>新北市淡水區中山路87巷7號</t>
+          <t>新竹市東區復興路22號</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(09)28824850</t>
+          <t>(03)5267890</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2029/01/05</t>
+          <t>2029/07/20</t>
         </is>
       </c>
     </row>
@@ -5061,22 +5061,22 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>旅悅國際青年旅館</t>
+          <t>旅行邦尼</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>高雄市前鎮區三多三路211號3樓及4樓</t>
+          <t>新北市淡水區中山路87巷7號</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(07)3359006</t>
+          <t>(09)28824850</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2027/10/13</t>
+          <t>2029/01/05</t>
         </is>
       </c>
     </row>
@@ -5098,32 +5098,32 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>桃園大溪笠復威斯汀度假酒店</t>
+          <t>旅悅國際青年旅館</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>桃園市大溪區日新路166號</t>
+          <t>高雄市前鎮區三多三路211號3樓及4樓</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(03)2725035</t>
+          <t>(07)3359006</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2027/10/13</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>桃園喜來登酒店</t>
+          <t>桃園大溪笠復威斯汀度假酒店</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>桃園市大園區大觀路777號</t>
+          <t>桃園市大溪區日新路166號</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(03)3850000#2605</t>
+          <t>(03)2725035</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026/10/29</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -5172,22 +5172,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>泰安觀止溫泉會館</t>
+          <t>桃園喜來登酒店</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>苗栗縣泰安鄉錦水村圓墩58-7號</t>
+          <t>桃園市大園區大觀路777號</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(037)941951#527</t>
+          <t>(03)3850000#2605</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2028/06/25</t>
+          <t>2026/10/29</t>
         </is>
       </c>
     </row>
@@ -5209,32 +5209,32 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>海福花園飯店</t>
+          <t>泰安觀止溫泉會館</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>金門縣金沙鎮高陽路1號</t>
+          <t>苗栗縣泰安鄉錦水村圓墩58-7號</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>(082)353888</t>
+          <t>(037)941951#527</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2029/09/01</t>
+          <t>2028/06/25</t>
         </is>
       </c>
     </row>
@@ -5246,22 +5246,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>海霞您的家</t>
+          <t>海福花園飯店</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>新北市貢寮區仁里里14鄰仁愛路38號</t>
+          <t>金門縣金沙鎮高陽路1號</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(09)35204895</t>
+          <t>(082)353888</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2029/09/01</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>海灣假日酒店</t>
+          <t>海霞您的家</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5293,22 +5293,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>新北市深坑區北深路3段265號</t>
+          <t>新北市貢寮區仁里里14鄰仁愛路38號</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(02)77035880</t>
+          <t>(09)35204895</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2028/12/17</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>神隱國度民宿</t>
+          <t>海灣假日酒店</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5330,22 +5330,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>新北市瑞芳區崙頂路90號</t>
+          <t>新北市深坑區北深路3段265號</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>(09)05788650</t>
+          <t>(02)77035880</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2028/12/17</t>
         </is>
       </c>
     </row>
@@ -5357,32 +5357,32 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>秧悦美地度假酒店</t>
+          <t>神隱國度民宿</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>花蓮縣吉安鄉干城村干城二街95-9號</t>
+          <t>新北市瑞芳區崙頂路90號</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>(03)8129168#2701</t>
+          <t>(09)05788650</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -5394,32 +5394,32 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>秘境41</t>
+          <t>秧悦美地度假酒店</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>桃園市大溪區興和里中央路41號</t>
+          <t>花蓮縣吉安鄉干城村干城二街95-9號</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(03)3887111</t>
+          <t>(03)8129168#2701</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2027/12/10</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -5431,22 +5431,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>秘境民宿</t>
+          <t>秘境41</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>屏東縣東港鎮屏東縣東港鎮水源路223號(新和段737-3地號)</t>
+          <t>桃園市大溪區興和里中央路41號</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>(08)8333345</t>
+          <t>(03)3887111</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2029/01/18</t>
+          <t>2027/12/10</t>
         </is>
       </c>
     </row>
@@ -5468,32 +5468,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>高雄中央公園英迪格酒店</t>
+          <t>秘境民宿</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>高雄市新興區中山一路4號</t>
+          <t>屏東縣東港鎮屏東縣東港鎮水源路223號(新和段737-3地號)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>(07)2721555#301</t>
+          <t>(08)8333345</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2029/01/18</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>高雄商旅</t>
+          <t>高雄中央公園英迪格酒店</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5515,22 +5515,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>高雄市新興區民族二路33號1、4~10樓；37號1、3~10樓</t>
+          <t>高雄市新興區中山一路4號</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>(09)19546590</t>
+          <t>(07)2721555#301</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>高雄富野渡假酒店</t>
+          <t>高雄商旅</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>高雄市前鎮區瑞田街99號</t>
+          <t>高雄市新興區民族二路33號1、4~10樓；37號1、3~10樓</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>(07)8215299#7102</t>
+          <t>(09)19546590</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2029/02/09</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>高雄圓山大飯店</t>
+          <t>高雄富野渡假酒店</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5589,22 +5589,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>高雄市鳥松區圓山路2號</t>
+          <t>高雄市前鎮區瑞田街99號</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>(07)3706007#519</t>
+          <t>(07)8215299#7102</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2029/02/09</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>高雄福華大飯店</t>
+          <t>高雄圓山大飯店</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>高雄市新興區七賢一路311號</t>
+          <t>高雄市鳥松區圓山路2號</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>(07)2307737</t>
+          <t>(07)3706007#519</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026/11/16</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -5653,32 +5653,32 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>國聯大飯店</t>
+          <t>高雄福華大飯店</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>臺北市大安區光復南路200號</t>
+          <t>高雄市新興區七賢一路311號</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(02)27731515#184</t>
+          <t>(07)2307737</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2029/09/15</t>
+          <t>2026/11/16</t>
         </is>
       </c>
     </row>
@@ -5690,22 +5690,22 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>基拉耳景觀民宿</t>
+          <t>國聯大飯店</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>桃園市復興區溪口路16巷29號</t>
+          <t>臺北市大安區光復南路200號</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(02)23965188#594</t>
+          <t>(02)27731515#184</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2028/06/15</t>
+          <t>2029/09/15</t>
         </is>
       </c>
     </row>
@@ -5727,32 +5727,32 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>將捷金鬱金香酒店</t>
+          <t>基拉耳景觀民宿</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>新北市淡水區中正路1段2之1號(A區地上3至6層、B區地上1至5層、C區地下3層至地上3層)</t>
+          <t>桃園市復興區溪口路16巷29號</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(02)26218555#2913</t>
+          <t>(02)23965188#594</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2027/04/14</t>
+          <t>2028/06/15</t>
         </is>
       </c>
     </row>
@@ -5764,32 +5764,32 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>康橋商旅-六合夜市七賢館</t>
+          <t>將捷金鬱金香酒店</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>高雄市新興區同愛街28號1樓、30號</t>
+          <t>新北市淡水區中正路1段2之1號(A區地上3至6層、B區地上1至5層、C區地下3層至地上3層)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(07)288-5588</t>
+          <t>(02)26218555#2913</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2027/04/14</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>康橋商旅臺南赤崁樓館</t>
+          <t>康橋商旅-六合夜市七賢館</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>臺南市中西區赤崁里民權路二段97號1至8樓</t>
+          <t>高雄市新興區同愛街28號1樓、30號</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(06)2253377</t>
+          <t>(07)288-5588</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2029/09/02</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>康橋慢旅</t>
+          <t>康橋商旅臺南赤崁樓館</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>臺南市中西區民生路二段416號</t>
+          <t>臺南市中西區赤崁里民權路二段97號1至8樓</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>(06)2805566</t>
+          <t>(06)2253377</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>捷絲旅 臺南虎山館</t>
+          <t>康橋慢旅</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5885,22 +5885,22 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>臺南市仁德區成功里5鄰文華路2段300號1~9樓，地下一、二樓</t>
+          <t>臺南市中西區民生路二段416號</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>(06)2662218#8321</t>
+          <t>(06)2805566</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2028/02/13</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -5912,22 +5912,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>捷絲旅臺北三重館</t>
+          <t>捷絲旅 臺南虎山館</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>新北市三重區三和路四段107-1號</t>
+          <t>臺南市仁德區成功里5鄰文華路2段300號1~9樓，地下一、二樓</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>(02)22806111#8304</t>
+          <t>(06)2662218#8321</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2028/10/12</t>
+          <t>2028/02/13</t>
         </is>
       </c>
     </row>
@@ -5949,32 +5949,32 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>捷絲旅西門町店</t>
+          <t>捷絲旅臺北三重館</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路一段41號5樓至9樓</t>
+          <t>新北市三重區三和路四段107-1號</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(02)25215000</t>
+          <t>(02)22806111#8304</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2027/05/12</t>
+          <t>2028/10/12</t>
         </is>
       </c>
     </row>
@@ -5986,32 +5986,32 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>捷絲旅花蓮中正館</t>
+          <t>捷絲旅西門町店</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市主睦里14鄰中正路396號</t>
+          <t>臺北市中正區中華路一段41號5樓至9樓</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>(03)8900069#8104</t>
+          <t>(02)25215000</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2027/05/12</t>
         </is>
       </c>
     </row>
@@ -6023,22 +6023,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>捷絲旅高雄中正館</t>
+          <t>捷絲旅花蓮中正館</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>高雄市苓雅區中正一路134號</t>
+          <t>花蓮縣花蓮市主睦里14鄰中正路396號</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(07)9733587#8104</t>
+          <t>(03)8900069#8104</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>捷絲旅高雄站前館</t>
+          <t>捷絲旅高雄中正館</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>高雄市新興區中山一路280號1至14樓</t>
+          <t>高雄市苓雅區中正一路134號</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2028/09/29</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>捷絲旅臺大尊賢館</t>
+          <t>捷絲旅高雄站前館</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>臺北市大安區羅斯福路四段83號1-10樓</t>
+          <t>高雄市新興區中山一路280號1至14樓</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(02)77355088</t>
+          <t>(07)9733587#8104</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/09/29</t>
         </is>
       </c>
     </row>
@@ -6134,32 +6134,32 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>捷絲旅礁溪館</t>
+          <t>捷絲旅臺大尊賢館</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉德陽路24巷8號、10號</t>
+          <t>臺北市大安區羅斯福路四段83號1-10樓</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(03)9102000#8104</t>
+          <t>(02)77355088</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2027/01/07</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6171,32 +6171,32 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>清新溫泉飯店</t>
+          <t>捷絲旅礁溪館</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>臺中市烏日區溫泉路2號</t>
+          <t>宜蘭縣礁溪鄉德陽路24巷8號、10號</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(04)23831088#7602</t>
+          <t>(03)9102000#8104</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2027/01/07</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>統一谷關渡假村</t>
+          <t>清新溫泉飯店</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6218,22 +6218,22 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>臺中市和平區博愛里東關路一段188號</t>
+          <t>臺中市烏日區溫泉路2號</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>(04)25950000</t>
+          <t>(04)23831088#7602</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2028/01/06</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -6245,22 +6245,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>統一渡假村</t>
+          <t>統一谷關渡假村</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>新竹縣關西鎮金山里34號</t>
+          <t>臺中市和平區博愛里東關路一段188號</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>(03)5478888</t>
+          <t>(04)25950000</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2027/12/20</t>
+          <t>2028/01/06</t>
         </is>
       </c>
     </row>
@@ -6282,22 +6282,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>鹿港澄悅酒店</t>
+          <t>統一渡假村</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮中正路598號1樓、5至8樓</t>
+          <t>新竹縣關西鎮金山里34號</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>(04)7785727</t>
+          <t>(03)5478888</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2029/03/02</t>
+          <t>2027/12/20</t>
         </is>
       </c>
     </row>
@@ -6319,32 +6319,32 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>傑仕堡有氧酒店</t>
+          <t>鹿港澄悅酒店</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>新北市板橋區縣民大道2段275號、275號2至17樓、277號2樓</t>
+          <t>彰化縣鹿港鎮中正路598號1樓、5至8樓</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>(02)77273000#54083</t>
+          <t>(04)7785727</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026/10/16</t>
+          <t>2029/03/02</t>
         </is>
       </c>
     </row>
@@ -6356,32 +6356,32 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>凱旋酒店</t>
+          <t>傑仕堡有氧酒店</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>臺北市內湖區江南街55號3樓至9樓</t>
+          <t>新北市板橋區縣民大道2段275號、275號2至17樓、277號2樓</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>(02)87527888#6203</t>
+          <t>(02)77273000#54083</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026/12/10</t>
+          <t>2026/10/16</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>凱達大飯店</t>
+          <t>凱旋酒店</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6403,22 +6403,22 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>臺北市萬華區艋舺大道167號1-26樓</t>
+          <t>臺北市內湖區江南街55號3樓至9樓</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(02)23836789#6321</t>
+          <t>(02)87527888#6203</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2027/06/02</t>
+          <t>2026/12/10</t>
         </is>
       </c>
     </row>
@@ -6430,32 +6430,32 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>凱撒大飯店</t>
+          <t>凱達大飯店</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁路6號</t>
+          <t>臺北市萬華區艋舺大道167號1-26樓</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(08)8861888</t>
+          <t>(02)23836789#6321</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2028/09/16</t>
+          <t>2027/06/02</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>勝利127民宿</t>
+          <t>凱撒大飯店</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6477,22 +6477,22 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>屏東縣屏東市勝利路127號</t>
+          <t>屏東縣恆春鎮墾丁路6號</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(08)7320099</t>
+          <t>(08)8861888</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026/12/14</t>
+          <t>2028/09/16</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>勝利131民宿</t>
+          <t>勝利127民宿</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>屏東縣屏東市勝利路131號</t>
+          <t>屏東縣屏東市勝利路127號</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6541,32 +6541,32 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>寒居酒店</t>
+          <t>勝利131民宿</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>臺北市中山區松江路116號1樓至9樓</t>
+          <t>屏東縣屏東市勝利路131號</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(02)66008000#8886</t>
+          <t>(08)7320099</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2028/07/17</t>
+          <t>2026/12/14</t>
         </is>
       </c>
     </row>
@@ -6578,32 +6578,32 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>寒軒國際大飯店</t>
+          <t>寒居酒店</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>高雄市苓雅區四維三路三十三號</t>
+          <t>臺北市中山區松江路116號1樓至9樓</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>(0980)556224</t>
+          <t>(02)66008000#8886</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2028/12/11</t>
+          <t>2028/07/17</t>
         </is>
       </c>
     </row>
@@ -6615,22 +6615,22 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>富光大旅社</t>
+          <t>寒軒國際大飯店</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公園路19-7號</t>
+          <t>高雄市苓雅區四維三路三十三號</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>(08)7345656</t>
+          <t>(0980)556224</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2028/05/28</t>
+          <t>2028/12/11</t>
         </is>
       </c>
     </row>
@@ -6652,32 +6652,32 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>富信大飯店</t>
+          <t>富光大旅社</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>新北市汐止區大同路一段152號</t>
+          <t>屏東縣屏東市公園路19-7號</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>(02)26416422#5112</t>
+          <t>(08)7345656</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2028/03/13</t>
+          <t>2028/05/28</t>
         </is>
       </c>
     </row>
@@ -6689,32 +6689,32 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>尊爵大飯店</t>
+          <t>富信大飯店</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>桃園市桃園區莊敬路一段300號</t>
+          <t>新北市汐止區大同路一段152號</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>(03)3169090#8502</t>
+          <t>(02)26416422#5112</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026/12/21</t>
+          <t>2028/03/13</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>尊爵天際大飯店</t>
+          <t>尊爵大飯店</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>桃園市蘆竹區南崁路一段108號</t>
+          <t>桃園市桃園區莊敬路一段300號</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>(03)2228100#6081</t>
+          <t>(03)3169090#8502</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2028/08/31</t>
+          <t>2026/12/21</t>
         </is>
       </c>
     </row>
@@ -6763,32 +6763,32 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>惠來谷關溫泉會館</t>
+          <t>尊爵天際大飯店</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>臺中市和平區東關路一段溫泉巷十號</t>
+          <t>桃園市蘆竹區南崁路一段108號</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(04)25951998#621</t>
+          <t>(03)2228100#6081</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2029/08/13</t>
+          <t>2028/08/31</t>
         </is>
       </c>
     </row>
@@ -6800,32 +6800,32 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>提米好旅</t>
+          <t>惠來谷關溫泉會館</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>彰化縣彰化市成功路277號</t>
+          <t>臺中市和平區東關路一段溫泉巷十號</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(04)7061086#9</t>
+          <t>(04)25951998#621</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>2029/08/13</t>
         </is>
       </c>
     </row>
@@ -6837,32 +6837,32 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>揚昊民宿</t>
+          <t>提米好旅</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之6號</t>
+          <t>彰化縣彰化市成功路277號</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(037)747711#9</t>
+          <t>(04)7061086#9</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2028/09/08</t>
+          <t>2027/11/27</t>
         </is>
       </c>
     </row>
@@ -6874,22 +6874,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>晶泉丰旅</t>
+          <t>揚昊民宿</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉溫泉路67號2至10樓</t>
+          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之6號</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>(03)9100000#6105</t>
+          <t>(037)747711#9</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2027/05/22</t>
+          <t>2028/09/08</t>
         </is>
       </c>
     </row>
@@ -6911,22 +6911,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>智醫康寓</t>
+          <t>晶泉丰旅</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>桃園市桃園區民生路107號1-3樓及7-20樓</t>
+          <t>宜蘭縣礁溪鄉溫泉路67號2至10樓</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>(03)3362575</t>
+          <t>(03)9100000#6105</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026/10/30</t>
+          <t>2027/05/22</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>渴望會館</t>
+          <t>智醫康寓</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6958,22 +6958,22 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>桃園市龍潭區渴望路428號3-5樓</t>
+          <t>桃園市桃園區民生路107號1-3樓及7-20樓</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>(03)4072999#7110</t>
+          <t>(03)3362575</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2026/10/30</t>
         </is>
       </c>
     </row>
@@ -6985,22 +6985,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>然一酒店</t>
+          <t>渴望會館</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>高雄市前鎮區中山二路199號</t>
+          <t>桃園市龍潭區渴望路428號3-5樓</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>(07)9730186#1666</t>
+          <t>(03)4072999#7110</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2027/06/03</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -7022,32 +7022,32 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>發現號特色民宿</t>
+          <t>然一酒店</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>屏東縣林邊鄉崎峰村裕後路90號</t>
+          <t>高雄市前鎮區中山二路199號</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>(08)8750300</t>
+          <t>(07)9730186#1666</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2027/06/03</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>華泰瑞苑</t>
+          <t>發現號特色民宿</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7069,22 +7069,22 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮公園路101號</t>
+          <t>屏東縣林邊鄉崎峰村裕後路90號</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>(08)8863666</t>
+          <t>(08)8750300</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2027/06/21</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -7096,32 +7096,32 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>貳十二度行旅</t>
+          <t>華泰瑞苑</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>宜蘭縣蘇澳鎮信義路177號</t>
+          <t>屏東縣恆春鎮公園路101號</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>(03)9901888</t>
+          <t>(08)8863666</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2029/05/24</t>
+          <t>2027/06/21</t>
         </is>
       </c>
     </row>
@@ -7133,32 +7133,32 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>陽明山天籟渡假酒店</t>
+          <t>貳十二度行旅</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>新北市金山區名流路1之6號、1之7號、1之9號、1之9號5樓及1之9號5樓之1至之8</t>
+          <t>宜蘭縣蘇澳鎮信義路177號</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>(02)24080400#1700</t>
+          <t>(03)9901888</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2029/02/11</t>
+          <t>2029/05/24</t>
         </is>
       </c>
     </row>
@@ -7170,32 +7170,32 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>雅霖大飯店</t>
+          <t>陽明山天籟渡假酒店</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市同和路100號</t>
+          <t>新北市金山區名流路1之6號、1之7號、1之9號、1之9號5樓及1之9號5樓之1至之8</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>(06)9261366</t>
+          <t>(02)24080400#1700</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2029/02/11</t>
         </is>
       </c>
     </row>
@@ -7207,32 +7207,32 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>雲品溫泉酒店日月潭</t>
+          <t>雅霖大飯店</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉水社村中正路23號</t>
+          <t>澎湖縣馬公市同和路100號</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>(049)2212959</t>
+          <t>(06)9261366</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2029/05/05</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -7244,32 +7244,32 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>雲頂國際商旅</t>
+          <t>雲品溫泉酒店日月潭</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>臺南市南區大同路二段530號</t>
+          <t>南投縣魚池鄉水社村中正路23號</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>(06)2687766</t>
+          <t>(049)2212959</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2029/02/25</t>
+          <t>2029/05/05</t>
         </is>
       </c>
     </row>
@@ -7281,32 +7281,32 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>圓山大飯店</t>
+          <t>雲頂國際商旅</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路4段1巷1號</t>
+          <t>臺南市南區大同路二段530號</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>(02)28861818#1007</t>
+          <t>(06)2687766</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2029/02/25</t>
         </is>
       </c>
     </row>
@@ -7318,32 +7318,32 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>奧斯卡去旅行民宿</t>
+          <t>圓山大飯店</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>臺東縣臺東市興安路一段167號</t>
+          <t>臺北市中山區中山北路4段1巷1號</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>(0910)633944</t>
+          <t>(02)28861818#1007</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2027/01/29</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>奧斯卡民宿</t>
+          <t>奧斯卡去旅行民宿</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>臺東縣台東市興安路1段175號</t>
+          <t>臺東縣臺東市興安路一段167號</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>(0965)329000</t>
+          <t>(0910)633944</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2027/01/18</t>
+          <t>2027/01/29</t>
         </is>
       </c>
     </row>
@@ -7392,22 +7392,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>新竹安捷國際酒店</t>
+          <t>奧斯卡民宿</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>新竹縣竹北市復興三路二段168號14樓-18樓</t>
+          <t>臺東縣台東市興安路1段175號</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>(03)6209777#660</t>
+          <t>(0965)329000</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2028/07/13</t>
+          <t>2027/01/18</t>
         </is>
       </c>
     </row>
@@ -7429,22 +7429,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>新竹老爺大酒店</t>
+          <t>新竹安捷國際酒店</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>新竹市東區光復路一段227號</t>
+          <t>新竹縣竹北市復興三路二段168號14樓-18樓</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>(03)5631285#204</t>
+          <t>(03)6209777#660</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2028/07/13</t>
         </is>
       </c>
     </row>
@@ -7466,32 +7466,32 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>新竹喜來登大飯店</t>
+          <t>新竹老爺大酒店</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>新竹縣竹北市光明六路東一段265號</t>
+          <t>新竹市東區光復路一段227號</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>(03)6206126</t>
+          <t>(03)5631285#204</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -7503,32 +7503,32 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>新竹福華大飯店</t>
+          <t>新竹喜來登大飯店</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>新竹市中正路178號</t>
+          <t>新竹縣竹北市光明六路東一段265號</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>(03)5282323#5303</t>
+          <t>(03)6206126</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -7540,22 +7540,22 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>新南一二文創商行</t>
+          <t>新竹福華大飯店</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>桃園市大溪區中山路１２號</t>
+          <t>新竹市中正路178號</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>(03)3884466</t>
+          <t>(03)5282323#5303</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2029/02/05</t>
+          <t>2026/10/26</t>
         </is>
       </c>
     </row>
@@ -7577,32 +7577,32 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>新悦花園酒店</t>
+          <t>新南一二文創商行</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>嘉義市東區後湖里6鄰保順路69號</t>
+          <t>桃園市大溪區中山路１２號</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>(05)2777266#5801</t>
+          <t>(03)3884466</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2027/04/07</t>
+          <t>2029/02/05</t>
         </is>
       </c>
     </row>
@@ -7614,32 +7614,32 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>溪頭福華渡假飯店-溪頭漢光樓</t>
+          <t>新悦花園酒店</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>南投縣鹿谷鄉森林巷11、12號</t>
+          <t>嘉義市東區後湖里6鄰保順路69號</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>(049)2612588#3005</t>
+          <t>(05)2777266#5801</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2028/12/01</t>
+          <t>2027/04/07</t>
         </is>
       </c>
     </row>
@@ -7651,32 +7651,32 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>溪邊小築民宿</t>
+          <t>溪頭福華渡假飯店-溪頭漢光樓</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>新北市瑞芳區祈堂路133號</t>
+          <t>南投縣鹿谷鄉森林巷11、12號</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>(02)24961191</t>
+          <t>(049)2612588#3005</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2029/06/21</t>
+          <t>2028/12/01</t>
         </is>
       </c>
     </row>
@@ -7688,32 +7688,32 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>煙波大飯店臺南館</t>
+          <t>溪邊小築民宿</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>臺南市中西區永福路1段269號1-12樓及地下一層至三層</t>
+          <t>新北市瑞芳區祈堂路133號</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>(06)2156000#1171</t>
+          <t>(02)24961191</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2029/06/09</t>
+          <t>2029/06/21</t>
         </is>
       </c>
     </row>
@@ -7725,22 +7725,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>煙波大飯店宜蘭館</t>
+          <t>煙波大飯店臺南館</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>宜蘭縣宜蘭市凱旋路135號 、135號2至9樓</t>
+          <t>臺南市中西區永福路1段269號1-12樓及地下一層至三層</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>(09)9256899#1171</t>
+          <t>(06)2156000#1171</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/06/09</t>
         </is>
       </c>
     </row>
@@ -7762,22 +7762,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮太魯閣山闊館</t>
+          <t>煙波大飯店宜蘭館</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村草林10-7號</t>
+          <t>宜蘭縣宜蘭市凱旋路135號 、135號2至9樓</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>(03)8612000#1470</t>
+          <t>(09)9256899#1171</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026/11/05</t>
+          <t>2029/05/06</t>
         </is>
       </c>
     </row>
@@ -7799,7 +7799,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮太魯閣沁海館</t>
+          <t>煙波大飯店花蓮太魯閣山闊館</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村6鄰草林10之6號</t>
+          <t>花蓮縣新城鄉順安村草林10-7號</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>(03)8228835#1174</t>
+          <t>(03)8612000#1470</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2029/04/19</t>
+          <t>2026/11/05</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮館</t>
+          <t>煙波大飯店花蓮太魯閣沁海館</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市民立里1鄰中美路142號</t>
+          <t>花蓮縣新城鄉順安村6鄰草林10之6號</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -7873,22 +7873,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>煙波花時間 宜蘭傳藝</t>
+          <t>煙波大飯店花蓮館</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉五濱路二段201號</t>
+          <t>花蓮縣花蓮市民立里1鄰中美路142號</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>(03)9256899#1171</t>
+          <t>(03)8228835#1174</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2027/07/09</t>
+          <t>2029/04/19</t>
         </is>
       </c>
     </row>
@@ -7910,22 +7910,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>煙波花時間 花蓮</t>
+          <t>煙波花時間 宜蘭傳藝</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村草林10-5號2~6樓</t>
+          <t>宜蘭縣五結鄉五濱路二段201號</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>(03)8612000#1470</t>
+          <t>(03)9256899#1171</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026/11/16</t>
+          <t>2027/07/09</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>瑞穗天合國際觀光酒店</t>
+          <t>煙波花時間 花蓮</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7957,22 +7957,22 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>花蓮縣瑞穗鄉溫泉路二段368號</t>
+          <t>花蓮縣新城鄉順安村草林10-5號2~6樓</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>(03)8876000#3260</t>
+          <t>(03)8612000#1470</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2028/01/19</t>
+          <t>2026/11/16</t>
         </is>
       </c>
     </row>
@@ -7984,22 +7984,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>裕元花園酒店</t>
+          <t>瑞穗天合國際觀光酒店</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>臺中市西屯區臺灣大道四段610號</t>
+          <t>花蓮縣瑞穗鄉溫泉路二段368號</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>(04)24655660#5030</t>
+          <t>(03)8876000#3260</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2027/11/19</t>
+          <t>2028/01/19</t>
         </is>
       </c>
     </row>
@@ -8021,32 +8021,32 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>遇見民宿</t>
+          <t>裕元花園酒店</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>屏東縣東港鎮水源路221號(新和段737-4地號)</t>
+          <t>臺中市西屯區臺灣大道四段610號</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>(08)8333345</t>
+          <t>(04)24655660#5030</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2027/11/19</t>
         </is>
       </c>
     </row>
@@ -8058,22 +8058,22 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>頌華私墅肆區民宿</t>
+          <t>遇見民宿</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>澎湖縣湖西鄉許家村6鄰港子尾120之5號</t>
+          <t>屏東縣東港鎮水源路221號(新和段737-4地號)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>(06)9212953</t>
+          <t>(08)8333345</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2029/01/25</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -8095,22 +8095,22 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>嘉仕特飯店</t>
+          <t>頌華私墅肆區民宿</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>桃園市桃園區中山路203號</t>
+          <t>澎湖縣湖西鄉許家村6鄰港子尾120之5號</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>(03)3343999</t>
+          <t>(06)9212953</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>2029/01/25</t>
         </is>
       </c>
     </row>
@@ -8132,32 +8132,32 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>嘉義富野渡假酒店</t>
+          <t>嘉仕特飯店</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>嘉義縣民雄鄉三興村升學一街3、5、7、9、11、13、15、17、19、21、23、25、27號</t>
+          <t>桃園市桃園區中山路203號</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>(05)2721688</t>
+          <t>(03)3343999</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2028/08/12</t>
+          <t>2027/11/27</t>
         </is>
       </c>
     </row>
@@ -8169,32 +8169,32 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>嘉義智選假日酒店</t>
+          <t>嘉義富野渡假酒店</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>嘉義市西區中興路69號B2至13層樓</t>
+          <t>嘉義縣民雄鄉三興村升學一街3、5、7、9、11、13、15、17、19、21、23、25、27號</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>(05)2335899#801</t>
+          <t>(05)2721688</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2027/11/24</t>
+          <t>2028/08/12</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>嘉義福容voco酒店</t>
+          <t>嘉義智選假日酒店</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -8216,22 +8216,22 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>嘉義市西區世賢路一段789號B4-4樓、7樓、16樓-32樓</t>
+          <t>嘉義市西區中興路69號B2至13層樓</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>(05)232338971</t>
+          <t>(05)2335899#801</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2029/06/15</t>
+          <t>2027/11/24</t>
         </is>
       </c>
     </row>
@@ -8243,32 +8243,32 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>夢想森林親子民宿</t>
+          <t>嘉義福容voco酒店</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉三星鄉大德路二段613號</t>
+          <t>嘉義市西區世賢路一段789號B4-4樓、7樓、16樓-32樓</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>(03)9898113</t>
+          <t>(05)232338971</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2029/06/15</t>
         </is>
       </c>
     </row>
@@ -8280,32 +8280,32 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>榮美金鬱金香酒店</t>
+          <t>夢想森林親子民宿</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>臺南市北區海安路三段50號</t>
+          <t>宜蘭縣三星鄉三星鄉大德路二段613號</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>(06)2200800#6001</t>
+          <t>(03)9898113</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2027/11/04</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>榮興金鬱金香酒店</t>
+          <t>榮美金鬱金香酒店</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -8327,17 +8327,17 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>臺南市中西區民族路二段128號</t>
+          <t>臺南市北區海安路三段50號</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>(06)2200800#6006</t>
+          <t>(06)2200800#6001</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -8354,22 +8354,22 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>福美民宿</t>
+          <t>榮興金鬱金香酒店</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>臺東縣台東市精誠路241號</t>
+          <t>臺南市中西區民族路二段128號</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>(089)328466</t>
+          <t>(06)2200800#6006</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2027/01/09</t>
+          <t>2027/11/04</t>
         </is>
       </c>
     </row>
@@ -8391,32 +8391,32 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>福容大飯店 臺北二館</t>
+          <t>福美民宿</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>新北市深坑區北深路三段236號</t>
+          <t>臺東縣台東市精誠路241號</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>(02)26620088#186</t>
+          <t>(089)328466</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2028/01/05</t>
+          <t>2027/01/09</t>
         </is>
       </c>
     </row>
@@ -8428,32 +8428,32 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>福容大飯店 桃園</t>
+          <t>福容大飯店 臺北二館</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>桃園市桃園區同安里大興西路一段200號</t>
+          <t>新北市深坑區北深路三段236號</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>(03)3265800#300</t>
+          <t>(02)26620088#186</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2027/12/17</t>
+          <t>2028/01/05</t>
         </is>
       </c>
     </row>
@@ -8465,7 +8465,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>福容大飯店 桃園機場捷運 A8</t>
+          <t>福容大飯店 桃園</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>桃園市龜山區復興一路2號3樓</t>
+          <t>桃園市桃園區同安里大興西路一段200號</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>(03)3285688#8770</t>
+          <t>(03)3265800#300</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2027/08/12</t>
+          <t>2027/12/17</t>
         </is>
       </c>
     </row>
@@ -8502,32 +8502,32 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>福容大飯店 高雄</t>
+          <t>福容大飯店 桃園機場捷運 A8</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區五福四路45號</t>
+          <t>桃園市龜山區復興一路2號3樓</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>(07)5317777#7782</t>
+          <t>(03)3285688#8770</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2028/08/14</t>
+          <t>2027/08/12</t>
         </is>
       </c>
     </row>
@@ -8539,22 +8539,22 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>福容大飯店 淡水漁人碼頭</t>
+          <t>福容大飯店 高雄</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>新北市淡水區觀海路83號</t>
+          <t>高雄市鹽埕區五福四路45號</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>(02)2805 9958#8178</t>
+          <t>(07)5317777#7782</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2028/11/16</t>
+          <t>2028/08/14</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>福容大飯店　福隆</t>
+          <t>福容大飯店 淡水漁人碼頭</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>新北市貢寮區福隆里福隆街41號</t>
+          <t>新北市淡水區觀海路83號</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>(02)24992381</t>
+          <t>(02)2805 9958#8178</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2028/11/16</t>
         </is>
       </c>
     </row>
@@ -8613,32 +8613,32 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>福容大飯店 墾丁</t>
+          <t>福容大飯店　福隆</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮船帆路1000號</t>
+          <t>新北市貢寮區福隆里福隆街41號</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>(08)8856969#340</t>
+          <t>(02)24992381</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2028/05/28</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -8650,32 +8650,32 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>福容大飯店 麗寶樂園</t>
+          <t>福容大飯店 墾丁</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>臺中市后里區福容路88號</t>
+          <t>屏東縣恆春鎮船帆路1000號</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>(04)25571366#8343</t>
+          <t>(08)8856969#340</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2029/03/19</t>
+          <t>2028/05/28</t>
         </is>
       </c>
     </row>
@@ -8687,32 +8687,32 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>福容大飯店花蓮</t>
+          <t>福容大飯店 麗寶樂園</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市民生路51號</t>
+          <t>臺中市后里區福容路88號</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>(03)8239988#7507</t>
+          <t>(04)25571366#8343</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2027/11/10</t>
+          <t>2029/03/19</t>
         </is>
       </c>
     </row>
@@ -8724,32 +8724,32 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>福容徠旅 水里</t>
+          <t>福容大飯店花蓮</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>南投縣水里鄉東三街51號1樓至6樓</t>
+          <t>花蓮縣花蓮市民生路51號</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>(049)2771888#5560</t>
+          <t>(03)8239988#7507</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2029/07/09</t>
+          <t>2027/11/10</t>
         </is>
       </c>
     </row>
@@ -8761,32 +8761,32 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>福容徠旅林口</t>
+          <t>福容徠旅 水里</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>桃園市龜山區文二一街68號</t>
+          <t>南投縣水里鄉東三街51號1樓至6樓</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>(03)3277388#300</t>
+          <t>(049)2771888#5560</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2027/12/03</t>
+          <t>2029/07/09</t>
         </is>
       </c>
     </row>
@@ -8798,32 +8798,32 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>福容徠旅高雄</t>
+          <t>福容徠旅林口</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>高雄市前金區永恆街3號6-14樓</t>
+          <t>桃園市龜山區文二一街68號</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>(07)2156688#6309</t>
+          <t>(03)3277388#300</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2029/03/17</t>
+          <t>2027/12/03</t>
         </is>
       </c>
     </row>
@@ -8835,32 +8835,32 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>福華大飯店</t>
+          <t>福容徠旅高雄</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>臺北市大安區仁愛路三段160號</t>
+          <t>高雄市前金區永恆街3號6-14樓</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>(02)27002323#2411</t>
+          <t>(07)2156688#6309</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2029/03/17</t>
         </is>
       </c>
     </row>
@@ -8872,22 +8872,22 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>福華石門水庫渡假飯店</t>
+          <t>福華大飯店</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>桃園市龍潭區民富街176號</t>
+          <t>臺北市大安區仁愛路三段160號</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>(03)4714888</t>
+          <t>(02)27002323#2411</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2027/11/10</t>
+          <t>2026/10/26</t>
         </is>
       </c>
     </row>
@@ -8909,22 +8909,22 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>福華國際文教會館</t>
+          <t>福華石門水庫渡假飯店</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>臺北市大安區新生南路3段30號(住宿棟1樓及5樓至14樓)</t>
+          <t>桃園市龍潭區民富街176號</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>(02)77122323#2340</t>
+          <t>(03)4714888</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2027/12/11</t>
+          <t>2027/11/10</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>福爾摩沙遊艇酒店</t>
+          <t>福華國際文教會館</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>臺南市安平區王城里13鄰安平路988號1至10樓</t>
+          <t>臺北市大安區新生南路3段30號(住宿棟1樓及5樓至14樓)</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>(06)3911313</t>
+          <t>(02)77122323#2340</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2027/02/27</t>
+          <t>2027/12/11</t>
         </is>
       </c>
     </row>
@@ -8983,22 +8983,22 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>綠意山莊民宿</t>
+          <t>福爾摩沙遊艇酒店</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之5號</t>
+          <t>臺南市安平區王城里13鄰安平路988號1至10樓</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>(037)747711#9</t>
+          <t>(06)3911313</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2028/09/08</t>
+          <t>2027/02/27</t>
         </is>
       </c>
     </row>
@@ -9020,22 +9020,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>綠藤輕旅</t>
+          <t>綠意山莊民宿</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>桃園市大園區中山南路二段673號</t>
+          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之5號</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>(03)2873043</t>
+          <t>(037)747711#9</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2028/09/08</t>
         </is>
       </c>
     </row>
@@ -9057,22 +9057,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>維悅酒店</t>
+          <t>綠藤輕旅</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>臺南市安平區慶平路539號 1至5樓及地下1樓</t>
+          <t>桃園市大園區中山南路二段673號</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>(06)2950888#1125</t>
+          <t>(03)2873043</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2027/09/01</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -9094,22 +9094,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>臺中逢甲智選假日酒店</t>
+          <t>維悅酒店</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>臺中市西屯區福星北三街33巷28號</t>
+          <t>臺南市安平區慶平路539號 1至5樓及地下1樓</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>(04)27083911#6101</t>
+          <t>(06)2950888#1125</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/09/01</t>
         </is>
       </c>
     </row>
@@ -9131,27 +9131,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>臺邦商旅</t>
+          <t>臺中逢甲智選假日酒店</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>臺南市安平區永華二街199號</t>
+          <t>臺中市西屯區福星北三街33巷28號</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>(06)2931800#8603</t>
+          <t>(04)27083911#6101</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -9168,32 +9168,32 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>遠雄悅來大飯店</t>
+          <t>臺邦商旅</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>花蓮縣壽豐鄉鹽寮村山嶺18號</t>
+          <t>臺南市安平區永華二街199號</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>(03)8123900#8266</t>
+          <t>(06)2931800#8603</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2028/12/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9205,22 +9205,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>鳳山79 背包客</t>
+          <t>遠雄悅來大飯店</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>高雄市鳳山區黃埔新村東一巷79號</t>
+          <t>花蓮縣壽豐鄉鹽寮村山嶺18號</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>(07)5524545</t>
+          <t>(03)8123900#8266</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2028/12/03</t>
+          <t>2028/12/29</t>
         </is>
       </c>
     </row>
@@ -9242,32 +9242,32 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>劍湖山渡假大飯店</t>
+          <t>鳳山79 背包客</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>雲林縣古坑鄉永光村大湖口67-8號</t>
+          <t>高雄市鳳山區黃埔新村東一巷79號</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>(05)5829900#7214</t>
+          <t>(07)5524545</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2027/06/03</t>
+          <t>2028/12/03</t>
         </is>
       </c>
     </row>
@@ -9279,32 +9279,32 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>澄悅商旅</t>
+          <t>劍湖山渡假大飯店</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮埔崙里中正路510巷1號</t>
+          <t>雲林縣古坑鄉永光村大湖口67-8號</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>(04)7785727</t>
+          <t>(05)5829900#7214</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2029/09/07</t>
+          <t>2027/06/03</t>
         </is>
       </c>
     </row>
@@ -9316,32 +9316,32 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>澎湖福朋喜來登酒店</t>
+          <t>澄悅商旅</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市新店路197號</t>
+          <t>彰化縣鹿港鎮埔崙里中正路510巷1號</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>(06)9279955#3701</t>
+          <t>(04)7785727</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2028/05/27</t>
+          <t>2029/09/07</t>
         </is>
       </c>
     </row>
@@ -9353,7 +9353,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>澎澄飯店</t>
+          <t>澎湖福朋喜來登酒店</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市同和路168號</t>
+          <t>澎湖縣馬公市新店路197號</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>(06)9235678#2103</t>
+          <t>(06)9279955#3701</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2029/08/03</t>
+          <t>2028/05/27</t>
         </is>
       </c>
     </row>
@@ -9390,32 +9390,32 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>緻麗伯爵酒店</t>
+          <t>澎澄飯店</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>雲林縣斗六市中山路6號</t>
+          <t>澎湖縣馬公市同和路168號</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>(05)5341666#3</t>
+          <t>(06)9235678#2103</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2029/02/10</t>
+          <t>2029/08/03</t>
         </is>
       </c>
     </row>
@@ -9427,32 +9427,32 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>緣羊軒民宿</t>
+          <t>緻麗伯爵酒店</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>臺東縣台東市南一街96號</t>
+          <t>雲林縣斗六市中山路6號</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>089326400</t>
+          <t>(05)5341666#3</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026/12/05</t>
+          <t>2029/02/10</t>
         </is>
       </c>
     </row>
@@ -9464,32 +9464,32 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺北</t>
+          <t>緣羊軒民宿</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
+          <t>臺東縣台東市南一街96號</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>(02)29583000#7701</t>
+          <t>089326400</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2028/03/31</t>
+          <t>2026/12/05</t>
         </is>
       </c>
     </row>
@@ -9501,32 +9501,32 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺東</t>
+          <t>趣淘漫旅-臺北</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>臺東縣台東市新站路260號</t>
+          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>(089)231188#7187</t>
+          <t>(02)29583000#7701</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2027/12/05</t>
+          <t>2028/03/31</t>
         </is>
       </c>
     </row>
@@ -9538,32 +9538,32 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>墾丁夏都沙灘酒店</t>
+          <t>趣淘漫旅-臺東</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁路451號</t>
+          <t>臺東縣台東市新站路260號</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>(0910)371823</t>
+          <t>(089)231188#7187</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2028/03/09</t>
+          <t>2027/12/05</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>墾丁福華渡假飯店</t>
+          <t>墾丁夏都沙灘酒店</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9585,22 +9585,22 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
+          <t>屏東縣恆春鎮墾丁路451號</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>(08)8862324#2701</t>
+          <t>(0910)371823</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2029/04/12</t>
+          <t>2028/03/09</t>
         </is>
       </c>
     </row>
@@ -9612,22 +9612,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>橘子民宿</t>
+          <t>墾丁福華渡假飯店</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
+          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>(0972)092658</t>
+          <t>(08)8862324#2701</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2027/11/06</t>
+          <t>2029/04/12</t>
         </is>
       </c>
     </row>
@@ -9649,32 +9649,32 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>翰品酒店 高雄</t>
+          <t>橘子民宿</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區大仁路43號</t>
+          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>(07)5614688#3110</t>
+          <t>(0972)092658</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2027/02/16</t>
+          <t>2027/11/06</t>
         </is>
       </c>
     </row>
@@ -9686,22 +9686,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>礁溪老爺酒店</t>
+          <t>翰品酒店 高雄</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
+          <t>高雄市鹽埕區大仁路43號</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>(03)9885211#8006</t>
+          <t>(07)5614688#3110</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2028/08/24</t>
+          <t>2027/02/16</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>礁溪寒沐酒店</t>
+          <t>礁溪老爺酒店</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9733,12 +9733,12 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
+          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>(03)9058007</t>
+          <t>(03)9885211#8006</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2028/08/24</t>
         </is>
       </c>
     </row>
@@ -9760,32 +9760,32 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>禧榕軒大飯店</t>
+          <t>礁溪寒沐酒店</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>臺南市北區成功路28號</t>
+          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>(06)2222788#2203</t>
+          <t>(03)9058007</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2029/05/10</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -9797,32 +9797,32 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>薆悅酒店野柳渡假館一館</t>
+          <t>禧榕軒大飯店</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>新北市萬里區野柳里港東路162號之2</t>
+          <t>臺南市北區成功路28號</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>(02)77035770#623</t>
+          <t>(06)2222788#2203</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2029/05/10</t>
         </is>
       </c>
     </row>
@@ -9834,22 +9834,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>藍水輕旅</t>
+          <t>薆悅酒店野柳渡假館一館</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>桃園市大園區高鐵南路一段126號</t>
+          <t>新北市萬里區野柳里港東路162號之2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>(03)2871855</t>
+          <t>(02)77035770#623</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -9871,22 +9871,22 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>關子嶺富野溫泉會館</t>
+          <t>藍水輕旅</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>臺南市白河區關子嶺28號</t>
+          <t>桃園市大園區高鐵南路一段126號</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>(06)6822288</t>
+          <t>(03)2871855</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2029/01/07</t>
+          <t>2026/11/23</t>
         </is>
       </c>
     </row>
@@ -9908,22 +9908,22 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>麗格休閒飯店</t>
+          <t>關子嶺富野溫泉會館</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市商校街258.260.262號</t>
+          <t>臺南市白河區關子嶺28號</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>(03)8349922</t>
+          <t>(06)6822288</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2029/01/07</t>
         </is>
       </c>
     </row>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>麗軒國際飯店</t>
+          <t>麗格休閒飯店</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市中美路99之1號</t>
+          <t>花蓮縣花蓮市商校街258.260.262號</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>(03)8246898</t>
+          <t>(03)8349922</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>麗翔大飯店</t>
+          <t>麗軒國際飯店</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
+          <t>花蓮縣花蓮市中美路99之1號</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>(03)8323737</t>
+          <t>(03)8246898</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2028/01/12</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -10019,22 +10019,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>讀好民宿</t>
+          <t>麗翔大飯店</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
+          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>(0920)023139</t>
+          <t>(03)8323737</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2028/01/12</t>
         </is>
       </c>
     </row>
@@ -10056,32 +10056,32 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>觀霧山莊</t>
+          <t>讀好民宿</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
+          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>(03)3343818</t>
+          <t>(0920)023139</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2029/01/22</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -10093,22 +10093,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>綉溪安平</t>
+          <t>觀霧山莊</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>(06)3910988#3111</t>
+          <t>(03)3343818</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2028/10/12</t>
+          <t>2029/01/22</t>
         </is>
       </c>
     </row>
@@ -10130,30 +10130,67 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
+          <t>綉溪安平</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>臺南市</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>(06)3910988#3111</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>銀級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>2028/10/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
           <t>鐡馬騎跡</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
+      <c r="C264" t="inlineStr">
         <is>
           <t>屏東縣</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D264" t="inlineStr">
         <is>
           <t>屏東縣東港鎮新學路50號</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="E264" t="inlineStr">
         <is>
           <t>(0952)848898</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>銅級環保旅宿</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
         <is>
           <t>2029/01/18</t>
         </is>

--- a/環保旅宿_Selenium結果.xlsx
+++ b/環保旅宿_Selenium結果.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G264"/>
+  <dimension ref="A1:G269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>臺北旅人國際青年旅館</t>
+          <t>臺北花園大酒店</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>新北市淡水區三民街22、22之1、22之2、22之3、22之4號</t>
+          <t>臺北市中正區中華路2段1號</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(02)26258222</t>
+          <t>(02)23143300#3331</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2029/09/28</t>
         </is>
       </c>
     </row>
@@ -2212,32 +2212,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>臺北時代寓所</t>
+          <t>臺北旅人國際青年旅館</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>臺北市中正區林森南路7號1至14樓，7-1號1樓</t>
+          <t>新北市淡水區三民街22、22之1、22之2、22之3、22之4號</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(02)77521801</t>
+          <t>(02)26258222</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2028/09/29</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -2249,22 +2249,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>臺北新板希爾頓酒店</t>
+          <t>臺北時代寓所</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>新北市板橋區民權路88號、88號（2至31樓）90號</t>
+          <t>臺北市中正區林森南路7號1至14樓，7-1號1樓</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(02)29583000#7702</t>
+          <t>(02)77521801</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2028/03/31</t>
+          <t>2028/09/29</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>臺北萬豪酒店</t>
+          <t>臺北國泰萬怡酒店</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>臺北市中山區樂群二路199號</t>
+          <t>臺北市中山區民生東路三段6號地下1樓、1、2、14至20樓</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(02)21757999#1701</t>
+          <t>(02)77503371</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2028/12/07</t>
+          <t>2029/09/30</t>
         </is>
       </c>
     </row>
@@ -2323,32 +2323,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>臺北遠東香格里拉</t>
+          <t>臺北新板希爾頓酒店</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>臺北市大安區敦化南路二段201號</t>
+          <t>新北市板橋區民權路88號、88號（2至31樓）90號</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(02)23788888#6608</t>
+          <t>(02)29583000#7702</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2027/12/12</t>
+          <t>2028/03/31</t>
         </is>
       </c>
     </row>
@@ -2360,32 +2360,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>臺東Deer  House民宿</t>
+          <t>臺北萬豪酒店</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>臺東縣鹿野鄉永安村1鄰永安路７１號</t>
+          <t>臺北市中山區樂群二路199號</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(089)552224</t>
+          <t>(02)21757999#1701</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2028/12/07</t>
         </is>
       </c>
     </row>
@@ -2397,32 +2397,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>臺南大員皇冠假日酒店</t>
+          <t>臺北遠東香格里拉</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>臺南市安平區州平路289號</t>
+          <t>臺北市大安區敦化南路二段201號</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(06)5121888#6002</t>
+          <t>(02)23788888#6608</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2028/01/09</t>
+          <t>2027/12/12</t>
         </is>
       </c>
     </row>
@@ -2434,22 +2434,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>臺南大飯店</t>
+          <t>臺東Deer  House民宿</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>臺南市中西區成功路1號</t>
+          <t>臺東縣鹿野鄉永安村1鄰永安路７１號</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(06)2289101#2012</t>
+          <t>(089)552224</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>臺南安平雅樂軒酒店</t>
+          <t>臺南大員皇冠假日酒店</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>臺南市安平區光州路108號2-12樓、光州路108之1號</t>
+          <t>臺南市安平區州平路289號</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(06)3905000#8600</t>
+          <t>(06)5121888#6002</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2028/12/18</t>
+          <t>2028/01/09</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>臺南老爺行旅</t>
+          <t>臺南大飯店</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2518,22 +2518,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>臺南市東區中華東路一段368號1樓、6-10樓</t>
+          <t>臺南市中西區成功路1號</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(06)2361680#301</t>
+          <t>(06)2289101#2012</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2028/02/19</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>臺南遠東香格里拉</t>
+          <t>臺南安平雅樂軒酒店</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>臺南市東區大學路西段89號</t>
+          <t>臺南市安平區光州路108號2-12樓、光州路108之1號</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(06)7028888#6903</t>
+          <t>(06)3905000#8600</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2028/12/18</t>
         </is>
       </c>
     </row>
@@ -2582,32 +2582,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>臺糖臺北會館</t>
+          <t>臺南老爺行旅</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路一段39號3至5樓</t>
+          <t>臺南市東區中華東路一段368號1樓、6-10樓</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(02)23885522#5001</t>
+          <t>(06)2361680#301</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2027/03/10</t>
+          <t>2028/02/19</t>
         </is>
       </c>
     </row>
@@ -2619,22 +2619,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>臺糖花蓮旅館</t>
+          <t>臺南遠東香格里拉</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>花蓮縣光復鄉大進村糖廠街19號</t>
+          <t>臺南市東區大學路西段89號</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(03)8704125#621</t>
+          <t>(06)7028888#6903</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2027/03/21</t>
+          <t>2026/12/30</t>
         </is>
       </c>
     </row>
@@ -2656,22 +2656,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>臺糖長榮酒店(臺南)</t>
+          <t>臺糖臺北會館</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>臺南市東區中華東路三段336巷1號</t>
+          <t>臺北市中正區中華路一段39號3至5樓</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(06)3378888</t>
+          <t>(02)23885522#5001</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2027/03/10</t>
         </is>
       </c>
     </row>
@@ -2693,22 +2693,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>臺灣糖業股份有限公司池上牧野渡假村</t>
+          <t>臺糖花蓮旅館</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>臺東縣池上鄉新興村新興110號</t>
+          <t>花蓮縣光復鄉大進村糖廠街19號</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>(089)862736#1001</t>
+          <t>(03)8704125#621</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2028/04/15</t>
+          <t>2027/03/21</t>
         </is>
       </c>
     </row>
@@ -2730,32 +2730,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>四季時光</t>
+          <t>臺糖長榮酒店(臺南)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉頭社村平和巷103-11號</t>
+          <t>臺南市東區中華東路三段336巷1號</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>(0932)376767</t>
+          <t>(06)3378888</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2026/11/28</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>巨蛋旅店</t>
+          <t>臺灣糖業股份有限公司池上牧野渡假村</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>高雄市鼓山區文忠路1號</t>
+          <t>臺東縣池上鄉新興村新興110號</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(07)5868388#0</t>
+          <t>(089)862736#1001</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2028/10/07</t>
+          <t>2028/04/15</t>
         </is>
       </c>
     </row>
@@ -2804,32 +2804,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>打個蛋海旅民宿</t>
+          <t>四季時光</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>臺東縣太麻里鄉金崙4鄰129號</t>
+          <t>南投縣魚池鄉頭社村平和巷103-11號</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(089)771551</t>
+          <t>(0932)376767</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -2841,32 +2841,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>正好友生態環保旅店</t>
+          <t>巨蛋旅店</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>屏東縣琉球鄉中山路153號</t>
+          <t>高雄市鼓山區文忠路1號</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(0886)12270</t>
+          <t>(07)5868388#0</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2029/03/26</t>
+          <t>2028/10/07</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>伊塔原旅臺東縣原住民文化會館</t>
+          <t>打個蛋海旅民宿</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>臺東縣台東市中山路10號</t>
+          <t>臺東縣太麻里鄉金崙4鄰129號</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(089)34060</t>
+          <t>(089)771551</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -2915,32 +2915,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>兆品酒店</t>
+          <t>正好友生態環保旅店</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>嘉義市文化路257號B2-9F</t>
+          <t>屏東縣琉球鄉中山路153號</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(05)2292883#3130</t>
+          <t>(0886)12270</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2028/03/30</t>
+          <t>2029/03/26</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>好室民宿</t>
+          <t>伊塔原旅臺東縣原住民文化會館</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>臺東縣台東市中正路251巷9號</t>
+          <t>臺東縣台東市中山路10號</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(0905)583758</t>
+          <t>(089)34060</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2027/01/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>如一家精緻民宿</t>
+          <t>兆品酒店</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>金門縣金城鎮珠浦北路35-1號</t>
+          <t>嘉義市文化路257號B2-9F</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(082)322167</t>
+          <t>(05)2292883#3130</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2028/03/30</t>
         </is>
       </c>
     </row>
@@ -3026,22 +3026,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>安樓文旅</t>
+          <t>好室民宿</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>基隆市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>基隆市仁愛區仁三路11-4</t>
+          <t>臺東縣台東市中正路251巷9號</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(02)24200220</t>
+          <t>(0905)583758</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2029/07/09</t>
+          <t>2027/01/29</t>
         </is>
       </c>
     </row>
@@ -3063,22 +3063,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>老公老婆友善民宿</t>
+          <t>如一家精緻民宿</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>宜蘭縣冬山鄉境安路345號</t>
+          <t>金門縣金城鎮珠浦北路35-1號</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(03) 9519013</t>
+          <t>(082)322167</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026/12/28</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -3100,22 +3100,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>老爺大酒店</t>
+          <t>安樓文旅</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>基隆市</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路2段37-1號</t>
+          <t>基隆市仁愛區仁三路11-4</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(02)25423299#359</t>
+          <t>(02)24200220</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2029/07/09</t>
         </is>
       </c>
     </row>
@@ -3137,32 +3137,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>西湖渡假大飯店</t>
+          <t>老公老婆友善民宿</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>苗栗縣三義鄉西湖村西湖11號</t>
+          <t>宜蘭縣冬山鄉境安路345號</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(037)876699#1122</t>
+          <t>(03) 9519013</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2029/05/24</t>
+          <t>2026/12/28</t>
         </is>
       </c>
     </row>
@@ -3174,32 +3174,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>亞昕福朋喜來登酒店</t>
+          <t>老爺大酒店</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段1號、1號2樓、1號3樓</t>
+          <t>臺北市中山區中山北路2段37-1號</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(02)77276961</t>
+          <t>(02)25423299#359</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2028/09/25</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>享沐時光</t>
+          <t>西湖渡假大飯店</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3221,22 +3221,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮石鎮里錦山8-1,8-2號</t>
+          <t>苗栗縣三義鄉西湖村西湖11號</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(037)742878#124</t>
+          <t>(037)876699#1122</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2028/07/15</t>
+          <t>2029/05/24</t>
         </is>
       </c>
     </row>
@@ -3248,22 +3248,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>和逸．高雄中山館</t>
+          <t>亞昕福朋喜來登酒店</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>高雄市前鎮區中山二路260號22-29樓</t>
+          <t>新北市林口區文化三路一段1號、1號2樓、1號3樓</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>(07)9756670</t>
+          <t>(02)77276961</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2028/09/10</t>
+          <t>2028/09/25</t>
         </is>
       </c>
     </row>
@@ -3285,22 +3285,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>和逸·臺南西門館</t>
+          <t>享沐時光</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>臺南市中西區西門路一段658之2號4樓至13樓</t>
+          <t>苗栗縣苑裡鎮石鎮里錦山8-1,8-2號</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>(06)7026685</t>
+          <t>(037)742878#124</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2028/02/19</t>
+          <t>2028/07/15</t>
         </is>
       </c>
     </row>
@@ -3322,22 +3322,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>和逸飯店桃園青埔館</t>
+          <t>和逸．高雄中山館</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>桃園市中壢區春德路101號</t>
+          <t>高雄市前鎮區中山二路260號22-29樓</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>(03)2737692#2102</t>
+          <t>(07)9756670</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2028/09/10</t>
         </is>
       </c>
     </row>
@@ -3359,32 +3359,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>尚順君樂飯店</t>
+          <t>和逸·臺南西門館</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>苗栗縣頭份市育樂街6號</t>
+          <t>臺南市中西區西門路一段658之2號4樓至13樓</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(037)539999#8611</t>
+          <t>(06)7026685</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2029/07/29</t>
+          <t>2028/02/19</t>
         </is>
       </c>
     </row>
@@ -3396,32 +3396,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>幸福蝸牛</t>
+          <t>和逸飯店桃園青埔館</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉利澤西路6號</t>
+          <t>桃園市中壢區春德路101號</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(03)9500047</t>
+          <t>(03)2737692#2102</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -3433,32 +3433,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>承萬尊爵渡假酒店</t>
+          <t>宜蘭力麗威斯汀度假酒店</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>南投縣埔里鎮樹人路131號</t>
+          <t>宜蘭縣員山鄉永同路三段268號</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>(049)2995757#6316</t>
+          <t>(03)9232111</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2027/04/07</t>
+          <t>2029/10/01</t>
         </is>
       </c>
     </row>
@@ -3470,32 +3470,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>承億酒店</t>
+          <t>尚順君樂飯店</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>高雄市前鎮區林森四路189號</t>
+          <t>苗栗縣頭份市育樂街6號</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>(07)3332000#6870</t>
+          <t>(037)539999#8611</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2029/09/22</t>
+          <t>2029/07/29</t>
         </is>
       </c>
     </row>
@@ -3507,22 +3507,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>林口維多利亞民宿</t>
+          <t>幸福蝸牛</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>桃園市蘆竹區坑子里14鄰八德二路280巷11號</t>
+          <t>宜蘭縣五結鄉利澤西路6號</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>(0905)111918</t>
+          <t>(03)9500047</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2029/08/24</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -3544,32 +3544,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>板橋凱撒大飯店</t>
+          <t>承萬尊爵渡假酒店</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>新北市板橋區縣民大道二段8號</t>
+          <t>南投縣埔里鎮樹人路131號</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>(02)29583000#7701</t>
+          <t>(049)2995757#6316</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2029/02/12</t>
+          <t>2027/04/07</t>
         </is>
       </c>
     </row>
@@ -3581,32 +3581,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>武陵國民賓館</t>
+          <t>承億酒店</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>臺中市和平區平等里武陵路3-1號</t>
+          <t>高雄市前鎮區林森四路189號</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(04)25901258#2103</t>
+          <t>(07)3332000#6870</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026/12/25</t>
+          <t>2029/09/22</t>
         </is>
       </c>
     </row>
@@ -3618,32 +3618,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>武陵富野渡假村</t>
+          <t>林口維多利亞民宿</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>臺中市和平區武陵路3-16號</t>
+          <t>桃園市蘆竹區坑子里14鄰八德二路280巷11號</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(04)25901399#8912</t>
+          <t>(0905)111918</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2029/08/24</t>
         </is>
       </c>
     </row>
@@ -3655,32 +3655,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>河那灣</t>
+          <t>板橋凱撒大飯店</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>桃園市復興區澤仁里3鄰溪口台41號</t>
+          <t>新北市板橋區縣民大道二段8號</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(0919)235303</t>
+          <t>(02)29583000#7701</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2027/07/25</t>
+          <t>2029/02/12</t>
         </is>
       </c>
     </row>
@@ -3692,32 +3692,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>波西米亞民宿</t>
+          <t>武陵國民賓館</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>花蓮縣吉安鄉東昌村13鄰東海一街168號</t>
+          <t>臺中市和平區平等里武陵路3-1號</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(0385)31234</t>
+          <t>(04)25901258#2103</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2029/01/06</t>
+          <t>2026/12/25</t>
         </is>
       </c>
     </row>
@@ -3729,32 +3729,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>泡泡森林民宿</t>
+          <t>武陵富野渡假村</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>臺東縣台東市南一街40號</t>
+          <t>臺中市和平區武陵路3-16號</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0986866545</t>
+          <t>(04)25901399#8912</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026/12/06</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -3766,22 +3766,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>泊寓</t>
+          <t>河那灣</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮鹿興路57巷3號</t>
+          <t>桃園市復興區澤仁里3鄰溪口台41號</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(04)7115655#120</t>
+          <t>(0919)235303</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2027/07/25</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>爸爸萬歲民宿</t>
+          <t>波西米亞民宿</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市延平街68巷27號</t>
+          <t>花蓮縣吉安鄉東昌村13鄰東海一街168號</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>(0900)757520</t>
+          <t>(0385)31234</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2027/01/10</t>
+          <t>2029/01/06</t>
         </is>
       </c>
     </row>
@@ -3840,22 +3840,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>迎曦大飯店</t>
+          <t>泡泡森林民宿</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>新竹市東區親仁里文化街10號2-10樓</t>
+          <t>臺東縣台東市南一街40號</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(03)5347266#124</t>
+          <t>0986866545</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2028/04/28</t>
+          <t>2026/12/06</t>
         </is>
       </c>
     </row>
@@ -3877,32 +3877,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>金湖飯店</t>
+          <t>泊寓</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>金門縣金湖鎮太湖路二段218號</t>
+          <t>彰化縣鹿港鎮鹿興路57巷3號</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(082)379666#160</t>
+          <t>(04)7115655#120</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026/12/03</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -3914,32 +3914,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>長榮文苑酒店(嘉義)</t>
+          <t>爸爸萬歲民宿</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>嘉義縣太保市東勢里故宮大道777號</t>
+          <t>花蓮縣花蓮市延平街68巷27號</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>(05)3669988#2700</t>
+          <t>(0900)757520</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2027/04/11</t>
+          <t>2027/01/10</t>
         </is>
       </c>
     </row>
@@ -3951,32 +3951,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(臺中)</t>
+          <t>迎曦大飯店</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>臺中市西屯區臺灣大道二段666號</t>
+          <t>新竹市東區親仁里文化街10號2-10樓</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>(04)23242236#2700</t>
+          <t>(03)5347266#124</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2027/07/09</t>
+          <t>2028/04/28</t>
         </is>
       </c>
     </row>
@@ -3988,22 +3988,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(臺北)</t>
+          <t>金湖飯店</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>臺北市中山區松江路63號</t>
+          <t>金門縣金湖鎮太湖路二段218號</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(02)25019988#2701</t>
+          <t>(082)379666#160</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2028/10/22</t>
+          <t>2026/12/03</t>
         </is>
       </c>
     </row>
@@ -4025,32 +4025,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(基隆)</t>
+          <t>長榮文苑酒店(嘉義)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>基隆市</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>基隆市中正區中正路62號之1</t>
+          <t>嘉義縣太保市東勢里故宮大道777號</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>(02)24279988</t>
+          <t>(05)3669988#2700</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2028/05/22</t>
+          <t>2027/04/11</t>
         </is>
       </c>
     </row>
@@ -4062,32 +4062,32 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>長榮鳳凰酒店(礁溪)</t>
+          <t>長榮桂冠酒店(臺中)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉健康路77號</t>
+          <t>臺中市西屯區臺灣大道二段666號</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>(03)9100988#2335</t>
+          <t>(04)23242236#2700</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2027/09/15</t>
+          <t>2027/07/09</t>
         </is>
       </c>
     </row>
@@ -4099,32 +4099,32 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>阿里山東方明珠國際大飯店</t>
+          <t>長榮桂冠酒店(臺北)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>嘉義縣中埔鄉社口村檨仔林23號</t>
+          <t>臺北市中山區松江路63號</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>(05)2536999</t>
+          <t>(02)25019988#2701</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2027/12/12</t>
+          <t>2028/10/22</t>
         </is>
       </c>
     </row>
@@ -4136,32 +4136,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>阿里山英迪格酒店</t>
+          <t>長榮桂冠酒店(基隆)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>基隆市</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>嘉義縣番路鄉公田村2鄰龍頭20號2樓之1等10筆</t>
+          <t>基隆市中正區中正路62號之1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>(05)2586800#121</t>
+          <t>(02)24279988</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2028/10/21</t>
+          <t>2028/05/22</t>
         </is>
       </c>
     </row>
@@ -4173,32 +4173,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>阿里山賓館（現代館）</t>
+          <t>長榮鳳凰酒店(礁溪)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>嘉義縣阿里山鄉香林村西阿里山16-1號</t>
+          <t>宜蘭縣礁溪鄉健康路77號</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>(05)2679996#5117</t>
+          <t>(03)9100988#2335</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2027/06/19</t>
+          <t>2027/09/15</t>
         </is>
       </c>
     </row>
@@ -4210,22 +4210,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>阿爾卑斯莊園</t>
+          <t>阿里山東方明珠國際大飯店</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉協和村親河路二段88巷37號</t>
+          <t>嘉義縣中埔鄉社口村檨仔林23號</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>(0905)787698</t>
+          <t>(05)2536999</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2029/09/02</t>
+          <t>2027/12/12</t>
         </is>
       </c>
     </row>
@@ -4247,32 +4247,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>冠翔泉旅</t>
+          <t>阿里山英迪格酒店</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉仁愛路66巷6號</t>
+          <t>嘉義縣番路鄉公田村2鄰龍頭20號2樓之1等10筆</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>(03)9875599#119</t>
+          <t>(05)2586800#121</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2029/07/20</t>
+          <t>2028/10/21</t>
         </is>
       </c>
     </row>
@@ -4284,32 +4284,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>南港老爺行旅</t>
+          <t>阿里山賓館（現代館）</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>臺北市南港區經貿二路196號、196號10樓至20樓</t>
+          <t>嘉義縣阿里山鄉香林村西阿里山16-1號</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>(02)77500588</t>
+          <t>(05)2679996#5117</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2028/11/27</t>
+          <t>2027/06/19</t>
         </is>
       </c>
     </row>
@@ -4321,22 +4321,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>城市商旅美麗島館(HOTEL PAPA WHALE)</t>
+          <t>阿爾卑斯莊園</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>高雄市新興區民生一路328號1-7樓</t>
+          <t>宜蘭縣五結鄉協和村親河路二段88巷37號</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>(07)2519888</t>
+          <t>(0905)787698</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2028/09/24</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -4358,32 +4358,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>城市商旅高雄真愛館</t>
+          <t>冠翔泉旅</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區大義街1號</t>
+          <t>宜蘭縣礁溪鄉仁愛路66巷6號</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>(07)5215116#9303</t>
+          <t>(03)9875599#119</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2028/09/25</t>
+          <t>2029/07/20</t>
         </is>
       </c>
     </row>
@@ -4395,32 +4395,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>城市商旅駁二館</t>
+          <t>南港老爺行旅</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區公園二路83號1至11樓</t>
+          <t>臺北市南港區經貿二路196號、196號10樓至20樓</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>(07)5322777</t>
+          <t>(02)77500588</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2028/09/25</t>
+          <t>2028/11/27</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>城市商旅德立莊博愛館</t>
+          <t>城市商旅美麗島館(HOTEL PAPA WHALE)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>高雄市三民區博愛一路338號地上1至10樓</t>
+          <t>高雄市新興區民生一路328號1-7樓</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>(07)3238777#9301</t>
+          <t>(07)2519888</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2028/08/07</t>
+          <t>2028/09/24</t>
         </is>
       </c>
     </row>
@@ -4469,32 +4469,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>星8藝宿</t>
+          <t>城市商旅高雄真愛館</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉中山路三段192巷8號</t>
+          <t>高雄市鹽埕區大義街1號</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>(0932)495200</t>
+          <t>(07)5215116#9303</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2029/01/07</t>
+          <t>2028/09/25</t>
         </is>
       </c>
     </row>
@@ -4506,32 +4506,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>星漾商旅</t>
+          <t>城市商旅駁二館</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>臺中市北區錦南街17號,錦新街30號4樓至9樓,錦新街32號4樓至9樓</t>
+          <t>高雄市鹽埕區公園二路83號1至11樓</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>(04)22289008</t>
+          <t>(07)5322777</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2028/09/25</t>
         </is>
       </c>
     </row>
@@ -4543,32 +4543,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>星漾商旅(中清館)</t>
+          <t>城市商旅德立莊博愛館</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>臺中市北區中清路一段63號</t>
+          <t>高雄市三民區博愛一路338號地上1至10樓</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>(04)22083888</t>
+          <t>(07)3238777#9301</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2028/08/07</t>
         </is>
       </c>
     </row>
@@ -4580,22 +4580,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>柳營尖山埤渡假村</t>
+          <t>星8藝宿</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>臺南市柳營區旭山里60號</t>
+          <t>宜蘭縣三星鄉中山路三段192巷8號</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>(06)6233888#2100</t>
+          <t>(0932)495200</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2029/07/28</t>
+          <t>2029/01/07</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>美之旅商務飯店</t>
+          <t>星漾商旅</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4627,22 +4627,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>臺中市西區美村路一段269號1樓、2樓之1、2樓之2、3、4、5、6、7樓</t>
+          <t>臺中市北區錦南街17號,錦新街30號4樓至9樓,錦新街32號4樓至9樓</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>(04)23024330</t>
+          <t>(04)22289008</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2029/04/07</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -4654,22 +4654,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>美侖商旅</t>
+          <t>星漾商旅(中清館)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>臺北市中山區吉林路49號1至8樓</t>
+          <t>臺中市北區中清路一段63號</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>(02)25313535#878</t>
+          <t>(04)22083888</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2028/11/27</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>美墅館</t>
+          <t>柳營尖山埤渡假村</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4701,22 +4701,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>臺南市善化區昌隆里9鄰東勢寮131之8號</t>
+          <t>臺南市柳營區旭山里60號</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>(09)20656908</t>
+          <t>(06)6233888#2100</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2029/07/28</t>
         </is>
       </c>
     </row>
@@ -4728,22 +4728,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>美綠民宿</t>
+          <t>美之旅商務飯店</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>高雄市美濃區獅山里竹門14-2號</t>
+          <t>臺中市西區美村路一段269號1樓、2樓之1、2樓之2、3、4、5、6、7樓</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(07)6851111</t>
+          <t>(04)23024330</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2028/12/28</t>
+          <t>2029/04/07</t>
         </is>
       </c>
     </row>
@@ -4765,32 +4765,32 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>夏堤民宿</t>
+          <t>美侖商旅</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>屏東縣琉球鄉上福村2鄰杉板路51巷2號</t>
+          <t>臺北市中山區吉林路49號1至8樓</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(08)8611155</t>
+          <t>(02)25313535#878</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2029/02/25</t>
+          <t>2028/11/27</t>
         </is>
       </c>
     </row>
@@ -4802,22 +4802,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>夏優旅居</t>
+          <t>美墅館</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區新興街67號</t>
+          <t>臺南市善化區昌隆里9鄰東勢寮131之8號</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(07)5328885</t>
+          <t>(09)20656908</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2028/12/11</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -4839,22 +4839,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>娜路彎花園酒店</t>
+          <t>美綠民宿</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>臺東縣台東市新興路77號</t>
+          <t>高雄市美濃區獅山里竹門14-2號</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(089)231111</t>
+          <t>(07)6851111</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2028/12/28</t>
         </is>
       </c>
     </row>
@@ -4876,22 +4876,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>娜路彎會館</t>
+          <t>夏堤民宿</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>臺東縣台東市中興路2段385號</t>
+          <t>屏東縣琉球鄉上福村2鄰杉板路51巷2號</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(089)235500</t>
+          <t>(08)8611155</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>2029/02/25</t>
         </is>
       </c>
     </row>
@@ -4913,22 +4913,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>娜路彎銀河行館</t>
+          <t>夏優旅居</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>臺東縣台東市豐興路88號</t>
+          <t>高雄市鹽埕區新興街67號</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(089)383366</t>
+          <t>(07)5328885</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2028/09/16</t>
+          <t>2028/12/11</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>娜路彎銀河酒店</t>
+          <t>娜路彎花園酒店</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4960,22 +4960,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>臺東縣台東市豐興路66號</t>
+          <t>臺東縣台東市新興路77號</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(089)225000#8263</t>
+          <t>(089)231111</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2028/09/03</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -4987,22 +4987,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>悅徠舘</t>
+          <t>娜路彎會館</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>桃園市龜山區興華三街18號2樓之1</t>
+          <t>臺東縣台東市中興路2段385號</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>(03)3280177</t>
+          <t>(089)235500</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -5024,22 +5024,22 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>悅豪大飯店</t>
+          <t>娜路彎銀河行館</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>新竹市東區復興路22號</t>
+          <t>臺東縣台東市豐興路88號</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(03)5267890</t>
+          <t>(089)383366</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2029/07/20</t>
+          <t>2028/09/16</t>
         </is>
       </c>
     </row>
@@ -5061,32 +5061,32 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>旅行邦尼</t>
+          <t>娜路彎銀河酒店</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>新北市淡水區中山路87巷7號</t>
+          <t>臺東縣台東市豐興路66號</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(09)28824850</t>
+          <t>(089)225000#8263</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2029/01/05</t>
+          <t>2028/09/03</t>
         </is>
       </c>
     </row>
@@ -5098,22 +5098,22 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>旅悅國際青年旅館</t>
+          <t>悅徠舘</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>高雄市前鎮區三多三路211號3樓及4樓</t>
+          <t>桃園市龜山區興華三街18號2樓之1</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(07)3359006</t>
+          <t>(03)3280177</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2027/10/13</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -5135,32 +5135,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>桃園大溪笠復威斯汀度假酒店</t>
+          <t>悅豪大飯店</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>桃園市大溪區日新路166號</t>
+          <t>新竹市東區復興路22號</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(03)2725035</t>
+          <t>(03)5267890</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2029/07/20</t>
         </is>
       </c>
     </row>
@@ -5172,32 +5172,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>桃園喜來登酒店</t>
+          <t>挪威森林頂級汽車旅館</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>桃園市大園區大觀路777號</t>
+          <t>新北市板橋區和平路14巷3號</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(03)3850000#2605</t>
+          <t>(02)29562211</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026/10/29</t>
+          <t>2029/09/30</t>
         </is>
       </c>
     </row>
@@ -5209,32 +5209,32 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>泰安觀止溫泉會館</t>
+          <t>旅行邦尼</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>苗栗縣泰安鄉錦水村圓墩58-7號</t>
+          <t>新北市淡水區中山路87巷7號</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>(037)941951#527</t>
+          <t>(09)28824850</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2028/06/25</t>
+          <t>2029/01/05</t>
         </is>
       </c>
     </row>
@@ -5246,22 +5246,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>海福花園飯店</t>
+          <t>旅悅國際青年旅館</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>金門縣金沙鎮高陽路1號</t>
+          <t>高雄市前鎮區三多三路211號3樓及4樓</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(082)353888</t>
+          <t>(07)3359006</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2029/09/01</t>
+          <t>2027/10/13</t>
         </is>
       </c>
     </row>
@@ -5283,32 +5283,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>海霞您的家</t>
+          <t>桃園大溪笠復威斯汀度假酒店</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>新北市貢寮區仁里里14鄰仁愛路38號</t>
+          <t>桃園市大溪區日新路166號</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(09)35204895</t>
+          <t>(03)2725035</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -5320,22 +5320,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>海灣假日酒店</t>
+          <t>桃園喜來登酒店</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>新北市深坑區北深路3段265號</t>
+          <t>桃園市大園區大觀路777號</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>(02)77035880</t>
+          <t>(03)3850000#2605</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2028/12/17</t>
+          <t>2026/10/29</t>
         </is>
       </c>
     </row>
@@ -5357,32 +5357,32 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>神隱國度民宿</t>
+          <t>泰安觀止溫泉會館</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>新北市瑞芳區崙頂路90號</t>
+          <t>苗栗縣泰安鄉錦水村圓墩58-7號</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>(09)05788650</t>
+          <t>(037)941951#527</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2028/06/25</t>
         </is>
       </c>
     </row>
@@ -5394,32 +5394,32 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>秧悦美地度假酒店</t>
+          <t>海福花園飯店</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>花蓮縣吉安鄉干城村干城二街95-9號</t>
+          <t>金門縣金沙鎮高陽路1號</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(03)8129168#2701</t>
+          <t>(082)353888</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2029/09/01</t>
         </is>
       </c>
     </row>
@@ -5431,22 +5431,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>秘境41</t>
+          <t>海霞您的家</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>桃園市大溪區興和里中央路41號</t>
+          <t>新北市貢寮區仁里里14鄰仁愛路38號</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>(03)3887111</t>
+          <t>(09)35204895</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2027/12/10</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -5468,32 +5468,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>秘境民宿</t>
+          <t>海灣假日酒店</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>屏東縣東港鎮屏東縣東港鎮水源路223號(新和段737-3地號)</t>
+          <t>新北市深坑區北深路3段265號</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>(08)8333345</t>
+          <t>(02)77035880</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2029/01/18</t>
+          <t>2028/12/17</t>
         </is>
       </c>
     </row>
@@ -5505,32 +5505,32 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>高雄中央公園英迪格酒店</t>
+          <t>神隱國度民宿</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>高雄市新興區中山一路4號</t>
+          <t>新北市瑞芳區崙頂路90號</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>(07)2721555#301</t>
+          <t>(09)05788650</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -5542,32 +5542,32 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>高雄商旅</t>
+          <t>秧悦美地度假酒店</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>高雄市新興區民族二路33號1、4~10樓；37號1、3~10樓</t>
+          <t>花蓮縣吉安鄉干城村干城二街95-9號</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>(09)19546590</t>
+          <t>(03)8129168#2701</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -5579,22 +5579,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>高雄富野渡假酒店</t>
+          <t>秘境41</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>高雄市前鎮區瑞田街99號</t>
+          <t>桃園市大溪區興和里中央路41號</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>(07)8215299#7102</t>
+          <t>(03)3887111</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2029/02/09</t>
+          <t>2027/12/10</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>高雄圓山大飯店</t>
+          <t>秘境民宿</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>高雄市鳥松區圓山路2號</t>
+          <t>屏東縣東港鎮屏東縣東港鎮水源路223號(新和段737-3地號)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>(07)3706007#519</t>
+          <t>(08)8333345</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2029/01/18</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>高雄福華大飯店</t>
+          <t>高雄中央公園英迪格酒店</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>高雄市新興區七賢一路311號</t>
+          <t>高雄市新興區中山一路4號</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(07)2307737</t>
+          <t>(07)2721555#301</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026/11/16</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -5690,22 +5690,22 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>國聯大飯店</t>
+          <t>高雄商旅</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>臺北市大安區光復南路200號</t>
+          <t>高雄市新興區民族二路33號1、4~10樓；37號1、3~10樓</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(02)27731515#184</t>
+          <t>(09)19546590</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2029/09/15</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -5727,22 +5727,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>基拉耳景觀民宿</t>
+          <t>高雄富野渡假酒店</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>桃園市復興區溪口路16巷29號</t>
+          <t>高雄市前鎮區瑞田街99號</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(02)23965188#594</t>
+          <t>(07)8215299#7102</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2028/06/15</t>
+          <t>2029/02/09</t>
         </is>
       </c>
     </row>
@@ -5764,32 +5764,32 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>將捷金鬱金香酒店</t>
+          <t>高雄圓山大飯店</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>新北市淡水區中正路1段2之1號(A區地上3至6層、B區地上1至5層、C區地下3層至地上3層)</t>
+          <t>高雄市鳥松區圓山路2號</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(02)26218555#2913</t>
+          <t>(07)3706007#519</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2027/04/14</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>康橋商旅-六合夜市七賢館</t>
+          <t>高雄福華大飯店</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5811,22 +5811,22 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>高雄市新興區同愛街28號1樓、30號</t>
+          <t>高雄市新興區七賢一路311號</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(07)288-5588</t>
+          <t>(07)2307737</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2026/11/16</t>
         </is>
       </c>
     </row>
@@ -5838,22 +5838,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>康橋商旅臺南赤崁樓館</t>
+          <t>國聯大飯店</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>臺南市中西區赤崁里民權路二段97號1至8樓</t>
+          <t>臺北市大安區光復南路200號</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>(06)2253377</t>
+          <t>(02)27731515#184</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2029/09/02</t>
+          <t>2029/09/15</t>
         </is>
       </c>
     </row>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>康橋慢旅</t>
+          <t>基拉耳景觀民宿</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>臺南市中西區民生路二段416號</t>
+          <t>桃園市復興區溪口路16巷29號</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>(06)2805566</t>
+          <t>(02)23965188#594</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2029/09/02</t>
+          <t>2028/06/15</t>
         </is>
       </c>
     </row>
@@ -5912,32 +5912,32 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>捷絲旅 臺南虎山館</t>
+          <t>將捷金鬱金香酒店</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>臺南市仁德區成功里5鄰文華路2段300號1~9樓，地下一、二樓</t>
+          <t>新北市淡水區中正路1段2之1號(A區地上3至6層、B區地上1至5層、C區地下3層至地上3層)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>(06)2662218#8321</t>
+          <t>(02)26218555#2913</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2028/02/13</t>
+          <t>2027/04/14</t>
         </is>
       </c>
     </row>
@@ -5949,32 +5949,32 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>捷絲旅臺北三重館</t>
+          <t>康橋商旅-六合夜市七賢館</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>新北市三重區三和路四段107-1號</t>
+          <t>高雄市新興區同愛街28號1樓、30號</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(02)22806111#8304</t>
+          <t>(07)288-5588</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2028/10/12</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -5986,22 +5986,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>捷絲旅西門町店</t>
+          <t>康橋商旅臺南赤崁樓館</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路一段41號5樓至9樓</t>
+          <t>臺南市中西區赤崁里民權路二段97號1至8樓</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>(02)25215000</t>
+          <t>(06)2253377</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2027/05/12</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -6023,32 +6023,32 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>捷絲旅花蓮中正館</t>
+          <t>康橋慢旅</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市主睦里14鄰中正路396號</t>
+          <t>臺南市中西區民生路二段416號</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(03)8900069#8104</t>
+          <t>(06)2805566</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -6060,22 +6060,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>捷絲旅高雄中正館</t>
+          <t>捷絲旅 臺南虎山館</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>高雄市苓雅區中正一路134號</t>
+          <t>臺南市仁德區成功里5鄰文華路2段300號1~9樓，地下一、二樓</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(07)9733587#8104</t>
+          <t>(06)2662218#8321</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>2028/02/13</t>
         </is>
       </c>
     </row>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>捷絲旅高雄站前館</t>
+          <t>捷絲旅臺北三重館</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>高雄市新興區中山一路280號1至14樓</t>
+          <t>新北市三重區三和路四段107-1號</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(07)9733587#8104</t>
+          <t>(02)22806111#8304</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2028/09/29</t>
+          <t>2028/10/12</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>捷絲旅臺大尊賢館</t>
+          <t>捷絲旅西門町店</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6144,22 +6144,22 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>臺北市大安區羅斯福路四段83號1-10樓</t>
+          <t>臺北市中正區中華路一段41號5樓至9樓</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(02)77355088</t>
+          <t>(02)25215000</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/05/12</t>
         </is>
       </c>
     </row>
@@ -6171,32 +6171,32 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>捷絲旅礁溪館</t>
+          <t>捷絲旅花蓮中正館</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉德陽路24巷8號、10號</t>
+          <t>花蓮縣花蓮市主睦里14鄰中正路396號</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(03)9102000#8104</t>
+          <t>(03)8900069#8104</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2027/01/07</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -6208,22 +6208,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>清新溫泉飯店</t>
+          <t>捷絲旅高雄中正館</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>臺中市烏日區溫泉路2號</t>
+          <t>高雄市苓雅區中正一路134號</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>(04)23831088#7602</t>
+          <t>(07)9733587#8104</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -6245,32 +6245,32 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>統一谷關渡假村</t>
+          <t>捷絲旅高雄站前館</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>臺中市和平區博愛里東關路一段188號</t>
+          <t>高雄市新興區中山一路280號1至14樓</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>(04)25950000</t>
+          <t>(07)9733587#8104</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2028/01/06</t>
+          <t>2028/09/29</t>
         </is>
       </c>
     </row>
@@ -6282,32 +6282,32 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>統一渡假村</t>
+          <t>捷絲旅臺大尊賢館</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>新竹縣關西鎮金山里34號</t>
+          <t>臺北市大安區羅斯福路四段83號1-10樓</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>(03)5478888</t>
+          <t>(02)77355088</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2027/12/20</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6319,22 +6319,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>鹿港澄悅酒店</t>
+          <t>捷絲旅礁溪館</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮中正路598號1樓、5至8樓</t>
+          <t>宜蘭縣礁溪鄉德陽路24巷8號、10號</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>(04)7785727</t>
+          <t>(03)9102000#8104</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2029/03/02</t>
+          <t>2027/01/07</t>
         </is>
       </c>
     </row>
@@ -6356,32 +6356,32 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>傑仕堡有氧酒店</t>
+          <t>清新溫泉飯店</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>新北市板橋區縣民大道2段275號、275號2至17樓、277號2樓</t>
+          <t>臺中市烏日區溫泉路2號</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>(02)77273000#54083</t>
+          <t>(04)23831088#7602</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026/10/16</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -6393,32 +6393,32 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>凱旋酒店</t>
+          <t>統一谷關渡假村</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>臺北市內湖區江南街55號3樓至9樓</t>
+          <t>臺中市和平區博愛里東關路一段188號</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(02)87527888#6203</t>
+          <t>(04)25950000</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026/12/10</t>
+          <t>2028/01/06</t>
         </is>
       </c>
     </row>
@@ -6430,32 +6430,32 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>凱達大飯店</t>
+          <t>統一渡假村</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>臺北市萬華區艋舺大道167號1-26樓</t>
+          <t>新竹縣關西鎮金山里34號</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(02)23836789#6321</t>
+          <t>(03)5478888</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2027/06/02</t>
+          <t>2027/12/20</t>
         </is>
       </c>
     </row>
@@ -6467,32 +6467,32 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>凱撒大飯店</t>
+          <t>鹿港澄悅酒店</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁路6號</t>
+          <t>彰化縣鹿港鎮中正路598號1樓、5至8樓</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(08)8861888</t>
+          <t>(04)7785727</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2028/09/16</t>
+          <t>2029/03/02</t>
         </is>
       </c>
     </row>
@@ -6504,32 +6504,32 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>勝利127民宿</t>
+          <t>傑仕堡有氧酒店</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>屏東縣屏東市勝利路127號</t>
+          <t>新北市板橋區縣民大道2段275號、275號2至17樓、277號2樓</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(08)7320099</t>
+          <t>(02)77273000#54083</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026/12/14</t>
+          <t>2026/10/16</t>
         </is>
       </c>
     </row>
@@ -6541,32 +6541,32 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>勝利131民宿</t>
+          <t>凱旋酒店</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>屏東縣屏東市勝利路131號</t>
+          <t>臺北市內湖區江南街55號3樓至9樓</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(08)7320099</t>
+          <t>(02)87527888#6203</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026/12/14</t>
+          <t>2026/12/10</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>寒居酒店</t>
+          <t>凱達大飯店</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>臺北市中山區松江路116號1樓至9樓</t>
+          <t>臺北市萬華區艋舺大道167號1-26樓</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>(02)66008000#8886</t>
+          <t>(02)23836789#6321</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2028/07/17</t>
+          <t>2027/06/02</t>
         </is>
       </c>
     </row>
@@ -6615,32 +6615,32 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>寒軒國際大飯店</t>
+          <t>凱撒大飯店</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>高雄市苓雅區四維三路三十三號</t>
+          <t>屏東縣恆春鎮墾丁路6號</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>(0980)556224</t>
+          <t>(08)8861888</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2028/12/11</t>
+          <t>2028/09/16</t>
         </is>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>富光大旅社</t>
+          <t>勝利127民宿</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公園路19-7號</t>
+          <t>屏東縣屏東市勝利路127號</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>(08)7345656</t>
+          <t>(08)7320099</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2028/05/28</t>
+          <t>2026/12/14</t>
         </is>
       </c>
     </row>
@@ -6689,32 +6689,32 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>富信大飯店</t>
+          <t>勝利131民宿</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>新北市汐止區大同路一段152號</t>
+          <t>屏東縣屏東市勝利路131號</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>(02)26416422#5112</t>
+          <t>(08)7320099</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2028/03/13</t>
+          <t>2026/12/14</t>
         </is>
       </c>
     </row>
@@ -6726,32 +6726,32 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>尊爵大飯店</t>
+          <t>寒居酒店</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>桃園市桃園區莊敬路一段300號</t>
+          <t>臺北市中山區松江路116號1樓至9樓</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>(03)3169090#8502</t>
+          <t>(02)66008000#8886</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026/12/21</t>
+          <t>2028/07/17</t>
         </is>
       </c>
     </row>
@@ -6763,32 +6763,32 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>尊爵天際大飯店</t>
+          <t>寒軒國際大飯店</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>桃園市蘆竹區南崁路一段108號</t>
+          <t>高雄市苓雅區四維三路三十三號</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(03)2228100#6081</t>
+          <t>(0980)556224</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2028/08/31</t>
+          <t>2028/12/11</t>
         </is>
       </c>
     </row>
@@ -6800,22 +6800,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>惠來谷關溫泉會館</t>
+          <t>富光大旅社</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>臺中市和平區東關路一段溫泉巷十號</t>
+          <t>屏東縣屏東市公園路19-7號</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(04)25951998#621</t>
+          <t>(08)7345656</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2029/08/13</t>
+          <t>2028/05/28</t>
         </is>
       </c>
     </row>
@@ -6837,32 +6837,32 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>提米好旅</t>
+          <t>富信大飯店</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>彰化縣彰化市成功路277號</t>
+          <t>新北市汐止區大同路一段152號</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(04)7061086#9</t>
+          <t>(02)26416422#5112</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>2028/03/13</t>
         </is>
       </c>
     </row>
@@ -6874,32 +6874,32 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>揚昊民宿</t>
+          <t>富翔大飯店</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之6號</t>
+          <t>宜蘭縣宜蘭市校舍路19號</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>(037)747711#9</t>
+          <t>(03)9388386</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2028/09/08</t>
+          <t>2029/09/28</t>
         </is>
       </c>
     </row>
@@ -6911,32 +6911,32 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>晶泉丰旅</t>
+          <t>尊爵大飯店</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉溫泉路67號2至10樓</t>
+          <t>桃園市桃園區莊敬路一段300號</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>(03)9100000#6105</t>
+          <t>(03)3169090#8502</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2027/05/22</t>
+          <t>2026/12/21</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>智醫康寓</t>
+          <t>尊爵天際大飯店</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6958,22 +6958,22 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>桃園市桃園區民生路107號1-3樓及7-20樓</t>
+          <t>桃園市蘆竹區南崁路一段108號</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>(03)3362575</t>
+          <t>(03)2228100#6081</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026/10/30</t>
+          <t>2028/08/31</t>
         </is>
       </c>
     </row>
@@ -6985,32 +6985,32 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>渴望會館</t>
+          <t>惠來谷關溫泉會館</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>桃園市龍潭區渴望路428號3-5樓</t>
+          <t>臺中市和平區東關路一段溫泉巷十號</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>(03)4072999#7110</t>
+          <t>(04)25951998#621</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2029/08/13</t>
         </is>
       </c>
     </row>
@@ -7022,32 +7022,32 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>然一酒店</t>
+          <t>提米好旅</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>高雄市前鎮區中山二路199號</t>
+          <t>彰化縣彰化市成功路277號</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>(07)9730186#1666</t>
+          <t>(04)7061086#9</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2027/06/03</t>
+          <t>2027/11/27</t>
         </is>
       </c>
     </row>
@@ -7059,22 +7059,22 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>發現號特色民宿</t>
+          <t>揚昊民宿</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>屏東縣林邊鄉崎峰村裕後路90號</t>
+          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之6號</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>(08)8750300</t>
+          <t>(037)747711#9</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2028/09/08</t>
         </is>
       </c>
     </row>
@@ -7096,32 +7096,32 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>華泰瑞苑</t>
+          <t>晶泉丰旅</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮公園路101號</t>
+          <t>宜蘭縣礁溪鄉溫泉路67號2至10樓</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>(08)8863666</t>
+          <t>(03)9100000#6105</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2027/06/21</t>
+          <t>2027/05/22</t>
         </is>
       </c>
     </row>
@@ -7133,22 +7133,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>貳十二度行旅</t>
+          <t>智醫康寓</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>宜蘭縣蘇澳鎮信義路177號</t>
+          <t>桃園市桃園區民生路107號1-3樓及7-20樓</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>(03)9901888</t>
+          <t>(03)3362575</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2029/05/24</t>
+          <t>2026/10/30</t>
         </is>
       </c>
     </row>
@@ -7170,32 +7170,32 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>陽明山天籟渡假酒店</t>
+          <t>渴望會館</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>新北市金山區名流路1之6號、1之7號、1之9號、1之9號5樓及1之9號5樓之1至之8</t>
+          <t>桃園市龍潭區渴望路428號3-5樓</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>(02)24080400#1700</t>
+          <t>(03)4072999#7110</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2029/02/11</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -7207,32 +7207,32 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>雅霖大飯店</t>
+          <t>然一酒店</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市同和路100號</t>
+          <t>高雄市前鎮區中山二路199號</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>(06)9261366</t>
+          <t>(07)9730186#1666</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2027/06/03</t>
         </is>
       </c>
     </row>
@@ -7244,32 +7244,32 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>雲品溫泉酒店日月潭</t>
+          <t>發現號特色民宿</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉水社村中正路23號</t>
+          <t>屏東縣林邊鄉崎峰村裕後路90號</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>(049)2212959</t>
+          <t>(08)8750300</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2029/05/05</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -7281,32 +7281,32 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>雲頂國際商旅</t>
+          <t>華泰瑞苑</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>臺南市南區大同路二段530號</t>
+          <t>屏東縣恆春鎮公園路101號</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>(06)2687766</t>
+          <t>(08)8863666</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2029/02/25</t>
+          <t>2027/06/21</t>
         </is>
       </c>
     </row>
@@ -7318,32 +7318,32 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>圓山大飯店</t>
+          <t>貳十二度行旅</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路4段1巷1號</t>
+          <t>宜蘭縣蘇澳鎮信義路177號</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>(02)28861818#1007</t>
+          <t>(03)9901888</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2029/05/24</t>
         </is>
       </c>
     </row>
@@ -7355,32 +7355,32 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>奧斯卡去旅行民宿</t>
+          <t>陽明山天籟渡假酒店</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>臺東縣臺東市興安路一段167號</t>
+          <t>新北市金山區名流路1之6號、1之7號、1之9號、1之9號5樓及1之9號5樓之1至之8</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>(0910)633944</t>
+          <t>(02)24080400#1700</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2027/01/29</t>
+          <t>2029/02/11</t>
         </is>
       </c>
     </row>
@@ -7392,22 +7392,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>奧斯卡民宿</t>
+          <t>雅霖大飯店</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>臺東縣台東市興安路1段175號</t>
+          <t>澎湖縣馬公市同和路100號</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>(0965)329000</t>
+          <t>(06)9261366</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2027/01/18</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -7429,32 +7429,32 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>新竹安捷國際酒店</t>
+          <t>雲品溫泉酒店日月潭</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>新竹縣竹北市復興三路二段168號14樓-18樓</t>
+          <t>南投縣魚池鄉水社村中正路23號</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>(03)6209777#660</t>
+          <t>(049)2212959</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2028/07/13</t>
+          <t>2029/05/05</t>
         </is>
       </c>
     </row>
@@ -7466,22 +7466,22 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>新竹老爺大酒店</t>
+          <t>雲頂國際商旅</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>新竹市東區光復路一段227號</t>
+          <t>臺南市南區大同路二段530號</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>(03)5631285#204</t>
+          <t>(06)2687766</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2029/02/25</t>
         </is>
       </c>
     </row>
@@ -7503,22 +7503,22 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>新竹喜來登大飯店</t>
+          <t>圓山大飯店</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>新竹縣竹北市光明六路東一段265號</t>
+          <t>臺北市中山區中山北路4段1巷1號</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>(03)6206126</t>
+          <t>(02)28861818#1007</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -7540,22 +7540,22 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>新竹福華大飯店</t>
+          <t>奧斯卡去旅行民宿</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>新竹市中正路178號</t>
+          <t>臺東縣臺東市興安路一段167號</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>(03)5282323#5303</t>
+          <t>(0910)633944</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2027/01/29</t>
         </is>
       </c>
     </row>
@@ -7577,22 +7577,22 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>新南一二文創商行</t>
+          <t>奧斯卡民宿</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>桃園市大溪區中山路１２號</t>
+          <t>臺東縣台東市興安路1段175號</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>(03)3884466</t>
+          <t>(0965)329000</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2029/02/05</t>
+          <t>2027/01/18</t>
         </is>
       </c>
     </row>
@@ -7614,32 +7614,32 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>新悦花園酒店</t>
+          <t>新竹安捷國際酒店</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>嘉義市東區後湖里6鄰保順路69號</t>
+          <t>新竹縣竹北市復興三路二段168號14樓-18樓</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>(05)2777266#5801</t>
+          <t>(03)6209777#660</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2027/04/07</t>
+          <t>2028/07/13</t>
         </is>
       </c>
     </row>
@@ -7651,32 +7651,32 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>溪頭福華渡假飯店-溪頭漢光樓</t>
+          <t>新竹老爺大酒店</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>南投縣鹿谷鄉森林巷11、12號</t>
+          <t>新竹市東區光復路一段227號</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>(049)2612588#3005</t>
+          <t>(03)5631285#204</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2028/12/01</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -7688,32 +7688,32 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>溪邊小築民宿</t>
+          <t>新竹喜來登大飯店</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>新北市瑞芳區祈堂路133號</t>
+          <t>新竹縣竹北市光明六路東一段265號</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>(02)24961191</t>
+          <t>(03)6206126</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2029/06/21</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -7725,32 +7725,32 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>煙波大飯店臺南館</t>
+          <t>新竹福華大飯店</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>臺南市中西區永福路1段269號1-12樓及地下一層至三層</t>
+          <t>新竹市中正路178號</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>(06)2156000#1171</t>
+          <t>(03)5282323#5303</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2029/06/09</t>
+          <t>2026/10/26</t>
         </is>
       </c>
     </row>
@@ -7762,32 +7762,32 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>煙波大飯店宜蘭館</t>
+          <t>新南一二文創商行</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>宜蘭縣宜蘭市凱旋路135號 、135號2至9樓</t>
+          <t>桃園市大溪區中山路１２號</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>(09)9256899#1171</t>
+          <t>(03)3884466</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2029/05/06</t>
+          <t>2029/02/05</t>
         </is>
       </c>
     </row>
@@ -7799,22 +7799,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮太魯閣山闊館</t>
+          <t>新悦花園酒店</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村草林10-7號</t>
+          <t>嘉義市東區後湖里6鄰保順路69號</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>(03)8612000#1470</t>
+          <t>(05)2777266#5801</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026/11/05</t>
+          <t>2027/04/07</t>
         </is>
       </c>
     </row>
@@ -7836,32 +7836,32 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮太魯閣沁海館</t>
+          <t>溪頭福華渡假飯店-溪頭漢光樓</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村6鄰草林10之6號</t>
+          <t>南投縣鹿谷鄉森林巷11、12號</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>(03)8228835#1174</t>
+          <t>(049)2612588#3005</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2029/04/19</t>
+          <t>2028/12/01</t>
         </is>
       </c>
     </row>
@@ -7873,32 +7873,32 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮館</t>
+          <t>溪邊小築民宿</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市民立里1鄰中美路142號</t>
+          <t>新北市瑞芳區祈堂路133號</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>(03)8228835#1174</t>
+          <t>(02)24961191</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2029/04/19</t>
+          <t>2029/06/21</t>
         </is>
       </c>
     </row>
@@ -7910,22 +7910,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>煙波花時間 宜蘭傳藝</t>
+          <t>煙波大飯店臺南館</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉五濱路二段201號</t>
+          <t>臺南市中西區永福路1段269號1-12樓及地下一層至三層</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>(03)9256899#1171</t>
+          <t>(06)2156000#1171</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2027/07/09</t>
+          <t>2029/06/09</t>
         </is>
       </c>
     </row>
@@ -7947,22 +7947,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>煙波花時間 花蓮</t>
+          <t>煙波大飯店宜蘭館</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村草林10-5號2~6樓</t>
+          <t>宜蘭縣宜蘭市凱旋路135號 、135號2至9樓</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>(03)8612000#1470</t>
+          <t>(09)9256899#1171</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026/11/16</t>
+          <t>2029/05/06</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>瑞穗天合國際觀光酒店</t>
+          <t>煙波大飯店花蓮太魯閣山闊館</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7994,22 +7994,22 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>花蓮縣瑞穗鄉溫泉路二段368號</t>
+          <t>花蓮縣新城鄉順安村草林10-7號</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>(03)8876000#3260</t>
+          <t>(03)8612000#1470</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2028/01/19</t>
+          <t>2026/11/05</t>
         </is>
       </c>
     </row>
@@ -8021,32 +8021,32 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>裕元花園酒店</t>
+          <t>煙波大飯店花蓮太魯閣沁海館</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>臺中市西屯區臺灣大道四段610號</t>
+          <t>花蓮縣新城鄉順安村6鄰草林10之6號</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>(04)24655660#5030</t>
+          <t>(03)8228835#1174</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2027/11/19</t>
+          <t>2029/04/19</t>
         </is>
       </c>
     </row>
@@ -8058,32 +8058,32 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>遇見民宿</t>
+          <t>煙波大飯店花蓮館</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>屏東縣東港鎮水源路221號(新和段737-4地號)</t>
+          <t>花蓮縣花蓮市民立里1鄰中美路142號</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>(08)8333345</t>
+          <t>(03)8228835#1174</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2029/04/19</t>
         </is>
       </c>
     </row>
@@ -8095,32 +8095,32 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>頌華私墅肆區民宿</t>
+          <t>煙波花時間 宜蘭傳藝</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>澎湖縣湖西鄉許家村6鄰港子尾120之5號</t>
+          <t>宜蘭縣五結鄉五濱路二段201號</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>(06)9212953</t>
+          <t>(03)9256899#1171</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2029/01/25</t>
+          <t>2027/07/09</t>
         </is>
       </c>
     </row>
@@ -8132,32 +8132,32 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>嘉仕特飯店</t>
+          <t>煙波花時間 花蓮</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>桃園市桃園區中山路203號</t>
+          <t>花蓮縣新城鄉順安村草林10-5號2~6樓</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>(03)3343999</t>
+          <t>(03)8612000#1470</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>2026/11/16</t>
         </is>
       </c>
     </row>
@@ -8169,22 +8169,22 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>嘉義富野渡假酒店</t>
+          <t>瑞穗天合國際觀光酒店</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>嘉義縣民雄鄉三興村升學一街3、5、7、9、11、13、15、17、19、21、23、25、27號</t>
+          <t>花蓮縣瑞穗鄉溫泉路二段368號</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>(05)2721688</t>
+          <t>(03)8876000#3260</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2028/08/12</t>
+          <t>2028/01/19</t>
         </is>
       </c>
     </row>
@@ -8206,32 +8206,32 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>嘉義智選假日酒店</t>
+          <t>裕元花園酒店</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>嘉義市西區中興路69號B2至13層樓</t>
+          <t>臺中市西屯區臺灣大道四段610號</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>(05)2335899#801</t>
+          <t>(04)24655660#5030</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2027/11/24</t>
+          <t>2027/11/19</t>
         </is>
       </c>
     </row>
@@ -8243,32 +8243,32 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>嘉義福容voco酒店</t>
+          <t>遇見民宿</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>嘉義市西區世賢路一段789號B4-4樓、7樓、16樓-32樓</t>
+          <t>屏東縣東港鎮水源路221號(新和段737-4地號)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>(05)232338971</t>
+          <t>(08)8333345</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2029/06/15</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -8280,22 +8280,22 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>夢想森林親子民宿</t>
+          <t>頌華私墅肆區民宿</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉三星鄉大德路二段613號</t>
+          <t>澎湖縣湖西鄉許家村6鄰港子尾120之5號</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>(03)9898113</t>
+          <t>(06)9212953</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2029/01/25</t>
         </is>
       </c>
     </row>
@@ -8317,32 +8317,32 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>榮美金鬱金香酒店</t>
+          <t>嘉仕特飯店</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>臺南市北區海安路三段50號</t>
+          <t>桃園市桃園區中山路203號</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>(06)2200800#6001</t>
+          <t>(03)3343999</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2027/11/04</t>
+          <t>2027/11/27</t>
         </is>
       </c>
     </row>
@@ -8354,32 +8354,32 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>榮興金鬱金香酒店</t>
+          <t>嘉義富野渡假酒店</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>臺南市中西區民族路二段128號</t>
+          <t>嘉義縣民雄鄉三興村升學一街3、5、7、9、11、13、15、17、19、21、23、25、27號</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>(06)2200800#6006</t>
+          <t>(05)2721688</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2027/11/04</t>
+          <t>2028/08/12</t>
         </is>
       </c>
     </row>
@@ -8391,22 +8391,22 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>福美民宿</t>
+          <t>嘉義智選假日酒店</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>臺東縣台東市精誠路241號</t>
+          <t>嘉義市西區中興路69號B2至13層樓</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>(089)328466</t>
+          <t>(05)2335899#801</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2027/01/09</t>
+          <t>2027/11/24</t>
         </is>
       </c>
     </row>
@@ -8428,22 +8428,22 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>福容大飯店 臺北二館</t>
+          <t>嘉義福容voco酒店</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>新北市深坑區北深路三段236號</t>
+          <t>嘉義市西區世賢路一段789號B4-4樓、7樓、16樓-32樓</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>(02)26620088#186</t>
+          <t>(05)232338971</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2028/01/05</t>
+          <t>2029/06/15</t>
         </is>
       </c>
     </row>
@@ -8465,32 +8465,32 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>福容大飯店 桃園</t>
+          <t>夢想森林親子民宿</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>桃園市桃園區同安里大興西路一段200號</t>
+          <t>宜蘭縣三星鄉三星鄉大德路二段613號</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>(03)3265800#300</t>
+          <t>(03)9898113</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2027/12/17</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -8502,22 +8502,22 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>福容大飯店 桃園機場捷運 A8</t>
+          <t>榮美金鬱金香酒店</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>桃園市龜山區復興一路2號3樓</t>
+          <t>臺南市北區海安路三段50號</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>(03)3285688#8770</t>
+          <t>(06)2200800#6001</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2027/08/12</t>
+          <t>2027/11/04</t>
         </is>
       </c>
     </row>
@@ -8539,32 +8539,32 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>福容大飯店 高雄</t>
+          <t>榮興金鬱金香酒店</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區五福四路45號</t>
+          <t>臺南市中西區民族路二段128號</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>(07)5317777#7782</t>
+          <t>(06)2200800#6006</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2028/08/14</t>
+          <t>2027/11/04</t>
         </is>
       </c>
     </row>
@@ -8576,32 +8576,32 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>福容大飯店 淡水漁人碼頭</t>
+          <t>福美民宿</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>新北市淡水區觀海路83號</t>
+          <t>臺東縣台東市精誠路241號</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>(02)2805 9958#8178</t>
+          <t>(089)328466</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2028/11/16</t>
+          <t>2027/01/09</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>福容大飯店　福隆</t>
+          <t>福容大飯店 臺北二館</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>新北市貢寮區福隆里福隆街41號</t>
+          <t>新北市深坑區北深路三段236號</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>(02)24992381</t>
+          <t>(02)26620088#186</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2028/01/05</t>
         </is>
       </c>
     </row>
@@ -8650,22 +8650,22 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>福容大飯店 墾丁</t>
+          <t>福容大飯店 桃園</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮船帆路1000號</t>
+          <t>桃園市桃園區同安里大興西路一段200號</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>(08)8856969#340</t>
+          <t>(03)3265800#300</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2028/05/28</t>
+          <t>2027/12/17</t>
         </is>
       </c>
     </row>
@@ -8687,32 +8687,32 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>福容大飯店 麗寶樂園</t>
+          <t>福容大飯店 桃園機場捷運 A8</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>臺中市后里區福容路88號</t>
+          <t>桃園市龜山區復興一路2號3樓</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>(04)25571366#8343</t>
+          <t>(03)3285688#8770</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2029/03/19</t>
+          <t>2027/08/12</t>
         </is>
       </c>
     </row>
@@ -8724,32 +8724,32 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>福容大飯店花蓮</t>
+          <t>福容大飯店 高雄</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市民生路51號</t>
+          <t>高雄市鹽埕區五福四路45號</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>(03)8239988#7507</t>
+          <t>(07)5317777#7782</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2027/11/10</t>
+          <t>2028/08/14</t>
         </is>
       </c>
     </row>
@@ -8761,22 +8761,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>福容徠旅 水里</t>
+          <t>福容大飯店 淡水漁人碼頭</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>南投縣水里鄉東三街51號1樓至6樓</t>
+          <t>新北市淡水區觀海路83號</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>(049)2771888#5560</t>
+          <t>(02)2805 9958#8178</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2029/07/09</t>
+          <t>2028/11/16</t>
         </is>
       </c>
     </row>
@@ -8798,32 +8798,32 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>福容徠旅林口</t>
+          <t>福容大飯店　福隆</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>桃園市龜山區文二一街68號</t>
+          <t>新北市貢寮區福隆里福隆街41號</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>(03)3277388#300</t>
+          <t>(02)24992381</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2027/12/03</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -8835,32 +8835,32 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>福容徠旅高雄</t>
+          <t>福容大飯店 墾丁</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>高雄市前金區永恆街3號6-14樓</t>
+          <t>屏東縣恆春鎮船帆路1000號</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>(07)2156688#6309</t>
+          <t>(08)8856969#340</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2029/03/17</t>
+          <t>2028/05/28</t>
         </is>
       </c>
     </row>
@@ -8872,32 +8872,32 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>福華大飯店</t>
+          <t>福容大飯店 麗寶樂園</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>臺北市大安區仁愛路三段160號</t>
+          <t>臺中市后里區福容路88號</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>(02)27002323#2411</t>
+          <t>(04)25571366#8343</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2029/03/19</t>
         </is>
       </c>
     </row>
@@ -8909,22 +8909,22 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>福華石門水庫渡假飯店</t>
+          <t>福容大飯店花蓮</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>桃園市龍潭區民富街176號</t>
+          <t>花蓮縣花蓮市民生路51號</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>(03)4714888</t>
+          <t>(03)8239988#7507</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8946,32 +8946,32 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>福華國際文教會館</t>
+          <t>福容徠旅 水里</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>臺北市大安區新生南路3段30號(住宿棟1樓及5樓至14樓)</t>
+          <t>南投縣水里鄉東三街51號1樓至6樓</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>(02)77122323#2340</t>
+          <t>(049)2771888#5560</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2027/12/11</t>
+          <t>2029/07/09</t>
         </is>
       </c>
     </row>
@@ -8983,32 +8983,32 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>福爾摩沙遊艇酒店</t>
+          <t>福容徠旅林口</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>臺南市安平區王城里13鄰安平路988號1至10樓</t>
+          <t>桃園市龜山區文二一街68號</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>(06)3911313</t>
+          <t>(03)3277388#300</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2027/02/27</t>
+          <t>2027/12/03</t>
         </is>
       </c>
     </row>
@@ -9020,32 +9020,32 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>綠意山莊民宿</t>
+          <t>福容徠旅高雄</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之5號</t>
+          <t>高雄市前金區永恆街3號6-14樓</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>(037)747711#9</t>
+          <t>(07)2156688#6309</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2028/09/08</t>
+          <t>2029/03/17</t>
         </is>
       </c>
     </row>
@@ -9057,32 +9057,32 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>綠藤輕旅</t>
+          <t>福華大飯店</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>桃園市大園區中山南路二段673號</t>
+          <t>臺北市大安區仁愛路三段160號</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>(03)2873043</t>
+          <t>(02)27002323#2411</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2026/10/26</t>
         </is>
       </c>
     </row>
@@ -9094,32 +9094,32 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>維悅酒店</t>
+          <t>福華石門水庫渡假飯店</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>臺南市安平區慶平路539號 1至5樓及地下1樓</t>
+          <t>桃園市龍潭區民富街176號</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>(06)2950888#1125</t>
+          <t>(03)4714888</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2027/09/01</t>
+          <t>2027/11/10</t>
         </is>
       </c>
     </row>
@@ -9131,32 +9131,32 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>臺中逢甲智選假日酒店</t>
+          <t>福華國際文教會館</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>臺中市西屯區福星北三街33巷28號</t>
+          <t>臺北市大安區新生南路3段30號(住宿棟1樓及5樓至14樓)</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>(04)27083911#6101</t>
+          <t>(02)77122323#2340</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/12/11</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>臺邦商旅</t>
+          <t>福爾摩沙遊艇酒店</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -9178,22 +9178,22 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>臺南市安平區永華二街199號</t>
+          <t>臺南市安平區王城里13鄰安平路988號1至10樓</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>(06)2931800#8603</t>
+          <t>(06)3911313</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/02/27</t>
         </is>
       </c>
     </row>
@@ -9205,22 +9205,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>遠雄悅來大飯店</t>
+          <t>綠意山莊民宿</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>花蓮縣壽豐鄉鹽寮村山嶺18號</t>
+          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之5號</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>(03)8123900#8266</t>
+          <t>(037)747711#9</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2028/12/29</t>
+          <t>2028/09/08</t>
         </is>
       </c>
     </row>
@@ -9242,22 +9242,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>鳳山79 背包客</t>
+          <t>綠藤輕旅</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>高雄市鳳山區黃埔新村東一巷79號</t>
+          <t>桃園市大園區中山南路二段673號</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>(07)5524545</t>
+          <t>(03)2873043</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2028/12/03</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -9279,32 +9279,32 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>劍湖山渡假大飯店</t>
+          <t>維悅酒店</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>雲林縣古坑鄉永光村大湖口67-8號</t>
+          <t>臺南市安平區慶平路539號 1至5樓及地下1樓</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>(05)5829900#7214</t>
+          <t>(06)2950888#1125</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2027/06/03</t>
+          <t>2027/09/01</t>
         </is>
       </c>
     </row>
@@ -9316,22 +9316,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>澄悅商旅</t>
+          <t>臺中逢甲智選假日酒店</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮埔崙里中正路510巷1號</t>
+          <t>臺中市西屯區福星北三街33巷28號</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>(04)7785727</t>
+          <t>(04)27083911#6101</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2029/09/07</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9353,32 +9353,32 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>澎湖福朋喜來登酒店</t>
+          <t>臺邦商旅</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市新店路197號</t>
+          <t>臺南市安平區永華二街199號</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>(06)9279955#3701</t>
+          <t>(06)2931800#8603</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2028/05/27</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9390,32 +9390,32 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>澎澄飯店</t>
+          <t>遠雄悅來大飯店</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市同和路168號</t>
+          <t>花蓮縣壽豐鄉鹽寮村山嶺18號</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>(06)9235678#2103</t>
+          <t>(03)8123900#8266</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2029/08/03</t>
+          <t>2028/12/29</t>
         </is>
       </c>
     </row>
@@ -9427,32 +9427,32 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>緻麗伯爵酒店</t>
+          <t>鳳山79 背包客</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>雲林縣斗六市中山路6號</t>
+          <t>高雄市鳳山區黃埔新村東一巷79號</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>(05)5341666#3</t>
+          <t>(07)5524545</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2029/02/10</t>
+          <t>2028/12/03</t>
         </is>
       </c>
     </row>
@@ -9464,32 +9464,32 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>緣羊軒民宿</t>
+          <t>劍湖山渡假大飯店</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>臺東縣台東市南一街96號</t>
+          <t>雲林縣古坑鄉永光村大湖口67-8號</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>089326400</t>
+          <t>(05)5829900#7214</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026/12/05</t>
+          <t>2027/06/03</t>
         </is>
       </c>
     </row>
@@ -9501,32 +9501,32 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺北</t>
+          <t>澄悅商旅</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
+          <t>彰化縣鹿港鎮埔崙里中正路510巷1號</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>(02)29583000#7701</t>
+          <t>(04)7785727</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2028/03/31</t>
+          <t>2029/09/07</t>
         </is>
       </c>
     </row>
@@ -9538,32 +9538,32 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺東</t>
+          <t>澎湖福朋喜來登酒店</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>臺東縣台東市新站路260號</t>
+          <t>澎湖縣馬公市新店路197號</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>(089)231188#7187</t>
+          <t>(06)9279955#3701</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2027/12/05</t>
+          <t>2028/05/27</t>
         </is>
       </c>
     </row>
@@ -9575,32 +9575,32 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>墾丁夏都沙灘酒店</t>
+          <t>澎澄飯店</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁路451號</t>
+          <t>澎湖縣馬公市同和路168號</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>(0910)371823</t>
+          <t>(06)9235678#2103</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2028/03/09</t>
+          <t>2029/08/03</t>
         </is>
       </c>
     </row>
@@ -9612,32 +9612,32 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>墾丁福華渡假飯店</t>
+          <t>緻麗伯爵酒店</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
+          <t>雲林縣斗六市中山路6號</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>(08)8862324#2701</t>
+          <t>(05)5341666#3</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2029/04/12</t>
+          <t>2029/02/10</t>
         </is>
       </c>
     </row>
@@ -9649,22 +9649,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>橘子民宿</t>
+          <t>緣羊軒民宿</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
+          <t>臺東縣台東市南一街96號</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>(0972)092658</t>
+          <t>089326400</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2027/11/06</t>
+          <t>2026/12/05</t>
         </is>
       </c>
     </row>
@@ -9686,22 +9686,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>翰品酒店 高雄</t>
+          <t>趣淘漫旅-臺北</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區大仁路43號</t>
+          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>(07)5614688#3110</t>
+          <t>(02)29583000#7701</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2027/02/16</t>
+          <t>2028/03/31</t>
         </is>
       </c>
     </row>
@@ -9723,32 +9723,32 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>礁溪老爺酒店</t>
+          <t>趣淘漫旅-臺東</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
+          <t>臺東縣台東市新站路260號</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>(03)9885211#8006</t>
+          <t>(089)231188#7187</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2028/08/24</t>
+          <t>2027/12/05</t>
         </is>
       </c>
     </row>
@@ -9760,32 +9760,32 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>礁溪寒沐酒店</t>
+          <t>墾丁夏都沙灘酒店</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
+          <t>屏東縣恆春鎮墾丁路451號</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>(03)9058007</t>
+          <t>(0910)371823</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2028/03/09</t>
         </is>
       </c>
     </row>
@@ -9797,32 +9797,32 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>禧榕軒大飯店</t>
+          <t>墾丁福華渡假飯店</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>臺南市北區成功路28號</t>
+          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>(06)2222788#2203</t>
+          <t>(08)8862324#2701</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2029/05/10</t>
+          <t>2029/04/12</t>
         </is>
       </c>
     </row>
@@ -9834,22 +9834,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>薆悅酒店野柳渡假館一館</t>
+          <t>橘子民宿</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>新北市萬里區野柳里港東路162號之2</t>
+          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>(02)77035770#623</t>
+          <t>(0972)092658</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2027/11/06</t>
         </is>
       </c>
     </row>
@@ -9871,32 +9871,32 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>藍水輕旅</t>
+          <t>翰品酒店 高雄</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>桃園市大園區高鐵南路一段126號</t>
+          <t>高雄市鹽埕區大仁路43號</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>(03)2871855</t>
+          <t>(07)5614688#3110</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2027/02/16</t>
         </is>
       </c>
     </row>
@@ -9908,32 +9908,32 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>關子嶺富野溫泉會館</t>
+          <t>礁溪老爺酒店</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>臺南市白河區關子嶺28號</t>
+          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>(06)6822288</t>
+          <t>(03)9885211#8006</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2029/01/07</t>
+          <t>2028/08/24</t>
         </is>
       </c>
     </row>
@@ -9945,32 +9945,32 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>麗格休閒飯店</t>
+          <t>礁溪寒沐酒店</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市商校街258.260.262號</t>
+          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>(03)8349922</t>
+          <t>(03)9058007</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -9982,32 +9982,32 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>麗軒國際飯店</t>
+          <t>禧榕軒大飯店</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市中美路99之1號</t>
+          <t>臺南市北區成功路28號</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>(03)8246898</t>
+          <t>(06)2222788#2203</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2029/05/10</t>
         </is>
       </c>
     </row>
@@ -10019,22 +10019,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>麗翔大飯店</t>
+          <t>薆悅酒店野柳渡假館一館</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
+          <t>新北市萬里區野柳里港東路162號之2</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>(03)8323737</t>
+          <t>(02)77035770#623</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2028/01/12</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -10056,22 +10056,22 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>讀好民宿</t>
+          <t>藍水輕旅</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
+          <t>桃園市大園區高鐵南路一段126號</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>(0920)023139</t>
+          <t>(03)2871855</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2026/11/23</t>
         </is>
       </c>
     </row>
@@ -10093,32 +10093,32 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>觀霧山莊</t>
+          <t>關子嶺富野溫泉會館</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
+          <t>臺南市白河區關子嶺28號</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>(03)3343818</t>
+          <t>(06)6822288</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2029/01/22</t>
+          <t>2029/01/07</t>
         </is>
       </c>
     </row>
@@ -10130,32 +10130,32 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>綉溪安平</t>
+          <t>麗格休閒飯店</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+          <t>花蓮縣花蓮市商校街258.260.262號</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>(06)3910988#3111</t>
+          <t>(03)8349922</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2028/10/12</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -10167,30 +10167,215 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
+          <t>麗軒國際飯店</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>花蓮縣</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>花蓮縣花蓮市中美路99之1號</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>(03)8246898</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>2029/01/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>麗翔大飯店</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>花蓮縣</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>(03)8323737</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>2028/01/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>讀好民宿</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>宜蘭縣</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>(0920)023139</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>2029/01/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>觀霧山莊</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>苗栗縣</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>(03)3343818</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>銀級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>2029/01/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>綉溪安平</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>臺南市</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>(06)3910988#3111</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>銀級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>2028/10/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
           <t>鐡馬騎跡</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
+      <c r="C269" t="inlineStr">
         <is>
           <t>屏東縣</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D269" t="inlineStr">
         <is>
           <t>屏東縣東港鎮新學路50號</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="E269" t="inlineStr">
         <is>
           <t>(0952)848898</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>銅級環保旅宿</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
         <is>
           <t>2029/01/18</t>
         </is>

--- a/環保旅宿_Selenium結果.xlsx
+++ b/環保旅宿_Selenium結果.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G269"/>
+  <dimension ref="A1:G271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4876,32 +4876,32 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>夏堤民宿</t>
+          <t>香格里拉冬山河旅館</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>屏東縣琉球鄉上福村2鄰杉板路51巷2號</t>
+          <t>宜蘭縣五結鄉協和村公園二路15號</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(08)8611155</t>
+          <t>(03)9605388#212</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2029/02/25</t>
+          <t>2029/10/06</t>
         </is>
       </c>
     </row>
@@ -4913,22 +4913,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>夏優旅居</t>
+          <t>夏堤民宿</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區新興街67號</t>
+          <t>屏東縣琉球鄉上福村2鄰杉板路51巷2號</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(07)5328885</t>
+          <t>(08)8611155</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2028/12/11</t>
+          <t>2029/02/25</t>
         </is>
       </c>
     </row>
@@ -4950,22 +4950,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>娜路彎花園酒店</t>
+          <t>夏優旅居</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>臺東縣台東市新興路77號</t>
+          <t>高雄市鹽埕區新興街67號</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(089)231111</t>
+          <t>(07)5328885</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2028/12/11</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>娜路彎會館</t>
+          <t>娜路彎花園酒店</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>臺東縣台東市中興路2段385號</t>
+          <t>臺東縣台東市新興路77號</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>(089)235500</t>
+          <t>(089)231111</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>娜路彎銀河行館</t>
+          <t>娜路彎會館</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>臺東縣台東市豐興路88號</t>
+          <t>臺東縣台東市中興路2段385號</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(089)383366</t>
+          <t>(089)235500</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2028/09/16</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>娜路彎銀河酒店</t>
+          <t>娜路彎銀河行館</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5071,22 +5071,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>臺東縣台東市豐興路66號</t>
+          <t>臺東縣台東市豐興路88號</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(089)225000#8263</t>
+          <t>(089)383366</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2028/09/03</t>
+          <t>2028/09/16</t>
         </is>
       </c>
     </row>
@@ -5098,32 +5098,32 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>悅徠舘</t>
+          <t>娜路彎銀河酒店</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>桃園市龜山區興華三街18號2樓之1</t>
+          <t>臺東縣台東市豐興路66號</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(03)3280177</t>
+          <t>(089)225000#8263</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2028/09/03</t>
         </is>
       </c>
     </row>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>悅豪大飯店</t>
+          <t>悅徠舘</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>新竹市東區復興路22號</t>
+          <t>桃園市龜山區興華三街18號2樓之1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(03)5267890</t>
+          <t>(03)3280177</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2029/07/20</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -5172,22 +5172,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>挪威森林頂級汽車旅館</t>
+          <t>悅豪大飯店</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>新北市板橋區和平路14巷3號</t>
+          <t>新竹市東區復興路22號</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(02)29562211</t>
+          <t>(03)5267890</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2029/09/30</t>
+          <t>2029/07/20</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>旅行邦尼</t>
+          <t>挪威森林頂級汽車旅館</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>新北市淡水區中山路87巷7號</t>
+          <t>新北市板橋區和平路14巷3號</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>(09)28824850</t>
+          <t>(02)29562211</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2029/01/05</t>
+          <t>2029/09/30</t>
         </is>
       </c>
     </row>
@@ -5246,22 +5246,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>旅悅國際青年旅館</t>
+          <t>旅行邦尼</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>高雄市前鎮區三多三路211號3樓及4樓</t>
+          <t>新北市淡水區中山路87巷7號</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(07)3359006</t>
+          <t>(09)28824850</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2027/10/13</t>
+          <t>2029/01/05</t>
         </is>
       </c>
     </row>
@@ -5283,32 +5283,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>桃園大溪笠復威斯汀度假酒店</t>
+          <t>旅悅國際青年旅館</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>桃園市大溪區日新路166號</t>
+          <t>高雄市前鎮區三多三路211號3樓及4樓</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(03)2725035</t>
+          <t>(07)3359006</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2027/10/13</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>桃園喜來登酒店</t>
+          <t>桃園大溪笠復威斯汀度假酒店</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>桃園市大園區大觀路777號</t>
+          <t>桃園市大溪區日新路166號</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>(03)3850000#2605</t>
+          <t>(03)2725035</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026/10/29</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -5357,22 +5357,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>泰安觀止溫泉會館</t>
+          <t>桃園喜來登酒店</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>苗栗縣泰安鄉錦水村圓墩58-7號</t>
+          <t>桃園市大園區大觀路777號</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>(037)941951#527</t>
+          <t>(03)3850000#2605</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2028/06/25</t>
+          <t>2026/10/29</t>
         </is>
       </c>
     </row>
@@ -5394,32 +5394,32 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>海福花園飯店</t>
+          <t>泰安觀止溫泉會館</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>金門縣金沙鎮高陽路1號</t>
+          <t>苗栗縣泰安鄉錦水村圓墩58-7號</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(082)353888</t>
+          <t>(037)941951#527</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2029/09/01</t>
+          <t>2028/06/25</t>
         </is>
       </c>
     </row>
@@ -5431,22 +5431,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>海霞您的家</t>
+          <t>海福花園飯店</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>新北市貢寮區仁里里14鄰仁愛路38號</t>
+          <t>金門縣金沙鎮高陽路1號</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>(09)35204895</t>
+          <t>(082)353888</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2029/09/01</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>海灣假日酒店</t>
+          <t>海霞您的家</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>新北市深坑區北深路3段265號</t>
+          <t>新北市貢寮區仁里里14鄰仁愛路38號</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>(02)77035880</t>
+          <t>(09)35204895</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2028/12/17</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>神隱國度民宿</t>
+          <t>海灣假日酒店</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5515,22 +5515,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>新北市瑞芳區崙頂路90號</t>
+          <t>新北市深坑區北深路3段265號</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>(09)05788650</t>
+          <t>(02)77035880</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2028/12/17</t>
         </is>
       </c>
     </row>
@@ -5542,32 +5542,32 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>秧悦美地度假酒店</t>
+          <t>神隱國度民宿</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>花蓮縣吉安鄉干城村干城二街95-9號</t>
+          <t>新北市瑞芳區崙頂路90號</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>(03)8129168#2701</t>
+          <t>(09)05788650</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -5579,32 +5579,32 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>秘境41</t>
+          <t>秧悦美地度假酒店</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>桃園市大溪區興和里中央路41號</t>
+          <t>花蓮縣吉安鄉干城村干城二街95-9號</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>(03)3887111</t>
+          <t>(03)8129168#2701</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2027/12/10</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -5616,22 +5616,22 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>秘境民宿</t>
+          <t>秘境41</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>屏東縣東港鎮屏東縣東港鎮水源路223號(新和段737-3地號)</t>
+          <t>桃園市大溪區興和里中央路41號</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>(08)8333345</t>
+          <t>(03)3887111</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2029/01/18</t>
+          <t>2027/12/10</t>
         </is>
       </c>
     </row>
@@ -5653,32 +5653,32 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>高雄中央公園英迪格酒店</t>
+          <t>秘境民宿</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>高雄市新興區中山一路4號</t>
+          <t>屏東縣東港鎮屏東縣東港鎮水源路223號(新和段737-3地號)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(07)2721555#301</t>
+          <t>(08)8333345</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2029/01/18</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>高雄商旅</t>
+          <t>高雄中央公園英迪格酒店</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5700,22 +5700,22 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>高雄市新興區民族二路33號1、4~10樓；37號1、3~10樓</t>
+          <t>高雄市新興區中山一路4號</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(09)19546590</t>
+          <t>(07)2721555#301</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>高雄富野渡假酒店</t>
+          <t>高雄商旅</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5737,12 +5737,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>高雄市前鎮區瑞田街99號</t>
+          <t>高雄市新興區民族二路33號1、4~10樓；37號1、3~10樓</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(07)8215299#7102</t>
+          <t>(09)19546590</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2029/02/09</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>高雄圓山大飯店</t>
+          <t>高雄富野渡假酒店</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5774,22 +5774,22 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>高雄市鳥松區圓山路2號</t>
+          <t>高雄市前鎮區瑞田街99號</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(07)3706007#519</t>
+          <t>(07)8215299#7102</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2029/02/09</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>高雄福華大飯店</t>
+          <t>高雄圓山大飯店</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>高雄市新興區七賢一路311號</t>
+          <t>高雄市鳥松區圓山路2號</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(07)2307737</t>
+          <t>(07)3706007#519</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026/11/16</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>國聯大飯店</t>
+          <t>高雄福華大飯店</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>臺北市大安區光復南路200號</t>
+          <t>高雄市新興區七賢一路311號</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>(02)27731515#184</t>
+          <t>(07)2307737</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2029/09/15</t>
+          <t>2026/11/16</t>
         </is>
       </c>
     </row>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>基拉耳景觀民宿</t>
+          <t>國聯大飯店</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>桃園市復興區溪口路16巷29號</t>
+          <t>臺北市大安區光復南路200號</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>(02)23965188#594</t>
+          <t>(02)27731515#184</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2028/06/15</t>
+          <t>2029/09/15</t>
         </is>
       </c>
     </row>
@@ -5912,32 +5912,32 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>將捷金鬱金香酒店</t>
+          <t>基拉耳景觀民宿</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>新北市淡水區中正路1段2之1號(A區地上3至6層、B區地上1至5層、C區地下3層至地上3層)</t>
+          <t>桃園市復興區溪口路16巷29號</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>(02)26218555#2913</t>
+          <t>(02)23965188#594</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2027/04/14</t>
+          <t>2028/06/15</t>
         </is>
       </c>
     </row>
@@ -5949,32 +5949,32 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>康橋商旅-六合夜市七賢館</t>
+          <t>將捷金鬱金香酒店</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>高雄市新興區同愛街28號1樓、30號</t>
+          <t>新北市淡水區中正路1段2之1號(A區地上3至6層、B區地上1至5層、C區地下3層至地上3層)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(07)288-5588</t>
+          <t>(02)26218555#2913</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2027/04/14</t>
         </is>
       </c>
     </row>
@@ -5986,22 +5986,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>康橋商旅臺南赤崁樓館</t>
+          <t>康橋商旅-六合夜市七賢館</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>臺南市中西區赤崁里民權路二段97號1至8樓</t>
+          <t>高雄市新興區同愛街28號1樓、30號</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>(06)2253377</t>
+          <t>(07)288-5588</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2029/09/02</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>康橋慢旅</t>
+          <t>康橋商旅臺南赤崁樓館</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>臺南市中西區民生路二段416號</t>
+          <t>臺南市中西區赤崁里民權路二段97號1至8樓</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(06)2805566</t>
+          <t>(06)2253377</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>捷絲旅 臺南虎山館</t>
+          <t>康橋慢旅</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6070,22 +6070,22 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>臺南市仁德區成功里5鄰文華路2段300號1~9樓，地下一、二樓</t>
+          <t>臺南市中西區民生路二段416號</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(06)2662218#8321</t>
+          <t>(06)2805566</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2028/02/13</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -6097,22 +6097,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>捷絲旅臺北三重館</t>
+          <t>捷絲旅 臺南虎山館</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>新北市三重區三和路四段107-1號</t>
+          <t>臺南市仁德區成功里5鄰文華路2段300號1~9樓，地下一、二樓</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(02)22806111#8304</t>
+          <t>(06)2662218#8321</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2028/10/12</t>
+          <t>2028/02/13</t>
         </is>
       </c>
     </row>
@@ -6134,32 +6134,32 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>捷絲旅西門町店</t>
+          <t>捷絲旅臺北三重館</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路一段41號5樓至9樓</t>
+          <t>新北市三重區三和路四段107-1號</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(02)25215000</t>
+          <t>(02)22806111#8304</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2027/05/12</t>
+          <t>2028/10/12</t>
         </is>
       </c>
     </row>
@@ -6171,32 +6171,32 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>捷絲旅花蓮中正館</t>
+          <t>捷絲旅西門町店</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市主睦里14鄰中正路396號</t>
+          <t>臺北市中正區中華路一段41號5樓至9樓</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(03)8900069#8104</t>
+          <t>(02)25215000</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2027/05/12</t>
         </is>
       </c>
     </row>
@@ -6208,22 +6208,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>捷絲旅高雄中正館</t>
+          <t>捷絲旅花蓮中正館</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>高雄市苓雅區中正一路134號</t>
+          <t>花蓮縣花蓮市主睦里14鄰中正路396號</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>(07)9733587#8104</t>
+          <t>(03)8900069#8104</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>捷絲旅高雄站前館</t>
+          <t>捷絲旅高雄中正館</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>高雄市新興區中山一路280號1至14樓</t>
+          <t>高雄市苓雅區中正一路134號</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2028/09/29</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -6282,22 +6282,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>捷絲旅臺大尊賢館</t>
+          <t>捷絲旅高雄站前館</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>臺北市大安區羅斯福路四段83號1-10樓</t>
+          <t>高雄市新興區中山一路280號1至14樓</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>(02)77355088</t>
+          <t>(07)9733587#8104</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/09/29</t>
         </is>
       </c>
     </row>
@@ -6319,32 +6319,32 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>捷絲旅礁溪館</t>
+          <t>捷絲旅臺大尊賢館</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉德陽路24巷8號、10號</t>
+          <t>臺北市大安區羅斯福路四段83號1-10樓</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>(03)9102000#8104</t>
+          <t>(02)77355088</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2027/01/07</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6356,32 +6356,32 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>清新溫泉飯店</t>
+          <t>捷絲旅礁溪館</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>臺中市烏日區溫泉路2號</t>
+          <t>宜蘭縣礁溪鄉德陽路24巷8號、10號</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>(04)23831088#7602</t>
+          <t>(03)9102000#8104</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2027/01/07</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>統一谷關渡假村</t>
+          <t>清新溫泉飯店</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6403,22 +6403,22 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>臺中市和平區博愛里東關路一段188號</t>
+          <t>臺中市烏日區溫泉路2號</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(04)25950000</t>
+          <t>(04)23831088#7602</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2028/01/06</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -6430,22 +6430,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>統一渡假村</t>
+          <t>統一谷關渡假村</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>新竹縣關西鎮金山里34號</t>
+          <t>臺中市和平區博愛里東關路一段188號</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(03)5478888</t>
+          <t>(04)25950000</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2027/12/20</t>
+          <t>2028/01/06</t>
         </is>
       </c>
     </row>
@@ -6467,22 +6467,22 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>鹿港澄悅酒店</t>
+          <t>統一渡假村</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮中正路598號1樓、5至8樓</t>
+          <t>新竹縣關西鎮金山里34號</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(04)7785727</t>
+          <t>(03)5478888</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2029/03/02</t>
+          <t>2027/12/20</t>
         </is>
       </c>
     </row>
@@ -6504,32 +6504,32 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>傑仕堡有氧酒店</t>
+          <t>鹿港澄悅酒店</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>新北市板橋區縣民大道2段275號、275號2至17樓、277號2樓</t>
+          <t>彰化縣鹿港鎮中正路598號1樓、5至8樓</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(02)77273000#54083</t>
+          <t>(04)7785727</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026/10/16</t>
+          <t>2029/03/02</t>
         </is>
       </c>
     </row>
@@ -6541,32 +6541,32 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>凱旋酒店</t>
+          <t>傑仕堡有氧酒店</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>臺北市內湖區江南街55號3樓至9樓</t>
+          <t>新北市板橋區縣民大道2段275號、275號2至17樓、277號2樓</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(02)87527888#6203</t>
+          <t>(02)77273000#54083</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026/12/10</t>
+          <t>2026/10/16</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>凱達大飯店</t>
+          <t>凱旋酒店</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6588,22 +6588,22 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>臺北市萬華區艋舺大道167號1-26樓</t>
+          <t>臺北市內湖區江南街55號3樓至9樓</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>(02)23836789#6321</t>
+          <t>(02)87527888#6203</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2027/06/02</t>
+          <t>2026/12/10</t>
         </is>
       </c>
     </row>
@@ -6615,32 +6615,32 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>凱撒大飯店</t>
+          <t>凱達大飯店</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁路6號</t>
+          <t>臺北市萬華區艋舺大道167號1-26樓</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>(08)8861888</t>
+          <t>(02)23836789#6321</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2028/09/16</t>
+          <t>2027/06/02</t>
         </is>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>勝利127民宿</t>
+          <t>凱撒大飯店</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6662,22 +6662,22 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>屏東縣屏東市勝利路127號</t>
+          <t>屏東縣恆春鎮墾丁路6號</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>(08)7320099</t>
+          <t>(08)8861888</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026/12/14</t>
+          <t>2028/09/16</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>勝利131民宿</t>
+          <t>勝利127民宿</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>屏東縣屏東市勝利路131號</t>
+          <t>屏東縣屏東市勝利路127號</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6726,32 +6726,32 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>寒居酒店</t>
+          <t>勝利131民宿</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>臺北市中山區松江路116號1樓至9樓</t>
+          <t>屏東縣屏東市勝利路131號</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>(02)66008000#8886</t>
+          <t>(08)7320099</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2028/07/17</t>
+          <t>2026/12/14</t>
         </is>
       </c>
     </row>
@@ -6763,32 +6763,32 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>寒軒國際大飯店</t>
+          <t>寒居酒店</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>高雄市苓雅區四維三路三十三號</t>
+          <t>臺北市中山區松江路116號1樓至9樓</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(0980)556224</t>
+          <t>(02)66008000#8886</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2028/12/11</t>
+          <t>2028/07/17</t>
         </is>
       </c>
     </row>
@@ -6800,22 +6800,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>富光大旅社</t>
+          <t>寒軒國際大飯店</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公園路19-7號</t>
+          <t>高雄市苓雅區四維三路三十三號</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(08)7345656</t>
+          <t>(0980)556224</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2028/05/28</t>
+          <t>2028/12/11</t>
         </is>
       </c>
     </row>
@@ -6837,32 +6837,32 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>富信大飯店</t>
+          <t>富光大旅社</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>新北市汐止區大同路一段152號</t>
+          <t>屏東縣屏東市公園路19-7號</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(02)26416422#5112</t>
+          <t>(08)7345656</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2028/03/13</t>
+          <t>2028/05/28</t>
         </is>
       </c>
     </row>
@@ -6874,32 +6874,32 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>富翔大飯店</t>
+          <t>富信大飯店</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>宜蘭縣宜蘭市校舍路19號</t>
+          <t>新北市汐止區大同路一段152號</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>(03)9388386</t>
+          <t>(02)26416422#5112</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2029/09/28</t>
+          <t>2028/03/13</t>
         </is>
       </c>
     </row>
@@ -6911,22 +6911,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>尊爵大飯店</t>
+          <t>富翔大飯店</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>桃園市桃園區莊敬路一段300號</t>
+          <t>宜蘭縣宜蘭市校舍路19號</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>(03)3169090#8502</t>
+          <t>(03)9388386</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026/12/21</t>
+          <t>2029/09/28</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>尊爵天際大飯店</t>
+          <t>尊爵大飯店</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>桃園市蘆竹區南崁路一段108號</t>
+          <t>桃園市桃園區莊敬路一段300號</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>(03)2228100#6081</t>
+          <t>(03)3169090#8502</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2028/08/31</t>
+          <t>2026/12/21</t>
         </is>
       </c>
     </row>
@@ -6985,32 +6985,32 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>惠來谷關溫泉會館</t>
+          <t>尊爵天際大飯店</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>臺中市和平區東關路一段溫泉巷十號</t>
+          <t>桃園市蘆竹區南崁路一段108號</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>(04)25951998#621</t>
+          <t>(03)2228100#6081</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2029/08/13</t>
+          <t>2028/08/31</t>
         </is>
       </c>
     </row>
@@ -7022,32 +7022,32 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>提米好旅</t>
+          <t>惠來谷關溫泉會館</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>彰化縣彰化市成功路277號</t>
+          <t>臺中市和平區東關路一段溫泉巷十號</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>(04)7061086#9</t>
+          <t>(04)25951998#621</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>2029/08/13</t>
         </is>
       </c>
     </row>
@@ -7059,32 +7059,32 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>揚昊民宿</t>
+          <t>提米好旅</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之6號</t>
+          <t>彰化縣彰化市成功路277號</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>(037)747711#9</t>
+          <t>(04)7061086#9</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2028/09/08</t>
+          <t>2027/11/27</t>
         </is>
       </c>
     </row>
@@ -7096,22 +7096,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>晶泉丰旅</t>
+          <t>揚昊民宿</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉溫泉路67號2至10樓</t>
+          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之6號</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>(03)9100000#6105</t>
+          <t>(037)747711#9</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2027/05/22</t>
+          <t>2028/09/08</t>
         </is>
       </c>
     </row>
@@ -7133,22 +7133,22 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>智醫康寓</t>
+          <t>晶泉丰旅</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>桃園市桃園區民生路107號1-3樓及7-20樓</t>
+          <t>宜蘭縣礁溪鄉溫泉路67號2至10樓</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>(03)3362575</t>
+          <t>(03)9100000#6105</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026/10/30</t>
+          <t>2027/05/22</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>渴望會館</t>
+          <t>智醫康寓</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7180,22 +7180,22 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>桃園市龍潭區渴望路428號3-5樓</t>
+          <t>桃園市桃園區民生路107號1-3樓及7-20樓</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>(03)4072999#7110</t>
+          <t>(03)3362575</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2026/10/30</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>然一酒店</t>
+          <t>渴望會館</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>高雄市前鎮區中山二路199號</t>
+          <t>桃園市龍潭區渴望路428號3-5樓</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>(07)9730186#1666</t>
+          <t>(03)4072999#7110</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2027/06/03</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -7244,32 +7244,32 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>發現號特色民宿</t>
+          <t>然一酒店</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>屏東縣林邊鄉崎峰村裕後路90號</t>
+          <t>高雄市前鎮區中山二路199號</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>(08)8750300</t>
+          <t>(07)9730186#1666</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2027/06/03</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>華泰瑞苑</t>
+          <t>發現號特色民宿</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -7291,22 +7291,22 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮公園路101號</t>
+          <t>屏東縣林邊鄉崎峰村裕後路90號</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>(08)8863666</t>
+          <t>(08)8750300</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2027/06/21</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -7318,32 +7318,32 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>貳十二度行旅</t>
+          <t>華泰瑞苑</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>宜蘭縣蘇澳鎮信義路177號</t>
+          <t>屏東縣恆春鎮公園路101號</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>(03)9901888</t>
+          <t>(08)8863666</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2029/05/24</t>
+          <t>2027/06/21</t>
         </is>
       </c>
     </row>
@@ -7355,22 +7355,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>陽明山天籟渡假酒店</t>
+          <t>華園大飯店草衙館</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>新北市金山區名流路1之6號、1之7號、1之9號、1之9號5樓及1之9號5樓之1至之8</t>
+          <t>高雄市前鎮區中安路一號</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>(02)24080400#1700</t>
+          <t>(07)2410123#220</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2029/02/11</t>
+          <t>2029/10/06</t>
         </is>
       </c>
     </row>
@@ -7392,22 +7392,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>雅霖大飯店</t>
+          <t>貳十二度行旅</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市同和路100號</t>
+          <t>宜蘭縣蘇澳鎮信義路177號</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>(06)9261366</t>
+          <t>(03)9901888</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2029/05/24</t>
         </is>
       </c>
     </row>
@@ -7429,32 +7429,32 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>雲品溫泉酒店日月潭</t>
+          <t>陽明山天籟渡假酒店</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉水社村中正路23號</t>
+          <t>新北市金山區名流路1之6號、1之7號、1之9號、1之9號5樓及1之9號5樓之1至之8</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>(049)2212959</t>
+          <t>(02)24080400#1700</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2029/05/05</t>
+          <t>2029/02/11</t>
         </is>
       </c>
     </row>
@@ -7466,22 +7466,22 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>雲頂國際商旅</t>
+          <t>雅霖大飯店</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>臺南市南區大同路二段530號</t>
+          <t>澎湖縣馬公市同和路100號</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>(06)2687766</t>
+          <t>(06)9261366</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2029/02/25</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -7503,32 +7503,32 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>圓山大飯店</t>
+          <t>雲品溫泉酒店日月潭</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路4段1巷1號</t>
+          <t>南投縣魚池鄉水社村中正路23號</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>(02)28861818#1007</t>
+          <t>(049)2212959</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2029/05/05</t>
         </is>
       </c>
     </row>
@@ -7540,22 +7540,22 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>奧斯卡去旅行民宿</t>
+          <t>雲頂國際商旅</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>臺東縣臺東市興安路一段167號</t>
+          <t>臺南市南區大同路二段530號</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>(0910)633944</t>
+          <t>(06)2687766</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2027/01/29</t>
+          <t>2029/02/25</t>
         </is>
       </c>
     </row>
@@ -7577,32 +7577,32 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>奧斯卡民宿</t>
+          <t>圓山大飯店</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>臺東縣台東市興安路1段175號</t>
+          <t>臺北市中山區中山北路4段1巷1號</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>(0965)329000</t>
+          <t>(02)28861818#1007</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2027/01/18</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -7614,22 +7614,22 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>新竹安捷國際酒店</t>
+          <t>奧斯卡去旅行民宿</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>新竹縣竹北市復興三路二段168號14樓-18樓</t>
+          <t>臺東縣臺東市興安路一段167號</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>(03)6209777#660</t>
+          <t>(0910)633944</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2028/07/13</t>
+          <t>2027/01/29</t>
         </is>
       </c>
     </row>
@@ -7651,22 +7651,22 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>新竹老爺大酒店</t>
+          <t>奧斯卡民宿</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>新竹市東區光復路一段227號</t>
+          <t>臺東縣台東市興安路1段175號</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>(03)5631285#204</t>
+          <t>(0965)329000</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2027/01/18</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>新竹喜來登大飯店</t>
+          <t>新竹安捷國際酒店</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7698,22 +7698,22 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>新竹縣竹北市光明六路東一段265號</t>
+          <t>新竹縣竹北市復興三路二段168號14樓-18樓</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>(03)6206126</t>
+          <t>(03)6209777#660</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2028/07/13</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>新竹福華大飯店</t>
+          <t>新竹老爺大酒店</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>新竹市中正路178號</t>
+          <t>新竹市東區光復路一段227號</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>(03)5282323#5303</t>
+          <t>(03)5631285#204</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -7762,32 +7762,32 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>新南一二文創商行</t>
+          <t>新竹喜來登大飯店</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>桃園市大溪區中山路１２號</t>
+          <t>新竹縣竹北市光明六路東一段265號</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>(03)3884466</t>
+          <t>(03)6206126</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2029/02/05</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -7799,32 +7799,32 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>新悦花園酒店</t>
+          <t>新竹福華大飯店</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>嘉義市東區後湖里6鄰保順路69號</t>
+          <t>新竹市中正路178號</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>(05)2777266#5801</t>
+          <t>(03)5282323#5303</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2027/04/07</t>
+          <t>2026/10/26</t>
         </is>
       </c>
     </row>
@@ -7836,32 +7836,32 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>溪頭福華渡假飯店-溪頭漢光樓</t>
+          <t>新南一二文創商行</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>南投縣鹿谷鄉森林巷11、12號</t>
+          <t>桃園市大溪區中山路１２號</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>(049)2612588#3005</t>
+          <t>(03)3884466</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2028/12/01</t>
+          <t>2029/02/05</t>
         </is>
       </c>
     </row>
@@ -7873,32 +7873,32 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>溪邊小築民宿</t>
+          <t>新悦花園酒店</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>新北市瑞芳區祈堂路133號</t>
+          <t>嘉義市東區後湖里6鄰保順路69號</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>(02)24961191</t>
+          <t>(05)2777266#5801</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2029/06/21</t>
+          <t>2027/04/07</t>
         </is>
       </c>
     </row>
@@ -7910,32 +7910,32 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>煙波大飯店臺南館</t>
+          <t>溪頭福華渡假飯店-溪頭漢光樓</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>臺南市中西區永福路1段269號1-12樓及地下一層至三層</t>
+          <t>南投縣鹿谷鄉森林巷11、12號</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>(06)2156000#1171</t>
+          <t>(049)2612588#3005</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2029/06/09</t>
+          <t>2028/12/01</t>
         </is>
       </c>
     </row>
@@ -7947,32 +7947,32 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>煙波大飯店宜蘭館</t>
+          <t>溪邊小築民宿</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>宜蘭縣宜蘭市凱旋路135號 、135號2至9樓</t>
+          <t>新北市瑞芳區祈堂路133號</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>(09)9256899#1171</t>
+          <t>(02)24961191</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2029/05/06</t>
+          <t>2029/06/21</t>
         </is>
       </c>
     </row>
@@ -7984,22 +7984,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮太魯閣山闊館</t>
+          <t>煙波大飯店臺南館</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村草林10-7號</t>
+          <t>臺南市中西區永福路1段269號1-12樓及地下一層至三層</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>(03)8612000#1470</t>
+          <t>(06)2156000#1171</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026/11/05</t>
+          <t>2029/06/09</t>
         </is>
       </c>
     </row>
@@ -8021,22 +8021,22 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮太魯閣沁海館</t>
+          <t>煙波大飯店宜蘭館</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村6鄰草林10之6號</t>
+          <t>宜蘭縣宜蘭市凱旋路135號 、135號2至9樓</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>(03)8228835#1174</t>
+          <t>(09)9256899#1171</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2029/04/19</t>
+          <t>2029/05/06</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮館</t>
+          <t>煙波大飯店花蓮太魯閣山闊館</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市民立里1鄰中美路142號</t>
+          <t>花蓮縣新城鄉順安村草林10-7號</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>(03)8228835#1174</t>
+          <t>(03)8612000#1470</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2029/04/19</t>
+          <t>2026/11/05</t>
         </is>
       </c>
     </row>
@@ -8095,22 +8095,22 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>煙波花時間 宜蘭傳藝</t>
+          <t>煙波大飯店花蓮太魯閣沁海館</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉五濱路二段201號</t>
+          <t>花蓮縣新城鄉順安村6鄰草林10之6號</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>(03)9256899#1171</t>
+          <t>(03)8228835#1174</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2027/07/09</t>
+          <t>2029/04/19</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>煙波花時間 花蓮</t>
+          <t>煙波大飯店花蓮館</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村草林10-5號2~6樓</t>
+          <t>花蓮縣花蓮市民立里1鄰中美路142號</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>(03)8612000#1470</t>
+          <t>(03)8228835#1174</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026/11/16</t>
+          <t>2029/04/19</t>
         </is>
       </c>
     </row>
@@ -8169,32 +8169,32 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>瑞穗天合國際觀光酒店</t>
+          <t>煙波花時間 宜蘭傳藝</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>花蓮縣瑞穗鄉溫泉路二段368號</t>
+          <t>宜蘭縣五結鄉五濱路二段201號</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>(03)8876000#3260</t>
+          <t>(03)9256899#1171</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2028/01/19</t>
+          <t>2027/07/09</t>
         </is>
       </c>
     </row>
@@ -8206,32 +8206,32 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>裕元花園酒店</t>
+          <t>煙波花時間 花蓮</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>臺中市西屯區臺灣大道四段610號</t>
+          <t>花蓮縣新城鄉順安村草林10-5號2~6樓</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>(04)24655660#5030</t>
+          <t>(03)8612000#1470</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2027/11/19</t>
+          <t>2026/11/16</t>
         </is>
       </c>
     </row>
@@ -8243,32 +8243,32 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>遇見民宿</t>
+          <t>瑞穗天合國際觀光酒店</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>屏東縣東港鎮水源路221號(新和段737-4地號)</t>
+          <t>花蓮縣瑞穗鄉溫泉路二段368號</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>(08)8333345</t>
+          <t>(03)8876000#3260</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2028/01/19</t>
         </is>
       </c>
     </row>
@@ -8280,32 +8280,32 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>頌華私墅肆區民宿</t>
+          <t>裕元花園酒店</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>澎湖縣湖西鄉許家村6鄰港子尾120之5號</t>
+          <t>臺中市西屯區臺灣大道四段610號</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>(06)9212953</t>
+          <t>(04)24655660#5030</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2029/01/25</t>
+          <t>2027/11/19</t>
         </is>
       </c>
     </row>
@@ -8317,22 +8317,22 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>嘉仕特飯店</t>
+          <t>遇見民宿</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>桃園市桃園區中山路203號</t>
+          <t>屏東縣東港鎮水源路221號(新和段737-4地號)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>(03)3343999</t>
+          <t>(08)8333345</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -8354,32 +8354,32 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>嘉義富野渡假酒店</t>
+          <t>頌華私墅肆區民宿</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>嘉義縣民雄鄉三興村升學一街3、5、7、9、11、13、15、17、19、21、23、25、27號</t>
+          <t>澎湖縣湖西鄉許家村6鄰港子尾120之5號</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>(05)2721688</t>
+          <t>(06)9212953</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2028/08/12</t>
+          <t>2029/01/25</t>
         </is>
       </c>
     </row>
@@ -8391,22 +8391,22 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>嘉義智選假日酒店</t>
+          <t>嘉仕特飯店</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>嘉義市西區中興路69號B2至13層樓</t>
+          <t>桃園市桃園區中山路203號</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>(05)2335899#801</t>
+          <t>(03)3343999</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2027/11/24</t>
+          <t>2027/11/27</t>
         </is>
       </c>
     </row>
@@ -8428,32 +8428,32 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>嘉義福容voco酒店</t>
+          <t>嘉義富野渡假酒店</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>嘉義市西區世賢路一段789號B4-4樓、7樓、16樓-32樓</t>
+          <t>嘉義縣民雄鄉三興村升學一街3、5、7、9、11、13、15、17、19、21、23、25、27號</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>(05)232338971</t>
+          <t>(05)2721688</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2029/06/15</t>
+          <t>2028/08/12</t>
         </is>
       </c>
     </row>
@@ -8465,22 +8465,22 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>夢想森林親子民宿</t>
+          <t>嘉義智選假日酒店</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉三星鄉大德路二段613號</t>
+          <t>嘉義市西區中興路69號B2至13層樓</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>(03)9898113</t>
+          <t>(05)2335899#801</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2027/11/24</t>
         </is>
       </c>
     </row>
@@ -8502,32 +8502,32 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>榮美金鬱金香酒店</t>
+          <t>嘉義福容voco酒店</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>臺南市北區海安路三段50號</t>
+          <t>嘉義市西區世賢路一段789號B4-4樓、7樓、16樓-32樓</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>(06)2200800#6001</t>
+          <t>(05)232338971</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2027/11/04</t>
+          <t>2029/06/15</t>
         </is>
       </c>
     </row>
@@ -8539,22 +8539,22 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>榮興金鬱金香酒店</t>
+          <t>夢想森林親子民宿</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>臺南市中西區民族路二段128號</t>
+          <t>宜蘭縣三星鄉三星鄉大德路二段613號</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>(06)2200800#6006</t>
+          <t>(03)9898113</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2027/11/04</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -8576,32 +8576,32 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>福美民宿</t>
+          <t>榮美金鬱金香酒店</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>臺東縣台東市精誠路241號</t>
+          <t>臺南市北區海安路三段50號</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>(089)328466</t>
+          <t>(06)2200800#6001</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2027/01/09</t>
+          <t>2027/11/04</t>
         </is>
       </c>
     </row>
@@ -8613,32 +8613,32 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>福容大飯店 臺北二館</t>
+          <t>榮興金鬱金香酒店</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>新北市深坑區北深路三段236號</t>
+          <t>臺南市中西區民族路二段128號</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>(02)26620088#186</t>
+          <t>(06)2200800#6006</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2028/01/05</t>
+          <t>2027/11/04</t>
         </is>
       </c>
     </row>
@@ -8650,32 +8650,32 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>福容大飯店 桃園</t>
+          <t>福美民宿</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>桃園市桃園區同安里大興西路一段200號</t>
+          <t>臺東縣台東市精誠路241號</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>(03)3265800#300</t>
+          <t>(089)328466</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2027/12/17</t>
+          <t>2027/01/09</t>
         </is>
       </c>
     </row>
@@ -8687,32 +8687,32 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>福容大飯店 桃園機場捷運 A8</t>
+          <t>福容大飯店 臺北二館</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>桃園市龜山區復興一路2號3樓</t>
+          <t>新北市深坑區北深路三段236號</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>(03)3285688#8770</t>
+          <t>(02)26620088#186</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2027/08/12</t>
+          <t>2028/01/05</t>
         </is>
       </c>
     </row>
@@ -8724,32 +8724,32 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>福容大飯店 高雄</t>
+          <t>福容大飯店 桃園</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區五福四路45號</t>
+          <t>桃園市桃園區同安里大興西路一段200號</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>(07)5317777#7782</t>
+          <t>(03)3265800#300</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2028/08/14</t>
+          <t>2027/12/17</t>
         </is>
       </c>
     </row>
@@ -8761,32 +8761,32 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>福容大飯店 淡水漁人碼頭</t>
+          <t>福容大飯店 桃園機場捷運 A8</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>新北市淡水區觀海路83號</t>
+          <t>桃園市龜山區復興一路2號3樓</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>(02)2805 9958#8178</t>
+          <t>(03)3285688#8770</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2028/11/16</t>
+          <t>2027/08/12</t>
         </is>
       </c>
     </row>
@@ -8798,22 +8798,22 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>福容大飯店　福隆</t>
+          <t>福容大飯店 高雄</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>新北市貢寮區福隆里福隆街41號</t>
+          <t>高雄市鹽埕區五福四路45號</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>(02)24992381</t>
+          <t>(07)5317777#7782</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2028/08/14</t>
         </is>
       </c>
     </row>
@@ -8835,32 +8835,32 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>福容大飯店 墾丁</t>
+          <t>福容大飯店 淡水漁人碼頭</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮船帆路1000號</t>
+          <t>新北市淡水區觀海路83號</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>(08)8856969#340</t>
+          <t>(02)2805 9958#8178</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2028/05/28</t>
+          <t>2028/11/16</t>
         </is>
       </c>
     </row>
@@ -8872,22 +8872,22 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>福容大飯店 麗寶樂園</t>
+          <t>福容大飯店　福隆</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>臺中市后里區福容路88號</t>
+          <t>新北市貢寮區福隆里福隆街41號</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>(04)25571366#8343</t>
+          <t>(02)24992381</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2029/03/19</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -8909,22 +8909,22 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>福容大飯店花蓮</t>
+          <t>福容大飯店 墾丁</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市民生路51號</t>
+          <t>屏東縣恆春鎮船帆路1000號</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>(03)8239988#7507</t>
+          <t>(08)8856969#340</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2027/11/10</t>
+          <t>2028/05/28</t>
         </is>
       </c>
     </row>
@@ -8946,22 +8946,22 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>福容徠旅 水里</t>
+          <t>福容大飯店 麗寶樂園</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>南投縣水里鄉東三街51號1樓至6樓</t>
+          <t>臺中市后里區福容路88號</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>(049)2771888#5560</t>
+          <t>(04)25571366#8343</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2029/07/09</t>
+          <t>2029/03/19</t>
         </is>
       </c>
     </row>
@@ -8983,22 +8983,22 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>福容徠旅林口</t>
+          <t>福容大飯店花蓮</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>桃園市龜山區文二一街68號</t>
+          <t>花蓮縣花蓮市民生路51號</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>(03)3277388#300</t>
+          <t>(03)8239988#7507</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2027/12/03</t>
+          <t>2027/11/10</t>
         </is>
       </c>
     </row>
@@ -9020,22 +9020,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>福容徠旅高雄</t>
+          <t>福容徠旅 水里</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>高雄市前金區永恆街3號6-14樓</t>
+          <t>南投縣水里鄉東三街51號1樓至6樓</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>(07)2156688#6309</t>
+          <t>(049)2771888#5560</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2029/03/17</t>
+          <t>2029/07/09</t>
         </is>
       </c>
     </row>
@@ -9057,22 +9057,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>福華大飯店</t>
+          <t>福容徠旅林口</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>臺北市大安區仁愛路三段160號</t>
+          <t>桃園市龜山區文二一街68號</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>(02)27002323#2411</t>
+          <t>(03)3277388#300</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2027/12/03</t>
         </is>
       </c>
     </row>
@@ -9094,32 +9094,32 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>福華石門水庫渡假飯店</t>
+          <t>福容徠旅高雄</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>桃園市龍潭區民富街176號</t>
+          <t>高雄市前金區永恆街3號6-14樓</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>(03)4714888</t>
+          <t>(07)2156688#6309</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2027/11/10</t>
+          <t>2029/03/17</t>
         </is>
       </c>
     </row>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>福華國際文教會館</t>
+          <t>福華大飯店</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>臺北市大安區新生南路3段30號(住宿棟1樓及5樓至14樓)</t>
+          <t>臺北市大安區仁愛路三段160號</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>(02)77122323#2340</t>
+          <t>(02)27002323#2411</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2027/12/11</t>
+          <t>2026/10/26</t>
         </is>
       </c>
     </row>
@@ -9168,32 +9168,32 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>福爾摩沙遊艇酒店</t>
+          <t>福華石門水庫渡假飯店</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>臺南市安平區王城里13鄰安平路988號1至10樓</t>
+          <t>桃園市龍潭區民富街176號</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>(06)3911313</t>
+          <t>(03)4714888</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2027/02/27</t>
+          <t>2027/11/10</t>
         </is>
       </c>
     </row>
@@ -9205,32 +9205,32 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>綠意山莊民宿</t>
+          <t>福華國際文教會館</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之5號</t>
+          <t>臺北市大安區新生南路3段30號(住宿棟1樓及5樓至14樓)</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>(037)747711#9</t>
+          <t>(02)77122323#2340</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2028/09/08</t>
+          <t>2027/12/11</t>
         </is>
       </c>
     </row>
@@ -9242,22 +9242,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>綠藤輕旅</t>
+          <t>福爾摩沙遊艇酒店</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>桃園市大園區中山南路二段673號</t>
+          <t>臺南市安平區王城里13鄰安平路988號1至10樓</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>(03)2873043</t>
+          <t>(06)3911313</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2027/02/27</t>
         </is>
       </c>
     </row>
@@ -9279,22 +9279,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>維悅酒店</t>
+          <t>綠意山莊民宿</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>臺南市安平區慶平路539號 1至5樓及地下1樓</t>
+          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之5號</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>(06)2950888#1125</t>
+          <t>(037)747711#9</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2027/09/01</t>
+          <t>2028/09/08</t>
         </is>
       </c>
     </row>
@@ -9316,22 +9316,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>臺中逢甲智選假日酒店</t>
+          <t>綠藤輕旅</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>臺中市西屯區福星北三街33巷28號</t>
+          <t>桃園市大園區中山南路二段673號</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>(04)27083911#6101</t>
+          <t>(03)2873043</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -9353,7 +9353,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>臺邦商旅</t>
+          <t>維悅酒店</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9363,22 +9363,22 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>臺南市安平區永華二街199號</t>
+          <t>臺南市安平區慶平路539號 1至5樓及地下1樓</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>(06)2931800#8603</t>
+          <t>(06)2950888#1125</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/09/01</t>
         </is>
       </c>
     </row>
@@ -9390,22 +9390,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>遠雄悅來大飯店</t>
+          <t>臺中逢甲智選假日酒店</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>花蓮縣壽豐鄉鹽寮村山嶺18號</t>
+          <t>臺中市西屯區福星北三街33巷28號</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>(03)8123900#8266</t>
+          <t>(04)27083911#6101</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2028/12/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9427,32 +9427,32 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>鳳山79 背包客</t>
+          <t>臺邦商旅</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>高雄市鳳山區黃埔新村東一巷79號</t>
+          <t>臺南市安平區永華二街199號</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>(07)5524545</t>
+          <t>(06)2931800#8603</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2028/12/03</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9464,32 +9464,32 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>劍湖山渡假大飯店</t>
+          <t>遠雄悅來大飯店</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>雲林縣古坑鄉永光村大湖口67-8號</t>
+          <t>花蓮縣壽豐鄉鹽寮村山嶺18號</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>(05)5829900#7214</t>
+          <t>(03)8123900#8266</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2027/06/03</t>
+          <t>2028/12/29</t>
         </is>
       </c>
     </row>
@@ -9501,22 +9501,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>澄悅商旅</t>
+          <t>鳳山79 背包客</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮埔崙里中正路510巷1號</t>
+          <t>高雄市鳳山區黃埔新村東一巷79號</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>(04)7785727</t>
+          <t>(07)5524545</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2029/09/07</t>
+          <t>2028/12/03</t>
         </is>
       </c>
     </row>
@@ -9538,32 +9538,32 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>澎湖福朋喜來登酒店</t>
+          <t>劍湖山渡假大飯店</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市新店路197號</t>
+          <t>雲林縣古坑鄉永光村大湖口67-8號</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>(06)9279955#3701</t>
+          <t>(05)5829900#7214</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2028/05/27</t>
+          <t>2027/06/03</t>
         </is>
       </c>
     </row>
@@ -9575,32 +9575,32 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>澎澄飯店</t>
+          <t>澄悅商旅</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市同和路168號</t>
+          <t>彰化縣鹿港鎮埔崙里中正路510巷1號</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>(06)9235678#2103</t>
+          <t>(04)7785727</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2029/08/03</t>
+          <t>2029/09/07</t>
         </is>
       </c>
     </row>
@@ -9612,32 +9612,32 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>緻麗伯爵酒店</t>
+          <t>澎湖福朋喜來登酒店</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>雲林縣斗六市中山路6號</t>
+          <t>澎湖縣馬公市新店路197號</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>(05)5341666#3</t>
+          <t>(06)9279955#3701</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2029/02/10</t>
+          <t>2028/05/27</t>
         </is>
       </c>
     </row>
@@ -9649,32 +9649,32 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>緣羊軒民宿</t>
+          <t>澎澄飯店</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>臺東縣台東市南一街96號</t>
+          <t>澎湖縣馬公市同和路168號</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>089326400</t>
+          <t>(06)9235678#2103</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026/12/05</t>
+          <t>2029/08/03</t>
         </is>
       </c>
     </row>
@@ -9686,32 +9686,32 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺北</t>
+          <t>緻麗伯爵酒店</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
+          <t>雲林縣斗六市中山路6號</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>(02)29583000#7701</t>
+          <t>(05)5341666#3</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2028/03/31</t>
+          <t>2029/02/10</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺東</t>
+          <t>緣羊軒民宿</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9733,12 +9733,12 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>臺東縣台東市新站路260號</t>
+          <t>臺東縣台東市南一街96號</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>(089)231188#7187</t>
+          <t>089326400</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2027/12/05</t>
+          <t>2026/12/05</t>
         </is>
       </c>
     </row>
@@ -9760,32 +9760,32 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>墾丁夏都沙灘酒店</t>
+          <t>趣淘漫旅-臺北</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁路451號</t>
+          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>(0910)371823</t>
+          <t>(02)29583000#7701</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2028/03/09</t>
+          <t>2028/03/31</t>
         </is>
       </c>
     </row>
@@ -9797,22 +9797,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>墾丁福華渡假飯店</t>
+          <t>趣淘漫旅-臺東</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
+          <t>臺東縣台東市新站路260號</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>(08)8862324#2701</t>
+          <t>(089)231188#7187</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2029/04/12</t>
+          <t>2027/12/05</t>
         </is>
       </c>
     </row>
@@ -9834,32 +9834,32 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>橘子民宿</t>
+          <t>墾丁夏都沙灘酒店</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
+          <t>屏東縣恆春鎮墾丁路451號</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>(0972)092658</t>
+          <t>(0910)371823</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2027/11/06</t>
+          <t>2028/03/09</t>
         </is>
       </c>
     </row>
@@ -9871,32 +9871,32 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>翰品酒店 高雄</t>
+          <t>墾丁福華渡假飯店</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區大仁路43號</t>
+          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>(07)5614688#3110</t>
+          <t>(08)8862324#2701</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2027/02/16</t>
+          <t>2029/04/12</t>
         </is>
       </c>
     </row>
@@ -9908,32 +9908,32 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>礁溪老爺酒店</t>
+          <t>橘子民宿</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
+          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>(03)9885211#8006</t>
+          <t>(0972)092658</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2028/08/24</t>
+          <t>2027/11/06</t>
         </is>
       </c>
     </row>
@@ -9945,22 +9945,22 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>礁溪寒沐酒店</t>
+          <t>翰品酒店 高雄</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
+          <t>高雄市鹽埕區大仁路43號</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>(03)9058007</t>
+          <t>(07)5614688#3110</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2027/02/16</t>
         </is>
       </c>
     </row>
@@ -9982,32 +9982,32 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>禧榕軒大飯店</t>
+          <t>礁溪老爺酒店</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>臺南市北區成功路28號</t>
+          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>(06)2222788#2203</t>
+          <t>(03)9885211#8006</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2029/05/10</t>
+          <t>2028/08/24</t>
         </is>
       </c>
     </row>
@@ -10019,32 +10019,32 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>薆悅酒店野柳渡假館一館</t>
+          <t>礁溪寒沐酒店</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>新北市萬里區野柳里港東路162號之2</t>
+          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>(02)77035770#623</t>
+          <t>(03)9058007</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -10056,32 +10056,32 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>藍水輕旅</t>
+          <t>禧榕軒大飯店</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>桃園市大園區高鐵南路一段126號</t>
+          <t>臺南市北區成功路28號</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>(03)2871855</t>
+          <t>(06)2222788#2203</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2029/05/10</t>
         </is>
       </c>
     </row>
@@ -10093,22 +10093,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>關子嶺富野溫泉會館</t>
+          <t>薆悅酒店野柳渡假館一館</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>臺南市白河區關子嶺28號</t>
+          <t>新北市萬里區野柳里港東路162號之2</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>(06)6822288</t>
+          <t>(02)77035770#623</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2029/01/07</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -10130,22 +10130,22 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>麗格休閒飯店</t>
+          <t>藍水輕旅</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市商校街258.260.262號</t>
+          <t>桃園市大園區高鐵南路一段126號</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>(03)8349922</t>
+          <t>(03)2871855</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2026/11/23</t>
         </is>
       </c>
     </row>
@@ -10167,22 +10167,22 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>麗軒國際飯店</t>
+          <t>關子嶺富野溫泉會館</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市中美路99之1號</t>
+          <t>臺南市白河區關子嶺28號</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>(03)8246898</t>
+          <t>(06)6822288</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2029/01/07</t>
         </is>
       </c>
     </row>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>麗翔大飯店</t>
+          <t>麗格休閒飯店</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -10214,12 +10214,12 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
+          <t>花蓮縣花蓮市商校街258.260.262號</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>(03)8323737</t>
+          <t>(03)8349922</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2028/01/12</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -10241,22 +10241,22 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>讀好民宿</t>
+          <t>麗軒國際飯店</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
+          <t>花蓮縣花蓮市中美路99之1號</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>(0920)023139</t>
+          <t>(03)8246898</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -10278,32 +10278,32 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>觀霧山莊</t>
+          <t>麗翔大飯店</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
+          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>(03)3343818</t>
+          <t>(03)8323737</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2029/01/22</t>
+          <t>2028/01/12</t>
         </is>
       </c>
     </row>
@@ -10315,32 +10315,32 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>綉溪安平</t>
+          <t>讀好民宿</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>(06)3910988#3111</t>
+          <t>(0920)023139</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2028/10/12</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -10352,30 +10352,104 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
+          <t>觀霧山莊</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>苗栗縣</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>(03)3343818</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>銀級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>2029/01/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>綉溪安平</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>臺南市</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>(06)3910988#3111</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>銀級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>2028/10/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
           <t>鐡馬騎跡</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
+      <c r="C271" t="inlineStr">
         <is>
           <t>屏東縣</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
+      <c r="D271" t="inlineStr">
         <is>
           <t>屏東縣東港鎮新學路50號</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
+      <c r="E271" t="inlineStr">
         <is>
           <t>(0952)848898</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>銅級環保旅宿</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
         <is>
           <t>2029/01/18</t>
         </is>

--- a/環保旅宿_Selenium結果.xlsx
+++ b/環保旅宿_Selenium結果.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G271"/>
+  <dimension ref="A1:G278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>山形閣</t>
+          <t>山多利大飯店</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉中山路二段187號</t>
+          <t>宜蘭縣礁溪鄉興農路291巷1號</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(03)9872323</t>
+          <t>(03)9888047#1812</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2027/06/02</t>
+          <t>2029/10/13</t>
         </is>
       </c>
     </row>
@@ -1139,32 +1139,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>山慕民宿</t>
+          <t>山形閣</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉水社村中山路216號</t>
+          <t>宜蘭縣礁溪鄉中山路二段187號</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(0925)97162</t>
+          <t>(03)9872323</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2029/06/11</t>
+          <t>2027/06/02</t>
         </is>
       </c>
     </row>
@@ -1176,22 +1176,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>山鄰山林青年文旅</t>
+          <t>山慕民宿</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮大同路226.228號</t>
+          <t>南投縣魚池鄉水社村中山路216號</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(03)8887228</t>
+          <t>(0925)97162</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2027/11/10</t>
+          <t>2029/06/11</t>
         </is>
       </c>
     </row>
@@ -1213,32 +1213,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>仁義湖岸大酒店</t>
+          <t>山鄰山林青年文旅</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>嘉義縣番路鄉內甕村後坑仔35號</t>
+          <t>花蓮縣玉里鎮大同路226.228號</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(05)2769388</t>
+          <t>(03)8887228</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2028/08/31</t>
+          <t>2027/11/10</t>
         </is>
       </c>
     </row>
@@ -1250,32 +1250,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>今古安民宿</t>
+          <t>仁義湖岸大酒店</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市重慶路353巷30號</t>
+          <t>嘉義縣番路鄉內甕村後坑仔35號</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(03)8345555</t>
+          <t>(05)2769388</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2029/01/06</t>
+          <t>2028/08/31</t>
         </is>
       </c>
     </row>
@@ -1287,32 +1287,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>天成大飯店</t>
+          <t>今古安民宿</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>臺北市中正區忠孝西路一段43號</t>
+          <t>花蓮縣花蓮市重慶路353巷30號</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(02)23118905#3705</t>
+          <t>(03)8345555</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2027/03/07</t>
+          <t>2029/01/06</t>
         </is>
       </c>
     </row>
@@ -1324,22 +1324,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>太子文旅</t>
+          <t>天成大飯店</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>臺南市東區大學路2號(3，5-10F)</t>
+          <t>臺北市中正區忠孝西路一段43號</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(06)2095199#6103</t>
+          <t>(02)23118905#3705</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2029/07/08</t>
+          <t>2027/03/07</t>
         </is>
       </c>
     </row>
@@ -1361,32 +1361,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>太平⼭莊</t>
+          <t>太子文旅</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>宜蘭縣大同鄉太平村太平巷58之1號</t>
+          <t>臺南市東區大學路2號(3，5-10F)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(03)9545114#607</t>
+          <t>(06)2095199#6103</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2027/10/15</t>
+          <t>2029/07/08</t>
         </is>
       </c>
     </row>
@@ -1398,32 +1398,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>日日森旅二館</t>
+          <t>太平⼭莊</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>彰化縣田尾鄉民族路一段185巷11號</t>
+          <t>宜蘭縣大同鄉太平村太平巷58之1號</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(04)8221669</t>
+          <t>(03)9545114#607</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/10/15</t>
         </is>
       </c>
     </row>
@@ -1435,32 +1435,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>日月潭力麗溫德姆溫泉酒店</t>
+          <t>日日森旅二館</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉日月村中正路312號</t>
+          <t>彰化縣田尾鄉民族路一段185巷11號</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(049)2850085#8802</t>
+          <t>(04)8221669</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2029/01/01</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -1472,32 +1472,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>日玥居</t>
+          <t>日月潭力麗溫德姆溫泉酒店</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>金門縣金寧鄉南山19號</t>
+          <t>南投縣魚池鄉日月村中正路312號</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(0987)397327</t>
+          <t>(049)2850085#8802</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2029/01/01</t>
         </is>
       </c>
     </row>
@@ -1509,22 +1509,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>月光寶盒旅店</t>
+          <t>日玥居</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>高雄市鳳山區黃埔新村東一巷80號</t>
+          <t>金門縣金寧鄉南山19號</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(09)33631615</t>
+          <t>(0987)397327</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2026/11/28</t>
         </is>
       </c>
     </row>
@@ -1546,32 +1546,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>北投老爺酒店</t>
+          <t>月光寶盒旅店</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>臺北市北投區中和街2號</t>
+          <t>高雄市鳳山區黃埔新村東一巷80號</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(02)28966966#8878</t>
+          <t>(09)33631615</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2028/01/06</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>北投麗禧溫泉酒店</t>
+          <t>北投老爺酒店</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>臺北市北投區幽雅路30號</t>
+          <t>臺北市北投區中和街2號</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(02)28967799#738</t>
+          <t>(02)28966966#8878</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2028/04/13</t>
+          <t>2028/01/06</t>
         </is>
       </c>
     </row>
@@ -1620,32 +1620,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>臺中李方艾美酒店</t>
+          <t>北投麗禧溫泉酒店</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>臺中市中區建國路111號</t>
+          <t>臺北市北投區幽雅路30號</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(04)22240888#81002</t>
+          <t>(02)28967799#738</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2028/11/05</t>
+          <t>2028/04/13</t>
         </is>
       </c>
     </row>
@@ -1657,22 +1657,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>臺中金典酒店</t>
+          <t>古寧歇心苑</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>臺中市西區健行路1049號</t>
+          <t>金門縣金寧鄉古寧村北山95號</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>(04)23288000#6692</t>
+          <t>(082)322395</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2028/11/19</t>
+          <t>2029/10/16</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>臺中港酒店</t>
+          <t>臺中李方艾美酒店</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>臺中市梧棲區大智路二段388號</t>
+          <t>臺中市中區建國路111號</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(04)37055888#6128</t>
+          <t>(04)22240888#81002</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2029/01/18</t>
+          <t>2028/11/05</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>臺中萬楓酒店</t>
+          <t>臺中金典酒店</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1741,22 +1741,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>臺中市西屯區環中路二段1155號、1149號2樓、1151號3至11樓(之1)</t>
+          <t>臺中市西區健行路1049號</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(04)36065188#2501</t>
+          <t>(04)23288000#6692</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2029/09/09</t>
+          <t>2028/11/19</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>臺中豐邑慕奇夕酒店</t>
+          <t>臺中港酒店</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1778,22 +1778,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>臺中市西屯區文心南六路288號、288號2樓、288號3樓(地上物3至17樓)</t>
+          <t>臺中市梧棲區大智路二段388號</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(04)36007009#7099</t>
+          <t>(04)37055888#6128</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2029/05/14</t>
+          <t>2029/01/18</t>
         </is>
       </c>
     </row>
@@ -1805,22 +1805,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>臺北W飯店</t>
+          <t>臺中萬楓酒店</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>臺北市信義區忠孝東路五段10號</t>
+          <t>臺中市西屯區環中路二段1155號、1149號2樓、1151號3至11樓(之1)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(02)77038765</t>
+          <t>(04)36065188#2501</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2028/08/07</t>
+          <t>2029/09/09</t>
         </is>
       </c>
     </row>
@@ -1842,32 +1842,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>臺北士林萬麗酒店</t>
+          <t>臺中豐邑慕奇夕酒店</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>臺北市士林區中山北路五段470巷8號</t>
+          <t>臺中市西屯區文心南六路288號、288號2樓、288號3樓(地上物3至17樓)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(02)88612389</t>
+          <t>(04)36007009#7099</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2028/07/10</t>
+          <t>2029/05/14</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>臺北中山九昱希爾頓逸林酒店</t>
+          <t>臺北W飯店</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1889,22 +1889,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路一段121巷1之1號, 121巷1號1樓至14樓</t>
+          <t>臺北市信義區忠孝東路五段10號</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(02)66253281</t>
+          <t>(02)77038765</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2028/08/07</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>臺北中山雅樂軒酒店</t>
+          <t>臺北士林萬麗酒店</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>臺北市中山區雙城街1號</t>
+          <t>臺北市士林區中山北路五段470巷8號</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(02)77439900</t>
+          <t>(02)88612389</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2028/11/13</t>
+          <t>2028/07/10</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>臺北中山意舍酒店</t>
+          <t>臺北中山九昱希爾頓逸林酒店</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1963,22 +1963,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路二段57之1號1至8樓</t>
+          <t>臺北市中山區中山北路一段121巷1之1號, 121巷1號1樓至14樓</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>(02)25652828</t>
+          <t>(02)66253281</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2028/09/17</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>臺北六福萬怡酒店</t>
+          <t>臺北中山雅樂軒酒店</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>臺北市南港區忠孝東路七段359號7至30樓</t>
+          <t>臺北市中山區雙城街1號</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>(02)66156565#5000</t>
+          <t>(02)77439900</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2029/04/09</t>
+          <t>2028/11/13</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>臺北艾麗酒店</t>
+          <t>臺北中山意舍酒店</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>臺北市信義區松高路18號</t>
+          <t>臺北市中山區中山北路二段57之1號1至8樓</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>(02)66318031</t>
+          <t>(02)25652828</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2029/04/08</t>
+          <t>2028/09/17</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>臺北西門町意舍酒店</t>
+          <t>臺北六福萬怡酒店</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>臺北市萬華區武昌街2段77號5樓至10樓</t>
+          <t>臺北市南港區忠孝東路七段359號7至30樓</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(02)23755111#2100</t>
+          <t>(02)66156565#5000</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2028/10/22</t>
+          <t>2029/04/09</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>臺北君品大酒店</t>
+          <t>臺北艾麗酒店</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>臺北市大同區承德路1段3號1樓、5樓~16樓及地下1樓、地下3樓</t>
+          <t>臺北市信義區松高路18號</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(02)21819999#3142</t>
+          <t>(02)66318031</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>2029/04/08</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>臺北松山意舍酒店</t>
+          <t>臺北西門町意舍酒店</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>臺北市南港區市民大道7段8號17樓至21樓</t>
+          <t>臺北市萬華區武昌街2段77號5樓至10樓</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(02)26532828#2100</t>
+          <t>(02)23755111#2100</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2027/11/28</t>
+          <t>2028/10/22</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>臺北花園大酒店</t>
+          <t>臺北君品大酒店</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路2段1號</t>
+          <t>臺北市大同區承德路1段3號1樓、5樓~16樓及地下1樓、地下3樓</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(02)23143300#3331</t>
+          <t>(02)21819999#3142</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2029/09/28</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -2212,32 +2212,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>臺北旅人國際青年旅館</t>
+          <t>臺北松山意舍酒店</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>新北市淡水區三民街22、22之1、22之2、22之3、22之4號</t>
+          <t>臺北市南港區市民大道7段8號17樓至21樓</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(02)26258222</t>
+          <t>(02)26532828#2100</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2027/11/28</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>臺北時代寓所</t>
+          <t>臺北花園大酒店</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>臺北市中正區林森南路7號1至14樓，7-1號1樓</t>
+          <t>臺北市中正區中華路2段1號</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(02)77521801</t>
+          <t>(02)23143300#3331</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2028/09/29</t>
+          <t>2029/09/28</t>
         </is>
       </c>
     </row>
@@ -2286,32 +2286,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>臺北國泰萬怡酒店</t>
+          <t>臺北旅人國際青年旅館</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>臺北市中山區民生東路三段6號地下1樓、1、2、14至20樓</t>
+          <t>新北市淡水區三民街22、22之1、22之2、22之3、22之4號</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(02)77503371</t>
+          <t>(02)26258222</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2029/09/30</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -2323,22 +2323,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>臺北新板希爾頓酒店</t>
+          <t>臺北時代寓所</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>新北市板橋區民權路88號、88號（2至31樓）90號</t>
+          <t>臺北市中正區林森南路7號1至14樓，7-1號1樓</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(02)29583000#7702</t>
+          <t>(02)77521801</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2028/03/31</t>
+          <t>2028/09/29</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>臺北萬豪酒店</t>
+          <t>臺北國泰萬怡酒店</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>臺北市中山區樂群二路199號</t>
+          <t>臺北市中山區民生東路三段6號地下1樓、1、2、14至20樓</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(02)21757999#1701</t>
+          <t>(02)77503371</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2028/12/07</t>
+          <t>2029/09/30</t>
         </is>
       </c>
     </row>
@@ -2397,32 +2397,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>臺北遠東香格里拉</t>
+          <t>臺北新板希爾頓酒店</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>臺北市大安區敦化南路二段201號</t>
+          <t>新北市板橋區民權路88號、88號（2至31樓）90號</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(02)23788888#6608</t>
+          <t>(02)29583000#7702</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2027/12/12</t>
+          <t>2028/03/31</t>
         </is>
       </c>
     </row>
@@ -2434,32 +2434,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>臺東Deer  House民宿</t>
+          <t>臺北萬豪酒店</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>臺東縣鹿野鄉永安村1鄰永安路７１號</t>
+          <t>臺北市中山區樂群二路199號</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(089)552224</t>
+          <t>(02)21757999#1701</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2028/12/07</t>
         </is>
       </c>
     </row>
@@ -2471,32 +2471,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>臺南大員皇冠假日酒店</t>
+          <t>臺北遠東香格里拉</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>臺南市安平區州平路289號</t>
+          <t>臺北市大安區敦化南路二段201號</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(06)5121888#6002</t>
+          <t>(02)23788888#6608</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2028/01/09</t>
+          <t>2027/12/12</t>
         </is>
       </c>
     </row>
@@ -2508,22 +2508,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>臺南大飯店</t>
+          <t>臺東Deer  House民宿</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>臺南市中西區成功路1號</t>
+          <t>臺東縣鹿野鄉永安村1鄰永安路７１號</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(06)2289101#2012</t>
+          <t>(089)552224</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>臺南安平雅樂軒酒店</t>
+          <t>臺南大員皇冠假日酒店</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>臺南市安平區光州路108號2-12樓、光州路108之1號</t>
+          <t>臺南市安平區州平路289號</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(06)3905000#8600</t>
+          <t>(06)5121888#6002</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2028/12/18</t>
+          <t>2028/01/09</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>臺南老爺行旅</t>
+          <t>臺南大飯店</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2592,22 +2592,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>臺南市東區中華東路一段368號1樓、6-10樓</t>
+          <t>臺南市中西區成功路1號</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(06)2361680#301</t>
+          <t>(06)2289101#2012</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2028/02/19</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>臺南遠東香格里拉</t>
+          <t>臺南安平雅樂軒酒店</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2629,22 +2629,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>臺南市東區大學路西段89號</t>
+          <t>臺南市安平區光州路108號2-12樓、光州路108之1號</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(06)7028888#6903</t>
+          <t>(06)3905000#8600</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2028/12/18</t>
         </is>
       </c>
     </row>
@@ -2656,32 +2656,32 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>臺糖臺北會館</t>
+          <t>臺南老爺行旅</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路一段39號3至5樓</t>
+          <t>臺南市東區中華東路一段368號1樓、6-10樓</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(02)23885522#5001</t>
+          <t>(06)2361680#301</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2027/03/10</t>
+          <t>2028/02/19</t>
         </is>
       </c>
     </row>
@@ -2693,22 +2693,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>臺糖花蓮旅館</t>
+          <t>臺南遠東香格里拉</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>花蓮縣光復鄉大進村糖廠街19號</t>
+          <t>臺南市東區大學路西段89號</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>(03)8704125#621</t>
+          <t>(06)7028888#6903</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2027/03/21</t>
+          <t>2026/12/30</t>
         </is>
       </c>
     </row>
@@ -2730,22 +2730,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>臺糖長榮酒店(臺南)</t>
+          <t>臺糖臺北會館</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>臺南市東區中華東路三段336巷1號</t>
+          <t>臺北市中正區中華路一段39號3至5樓</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>(06)3378888</t>
+          <t>(02)23885522#5001</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2027/03/10</t>
         </is>
       </c>
     </row>
@@ -2767,22 +2767,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>臺灣糖業股份有限公司池上牧野渡假村</t>
+          <t>臺糖花蓮旅館</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>臺東縣池上鄉新興村新興110號</t>
+          <t>花蓮縣光復鄉大進村糖廠街19號</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(089)862736#1001</t>
+          <t>(03)8704125#621</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2028/04/15</t>
+          <t>2027/03/21</t>
         </is>
       </c>
     </row>
@@ -2804,32 +2804,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>四季時光</t>
+          <t>臺糖長榮酒店(臺南)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉頭社村平和巷103-11號</t>
+          <t>臺南市東區中華東路三段336巷1號</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(0932)376767</t>
+          <t>(06)3378888</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2026/11/28</t>
         </is>
       </c>
     </row>
@@ -2841,32 +2841,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>巨蛋旅店</t>
+          <t>臺灣糖業股份有限公司池上牧野渡假村</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>高雄市鼓山區文忠路1號</t>
+          <t>臺東縣池上鄉新興村新興110號</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(07)5868388#0</t>
+          <t>(089)862736#1001</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2028/10/07</t>
+          <t>2028/04/15</t>
         </is>
       </c>
     </row>
@@ -2878,32 +2878,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>打個蛋海旅民宿</t>
+          <t>四季時光</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>臺東縣太麻里鄉金崙4鄰129號</t>
+          <t>南投縣魚池鄉頭社村平和巷103-11號</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(089)771551</t>
+          <t>(0932)376767</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -2915,32 +2915,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>正好友生態環保旅店</t>
+          <t>巨蛋旅店</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>屏東縣琉球鄉中山路153號</t>
+          <t>高雄市鼓山區文忠路1號</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(0886)12270</t>
+          <t>(07)5868388#0</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2029/03/26</t>
+          <t>2028/10/07</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>伊塔原旅臺東縣原住民文化會館</t>
+          <t>打個蛋海旅民宿</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>臺東縣台東市中山路10號</t>
+          <t>臺東縣太麻里鄉金崙4鄰129號</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(089)34060</t>
+          <t>(089)771551</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>兆品酒店</t>
+          <t>正好友生態環保旅店</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>嘉義市文化路257號B2-9F</t>
+          <t>屏東縣琉球鄉中山路153號</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(05)2292883#3130</t>
+          <t>(0886)12270</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2028/03/30</t>
+          <t>2029/03/26</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>好室民宿</t>
+          <t>伊塔原旅臺東縣原住民文化會館</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>臺東縣台東市中正路251巷9號</t>
+          <t>臺東縣台東市中山路10號</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(0905)583758</t>
+          <t>(089)34060</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2027/01/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -3063,32 +3063,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>如一家精緻民宿</t>
+          <t>兆品酒店</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>金門縣金城鎮珠浦北路35-1號</t>
+          <t>嘉義市文化路257號B2-9F</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(082)322167</t>
+          <t>(05)2292883#3130</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2028/03/30</t>
         </is>
       </c>
     </row>
@@ -3100,22 +3100,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>安樓文旅</t>
+          <t>好室民宿</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>基隆市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>基隆市仁愛區仁三路11-4</t>
+          <t>臺東縣台東市中正路251巷9號</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(02)24200220</t>
+          <t>(0905)583758</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2029/07/09</t>
+          <t>2027/01/29</t>
         </is>
       </c>
     </row>
@@ -3137,22 +3137,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>老公老婆友善民宿</t>
+          <t>如一家精緻民宿</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>宜蘭縣冬山鄉境安路345號</t>
+          <t>金門縣金城鎮珠浦北路35-1號</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(03) 9519013</t>
+          <t>(082)322167</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026/12/28</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -3174,22 +3174,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>老爺大酒店</t>
+          <t>安樓文旅</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>基隆市</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路2段37-1號</t>
+          <t>基隆市仁愛區仁三路11-4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(02)25423299#359</t>
+          <t>(02)24200220</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2029/07/09</t>
         </is>
       </c>
     </row>
@@ -3211,32 +3211,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>西湖渡假大飯店</t>
+          <t>老公老婆友善民宿</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>苗栗縣三義鄉西湖村西湖11號</t>
+          <t>宜蘭縣冬山鄉境安路345號</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(037)876699#1122</t>
+          <t>(03) 9519013</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2029/05/24</t>
+          <t>2026/12/28</t>
         </is>
       </c>
     </row>
@@ -3248,32 +3248,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>亞昕福朋喜來登酒店</t>
+          <t>老爺大酒店</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段1號、1號2樓、1號3樓</t>
+          <t>臺北市中山區中山北路2段37-1號</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>(02)77276961</t>
+          <t>(02)25423299#359</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2028/09/25</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>享沐時光</t>
+          <t>西湖渡假大飯店</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3295,22 +3295,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮石鎮里錦山8-1,8-2號</t>
+          <t>苗栗縣三義鄉西湖村西湖11號</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>(037)742878#124</t>
+          <t>(037)876699#1122</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2028/07/15</t>
+          <t>2029/05/24</t>
         </is>
       </c>
     </row>
@@ -3322,22 +3322,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>和逸．高雄中山館</t>
+          <t>亞昕福朋喜來登酒店</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>高雄市前鎮區中山二路260號22-29樓</t>
+          <t>新北市林口區文化三路一段1號、1號2樓、1號3樓</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>(07)9756670</t>
+          <t>(02)77276961</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2028/09/10</t>
+          <t>2028/09/25</t>
         </is>
       </c>
     </row>
@@ -3359,22 +3359,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>和逸·臺南西門館</t>
+          <t>享沐時光</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>臺南市中西區西門路一段658之2號4樓至13樓</t>
+          <t>苗栗縣苑裡鎮石鎮里錦山8-1,8-2號</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(06)7026685</t>
+          <t>(037)742878#124</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2028/02/19</t>
+          <t>2028/07/15</t>
         </is>
       </c>
     </row>
@@ -3396,22 +3396,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>和逸飯店桃園青埔館</t>
+          <t>和逸．高雄中山館</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>桃園市中壢區春德路101號</t>
+          <t>高雄市前鎮區中山二路260號22-29樓</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(03)2737692#2102</t>
+          <t>(07)9756670</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2028/09/10</t>
         </is>
       </c>
     </row>
@@ -3433,32 +3433,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>宜蘭力麗威斯汀度假酒店</t>
+          <t>和逸·臺南西門館</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>宜蘭縣員山鄉永同路三段268號</t>
+          <t>臺南市中西區西門路一段658之2號4樓至13樓</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>(03)9232111</t>
+          <t>(06)7026685</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2029/10/01</t>
+          <t>2028/02/19</t>
         </is>
       </c>
     </row>
@@ -3470,32 +3470,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>尚順君樂飯店</t>
+          <t>和逸飯店桃園青埔館</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>苗栗縣頭份市育樂街6號</t>
+          <t>桃園市中壢區春德路101號</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>(037)539999#8611</t>
+          <t>(03)2737692#2102</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2029/07/29</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>幸福蝸牛</t>
+          <t>宜蘭力麗威斯汀度假酒店</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3517,22 +3517,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉利澤西路6號</t>
+          <t>宜蘭縣員山鄉永同路三段268號</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>(03)9500047</t>
+          <t>(03)9232111</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2029/10/01</t>
         </is>
       </c>
     </row>
@@ -3544,32 +3544,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>承萬尊爵渡假酒店</t>
+          <t>尚順君樂飯店</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>南投縣埔里鎮樹人路131號</t>
+          <t>苗栗縣頭份市育樂街6號</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>(049)2995757#6316</t>
+          <t>(037)539999#8611</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2027/04/07</t>
+          <t>2029/07/29</t>
         </is>
       </c>
     </row>
@@ -3581,32 +3581,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>承億酒店</t>
+          <t>幸福蝸牛</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>高雄市前鎮區林森四路189號</t>
+          <t>宜蘭縣五結鄉利澤西路6號</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(07)3332000#6870</t>
+          <t>(03)9500047</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2029/09/22</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -3618,32 +3618,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>林口維多利亞民宿</t>
+          <t>承萬尊爵渡假酒店</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>桃園市蘆竹區坑子里14鄰八德二路280巷11號</t>
+          <t>南投縣埔里鎮樹人路131號</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(0905)111918</t>
+          <t>(049)2995757#6316</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2029/08/24</t>
+          <t>2027/04/07</t>
         </is>
       </c>
     </row>
@@ -3655,22 +3655,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>板橋凱撒大飯店</t>
+          <t>承億酒店</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>新北市板橋區縣民大道二段8號</t>
+          <t>高雄市前鎮區林森四路189號</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(02)29583000#7701</t>
+          <t>(07)3332000#6870</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2029/02/12</t>
+          <t>2029/09/22</t>
         </is>
       </c>
     </row>
@@ -3692,32 +3692,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>武陵國民賓館</t>
+          <t>林口維多利亞民宿</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>臺中市和平區平等里武陵路3-1號</t>
+          <t>桃園市蘆竹區坑子里14鄰八德二路280巷11號</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(04)25901258#2103</t>
+          <t>(0905)111918</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026/12/25</t>
+          <t>2029/08/24</t>
         </is>
       </c>
     </row>
@@ -3729,32 +3729,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>武陵富野渡假村</t>
+          <t>板橋凱撒大飯店</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>臺中市和平區武陵路3-16號</t>
+          <t>新北市板橋區縣民大道二段8號</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>(04)25901399#8912</t>
+          <t>(02)29583000#7701</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2029/02/12</t>
         </is>
       </c>
     </row>
@@ -3766,32 +3766,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>河那灣</t>
+          <t>武陵國民賓館</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>桃園市復興區澤仁里3鄰溪口台41號</t>
+          <t>臺中市和平區平等里武陵路3-1號</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(0919)235303</t>
+          <t>(04)25901258#2103</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2027/07/25</t>
+          <t>2026/12/25</t>
         </is>
       </c>
     </row>
@@ -3803,32 +3803,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>波西米亞民宿</t>
+          <t>武陵富野渡假村</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>花蓮縣吉安鄉東昌村13鄰東海一街168號</t>
+          <t>臺中市和平區武陵路3-16號</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>(0385)31234</t>
+          <t>(04)25901399#8912</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2029/01/06</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -3840,22 +3840,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>泡泡森林民宿</t>
+          <t>河那灣</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>臺東縣台東市南一街40號</t>
+          <t>桃園市復興區澤仁里3鄰溪口台41號</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0986866545</t>
+          <t>(0919)235303</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026/12/06</t>
+          <t>2027/07/25</t>
         </is>
       </c>
     </row>
@@ -3877,22 +3877,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>泊寓</t>
+          <t>波西米亞民宿</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮鹿興路57巷3號</t>
+          <t>花蓮縣吉安鄉東昌村13鄰東海一街168號</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(04)7115655#120</t>
+          <t>(0385)31234</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2029/01/06</t>
         </is>
       </c>
     </row>
@@ -3914,22 +3914,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>爸爸萬歲民宿</t>
+          <t>泡泡森林民宿</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市延平街68巷27號</t>
+          <t>臺東縣台東市南一街40號</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>(0900)757520</t>
+          <t>0986866545</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2027/01/10</t>
+          <t>2026/12/06</t>
         </is>
       </c>
     </row>
@@ -3951,22 +3951,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>迎曦大飯店</t>
+          <t>泊寓</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>新竹市東區親仁里文化街10號2-10樓</t>
+          <t>彰化縣鹿港鎮鹿興路57巷3號</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>(03)5347266#124</t>
+          <t>(04)7115655#120</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2028/04/28</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -3988,32 +3988,32 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>金湖飯店</t>
+          <t>爸爸萬歲民宿</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>金門縣金湖鎮太湖路二段218號</t>
+          <t>花蓮縣花蓮市延平街68巷27號</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(082)379666#160</t>
+          <t>(0900)757520</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026/12/03</t>
+          <t>2027/01/10</t>
         </is>
       </c>
     </row>
@@ -4025,32 +4025,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>長榮文苑酒店(嘉義)</t>
+          <t>迎曦大飯店</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>嘉義縣太保市東勢里故宮大道777號</t>
+          <t>新竹市東區親仁里文化街10號2-10樓</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>(05)3669988#2700</t>
+          <t>(03)5347266#124</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2027/04/11</t>
+          <t>2028/04/28</t>
         </is>
       </c>
     </row>
@@ -4062,22 +4062,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(臺中)</t>
+          <t>金湖飯店</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>臺中市西屯區臺灣大道二段666號</t>
+          <t>金門縣金湖鎮太湖路二段218號</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>(04)23242236#2700</t>
+          <t>(082)379666#160</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2027/07/09</t>
+          <t>2026/12/03</t>
         </is>
       </c>
     </row>
@@ -4099,22 +4099,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(臺北)</t>
+          <t>長榮文苑酒店(嘉義)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>臺北市中山區松江路63號</t>
+          <t>嘉義縣太保市東勢里故宮大道777號</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>(02)25019988#2701</t>
+          <t>(05)3669988#2700</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2028/10/22</t>
+          <t>2027/04/11</t>
         </is>
       </c>
     </row>
@@ -4136,32 +4136,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(基隆)</t>
+          <t>長榮桂冠酒店(臺中)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>基隆市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>基隆市中正區中正路62號之1</t>
+          <t>臺中市西屯區臺灣大道二段666號</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>(02)24279988</t>
+          <t>(04)23242236#2700</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2028/05/22</t>
+          <t>2027/07/09</t>
         </is>
       </c>
     </row>
@@ -4173,32 +4173,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>長榮鳳凰酒店(礁溪)</t>
+          <t>長榮桂冠酒店(臺北)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉健康路77號</t>
+          <t>臺北市中山區松江路63號</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>(03)9100988#2335</t>
+          <t>(02)25019988#2701</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2027/09/15</t>
+          <t>2028/10/22</t>
         </is>
       </c>
     </row>
@@ -4210,32 +4210,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>阿里山東方明珠國際大飯店</t>
+          <t>長榮桂冠酒店(基隆)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>基隆市</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>嘉義縣中埔鄉社口村檨仔林23號</t>
+          <t>基隆市中正區中正路62號之1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>(05)2536999</t>
+          <t>(02)24279988</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2027/12/12</t>
+          <t>2028/05/22</t>
         </is>
       </c>
     </row>
@@ -4247,32 +4247,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>阿里山英迪格酒店</t>
+          <t>長榮鳳凰酒店(礁溪)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>嘉義縣番路鄉公田村2鄰龍頭20號2樓之1等10筆</t>
+          <t>宜蘭縣礁溪鄉健康路77號</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>(05)2586800#121</t>
+          <t>(03)9100988#2335</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2028/10/21</t>
+          <t>2027/09/15</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>阿里山賓館（現代館）</t>
+          <t>阿里山東方明珠國際大飯店</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4294,22 +4294,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>嘉義縣阿里山鄉香林村西阿里山16-1號</t>
+          <t>嘉義縣中埔鄉社口村檨仔林23號</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>(05)2679996#5117</t>
+          <t>(05)2536999</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2027/06/19</t>
+          <t>2027/12/12</t>
         </is>
       </c>
     </row>
@@ -4321,32 +4321,32 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>阿爾卑斯莊園</t>
+          <t>阿里山英迪格酒店</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉協和村親河路二段88巷37號</t>
+          <t>嘉義縣番路鄉公田村2鄰龍頭20號2樓之1等10筆</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>(0905)787698</t>
+          <t>(05)2586800#121</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2029/09/02</t>
+          <t>2028/10/21</t>
         </is>
       </c>
     </row>
@@ -4358,32 +4358,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>冠翔泉旅</t>
+          <t>阿里山賓館（現代館）</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉仁愛路66巷6號</t>
+          <t>嘉義縣阿里山鄉香林村西阿里山16-1號</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>(03)9875599#119</t>
+          <t>(05)2679996#5117</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2029/07/20</t>
+          <t>2027/06/19</t>
         </is>
       </c>
     </row>
@@ -4395,32 +4395,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>南港老爺行旅</t>
+          <t>阿爾卑斯莊園</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>臺北市南港區經貿二路196號、196號10樓至20樓</t>
+          <t>宜蘭縣五結鄉協和村親河路二段88巷37號</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>(02)77500588</t>
+          <t>(0905)787698</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2028/11/27</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -4432,32 +4432,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>城市商旅美麗島館(HOTEL PAPA WHALE)</t>
+          <t>冠翔泉旅</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>高雄市新興區民生一路328號1-7樓</t>
+          <t>宜蘭縣礁溪鄉仁愛路66巷6號</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>(07)2519888</t>
+          <t>(03)9875599#119</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2028/09/24</t>
+          <t>2029/07/20</t>
         </is>
       </c>
     </row>
@@ -4469,32 +4469,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>城市商旅高雄真愛館</t>
+          <t>南港老爺行旅</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區大義街1號</t>
+          <t>臺北市南港區經貿二路196號、196號10樓至20樓</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>(07)5215116#9303</t>
+          <t>(02)77500588</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2028/09/25</t>
+          <t>2028/11/27</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>城市商旅駁二館</t>
+          <t>城市商旅美麗島館(HOTEL PAPA WHALE)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區公園二路83號1至11樓</t>
+          <t>高雄市新興區民生一路328號1-7樓</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>(07)5322777</t>
+          <t>(07)2519888</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2028/09/25</t>
+          <t>2028/09/24</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>城市商旅德立莊博愛館</t>
+          <t>城市商旅高雄真愛館</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>高雄市三民區博愛一路338號地上1至10樓</t>
+          <t>高雄市鹽埕區大義街1號</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>(07)3238777#9301</t>
+          <t>(07)5215116#9303</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2028/08/07</t>
+          <t>2028/09/25</t>
         </is>
       </c>
     </row>
@@ -4580,32 +4580,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>星8藝宿</t>
+          <t>城市商旅駁二館</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉中山路三段192巷8號</t>
+          <t>高雄市鹽埕區公園二路83號1至11樓</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>(0932)495200</t>
+          <t>(07)5322777</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2029/01/07</t>
+          <t>2028/09/25</t>
         </is>
       </c>
     </row>
@@ -4617,32 +4617,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>星漾商旅</t>
+          <t>城市商旅德立莊博愛館</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>臺中市北區錦南街17號,錦新街30號4樓至9樓,錦新街32號4樓至9樓</t>
+          <t>高雄市三民區博愛一路338號地上1至10樓</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>(04)22289008</t>
+          <t>(07)3238777#9301</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2028/08/07</t>
         </is>
       </c>
     </row>
@@ -4654,22 +4654,22 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>星漾商旅(中清館)</t>
+          <t>星8藝宿</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>臺中市北區中清路一段63號</t>
+          <t>宜蘭縣三星鄉中山路三段192巷8號</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>(04)22083888</t>
+          <t>(0932)495200</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2029/01/07</t>
         </is>
       </c>
     </row>
@@ -4691,22 +4691,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>柳營尖山埤渡假村</t>
+          <t>星漾商旅</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>臺南市柳營區旭山里60號</t>
+          <t>臺中市北區錦南街17號,錦新街30號4樓至9樓,錦新街32號4樓至9樓</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>(06)6233888#2100</t>
+          <t>(04)22289008</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2029/07/28</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>美之旅商務飯店</t>
+          <t>星漾商旅(中清館)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>臺中市西區美村路一段269號1樓、2樓之1、2樓之2、3、4、5、6、7樓</t>
+          <t>臺中市北區中清路一段63號</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(04)23024330</t>
+          <t>(04)22083888</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2029/04/07</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -4765,22 +4765,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>美侖商旅</t>
+          <t>柳營尖山埤渡假村</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>臺北市中山區吉林路49號1至8樓</t>
+          <t>臺南市柳營區旭山里60號</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(02)25313535#878</t>
+          <t>(06)6233888#2100</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2028/11/27</t>
+          <t>2029/07/28</t>
         </is>
       </c>
     </row>
@@ -4802,22 +4802,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>美墅館</t>
+          <t>美之旅商務飯店</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>臺南市善化區昌隆里9鄰東勢寮131之8號</t>
+          <t>臺中市西區美村路一段269號1樓、2樓之1、2樓之2、3、4、5、6、7樓</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(09)20656908</t>
+          <t>(04)23024330</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2029/04/07</t>
         </is>
       </c>
     </row>
@@ -4839,32 +4839,32 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>美綠民宿</t>
+          <t>美侖商旅</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>高雄市美濃區獅山里竹門14-2號</t>
+          <t>臺北市中山區吉林路49號1至8樓</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(07)6851111</t>
+          <t>(02)25313535#878</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2028/12/28</t>
+          <t>2028/11/27</t>
         </is>
       </c>
     </row>
@@ -4876,32 +4876,32 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>香格里拉冬山河旅館</t>
+          <t>美墅館</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉協和村公園二路15號</t>
+          <t>臺南市善化區昌隆里9鄰東勢寮131之8號</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(03)9605388#212</t>
+          <t>(09)20656908</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2029/10/06</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -4913,22 +4913,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>夏堤民宿</t>
+          <t>美綠民宿</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>屏東縣琉球鄉上福村2鄰杉板路51巷2號</t>
+          <t>高雄市美濃區獅山里竹門14-2號</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(08)8611155</t>
+          <t>(07)6851111</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2029/02/25</t>
+          <t>2028/12/28</t>
         </is>
       </c>
     </row>
@@ -4950,32 +4950,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>夏優旅居</t>
+          <t>香格里拉冬山河旅館</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區新興街67號</t>
+          <t>宜蘭縣五結鄉協和村公園二路15號</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(07)5328885</t>
+          <t>(03)9605388#212</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2028/12/11</t>
+          <t>2029/10/06</t>
         </is>
       </c>
     </row>
@@ -4987,22 +4987,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>娜路彎花園酒店</t>
+          <t>夏堤民宿</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>臺東縣台東市新興路77號</t>
+          <t>屏東縣琉球鄉上福村2鄰杉板路51巷2號</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>(089)231111</t>
+          <t>(08)8611155</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2029/02/25</t>
         </is>
       </c>
     </row>
@@ -5024,22 +5024,22 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>娜路彎會館</t>
+          <t>夏優旅居</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>臺東縣台東市中興路2段385號</t>
+          <t>高雄市鹽埕區新興街67號</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(089)235500</t>
+          <t>(07)5328885</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>2028/12/11</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>娜路彎銀河行館</t>
+          <t>娜路彎花園酒店</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>臺東縣台東市豐興路88號</t>
+          <t>臺東縣台東市新興路77號</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(089)383366</t>
+          <t>(089)231111</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2028/09/16</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>娜路彎銀河酒店</t>
+          <t>娜路彎會館</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5108,22 +5108,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>臺東縣台東市豐興路66號</t>
+          <t>臺東縣台東市中興路2段385號</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(089)225000#8263</t>
+          <t>(089)235500</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2028/09/03</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>悅徠舘</t>
+          <t>娜路彎銀河行館</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>桃園市龜山區興華三街18號2樓之1</t>
+          <t>臺東縣台東市豐興路88號</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(03)3280177</t>
+          <t>(089)383366</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2028/09/16</t>
         </is>
       </c>
     </row>
@@ -5172,32 +5172,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>悅豪大飯店</t>
+          <t>娜路彎銀河酒店</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>新竹市東區復興路22號</t>
+          <t>臺東縣台東市豐興路66號</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(03)5267890</t>
+          <t>(089)225000#8263</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2029/07/20</t>
+          <t>2028/09/03</t>
         </is>
       </c>
     </row>
@@ -5209,22 +5209,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>挪威森林頂級汽車旅館</t>
+          <t>悅徠舘</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>新北市板橋區和平路14巷3號</t>
+          <t>桃園市龜山區興華三街18號2樓之1</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>(02)29562211</t>
+          <t>(03)3280177</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2029/09/30</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -5246,22 +5246,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>旅行邦尼</t>
+          <t>悅豪大飯店</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>新北市淡水區中山路87巷7號</t>
+          <t>新竹市東區復興路22號</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(09)28824850</t>
+          <t>(03)5267890</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2029/01/05</t>
+          <t>2029/07/20</t>
         </is>
       </c>
     </row>
@@ -5283,22 +5283,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>旅悅國際青年旅館</t>
+          <t>挪威森林頂級汽車旅館</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>高雄市前鎮區三多三路211號3樓及4樓</t>
+          <t>新北市板橋區和平路14巷3號</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(07)3359006</t>
+          <t>(02)29562211</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2027/10/13</t>
+          <t>2029/09/30</t>
         </is>
       </c>
     </row>
@@ -5320,32 +5320,32 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>桃園大溪笠復威斯汀度假酒店</t>
+          <t>旅行邦尼</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>桃園市大溪區日新路166號</t>
+          <t>新北市淡水區中山路87巷7號</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>(03)2725035</t>
+          <t>(09)28824850</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2029/01/05</t>
         </is>
       </c>
     </row>
@@ -5357,32 +5357,32 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>桃園喜來登酒店</t>
+          <t>旅悅國際青年旅館</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>桃園市大園區大觀路777號</t>
+          <t>高雄市前鎮區三多三路211號3樓及4樓</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>(03)3850000#2605</t>
+          <t>(07)3359006</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026/10/29</t>
+          <t>2027/10/13</t>
         </is>
       </c>
     </row>
@@ -5394,22 +5394,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>泰安觀止溫泉會館</t>
+          <t>桃園大溪笠復威斯汀度假酒店</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>苗栗縣泰安鄉錦水村圓墩58-7號</t>
+          <t>桃園市大溪區日新路166號</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(037)941951#527</t>
+          <t>(03)2725035</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2028/06/25</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -5431,32 +5431,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>海福花園飯店</t>
+          <t>桃園喜來登酒店</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>金門縣金沙鎮高陽路1號</t>
+          <t>桃園市大園區大觀路777號</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>(082)353888</t>
+          <t>(03)3850000#2605</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2029/09/01</t>
+          <t>2026/10/29</t>
         </is>
       </c>
     </row>
@@ -5468,32 +5468,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>海霞您的家</t>
+          <t>泰安觀止溫泉會館</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>新北市貢寮區仁里里14鄰仁愛路38號</t>
+          <t>苗栗縣泰安鄉錦水村圓墩58-7號</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>(09)35204895</t>
+          <t>(037)941951#527</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2028/06/25</t>
         </is>
       </c>
     </row>
@@ -5505,32 +5505,32 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>海灣假日酒店</t>
+          <t>海福花園飯店</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>新北市深坑區北深路3段265號</t>
+          <t>金門縣金沙鎮高陽路1號</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>(02)77035880</t>
+          <t>(082)353888</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2028/12/17</t>
+          <t>2029/09/01</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>神隱國度民宿</t>
+          <t>海霞您的家</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>新北市瑞芳區崙頂路90號</t>
+          <t>新北市貢寮區仁里里14鄰仁愛路38號</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>(09)05788650</t>
+          <t>(09)35204895</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5579,22 +5579,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>秧悦美地度假酒店</t>
+          <t>海灣假日酒店</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>花蓮縣吉安鄉干城村干城二街95-9號</t>
+          <t>新北市深坑區北深路3段265號</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>(03)8129168#2701</t>
+          <t>(02)77035880</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2028/12/17</t>
         </is>
       </c>
     </row>
@@ -5616,22 +5616,22 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>秘境41</t>
+          <t>神隱國度民宿</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>桃園市大溪區興和里中央路41號</t>
+          <t>新北市瑞芳區崙頂路90號</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>(03)3887111</t>
+          <t>(09)05788650</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2027/12/10</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -5653,32 +5653,32 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>秘境民宿</t>
+          <t>秧悦美地度假酒店</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>屏東縣東港鎮屏東縣東港鎮水源路223號(新和段737-3地號)</t>
+          <t>花蓮縣吉安鄉干城村干城二街95-9號</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(08)8333345</t>
+          <t>(03)8129168#2701</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2029/01/18</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -5690,32 +5690,32 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>高雄中央公園英迪格酒店</t>
+          <t>秘境41</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>高雄市新興區中山一路4號</t>
+          <t>桃園市大溪區興和里中央路41號</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(07)2721555#301</t>
+          <t>(03)3887111</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2027/12/10</t>
         </is>
       </c>
     </row>
@@ -5727,22 +5727,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>高雄商旅</t>
+          <t>秘境民宿</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>高雄市新興區民族二路33號1、4~10樓；37號1、3~10樓</t>
+          <t>屏東縣東港鎮屏東縣東港鎮水源路223號(新和段737-3地號)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(09)19546590</t>
+          <t>(08)8333345</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2029/01/18</t>
         </is>
       </c>
     </row>
@@ -5764,22 +5764,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>高雄富野渡假酒店</t>
+          <t>茶田關舍民宿</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>高雄市前鎮區瑞田街99號</t>
+          <t>臺東縣關山鎮豐泉里3鄰平等路99號</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(07)8215299#7102</t>
+          <t>(089)812098</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2029/02/09</t>
+          <t>2029/10/16</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>高雄圓山大飯店</t>
+          <t>高雄中央公園英迪格酒店</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>高雄市鳥松區圓山路2號</t>
+          <t>高雄市新興區中山一路4號</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(07)3706007#519</t>
+          <t>(07)2721555#301</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>高雄福華大飯店</t>
+          <t>高雄商旅</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5848,22 +5848,22 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>高雄市新興區七賢一路311號</t>
+          <t>高雄市新興區民族二路33號1、4~10樓；37號1、3~10樓</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>(07)2307737</t>
+          <t>(09)19546590</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026/11/16</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>國聯大飯店</t>
+          <t>高雄富野渡假酒店</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>臺北市大安區光復南路200號</t>
+          <t>高雄市前鎮區瑞田街99號</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>(02)27731515#184</t>
+          <t>(07)8215299#7102</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2029/09/15</t>
+          <t>2029/02/09</t>
         </is>
       </c>
     </row>
@@ -5912,32 +5912,32 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>基拉耳景觀民宿</t>
+          <t>高雄圓山大飯店</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>桃園市復興區溪口路16巷29號</t>
+          <t>高雄市鳥松區圓山路2號</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>(02)23965188#594</t>
+          <t>(07)3706007#519</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2028/06/15</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -5949,32 +5949,32 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>將捷金鬱金香酒店</t>
+          <t>高雄福華大飯店</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>新北市淡水區中正路1段2之1號(A區地上3至6層、B區地上1至5層、C區地下3層至地上3層)</t>
+          <t>高雄市新興區七賢一路311號</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(02)26218555#2913</t>
+          <t>(07)2307737</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2027/04/14</t>
+          <t>2026/11/16</t>
         </is>
       </c>
     </row>
@@ -5986,22 +5986,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>康橋商旅-六合夜市七賢館</t>
+          <t>國聯大飯店</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>高雄市新興區同愛街28號1樓、30號</t>
+          <t>臺北市大安區光復南路200號</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>(07)288-5588</t>
+          <t>(02)27731515#184</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2029/09/15</t>
         </is>
       </c>
     </row>
@@ -6023,22 +6023,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>康橋商旅臺南赤崁樓館</t>
+          <t>基拉耳景觀民宿</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>臺南市中西區赤崁里民權路二段97號1至8樓</t>
+          <t>桃園市復興區溪口路16巷29號</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(06)2253377</t>
+          <t>(02)23965188#594</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2029/09/02</t>
+          <t>2028/06/15</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>康橋慢旅</t>
+          <t>將捷金鬱金香酒店</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>臺南市中西區民生路二段416號</t>
+          <t>新北市淡水區中正路1段2之1號(A區地上3至6層、B區地上1至5層、C區地下3層至地上3層)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(06)2805566</t>
+          <t>(02)26218555#2913</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2029/09/02</t>
+          <t>2027/04/14</t>
         </is>
       </c>
     </row>
@@ -6097,32 +6097,32 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>捷絲旅 臺南虎山館</t>
+          <t>康橋商旅-六合夜市七賢館</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>臺南市仁德區成功里5鄰文華路2段300號1~9樓，地下一、二樓</t>
+          <t>高雄市新興區同愛街28號1樓、30號</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(06)2662218#8321</t>
+          <t>(07)288-5588</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2028/02/13</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -6134,32 +6134,32 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>捷絲旅臺北三重館</t>
+          <t>康橋商旅-六合夜市中正館</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>新北市三重區三和路四段107-1號</t>
+          <t>高雄市前金區中正四路112號2至8樓</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(02)22806111#8304</t>
+          <t>(07)2881166</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2028/10/12</t>
+          <t>2029/10/13</t>
         </is>
       </c>
     </row>
@@ -6171,22 +6171,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>捷絲旅西門町店</t>
+          <t>康橋商旅臺南赤崁樓館</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路一段41號5樓至9樓</t>
+          <t>臺南市中西區赤崁里民權路二段97號1至8樓</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(02)25215000</t>
+          <t>(06)2253377</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2027/05/12</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6208,32 +6208,32 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>捷絲旅花蓮中正館</t>
+          <t>康橋商旅-高雄-光榮碼頭館</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市主睦里14鄰中正路396號</t>
+          <t>高雄市苓雅區青年二路169號</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>(03)8900069#8104</t>
+          <t>(07)3343377</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>捷絲旅高雄中正館</t>
+          <t>康橋商旅-高雄站前館</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6255,22 +6255,22 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>高雄市苓雅區中正一路134號</t>
+          <t>高雄市三民區建國二路295號</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>(07)9733587#8104</t>
+          <t>(07)2386677</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6282,32 +6282,32 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>捷絲旅高雄站前館</t>
+          <t>康橋慢旅</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>高雄市新興區中山一路280號1至14樓</t>
+          <t>臺南市中西區民生路二段416號</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>(07)9733587#8104</t>
+          <t>(06)2805566</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2028/09/29</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6319,22 +6319,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>捷絲旅臺大尊賢館</t>
+          <t>捷絲旅 臺南虎山館</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>臺北市大安區羅斯福路四段83號1-10樓</t>
+          <t>臺南市仁德區成功里5鄰文華路2段300號1~9樓，地下一、二樓</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>(02)77355088</t>
+          <t>(06)2662218#8321</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/02/13</t>
         </is>
       </c>
     </row>
@@ -6356,32 +6356,32 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>捷絲旅礁溪館</t>
+          <t>捷絲旅臺北三重館</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉德陽路24巷8號、10號</t>
+          <t>新北市三重區三和路四段107-1號</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>(03)9102000#8104</t>
+          <t>(02)22806111#8304</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2027/01/07</t>
+          <t>2028/10/12</t>
         </is>
       </c>
     </row>
@@ -6393,32 +6393,32 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>清新溫泉飯店</t>
+          <t>捷絲旅西門町店</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>臺中市烏日區溫泉路2號</t>
+          <t>臺北市中正區中華路一段41號5樓至9樓</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(04)23831088#7602</t>
+          <t>(02)25215000</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2027/05/12</t>
         </is>
       </c>
     </row>
@@ -6430,32 +6430,32 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>統一谷關渡假村</t>
+          <t>捷絲旅花蓮中正館</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>臺中市和平區博愛里東關路一段188號</t>
+          <t>花蓮縣花蓮市主睦里14鄰中正路396號</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(04)25950000</t>
+          <t>(03)8900069#8104</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2028/01/06</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -6467,32 +6467,32 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>統一渡假村</t>
+          <t>捷絲旅高雄中正館</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>新竹縣關西鎮金山里34號</t>
+          <t>高雄市苓雅區中正一路134號</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(03)5478888</t>
+          <t>(07)9733587#8104</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2027/12/20</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -6504,32 +6504,32 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>鹿港澄悅酒店</t>
+          <t>捷絲旅高雄站前館</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮中正路598號1樓、5至8樓</t>
+          <t>高雄市新興區中山一路280號1至14樓</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(04)7785727</t>
+          <t>(07)9733587#8104</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2029/03/02</t>
+          <t>2028/09/29</t>
         </is>
       </c>
     </row>
@@ -6541,32 +6541,32 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>傑仕堡有氧酒店</t>
+          <t>捷絲旅臺大尊賢館</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>新北市板橋區縣民大道2段275號、275號2至17樓、277號2樓</t>
+          <t>臺北市大安區羅斯福路四段83號1-10樓</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(02)77273000#54083</t>
+          <t>(02)77355088</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026/10/16</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6578,32 +6578,32 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>凱旋酒店</t>
+          <t>捷絲旅礁溪館</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>臺北市內湖區江南街55號3樓至9樓</t>
+          <t>宜蘭縣礁溪鄉德陽路24巷8號、10號</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>(02)87527888#6203</t>
+          <t>(03)9102000#8104</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026/12/10</t>
+          <t>2027/01/07</t>
         </is>
       </c>
     </row>
@@ -6615,32 +6615,32 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>凱達大飯店</t>
+          <t>清新溫泉飯店</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>臺北市萬華區艋舺大道167號1-26樓</t>
+          <t>臺中市烏日區溫泉路2號</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>(02)23836789#6321</t>
+          <t>(04)23831088#7602</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2027/06/02</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -6652,32 +6652,32 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>凱撒大飯店</t>
+          <t>統一谷關渡假村</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁路6號</t>
+          <t>臺中市和平區博愛里東關路一段188號</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>(08)8861888</t>
+          <t>(04)25950000</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2028/09/16</t>
+          <t>2028/01/06</t>
         </is>
       </c>
     </row>
@@ -6689,22 +6689,22 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>勝利127民宿</t>
+          <t>統一渡假村</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>屏東縣屏東市勝利路127號</t>
+          <t>新竹縣關西鎮金山里34號</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>(08)7320099</t>
+          <t>(03)5478888</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026/12/14</t>
+          <t>2027/12/20</t>
         </is>
       </c>
     </row>
@@ -6726,22 +6726,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>勝利131民宿</t>
+          <t>鹿港澄悅酒店</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>屏東縣屏東市勝利路131號</t>
+          <t>彰化縣鹿港鎮中正路598號1樓、5至8樓</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>(08)7320099</t>
+          <t>(04)7785727</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026/12/14</t>
+          <t>2029/03/02</t>
         </is>
       </c>
     </row>
@@ -6763,7 +6763,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>寒居酒店</t>
+          <t>凱旋酒店</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6773,22 +6773,22 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>臺北市中山區松江路116號1樓至9樓</t>
+          <t>臺北市內湖區江南街55號3樓至9樓</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(02)66008000#8886</t>
+          <t>(02)87527888#6203</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2028/07/17</t>
+          <t>2026/12/10</t>
         </is>
       </c>
     </row>
@@ -6800,32 +6800,32 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>寒軒國際大飯店</t>
+          <t>凱達大飯店</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>高雄市苓雅區四維三路三十三號</t>
+          <t>臺北市萬華區艋舺大道167號1-26樓</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(0980)556224</t>
+          <t>(02)23836789#6321</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2028/12/11</t>
+          <t>2027/06/02</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>富光大旅社</t>
+          <t>凱撒大飯店</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6847,22 +6847,22 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公園路19-7號</t>
+          <t>屏東縣恆春鎮墾丁路6號</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(08)7345656</t>
+          <t>(08)8861888</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2028/05/28</t>
+          <t>2028/09/16</t>
         </is>
       </c>
     </row>
@@ -6874,32 +6874,32 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>富信大飯店</t>
+          <t>勝利127民宿</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>新北市汐止區大同路一段152號</t>
+          <t>屏東縣屏東市勝利路127號</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>(02)26416422#5112</t>
+          <t>(08)7320099</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2028/03/13</t>
+          <t>2026/12/14</t>
         </is>
       </c>
     </row>
@@ -6911,32 +6911,32 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>富翔大飯店</t>
+          <t>勝利131民宿</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>宜蘭縣宜蘭市校舍路19號</t>
+          <t>屏東縣屏東市勝利路131號</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>(03)9388386</t>
+          <t>(08)7320099</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2029/09/28</t>
+          <t>2026/12/14</t>
         </is>
       </c>
     </row>
@@ -6948,32 +6948,32 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>尊爵大飯店</t>
+          <t>寒居酒店</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>桃園市桃園區莊敬路一段300號</t>
+          <t>臺北市中山區松江路116號1樓至9樓</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>(03)3169090#8502</t>
+          <t>(02)66008000#8886</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026/12/21</t>
+          <t>2028/07/17</t>
         </is>
       </c>
     </row>
@@ -6985,32 +6985,32 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>尊爵天際大飯店</t>
+          <t>寒軒國際大飯店</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>桃園市蘆竹區南崁路一段108號</t>
+          <t>高雄市苓雅區四維三路三十三號</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>(03)2228100#6081</t>
+          <t>(0980)556224</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2028/08/31</t>
+          <t>2028/12/11</t>
         </is>
       </c>
     </row>
@@ -7022,22 +7022,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>惠來谷關溫泉會館</t>
+          <t>富光大旅社</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>臺中市和平區東關路一段溫泉巷十號</t>
+          <t>屏東縣屏東市公園路19-7號</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>(04)25951998#621</t>
+          <t>(08)7345656</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2029/08/13</t>
+          <t>2028/05/28</t>
         </is>
       </c>
     </row>
@@ -7059,32 +7059,32 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>提米好旅</t>
+          <t>富信大飯店</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>彰化縣彰化市成功路277號</t>
+          <t>新北市汐止區大同路一段152號</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>(04)7061086#9</t>
+          <t>(02)26416422#5112</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>2028/03/13</t>
         </is>
       </c>
     </row>
@@ -7096,32 +7096,32 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>揚昊民宿</t>
+          <t>富翔大飯店</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之6號</t>
+          <t>宜蘭縣宜蘭市校舍路19號</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>(037)747711#9</t>
+          <t>(03)9388386</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2028/09/08</t>
+          <t>2029/09/28</t>
         </is>
       </c>
     </row>
@@ -7133,32 +7133,32 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>晶泉丰旅</t>
+          <t>尊爵大飯店</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉溫泉路67號2至10樓</t>
+          <t>桃園市桃園區莊敬路一段300號</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>(03)9100000#6105</t>
+          <t>(03)3169090#8502</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2027/05/22</t>
+          <t>2026/12/21</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>智醫康寓</t>
+          <t>尊爵天際大飯店</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7180,22 +7180,22 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>桃園市桃園區民生路107號1-3樓及7-20樓</t>
+          <t>桃園市蘆竹區南崁路一段108號</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>(03)3362575</t>
+          <t>(03)2228100#6081</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026/10/30</t>
+          <t>2028/08/31</t>
         </is>
       </c>
     </row>
@@ -7207,32 +7207,32 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>渴望會館</t>
+          <t>惠來谷關溫泉會館</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>桃園市龍潭區渴望路428號3-5樓</t>
+          <t>臺中市和平區東關路一段溫泉巷十號</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>(03)4072999#7110</t>
+          <t>(04)25951998#621</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2029/08/13</t>
         </is>
       </c>
     </row>
@@ -7244,32 +7244,32 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>然一酒店</t>
+          <t>提米好旅</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>高雄市前鎮區中山二路199號</t>
+          <t>彰化縣彰化市成功路277號</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>(07)9730186#1666</t>
+          <t>(04)7061086#9</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2027/06/03</t>
+          <t>2027/11/27</t>
         </is>
       </c>
     </row>
@@ -7281,22 +7281,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>發現號特色民宿</t>
+          <t>揚昊民宿</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>屏東縣林邊鄉崎峰村裕後路90號</t>
+          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之6號</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>(08)8750300</t>
+          <t>(037)747711#9</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2028/09/08</t>
         </is>
       </c>
     </row>
@@ -7318,32 +7318,32 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>華泰瑞苑</t>
+          <t>晶泉丰旅</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮公園路101號</t>
+          <t>宜蘭縣礁溪鄉溫泉路67號2至10樓</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>(08)8863666</t>
+          <t>(03)9100000#6105</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2027/06/21</t>
+          <t>2027/05/22</t>
         </is>
       </c>
     </row>
@@ -7355,32 +7355,32 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>華園大飯店草衙館</t>
+          <t>智醫康寓</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>高雄市前鎮區中安路一號</t>
+          <t>桃園市桃園區民生路107號1-3樓及7-20樓</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>(07)2410123#220</t>
+          <t>(03)3362575</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2029/10/06</t>
+          <t>2026/10/30</t>
         </is>
       </c>
     </row>
@@ -7392,32 +7392,32 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>貳十二度行旅</t>
+          <t>湛藍海寓民宿</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>宜蘭縣蘇澳鎮信義路177號</t>
+          <t>嘉義縣東石鄉東石村12鄰東石6之16號</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>(03)9901888</t>
+          <t>(05)3730252</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2029/05/24</t>
+          <t>2029/10/13</t>
         </is>
       </c>
     </row>
@@ -7429,32 +7429,32 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>陽明山天籟渡假酒店</t>
+          <t>渴望會館</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>新北市金山區名流路1之6號、1之7號、1之9號、1之9號5樓及1之9號5樓之1至之8</t>
+          <t>桃園市龍潭區渴望路428號3-5樓</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>(02)24080400#1700</t>
+          <t>(03)4072999#7110</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2029/02/11</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -7466,32 +7466,32 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>雅霖大飯店</t>
+          <t>然一酒店</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市同和路100號</t>
+          <t>高雄市前鎮區中山二路199號</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>(06)9261366</t>
+          <t>(07)9730186#1666</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2027/06/03</t>
         </is>
       </c>
     </row>
@@ -7503,32 +7503,32 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>雲品溫泉酒店日月潭</t>
+          <t>發現號特色民宿</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉水社村中正路23號</t>
+          <t>屏東縣林邊鄉崎峰村裕後路90號</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>(049)2212959</t>
+          <t>(08)8750300</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2029/05/05</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -7540,32 +7540,32 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>雲頂國際商旅</t>
+          <t>華泰瑞苑</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>臺南市南區大同路二段530號</t>
+          <t>屏東縣恆春鎮公園路101號</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>(06)2687766</t>
+          <t>(08)8863666</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2029/02/25</t>
+          <t>2027/06/21</t>
         </is>
       </c>
     </row>
@@ -7577,22 +7577,22 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>圓山大飯店</t>
+          <t>華園大飯店草衙館</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路4段1巷1號</t>
+          <t>高雄市前鎮區中安路一號</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>(02)28861818#1007</t>
+          <t>(07)2410123#220</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2029/10/06</t>
         </is>
       </c>
     </row>
@@ -7614,22 +7614,22 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>奧斯卡去旅行民宿</t>
+          <t>貳十二度行旅</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>臺東縣臺東市興安路一段167號</t>
+          <t>宜蘭縣蘇澳鎮信義路177號</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>(0910)633944</t>
+          <t>(03)9901888</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2027/01/29</t>
+          <t>2029/05/24</t>
         </is>
       </c>
     </row>
@@ -7651,32 +7651,32 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>奧斯卡民宿</t>
+          <t>陽明山天籟渡假酒店</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>臺東縣台東市興安路1段175號</t>
+          <t>新北市金山區名流路1之6號、1之7號、1之9號、1之9號5樓及1之9號5樓之1至之8</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>(0965)329000</t>
+          <t>(02)24080400#1700</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2027/01/18</t>
+          <t>2029/02/11</t>
         </is>
       </c>
     </row>
@@ -7688,22 +7688,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>新竹安捷國際酒店</t>
+          <t>雅霖大飯店</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>新竹縣竹北市復興三路二段168號14樓-18樓</t>
+          <t>澎湖縣馬公市同和路100號</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>(03)6209777#660</t>
+          <t>(06)9261366</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2028/07/13</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -7725,32 +7725,32 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>新竹老爺大酒店</t>
+          <t>雲品溫泉酒店日月潭</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>新竹市東區光復路一段227號</t>
+          <t>南投縣魚池鄉水社村中正路23號</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>(03)5631285#204</t>
+          <t>(049)2212959</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2029/05/05</t>
         </is>
       </c>
     </row>
@@ -7762,32 +7762,32 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>新竹喜來登大飯店</t>
+          <t>雲頂國際商旅</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>新竹縣竹北市光明六路東一段265號</t>
+          <t>臺南市南區大同路二段530號</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>(03)6206126</t>
+          <t>(06)2687766</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2029/02/25</t>
         </is>
       </c>
     </row>
@@ -7799,32 +7799,32 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>新竹福華大飯店</t>
+          <t>圓山大飯店</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>新竹市中正路178號</t>
+          <t>臺北市中山區中山北路4段1巷1號</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>(03)5282323#5303</t>
+          <t>(02)28861818#1007</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -7836,22 +7836,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>新南一二文創商行</t>
+          <t>奧斯卡去旅行民宿</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>桃園市大溪區中山路１２號</t>
+          <t>臺東縣臺東市興安路一段167號</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>(03)3884466</t>
+          <t>(0910)633944</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2029/02/05</t>
+          <t>2027/01/29</t>
         </is>
       </c>
     </row>
@@ -7873,32 +7873,32 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>新悦花園酒店</t>
+          <t>奧斯卡民宿</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>嘉義市東區後湖里6鄰保順路69號</t>
+          <t>臺東縣台東市興安路1段175號</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>(05)2777266#5801</t>
+          <t>(0965)329000</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2027/04/07</t>
+          <t>2027/01/18</t>
         </is>
       </c>
     </row>
@@ -7910,32 +7910,32 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>溪頭福華渡假飯店-溪頭漢光樓</t>
+          <t>新竹安捷國際酒店</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>南投縣鹿谷鄉森林巷11、12號</t>
+          <t>新竹縣竹北市復興三路二段168號14樓-18樓</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>(049)2612588#3005</t>
+          <t>(03)6209777#660</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2028/12/01</t>
+          <t>2028/07/13</t>
         </is>
       </c>
     </row>
@@ -7947,22 +7947,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>溪邊小築民宿</t>
+          <t>新竹老爺大酒店</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>新北市瑞芳區祈堂路133號</t>
+          <t>新竹市東區光復路一段227號</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>(02)24961191</t>
+          <t>(03)5631285#204</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2029/06/21</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -7984,32 +7984,32 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>煙波大飯店臺南館</t>
+          <t>新竹喜來登大飯店</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>臺南市中西區永福路1段269號1-12樓及地下一層至三層</t>
+          <t>新竹縣竹北市光明六路東一段265號</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>(06)2156000#1171</t>
+          <t>(03)6206126</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2029/06/09</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -8021,32 +8021,32 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>煙波大飯店宜蘭館</t>
+          <t>新竹福華大飯店</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>宜蘭縣宜蘭市凱旋路135號 、135號2至9樓</t>
+          <t>新竹市中正路178號</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>(09)9256899#1171</t>
+          <t>(03)5282323#5303</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2029/05/06</t>
+          <t>2026/10/26</t>
         </is>
       </c>
     </row>
@@ -8058,32 +8058,32 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮太魯閣山闊館</t>
+          <t>新南一二文創商行</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村草林10-7號</t>
+          <t>桃園市大溪區中山路１２號</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>(03)8612000#1470</t>
+          <t>(03)3884466</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026/11/05</t>
+          <t>2029/02/05</t>
         </is>
       </c>
     </row>
@@ -8095,22 +8095,22 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮太魯閣沁海館</t>
+          <t>新悦花園酒店</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村6鄰草林10之6號</t>
+          <t>嘉義市東區後湖里6鄰保順路69號</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>(03)8228835#1174</t>
+          <t>(05)2777266#5801</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2029/04/19</t>
+          <t>2027/04/07</t>
         </is>
       </c>
     </row>
@@ -8132,32 +8132,32 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮館</t>
+          <t>溪頭福華渡假飯店-溪頭漢光樓</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市民立里1鄰中美路142號</t>
+          <t>南投縣鹿谷鄉森林巷11、12號</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>(03)8228835#1174</t>
+          <t>(049)2612588#3005</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2029/04/19</t>
+          <t>2028/12/01</t>
         </is>
       </c>
     </row>
@@ -8169,32 +8169,32 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>煙波花時間 宜蘭傳藝</t>
+          <t>溪邊小築民宿</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉五濱路二段201號</t>
+          <t>新北市瑞芳區祈堂路133號</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>(03)9256899#1171</t>
+          <t>(02)24961191</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2027/07/09</t>
+          <t>2029/06/21</t>
         </is>
       </c>
     </row>
@@ -8206,22 +8206,22 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>煙波花時間 花蓮</t>
+          <t>煙波大飯店臺南館</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村草林10-5號2~6樓</t>
+          <t>臺南市中西區永福路1段269號1-12樓及地下一層至三層</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>(03)8612000#1470</t>
+          <t>(06)2156000#1171</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026/11/16</t>
+          <t>2029/06/09</t>
         </is>
       </c>
     </row>
@@ -8243,32 +8243,32 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>瑞穗天合國際觀光酒店</t>
+          <t>煙波大飯店宜蘭館</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>花蓮縣瑞穗鄉溫泉路二段368號</t>
+          <t>宜蘭縣宜蘭市凱旋路135號 、135號2至9樓</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>(03)8876000#3260</t>
+          <t>(09)9256899#1171</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2028/01/19</t>
+          <t>2029/05/06</t>
         </is>
       </c>
     </row>
@@ -8280,32 +8280,32 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>裕元花園酒店</t>
+          <t>煙波大飯店花蓮太魯閣山闊館</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>臺中市西屯區臺灣大道四段610號</t>
+          <t>花蓮縣新城鄉順安村草林10-7號</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>(04)24655660#5030</t>
+          <t>(03)8612000#1470</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2027/11/19</t>
+          <t>2026/11/05</t>
         </is>
       </c>
     </row>
@@ -8317,32 +8317,32 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>遇見民宿</t>
+          <t>煙波大飯店花蓮太魯閣沁海館</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>屏東縣東港鎮水源路221號(新和段737-4地號)</t>
+          <t>花蓮縣新城鄉順安村6鄰草林10之6號</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>(08)8333345</t>
+          <t>(03)8228835#1174</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2029/04/19</t>
         </is>
       </c>
     </row>
@@ -8354,32 +8354,32 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>頌華私墅肆區民宿</t>
+          <t>煙波大飯店花蓮館</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>澎湖縣湖西鄉許家村6鄰港子尾120之5號</t>
+          <t>花蓮縣花蓮市民立里1鄰中美路142號</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>(06)9212953</t>
+          <t>(03)8228835#1174</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2029/01/25</t>
+          <t>2029/04/19</t>
         </is>
       </c>
     </row>
@@ -8391,32 +8391,32 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>嘉仕特飯店</t>
+          <t>煙波花時間 宜蘭傳藝</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>桃園市桃園區中山路203號</t>
+          <t>宜蘭縣五結鄉五濱路二段201號</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>(03)3343999</t>
+          <t>(03)9256899#1171</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>2027/07/09</t>
         </is>
       </c>
     </row>
@@ -8428,32 +8428,32 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>嘉義富野渡假酒店</t>
+          <t>煙波花時間 花蓮</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>嘉義縣民雄鄉三興村升學一街3、5、7、9、11、13、15、17、19、21、23、25、27號</t>
+          <t>花蓮縣新城鄉順安村草林10-5號2~6樓</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>(05)2721688</t>
+          <t>(03)8612000#1470</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2028/08/12</t>
+          <t>2026/11/16</t>
         </is>
       </c>
     </row>
@@ -8465,32 +8465,32 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>嘉義智選假日酒店</t>
+          <t>瑞穗天合國際觀光酒店</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>嘉義市西區中興路69號B2至13層樓</t>
+          <t>花蓮縣瑞穗鄉溫泉路二段368號</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>(05)2335899#801</t>
+          <t>(03)8876000#3260</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2027/11/24</t>
+          <t>2028/01/19</t>
         </is>
       </c>
     </row>
@@ -8502,32 +8502,32 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>嘉義福容voco酒店</t>
+          <t>裕元花園酒店</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>嘉義市西區世賢路一段789號B4-4樓、7樓、16樓-32樓</t>
+          <t>臺中市西屯區臺灣大道四段610號</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>(05)232338971</t>
+          <t>(04)24655660#5030</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2029/06/15</t>
+          <t>2027/11/19</t>
         </is>
       </c>
     </row>
@@ -8539,22 +8539,22 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>夢想森林親子民宿</t>
+          <t>遇見民宿</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉三星鄉大德路二段613號</t>
+          <t>屏東縣東港鎮水源路221號(新和段737-4地號)</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>(03)9898113</t>
+          <t>(08)8333345</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -8576,32 +8576,32 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>榮美金鬱金香酒店</t>
+          <t>頌華私墅肆區民宿</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>臺南市北區海安路三段50號</t>
+          <t>澎湖縣湖西鄉許家村6鄰港子尾120之5號</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>(06)2200800#6001</t>
+          <t>(06)9212953</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2027/11/04</t>
+          <t>2029/01/25</t>
         </is>
       </c>
     </row>
@@ -8613,22 +8613,22 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>榮興金鬱金香酒店</t>
+          <t>嘉仕特飯店</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>臺南市中西區民族路二段128號</t>
+          <t>桃園市桃園區中山路203號</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>(06)2200800#6006</t>
+          <t>(03)3343999</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2027/11/04</t>
+          <t>2027/11/27</t>
         </is>
       </c>
     </row>
@@ -8650,32 +8650,32 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>福美民宿</t>
+          <t>嘉義富野渡假酒店</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>臺東縣台東市精誠路241號</t>
+          <t>嘉義縣民雄鄉三興村升學一街3、5、7、9、11、13、15、17、19、21、23、25、27號</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>(089)328466</t>
+          <t>(05)2721688</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2027/01/09</t>
+          <t>2028/08/12</t>
         </is>
       </c>
     </row>
@@ -8687,32 +8687,32 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>福容大飯店 臺北二館</t>
+          <t>嘉義智選假日酒店</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>新北市深坑區北深路三段236號</t>
+          <t>嘉義市西區中興路69號B2至13層樓</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>(02)26620088#186</t>
+          <t>(05)2335899#801</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2028/01/05</t>
+          <t>2027/11/24</t>
         </is>
       </c>
     </row>
@@ -8724,32 +8724,32 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>福容大飯店 桃園</t>
+          <t>嘉義福容voco酒店</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>桃園市桃園區同安里大興西路一段200號</t>
+          <t>嘉義市西區世賢路一段789號B4-4樓、7樓、16樓-32樓</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>(03)3265800#300</t>
+          <t>(05)232338971</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2027/12/17</t>
+          <t>2029/06/15</t>
         </is>
       </c>
     </row>
@@ -8761,32 +8761,32 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>福容大飯店 桃園機場捷運 A8</t>
+          <t>夢想森林親子民宿</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>桃園市龜山區復興一路2號3樓</t>
+          <t>宜蘭縣三星鄉三星鄉大德路二段613號</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>(03)3285688#8770</t>
+          <t>(03)9898113</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2027/08/12</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -8798,32 +8798,32 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>福容大飯店 高雄</t>
+          <t>榮美金鬱金香酒店</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區五福四路45號</t>
+          <t>臺南市北區海安路三段50號</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>(07)5317777#7782</t>
+          <t>(06)2200800#6001</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2028/08/14</t>
+          <t>2027/11/04</t>
         </is>
       </c>
     </row>
@@ -8835,32 +8835,32 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>福容大飯店 淡水漁人碼頭</t>
+          <t>榮興金鬱金香酒店</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>新北市淡水區觀海路83號</t>
+          <t>臺南市中西區民族路二段128號</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>(02)2805 9958#8178</t>
+          <t>(06)2200800#6006</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2028/11/16</t>
+          <t>2027/11/04</t>
         </is>
       </c>
     </row>
@@ -8872,32 +8872,32 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>福容大飯店　福隆</t>
+          <t>福美民宿</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>新北市貢寮區福隆里福隆街41號</t>
+          <t>臺東縣台東市精誠路241號</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>(02)24992381</t>
+          <t>(089)328466</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/01/09</t>
         </is>
       </c>
     </row>
@@ -8909,32 +8909,32 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>福容大飯店 墾丁</t>
+          <t>福容大飯店 臺北二館</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮船帆路1000號</t>
+          <t>新北市深坑區北深路三段236號</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>(08)8856969#340</t>
+          <t>(02)26620088#186</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2028/05/28</t>
+          <t>2028/01/05</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>福容大飯店 麗寶樂園</t>
+          <t>福容大飯店 桃園</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>臺中市后里區福容路88號</t>
+          <t>桃園市桃園區同安里大興西路一段200號</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>(04)25571366#8343</t>
+          <t>(03)3265800#300</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2029/03/19</t>
+          <t>2027/12/17</t>
         </is>
       </c>
     </row>
@@ -8983,22 +8983,22 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>福容大飯店花蓮</t>
+          <t>福容大飯店 桃園機場捷運 A8</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市民生路51號</t>
+          <t>桃園市龜山區復興一路2號3樓</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>(03)8239988#7507</t>
+          <t>(03)3285688#8770</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2027/11/10</t>
+          <t>2027/08/12</t>
         </is>
       </c>
     </row>
@@ -9020,22 +9020,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>福容徠旅 水里</t>
+          <t>福容大飯店 高雄</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>南投縣水里鄉東三街51號1樓至6樓</t>
+          <t>高雄市鹽埕區五福四路45號</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>(049)2771888#5560</t>
+          <t>(07)5317777#7782</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2029/07/09</t>
+          <t>2028/08/14</t>
         </is>
       </c>
     </row>
@@ -9057,32 +9057,32 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>福容徠旅林口</t>
+          <t>福容大飯店 淡水漁人碼頭</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>桃園市龜山區文二一街68號</t>
+          <t>新北市淡水區觀海路83號</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>(03)3277388#300</t>
+          <t>(02)2805 9958#8178</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2027/12/03</t>
+          <t>2028/11/16</t>
         </is>
       </c>
     </row>
@@ -9094,22 +9094,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>福容徠旅高雄</t>
+          <t>福容大飯店　福隆</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>高雄市前金區永恆街3號6-14樓</t>
+          <t>新北市貢寮區福隆里福隆街41號</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>(07)2156688#6309</t>
+          <t>(02)24992381</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2029/03/17</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -9131,22 +9131,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>福華大飯店</t>
+          <t>福容大飯店 墾丁</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>臺北市大安區仁愛路三段160號</t>
+          <t>屏東縣恆春鎮船帆路1000號</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>(02)27002323#2411</t>
+          <t>(08)8856969#340</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2028/05/28</t>
         </is>
       </c>
     </row>
@@ -9168,32 +9168,32 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>福華石門水庫渡假飯店</t>
+          <t>福容大飯店 麗寶樂園</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>桃園市龍潭區民富街176號</t>
+          <t>臺中市后里區福容路88號</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>(03)4714888</t>
+          <t>(04)25571366#8343</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2027/11/10</t>
+          <t>2029/03/19</t>
         </is>
       </c>
     </row>
@@ -9205,22 +9205,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>福華國際文教會館</t>
+          <t>福容大飯店花蓮</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>臺北市大安區新生南路3段30號(住宿棟1樓及5樓至14樓)</t>
+          <t>花蓮縣花蓮市民生路51號</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>(02)77122323#2340</t>
+          <t>(03)8239988#7507</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2027/12/11</t>
+          <t>2027/11/10</t>
         </is>
       </c>
     </row>
@@ -9242,32 +9242,32 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>福爾摩沙遊艇酒店</t>
+          <t>福容徠旅 水里</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>臺南市安平區王城里13鄰安平路988號1至10樓</t>
+          <t>南投縣水里鄉東三街51號1樓至6樓</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>(06)3911313</t>
+          <t>(049)2771888#5560</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2027/02/27</t>
+          <t>2029/07/09</t>
         </is>
       </c>
     </row>
@@ -9279,32 +9279,32 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>綠意山莊民宿</t>
+          <t>福容徠旅林口</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之5號</t>
+          <t>桃園市龜山區文二一街68號</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>(037)747711#9</t>
+          <t>(03)3277388#300</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2028/09/08</t>
+          <t>2027/12/03</t>
         </is>
       </c>
     </row>
@@ -9316,32 +9316,32 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>綠藤輕旅</t>
+          <t>福容徠旅高雄</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>桃園市大園區中山南路二段673號</t>
+          <t>高雄市前金區永恆街3號6-14樓</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>(03)2873043</t>
+          <t>(07)2156688#6309</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2029/03/17</t>
         </is>
       </c>
     </row>
@@ -9353,32 +9353,32 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>維悅酒店</t>
+          <t>福華大飯店</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>臺南市安平區慶平路539號 1至5樓及地下1樓</t>
+          <t>臺北市大安區仁愛路三段160號</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>(06)2950888#1125</t>
+          <t>(02)27002323#2411</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2027/09/01</t>
+          <t>2026/10/26</t>
         </is>
       </c>
     </row>
@@ -9390,32 +9390,32 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>臺中逢甲智選假日酒店</t>
+          <t>福華石門水庫渡假飯店</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>臺中市西屯區福星北三街33巷28號</t>
+          <t>桃園市龍潭區民富街176號</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>(04)27083911#6101</t>
+          <t>(03)4714888</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/11/10</t>
         </is>
       </c>
     </row>
@@ -9427,22 +9427,22 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>臺邦商旅</t>
+          <t>福華國際文教會館</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>臺南市安平區永華二街199號</t>
+          <t>臺北市大安區新生南路3段30號(住宿棟1樓及5樓至14樓)</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>(06)2931800#8603</t>
+          <t>(02)77122323#2340</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/12/11</t>
         </is>
       </c>
     </row>
@@ -9464,22 +9464,22 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>遠雄悅來大飯店</t>
+          <t>福爾摩沙遊艇酒店</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>花蓮縣壽豐鄉鹽寮村山嶺18號</t>
+          <t>臺南市安平區王城里13鄰安平路988號1至10樓</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>(03)8123900#8266</t>
+          <t>(06)3911313</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2028/12/29</t>
+          <t>2027/02/27</t>
         </is>
       </c>
     </row>
@@ -9501,22 +9501,22 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>鳳山79 背包客</t>
+          <t>綠意山莊民宿</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>高雄市鳳山區黃埔新村東一巷79號</t>
+          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之5號</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>(07)5524545</t>
+          <t>(037)747711#9</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2028/12/03</t>
+          <t>2028/09/08</t>
         </is>
       </c>
     </row>
@@ -9538,32 +9538,32 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>劍湖山渡假大飯店</t>
+          <t>綠藤輕旅</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>雲林縣古坑鄉永光村大湖口67-8號</t>
+          <t>桃園市大園區中山南路二段673號</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>(05)5829900#7214</t>
+          <t>(03)2873043</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2027/06/03</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -9575,22 +9575,22 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>澄悅商旅</t>
+          <t>維悅酒店</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮埔崙里中正路510巷1號</t>
+          <t>臺南市安平區慶平路539號 1至5樓及地下1樓</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>(04)7785727</t>
+          <t>(06)2950888#1125</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2029/09/07</t>
+          <t>2027/09/01</t>
         </is>
       </c>
     </row>
@@ -9612,32 +9612,32 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>澎湖福朋喜來登酒店</t>
+          <t>臺中逢甲智選假日酒店</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市新店路197號</t>
+          <t>臺中市西屯區福星北三街33巷28號</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>(06)9279955#3701</t>
+          <t>(04)27083911#6101</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2028/05/27</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9649,32 +9649,32 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>澎澄飯店</t>
+          <t>臺邦商旅</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市同和路168號</t>
+          <t>臺南市安平區永華二街199號</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>(06)9235678#2103</t>
+          <t>(06)2931800#8603</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2029/08/03</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9686,32 +9686,32 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>緻麗伯爵酒店</t>
+          <t>遠雄悅來大飯店</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>雲林縣斗六市中山路6號</t>
+          <t>花蓮縣壽豐鄉鹽寮村山嶺18號</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>(05)5341666#3</t>
+          <t>(03)8123900#8266</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2029/02/10</t>
+          <t>2028/12/29</t>
         </is>
       </c>
     </row>
@@ -9723,22 +9723,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>緣羊軒民宿</t>
+          <t>鳳山79 背包客</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>臺東縣台東市南一街96號</t>
+          <t>高雄市鳳山區黃埔新村東一巷79號</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>089326400</t>
+          <t>(07)5524545</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026/12/05</t>
+          <t>2028/12/03</t>
         </is>
       </c>
     </row>
@@ -9760,32 +9760,32 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺北</t>
+          <t>劍湖山渡假大飯店</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
+          <t>雲林縣古坑鄉永光村大湖口67-8號</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>(02)29583000#7701</t>
+          <t>(05)5829900#7214</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2028/03/31</t>
+          <t>2027/06/03</t>
         </is>
       </c>
     </row>
@@ -9797,22 +9797,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺東</t>
+          <t>澄悅商旅</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>臺東縣台東市新站路260號</t>
+          <t>彰化縣鹿港鎮埔崙里中正路510巷1號</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>(089)231188#7187</t>
+          <t>(04)7785727</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2027/12/05</t>
+          <t>2029/09/07</t>
         </is>
       </c>
     </row>
@@ -9834,32 +9834,32 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>墾丁夏都沙灘酒店</t>
+          <t>澎湖福朋喜來登酒店</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁路451號</t>
+          <t>澎湖縣馬公市新店路197號</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>(0910)371823</t>
+          <t>(06)9279955#3701</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2028/03/09</t>
+          <t>2028/05/27</t>
         </is>
       </c>
     </row>
@@ -9871,32 +9871,32 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>墾丁福華渡假飯店</t>
+          <t>澎澄飯店</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
+          <t>澎湖縣馬公市同和路168號</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>(08)8862324#2701</t>
+          <t>(06)9235678#2103</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2029/04/12</t>
+          <t>2029/08/03</t>
         </is>
       </c>
     </row>
@@ -9908,32 +9908,32 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>橘子民宿</t>
+          <t>緻麗伯爵酒店</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
+          <t>雲林縣斗六市中山路6號</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>(0972)092658</t>
+          <t>(05)5341666#3</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2027/11/06</t>
+          <t>2029/02/10</t>
         </is>
       </c>
     </row>
@@ -9945,32 +9945,32 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>翰品酒店 高雄</t>
+          <t>緣羊軒民宿</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區大仁路43號</t>
+          <t>臺東縣台東市南一街96號</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>(07)5614688#3110</t>
+          <t>089326400</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2027/02/16</t>
+          <t>2026/12/05</t>
         </is>
       </c>
     </row>
@@ -9982,22 +9982,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>礁溪老爺酒店</t>
+          <t>趣淘漫旅-臺北</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
+          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>(03)9885211#8006</t>
+          <t>(02)29583000#7701</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2028/08/24</t>
+          <t>2028/03/31</t>
         </is>
       </c>
     </row>
@@ -10019,32 +10019,32 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>礁溪寒沐酒店</t>
+          <t>趣淘漫旅-臺東</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
+          <t>臺東縣台東市新站路260號</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>(03)9058007</t>
+          <t>(089)231188#7187</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2027/12/05</t>
         </is>
       </c>
     </row>
@@ -10056,22 +10056,22 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>禧榕軒大飯店</t>
+          <t>墾丁夏都沙灘酒店</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>臺南市北區成功路28號</t>
+          <t>屏東縣恆春鎮墾丁路451號</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>(06)2222788#2203</t>
+          <t>(0910)371823</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2029/05/10</t>
+          <t>2028/03/09</t>
         </is>
       </c>
     </row>
@@ -10093,22 +10093,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>薆悅酒店野柳渡假館一館</t>
+          <t>墾丁福華渡假飯店</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>新北市萬里區野柳里港東路162號之2</t>
+          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>(02)77035770#623</t>
+          <t>(08)8862324#2701</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2029/04/12</t>
         </is>
       </c>
     </row>
@@ -10130,22 +10130,22 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>藍水輕旅</t>
+          <t>橘子民宿</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>桃園市大園區高鐵南路一段126號</t>
+          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>(03)2871855</t>
+          <t>(0972)092658</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2027/11/06</t>
         </is>
       </c>
     </row>
@@ -10167,32 +10167,32 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>關子嶺富野溫泉會館</t>
+          <t>翰品酒店 高雄</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>臺南市白河區關子嶺28號</t>
+          <t>高雄市鹽埕區大仁路43號</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>(06)6822288</t>
+          <t>(07)5614688#3110</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2029/01/07</t>
+          <t>2027/02/16</t>
         </is>
       </c>
     </row>
@@ -10204,22 +10204,22 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>麗格休閒飯店</t>
+          <t>興源行民宿</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市商校街258.260.262號</t>
+          <t>臺東縣關山鎮中福里15鄰中山路16號</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>(03)8349922</t>
+          <t>(0921)578123</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2029/10/13</t>
         </is>
       </c>
     </row>
@@ -10241,32 +10241,32 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>麗軒國際飯店</t>
+          <t>礁溪老爺酒店</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市中美路99之1號</t>
+          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>(03)8246898</t>
+          <t>(03)9885211#8006</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2028/08/24</t>
         </is>
       </c>
     </row>
@@ -10278,32 +10278,32 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>麗翔大飯店</t>
+          <t>礁溪寒沐酒店</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
+          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>(03)8323737</t>
+          <t>(03)9058007</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2028/01/12</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -10315,32 +10315,32 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>讀好民宿</t>
+          <t>禧榕軒大飯店</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
+          <t>臺南市北區成功路28號</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>(0920)023139</t>
+          <t>(06)2222788#2203</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2029/05/10</t>
         </is>
       </c>
     </row>
@@ -10352,32 +10352,32 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>觀霧山莊</t>
+          <t>薆悅酒店野柳渡假館一館</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
+          <t>新北市萬里區野柳里港東路162號之2</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>(03)3343818</t>
+          <t>(02)77035770#623</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2029/01/22</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -10389,32 +10389,32 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>綉溪安平</t>
+          <t>藍水輕旅</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+          <t>桃園市大園區高鐵南路一段126號</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>(06)3910988#3111</t>
+          <t>(03)2871855</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2028/10/12</t>
+          <t>2026/11/23</t>
         </is>
       </c>
     </row>
@@ -10426,30 +10426,289 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
+          <t>關子嶺富野溫泉會館</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>臺南市</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>臺南市白河區關子嶺28號</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>(06)6822288</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>2029/01/07</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>麗格休閒飯店</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>花蓮縣</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>花蓮縣花蓮市商校街258.260.262號</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>(03)8349922</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2029/01/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>麗軒國際飯店</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>花蓮縣</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>花蓮縣花蓮市中美路99之1號</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>(03)8246898</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>2029/01/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>麗翔大飯店</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>花蓮縣</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>(03)8323737</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>2028/01/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>讀好民宿</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>宜蘭縣</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>(0920)023139</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>2029/01/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>觀霧山莊</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>苗栗縣</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>(03)3343818</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>銀級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>2029/01/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>綉溪安平</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>臺南市</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>(06)3910988#3111</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>銀級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>2028/10/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
           <t>鐡馬騎跡</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
+      <c r="C278" t="inlineStr">
         <is>
           <t>屏東縣</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
+      <c r="D278" t="inlineStr">
         <is>
           <t>屏東縣東港鎮新學路50號</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
+      <c r="E278" t="inlineStr">
         <is>
           <t>(0952)848898</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>銅級環保旅宿</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
         <is>
           <t>2029/01/18</t>
         </is>

--- a/環保旅宿_Selenium結果.xlsx
+++ b/環保旅宿_Selenium結果.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G278"/>
+  <dimension ref="A1:G283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1250,32 +1250,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>仁義湖岸大酒店</t>
+          <t>弋式風莊園民宿</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>嘉義縣番路鄉內甕村後坑仔35號</t>
+          <t>臺東縣關山鎮里壠里29鄰崁頂59之1號</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(05)2769388</t>
+          <t>(089)814553</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2028/08/31</t>
+          <t>2029/10/19</t>
         </is>
       </c>
     </row>
@@ -1287,32 +1287,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>今古安民宿</t>
+          <t>仁義湖岸大酒店</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市重慶路353巷30號</t>
+          <t>嘉義縣番路鄉內甕村後坑仔35號</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(03)8345555</t>
+          <t>(05)2769388</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2029/01/06</t>
+          <t>2028/08/31</t>
         </is>
       </c>
     </row>
@@ -1324,32 +1324,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>天成大飯店</t>
+          <t>今古安民宿</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>臺北市中正區忠孝西路一段43號</t>
+          <t>花蓮縣花蓮市重慶路353巷30號</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(02)23118905#3705</t>
+          <t>(03)8345555</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2027/03/07</t>
+          <t>2029/01/06</t>
         </is>
       </c>
     </row>
@@ -1361,22 +1361,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>太子文旅</t>
+          <t>天成大飯店</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>臺南市東區大學路2號(3，5-10F)</t>
+          <t>臺北市中正區忠孝西路一段43號</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(06)2095199#6103</t>
+          <t>(02)23118905#3705</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2029/07/08</t>
+          <t>2027/03/07</t>
         </is>
       </c>
     </row>
@@ -1398,32 +1398,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>太平⼭莊</t>
+          <t>太子文旅</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>宜蘭縣大同鄉太平村太平巷58之1號</t>
+          <t>臺南市東區大學路2號(3，5-10F)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(03)9545114#607</t>
+          <t>(06)2095199#6103</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2027/10/15</t>
+          <t>2029/07/08</t>
         </is>
       </c>
     </row>
@@ -1435,32 +1435,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>日日森旅二館</t>
+          <t>太平⼭莊</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>彰化縣田尾鄉民族路一段185巷11號</t>
+          <t>宜蘭縣大同鄉太平村太平巷58之1號</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(04)8221669</t>
+          <t>(03)9545114#607</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/10/15</t>
         </is>
       </c>
     </row>
@@ -1472,32 +1472,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>日月潭力麗溫德姆溫泉酒店</t>
+          <t>日日森旅二館</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉日月村中正路312號</t>
+          <t>彰化縣田尾鄉民族路一段185巷11號</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(049)2850085#8802</t>
+          <t>(04)8221669</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2029/01/01</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -1509,32 +1509,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>日玥居</t>
+          <t>日月潭力麗溫德姆溫泉酒店</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>金門縣金寧鄉南山19號</t>
+          <t>南投縣魚池鄉日月村中正路312號</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(0987)397327</t>
+          <t>(049)2850085#8802</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2029/01/01</t>
         </is>
       </c>
     </row>
@@ -1546,22 +1546,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>月光寶盒旅店</t>
+          <t>日玥居</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>高雄市鳳山區黃埔新村東一巷80號</t>
+          <t>金門縣金寧鄉南山19號</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(09)33631615</t>
+          <t>(0987)397327</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2026/11/28</t>
         </is>
       </c>
     </row>
@@ -1583,32 +1583,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>北投老爺酒店</t>
+          <t>月光寶盒旅店</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>臺北市北投區中和街2號</t>
+          <t>高雄市鳳山區黃埔新村東一巷80號</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(02)28966966#8878</t>
+          <t>(09)33631615</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2028/01/06</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>北投麗禧溫泉酒店</t>
+          <t>北投老爺酒店</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>臺北市北投區幽雅路30號</t>
+          <t>臺北市北投區中和街2號</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(02)28967799#738</t>
+          <t>(02)28966966#8878</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2028/04/13</t>
+          <t>2028/01/06</t>
         </is>
       </c>
     </row>
@@ -1657,32 +1657,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>古寧歇心苑</t>
+          <t>北投麗禧溫泉酒店</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>金門縣金寧鄉古寧村北山95號</t>
+          <t>臺北市北投區幽雅路30號</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>(082)322395</t>
+          <t>(02)28967799#738</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2029/10/16</t>
+          <t>2028/04/13</t>
         </is>
       </c>
     </row>
@@ -1694,32 +1694,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>臺中李方艾美酒店</t>
+          <t>古寧歇心苑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>臺中市中區建國路111號</t>
+          <t>金門縣金寧鄉古寧村北山95號</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(04)22240888#81002</t>
+          <t>(082)322395</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2028/11/05</t>
+          <t>2029/10/16</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>臺中金典酒店</t>
+          <t>臺中李方艾美酒店</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1741,22 +1741,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>臺中市西區健行路1049號</t>
+          <t>臺中市中區建國路111號</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(04)23288000#6692</t>
+          <t>(04)22240888#81002</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2028/11/19</t>
+          <t>2028/11/05</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>臺中港酒店</t>
+          <t>臺中金典酒店</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1778,22 +1778,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>臺中市梧棲區大智路二段388號</t>
+          <t>臺中市西區健行路1049號</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(04)37055888#6128</t>
+          <t>(04)23288000#6692</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2029/01/18</t>
+          <t>2028/11/19</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>臺中萬楓酒店</t>
+          <t>臺中港酒店</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>臺中市西屯區環中路二段1155號、1149號2樓、1151號3至11樓(之1)</t>
+          <t>臺中市梧棲區大智路二段388號</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(04)36065188#2501</t>
+          <t>(04)37055888#6128</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2029/09/09</t>
+          <t>2029/01/18</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>臺中豐邑慕奇夕酒店</t>
+          <t>臺中萬楓酒店</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1852,22 +1852,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>臺中市西屯區文心南六路288號、288號2樓、288號3樓(地上物3至17樓)</t>
+          <t>臺中市西屯區環中路二段1155號、1149號2樓、1151號3至11樓(之1)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(04)36007009#7099</t>
+          <t>(04)36065188#2501</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2029/05/14</t>
+          <t>2029/09/09</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>臺北W飯店</t>
+          <t>臺中豐邑慕奇夕酒店</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>臺北市信義區忠孝東路五段10號</t>
+          <t>臺中市西屯區文心南六路288號、288號2樓、288號3樓(地上物3至17樓)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(02)77038765</t>
+          <t>(04)36007009#7099</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2028/08/07</t>
+          <t>2029/05/14</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>臺北士林萬麗酒店</t>
+          <t>臺北W飯店</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>臺北市士林區中山北路五段470巷8號</t>
+          <t>臺北市信義區忠孝東路五段10號</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(02)88612389</t>
+          <t>(02)77038765</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2028/07/10</t>
+          <t>2028/08/07</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>臺北中山九昱希爾頓逸林酒店</t>
+          <t>臺北士林萬麗酒店</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1963,22 +1963,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路一段121巷1之1號, 121巷1號1樓至14樓</t>
+          <t>臺北市士林區中山北路五段470巷8號</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>(02)66253281</t>
+          <t>(02)88612389</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2028/07/10</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>臺北中山雅樂軒酒店</t>
+          <t>臺北中山九昱希爾頓逸林酒店</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2000,22 +2000,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>臺北市中山區雙城街1號</t>
+          <t>臺北市中山區中山北路一段121巷1之1號, 121巷1號1樓至14樓</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>(02)77439900</t>
+          <t>(02)66253281</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2028/11/13</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>臺北中山意舍酒店</t>
+          <t>臺北中山雅樂軒酒店</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路二段57之1號1至8樓</t>
+          <t>臺北市中山區雙城街1號</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>(02)25652828</t>
+          <t>(02)77439900</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2028/09/17</t>
+          <t>2028/11/13</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>臺北六福萬怡酒店</t>
+          <t>臺北中山意舍酒店</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>臺北市南港區忠孝東路七段359號7至30樓</t>
+          <t>臺北市中山區中山北路二段57之1號1至8樓</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(02)66156565#5000</t>
+          <t>(02)25652828</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2029/04/09</t>
+          <t>2028/09/17</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>臺北艾麗酒店</t>
+          <t>臺北六福萬怡酒店</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2111,22 +2111,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>臺北市信義區松高路18號</t>
+          <t>臺北市南港區忠孝東路七段359號7至30樓</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(02)66318031</t>
+          <t>(02)66156565#5000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2029/04/08</t>
+          <t>2029/04/09</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>臺北西門町意舍酒店</t>
+          <t>臺北艾麗酒店</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>臺北市萬華區武昌街2段77號5樓至10樓</t>
+          <t>臺北市信義區松高路18號</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(02)23755111#2100</t>
+          <t>(02)66318031</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2028/10/22</t>
+          <t>2029/04/08</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>臺北君品大酒店</t>
+          <t>臺北西門町意舍酒店</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2185,22 +2185,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>臺北市大同區承德路1段3號1樓、5樓~16樓及地下1樓、地下3樓</t>
+          <t>臺北市萬華區武昌街2段77號5樓至10樓</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(02)21819999#3142</t>
+          <t>(02)23755111#2100</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>2028/10/22</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>臺北松山意舍酒店</t>
+          <t>臺北君品大酒店</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>臺北市南港區市民大道7段8號17樓至21樓</t>
+          <t>臺北市大同區承德路1段3號1樓、5樓~16樓及地下1樓、地下3樓</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(02)26532828#2100</t>
+          <t>(02)21819999#3142</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2027/11/28</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>臺北花園大酒店</t>
+          <t>臺北松山意舍酒店</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2259,22 +2259,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路2段1號</t>
+          <t>臺北市南港區市民大道7段8號17樓至21樓</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(02)23143300#3331</t>
+          <t>(02)26532828#2100</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2029/09/28</t>
+          <t>2027/11/28</t>
         </is>
       </c>
     </row>
@@ -2286,32 +2286,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>臺北旅人國際青年旅館</t>
+          <t>臺北花園大酒店</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>新北市淡水區三民街22、22之1、22之2、22之3、22之4號</t>
+          <t>臺北市中正區中華路2段1號</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(02)26258222</t>
+          <t>(02)23143300#3331</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2029/09/28</t>
         </is>
       </c>
     </row>
@@ -2323,32 +2323,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>臺北時代寓所</t>
+          <t>臺北旅人國際青年旅館</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>臺北市中正區林森南路7號1至14樓，7-1號1樓</t>
+          <t>新北市淡水區三民街22、22之1、22之2、22之3、22之4號</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(02)77521801</t>
+          <t>(02)26258222</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2028/09/29</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>臺北國泰萬怡酒店</t>
+          <t>臺北時代寓所</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2370,22 +2370,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>臺北市中山區民生東路三段6號地下1樓、1、2、14至20樓</t>
+          <t>臺北市中正區林森南路7號1至14樓，7-1號1樓</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(02)77503371</t>
+          <t>(02)77521801</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2029/09/30</t>
+          <t>2028/09/29</t>
         </is>
       </c>
     </row>
@@ -2397,32 +2397,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>臺北新板希爾頓酒店</t>
+          <t>臺北國泰萬怡酒店</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>新北市板橋區民權路88號、88號（2至31樓）90號</t>
+          <t>臺北市中山區民生東路三段6號地下1樓、1、2、14至20樓</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(02)29583000#7702</t>
+          <t>(02)77503371</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2028/03/31</t>
+          <t>2029/09/30</t>
         </is>
       </c>
     </row>
@@ -2434,32 +2434,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>臺北萬豪酒店</t>
+          <t>臺北新板希爾頓酒店</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>臺北市中山區樂群二路199號</t>
+          <t>新北市板橋區民權路88號、88號（2至31樓）90號</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(02)21757999#1701</t>
+          <t>(02)29583000#7702</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2028/12/07</t>
+          <t>2028/03/31</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>臺北遠東香格里拉</t>
+          <t>臺北萬豪酒店</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>臺北市大安區敦化南路二段201號</t>
+          <t>臺北市中山區樂群二路199號</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(02)23788888#6608</t>
+          <t>(02)21757999#1701</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2027/12/12</t>
+          <t>2028/12/07</t>
         </is>
       </c>
     </row>
@@ -2508,22 +2508,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>臺東Deer  House民宿</t>
+          <t>臺北遠東香格里拉</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>臺東縣鹿野鄉永安村1鄰永安路７１號</t>
+          <t>臺北市大安區敦化南路二段201號</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(089)552224</t>
+          <t>(02)23788888#6608</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2027/12/12</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>臺南大員皇冠假日酒店</t>
+          <t>臺東Deer  House民宿</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>臺南市安平區州平路289號</t>
+          <t>臺東縣鹿野鄉永安村1鄰永安路７１號</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>(06)5121888#6002</t>
+          <t>(089)552224</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2028/01/09</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>臺南大飯店</t>
+          <t>臺南大員皇冠假日酒店</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2592,22 +2592,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>臺南市中西區成功路1號</t>
+          <t>臺南市安平區州平路289號</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>(06)2289101#2012</t>
+          <t>(06)5121888#6002</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2028/01/09</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>臺南安平雅樂軒酒店</t>
+          <t>臺南大飯店</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2629,22 +2629,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>臺南市安平區光州路108號2-12樓、光州路108之1號</t>
+          <t>臺南市中西區成功路1號</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>(06)3905000#8600</t>
+          <t>(06)2289101#2012</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2028/12/18</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>臺南老爺行旅</t>
+          <t>臺南安平雅樂軒酒店</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>臺南市東區中華東路一段368號1樓、6-10樓</t>
+          <t>臺南市安平區光州路108號2-12樓、光州路108之1號</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>(06)2361680#301</t>
+          <t>(06)3905000#8600</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2028/02/19</t>
+          <t>2028/12/18</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>臺南遠東香格里拉</t>
+          <t>臺南老爺行旅</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2703,22 +2703,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>臺南市東區大學路西段89號</t>
+          <t>臺南市東區中華東路一段368號1樓、6-10樓</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>(06)7028888#6903</t>
+          <t>(06)2361680#301</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2028/02/19</t>
         </is>
       </c>
     </row>
@@ -2730,22 +2730,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>臺糖臺北會館</t>
+          <t>臺南遠東香格里拉</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路一段39號3至5樓</t>
+          <t>臺南市東區大學路西段89號</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>(02)23885522#5001</t>
+          <t>(06)7028888#6903</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2027/03/10</t>
+          <t>2026/12/30</t>
         </is>
       </c>
     </row>
@@ -2767,22 +2767,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>臺糖花蓮旅館</t>
+          <t>臺糖臺北會館</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>花蓮縣光復鄉大進村糖廠街19號</t>
+          <t>臺北市中正區中華路一段39號3至5樓</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(03)8704125#621</t>
+          <t>(02)23885522#5001</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2027/03/21</t>
+          <t>2027/03/10</t>
         </is>
       </c>
     </row>
@@ -2804,22 +2804,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>臺糖長榮酒店(臺南)</t>
+          <t>臺糖花蓮旅館</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>臺南市東區中華東路三段336巷1號</t>
+          <t>花蓮縣光復鄉大進村糖廠街19號</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(06)3378888</t>
+          <t>(03)8704125#621</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2027/03/21</t>
         </is>
       </c>
     </row>
@@ -2841,22 +2841,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>臺灣糖業股份有限公司池上牧野渡假村</t>
+          <t>臺糖長榮酒店(臺南)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>臺東縣池上鄉新興村新興110號</t>
+          <t>臺南市東區中華東路三段336巷1號</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(089)862736#1001</t>
+          <t>(06)3378888</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2028/04/15</t>
+          <t>2026/11/28</t>
         </is>
       </c>
     </row>
@@ -2878,32 +2878,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>四季時光</t>
+          <t>臺灣糖業股份有限公司池上牧野渡假村</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉頭社村平和巷103-11號</t>
+          <t>臺東縣池上鄉新興村新興110號</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>(0932)376767</t>
+          <t>(089)862736#1001</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2028/04/15</t>
         </is>
       </c>
     </row>
@@ -2915,32 +2915,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>巨蛋旅店</t>
+          <t>四季時光</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>高雄市鼓山區文忠路1號</t>
+          <t>南投縣魚池鄉頭社村平和巷103-11號</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>(07)5868388#0</t>
+          <t>(0932)376767</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2028/10/07</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -2952,32 +2952,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>打個蛋海旅民宿</t>
+          <t>巨蛋旅店</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>臺東縣太麻里鄉金崙4鄰129號</t>
+          <t>高雄市鼓山區文忠路1號</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>(089)771551</t>
+          <t>(07)5868388#0</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2028/10/07</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>正好友生態環保旅店</t>
+          <t>打個蛋海旅民宿</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>屏東縣琉球鄉中山路153號</t>
+          <t>臺東縣太麻里鄉金崙4鄰129號</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>(0886)12270</t>
+          <t>(089)771551</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2029/03/26</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -3026,32 +3026,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>伊塔原旅臺東縣原住民文化會館</t>
+          <t>正好友生態環保旅店</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>臺東縣台東市中山路10號</t>
+          <t>屏東縣琉球鄉中山路153號</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>(089)34060</t>
+          <t>(0886)12270</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/03/26</t>
         </is>
       </c>
     </row>
@@ -3063,32 +3063,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>兆品酒店</t>
+          <t>伊塔原旅臺東縣原住民文化會館</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>嘉義市文化路257號B2-9F</t>
+          <t>臺東縣台東市中山路10號</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>(05)2292883#3130</t>
+          <t>(089)34060</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2028/03/30</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -3100,32 +3100,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>好室民宿</t>
+          <t>兆品酒店</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>臺東縣台東市中正路251巷9號</t>
+          <t>嘉義市文化路257號B2-9F</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>(0905)583758</t>
+          <t>(05)2292883#3130</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2027/01/29</t>
+          <t>2028/03/30</t>
         </is>
       </c>
     </row>
@@ -3137,22 +3137,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>如一家精緻民宿</t>
+          <t>好室民宿</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>金門縣金城鎮珠浦北路35-1號</t>
+          <t>臺東縣台東市中正路251巷9號</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>(082)322167</t>
+          <t>(0905)583758</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2027/01/29</t>
         </is>
       </c>
     </row>
@@ -3174,22 +3174,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>安樓文旅</t>
+          <t>如一家精緻民宿</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>基隆市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>基隆市仁愛區仁三路11-4</t>
+          <t>金門縣金城鎮珠浦北路35-1號</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(02)24200220</t>
+          <t>(082)322167</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2029/07/09</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -3211,22 +3211,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>老公老婆友善民宿</t>
+          <t>安樓文旅</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>基隆市</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>宜蘭縣冬山鄉境安路345號</t>
+          <t>基隆市仁愛區仁三路11-4</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(03) 9519013</t>
+          <t>(02)24200220</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026/12/28</t>
+          <t>2029/07/09</t>
         </is>
       </c>
     </row>
@@ -3248,22 +3248,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>老爺大酒店</t>
+          <t>老公老婆友善民宿</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路2段37-1號</t>
+          <t>宜蘭縣冬山鄉境安路345號</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>(02)25423299#359</t>
+          <t>(03) 9519013</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2026/12/28</t>
         </is>
       </c>
     </row>
@@ -3285,32 +3285,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>西湖渡假大飯店</t>
+          <t>老爺大酒店</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>苗栗縣三義鄉西湖村西湖11號</t>
+          <t>臺北市中山區中山北路2段37-1號</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>(037)876699#1122</t>
+          <t>(02)25423299#359</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2029/05/24</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -3322,32 +3322,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>亞昕福朋喜來登酒店</t>
+          <t>西湖渡假大飯店</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段1號、1號2樓、1號3樓</t>
+          <t>苗栗縣三義鄉西湖村西湖11號</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>(02)77276961</t>
+          <t>(037)876699#1122</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2028/09/25</t>
+          <t>2029/05/24</t>
         </is>
       </c>
     </row>
@@ -3359,22 +3359,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>享沐時光</t>
+          <t>亞昕福朋喜來登酒店</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮石鎮里錦山8-1,8-2號</t>
+          <t>新北市林口區文化三路一段1號、1號2樓、1號3樓</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(037)742878#124</t>
+          <t>(02)77276961</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2028/07/15</t>
+          <t>2028/09/25</t>
         </is>
       </c>
     </row>
@@ -3396,22 +3396,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>和逸．高雄中山館</t>
+          <t>享沐時光</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>高雄市前鎮區中山二路260號22-29樓</t>
+          <t>苗栗縣苑裡鎮石鎮里錦山8-1,8-2號</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(07)9756670</t>
+          <t>(037)742878#124</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2028/09/10</t>
+          <t>2028/07/15</t>
         </is>
       </c>
     </row>
@@ -3433,22 +3433,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>和逸·臺南西門館</t>
+          <t>和逸．高雄中山館</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>臺南市中西區西門路一段658之2號4樓至13樓</t>
+          <t>高雄市前鎮區中山二路260號22-29樓</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>(06)7026685</t>
+          <t>(07)9756670</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2028/02/19</t>
+          <t>2028/09/10</t>
         </is>
       </c>
     </row>
@@ -3470,22 +3470,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>和逸飯店桃園青埔館</t>
+          <t>和逸·臺南西門館</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>桃園市中壢區春德路101號</t>
+          <t>臺南市中西區西門路一段658之2號4樓至13樓</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>(03)2737692#2102</t>
+          <t>(06)7026685</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2028/02/19</t>
         </is>
       </c>
     </row>
@@ -3507,32 +3507,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>宜蘭力麗威斯汀度假酒店</t>
+          <t>和逸飯店桃園青埔館</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>宜蘭縣員山鄉永同路三段268號</t>
+          <t>桃園市中壢區春德路101號</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>(03)9232111</t>
+          <t>(03)2737692#2102</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2029/10/01</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -3544,32 +3544,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>尚順君樂飯店</t>
+          <t>宜蘭力麗威斯汀度假酒店</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>苗栗縣頭份市育樂街6號</t>
+          <t>宜蘭縣員山鄉永同路三段268號</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>(037)539999#8611</t>
+          <t>(03)9232111</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2029/07/29</t>
+          <t>2029/10/01</t>
         </is>
       </c>
     </row>
@@ -3581,22 +3581,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>幸福蝸牛</t>
+          <t>尚順君樂飯店</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉利澤西路6號</t>
+          <t>苗栗縣頭份市育樂街6號</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(03)9500047</t>
+          <t>(037)539999#8611</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2029/07/29</t>
         </is>
       </c>
     </row>
@@ -3618,32 +3618,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>承萬尊爵渡假酒店</t>
+          <t>幸福蝸牛</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>南投縣埔里鎮樹人路131號</t>
+          <t>宜蘭縣五結鄉利澤西路6號</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(049)2995757#6316</t>
+          <t>(03)9500047</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2027/04/07</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -3655,32 +3655,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>承億酒店</t>
+          <t>承萬尊爵渡假酒店</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>高雄市前鎮區林森四路189號</t>
+          <t>南投縣埔里鎮樹人路131號</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(07)3332000#6870</t>
+          <t>(049)2995757#6316</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2029/09/22</t>
+          <t>2027/04/07</t>
         </is>
       </c>
     </row>
@@ -3692,32 +3692,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>林口維多利亞民宿</t>
+          <t>承億酒店</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>桃園市蘆竹區坑子里14鄰八德二路280巷11號</t>
+          <t>高雄市前鎮區林森四路189號</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(0905)111918</t>
+          <t>(07)3332000#6870</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2029/08/24</t>
+          <t>2029/09/22</t>
         </is>
       </c>
     </row>
@@ -3729,32 +3729,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>板橋凱撒大飯店</t>
+          <t>林口維多利亞民宿</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>新北市板橋區縣民大道二段8號</t>
+          <t>桃園市蘆竹區坑子里14鄰八德二路280巷11號</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>(02)29583000#7701</t>
+          <t>(0905)111918</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2029/02/12</t>
+          <t>2029/08/24</t>
         </is>
       </c>
     </row>
@@ -3766,32 +3766,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>武陵國民賓館</t>
+          <t>板橋凱撒大飯店</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>臺中市和平區平等里武陵路3-1號</t>
+          <t>新北市板橋區縣民大道二段8號</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(04)25901258#2103</t>
+          <t>(02)29583000#7701</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026/12/25</t>
+          <t>2029/02/12</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>武陵富野渡假村</t>
+          <t>武陵國民賓館</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>臺中市和平區武陵路3-16號</t>
+          <t>臺中市和平區平等里武陵路3-1號</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>(04)25901399#8912</t>
+          <t>(04)25901258#2103</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2026/12/25</t>
         </is>
       </c>
     </row>
@@ -3840,32 +3840,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>河那灣</t>
+          <t>武陵富野渡假村</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>桃園市復興區澤仁里3鄰溪口台41號</t>
+          <t>臺中市和平區武陵路3-16號</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(0919)235303</t>
+          <t>(04)25901399#8912</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2027/07/25</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -3877,22 +3877,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>波西米亞民宿</t>
+          <t>河那灣</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>花蓮縣吉安鄉東昌村13鄰東海一街168號</t>
+          <t>桃園市復興區澤仁里3鄰溪口台41號</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(0385)31234</t>
+          <t>(0919)235303</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2029/01/06</t>
+          <t>2027/07/25</t>
         </is>
       </c>
     </row>
@@ -3914,22 +3914,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>泡泡森林民宿</t>
+          <t>波西米亞民宿</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>臺東縣台東市南一街40號</t>
+          <t>花蓮縣吉安鄉東昌村13鄰東海一街168號</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0986866545</t>
+          <t>(0385)31234</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026/12/06</t>
+          <t>2029/01/06</t>
         </is>
       </c>
     </row>
@@ -3951,22 +3951,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>泊寓</t>
+          <t>泡泡森林民宿</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮鹿興路57巷3號</t>
+          <t>臺東縣台東市南一街40號</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>(04)7115655#120</t>
+          <t>0986866545</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2026/12/06</t>
         </is>
       </c>
     </row>
@@ -3988,22 +3988,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>爸爸萬歲民宿</t>
+          <t>泊寓</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市延平街68巷27號</t>
+          <t>彰化縣鹿港鎮鹿興路57巷3號</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>(0900)757520</t>
+          <t>(04)7115655#120</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2027/01/10</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -4025,22 +4025,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>迎曦大飯店</t>
+          <t>爸爸萬歲民宿</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>新竹市東區親仁里文化街10號2-10樓</t>
+          <t>花蓮縣花蓮市延平街68巷27號</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>(03)5347266#124</t>
+          <t>(0900)757520</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2028/04/28</t>
+          <t>2027/01/10</t>
         </is>
       </c>
     </row>
@@ -4062,32 +4062,32 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>金湖飯店</t>
+          <t>迎曦大飯店</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>金門縣金湖鎮太湖路二段218號</t>
+          <t>新竹市東區親仁里文化街10號2-10樓</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>(082)379666#160</t>
+          <t>(03)5347266#124</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026/12/03</t>
+          <t>2028/04/28</t>
         </is>
       </c>
     </row>
@@ -4099,22 +4099,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>長榮文苑酒店(嘉義)</t>
+          <t>金湖飯店</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>嘉義縣太保市東勢里故宮大道777號</t>
+          <t>金門縣金湖鎮太湖路二段218號</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>(05)3669988#2700</t>
+          <t>(082)379666#160</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2027/04/11</t>
+          <t>2026/12/03</t>
         </is>
       </c>
     </row>
@@ -4136,22 +4136,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(臺中)</t>
+          <t>長榮文苑酒店(嘉義)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>臺中市西屯區臺灣大道二段666號</t>
+          <t>嘉義縣太保市東勢里故宮大道777號</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>(04)23242236#2700</t>
+          <t>(05)3669988#2700</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2027/07/09</t>
+          <t>2027/04/11</t>
         </is>
       </c>
     </row>
@@ -4173,22 +4173,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(臺北)</t>
+          <t>長榮桂冠酒店(臺中)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>臺北市中山區松江路63號</t>
+          <t>臺中市西屯區臺灣大道二段666號</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>(02)25019988#2701</t>
+          <t>(04)23242236#2700</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2028/10/22</t>
+          <t>2027/07/09</t>
         </is>
       </c>
     </row>
@@ -4210,32 +4210,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>長榮桂冠酒店(基隆)</t>
+          <t>長榮桂冠酒店(臺北)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>基隆市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>基隆市中正區中正路62號之1</t>
+          <t>臺北市中山區松江路63號</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>(02)24279988</t>
+          <t>(02)25019988#2701</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2028/05/22</t>
+          <t>2028/10/22</t>
         </is>
       </c>
     </row>
@@ -4247,22 +4247,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>長榮鳳凰酒店(礁溪)</t>
+          <t>長榮桂冠酒店(基隆)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>基隆市</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉健康路77號</t>
+          <t>基隆市中正區中正路62號之1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>(03)9100988#2335</t>
+          <t>(02)24279988</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2027/09/15</t>
+          <t>2028/05/22</t>
         </is>
       </c>
     </row>
@@ -4284,32 +4284,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>阿里山東方明珠國際大飯店</t>
+          <t>長榮鳳凰酒店(礁溪)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>嘉義縣中埔鄉社口村檨仔林23號</t>
+          <t>宜蘭縣礁溪鄉健康路77號</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>(05)2536999</t>
+          <t>(03)9100988#2335</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2027/12/12</t>
+          <t>2027/09/15</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>阿里山英迪格酒店</t>
+          <t>阿里山東方明珠國際大飯店</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4331,22 +4331,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>嘉義縣番路鄉公田村2鄰龍頭20號2樓之1等10筆</t>
+          <t>嘉義縣中埔鄉社口村檨仔林23號</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>(05)2586800#121</t>
+          <t>(05)2536999</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2028/10/21</t>
+          <t>2027/12/12</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>阿里山賓館（現代館）</t>
+          <t>阿里山英迪格酒店</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4368,12 +4368,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>嘉義縣阿里山鄉香林村西阿里山16-1號</t>
+          <t>嘉義縣番路鄉公田村2鄰龍頭20號2樓之1等10筆</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>(05)2679996#5117</t>
+          <t>(05)2586800#121</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2027/06/19</t>
+          <t>2028/10/21</t>
         </is>
       </c>
     </row>
@@ -4395,32 +4395,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>阿爾卑斯莊園</t>
+          <t>阿里山賓館（現代館）</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉協和村親河路二段88巷37號</t>
+          <t>嘉義縣阿里山鄉香林村西阿里山16-1號</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>(0905)787698</t>
+          <t>(05)2679996#5117</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2029/09/02</t>
+          <t>2027/06/19</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>冠翔泉旅</t>
+          <t>阿爾卑斯莊園</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4442,22 +4442,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉仁愛路66巷6號</t>
+          <t>宜蘭縣五結鄉協和村親河路二段88巷37號</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>(03)9875599#119</t>
+          <t>(0905)787698</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2029/07/20</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -4469,22 +4469,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>南港老爺行旅</t>
+          <t>冠翔泉旅</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>臺北市南港區經貿二路196號、196號10樓至20樓</t>
+          <t>宜蘭縣礁溪鄉仁愛路66巷6號</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>(02)77500588</t>
+          <t>(03)9875599#119</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2028/11/27</t>
+          <t>2029/07/20</t>
         </is>
       </c>
     </row>
@@ -4506,32 +4506,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>城市商旅美麗島館(HOTEL PAPA WHALE)</t>
+          <t>南港老爺行旅</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>高雄市新興區民生一路328號1-7樓</t>
+          <t>臺北市南港區經貿二路196號、196號10樓至20樓</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>(07)2519888</t>
+          <t>(02)77500588</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2028/09/24</t>
+          <t>2028/11/27</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>城市商旅高雄真愛館</t>
+          <t>城市商旅美麗島館(HOTEL PAPA WHALE)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區大義街1號</t>
+          <t>高雄市新興區民生一路328號1-7樓</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>(07)5215116#9303</t>
+          <t>(07)2519888</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2028/09/25</t>
+          <t>2028/09/24</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>城市商旅駁二館</t>
+          <t>城市商旅高雄真愛館</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4590,12 +4590,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區公園二路83號1至11樓</t>
+          <t>高雄市鹽埕區大義街1號</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>(07)5322777</t>
+          <t>(07)5215116#9303</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>城市商旅德立莊博愛館</t>
+          <t>城市商旅駁二館</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>高雄市三民區博愛一路338號地上1至10樓</t>
+          <t>高雄市鹽埕區公園二路83號1至11樓</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>(07)3238777#9301</t>
+          <t>(07)5322777</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2028/08/07</t>
+          <t>2028/09/25</t>
         </is>
       </c>
     </row>
@@ -4654,32 +4654,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>星8藝宿</t>
+          <t>城市商旅德立莊博愛館</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉中山路三段192巷8號</t>
+          <t>高雄市三民區博愛一路338號地上1至10樓</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>(0932)495200</t>
+          <t>(07)3238777#9301</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2029/01/07</t>
+          <t>2028/08/07</t>
         </is>
       </c>
     </row>
@@ -4691,22 +4691,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>星漾商旅</t>
+          <t>星8藝宿</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>臺中市北區錦南街17號,錦新街30號4樓至9樓,錦新街32號4樓至9樓</t>
+          <t>宜蘭縣三星鄉中山路三段192巷8號</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>(04)22289008</t>
+          <t>(0932)495200</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2029/01/07</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>星漾商旅(中清館)</t>
+          <t>星漾商旅</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4738,12 +4738,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>臺中市北區中清路一段63號</t>
+          <t>臺中市北區錦南街17號,錦新街30號4樓至9樓,錦新街32號4樓至9樓</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(04)22083888</t>
+          <t>(04)22289008</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4765,22 +4765,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>柳營尖山埤渡假村</t>
+          <t>星漾商旅(中清館)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>臺南市柳營區旭山里60號</t>
+          <t>臺中市北區中清路一段63號</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(06)6233888#2100</t>
+          <t>(04)22083888</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2029/07/28</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -4802,32 +4802,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>美之旅商務飯店</t>
+          <t>柳營尖山埤渡假村</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>臺中市西區美村路一段269號1樓、2樓之1、2樓之2、3、4、5、6、7樓</t>
+          <t>臺南市柳營區旭山里60號</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(04)23024330</t>
+          <t>(06)6233888#2100</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2029/04/07</t>
+          <t>2029/07/28</t>
         </is>
       </c>
     </row>
@@ -4839,32 +4839,32 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>美侖商旅</t>
+          <t>美之旅商務飯店</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>臺北市中山區吉林路49號1至8樓</t>
+          <t>臺中市西區美村路一段269號1樓、2樓之1、2樓之2、3、4、5、6、7樓</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(02)25313535#878</t>
+          <t>(04)23024330</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2028/11/27</t>
+          <t>2029/04/07</t>
         </is>
       </c>
     </row>
@@ -4876,32 +4876,32 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>美墅館</t>
+          <t>美侖商旅</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>臺南市善化區昌隆里9鄰東勢寮131之8號</t>
+          <t>臺北市中山區吉林路49號1至8樓</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(09)20656908</t>
+          <t>(02)25313535#878</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2028/11/27</t>
         </is>
       </c>
     </row>
@@ -4913,22 +4913,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>美綠民宿</t>
+          <t>美墅館</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>高雄市美濃區獅山里竹門14-2號</t>
+          <t>臺南市善化區昌隆里9鄰東勢寮131之8號</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(07)6851111</t>
+          <t>(09)20656908</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2028/12/28</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -4950,32 +4950,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>香格里拉冬山河旅館</t>
+          <t>美綠民宿</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉協和村公園二路15號</t>
+          <t>高雄市美濃區獅山里竹門14-2號</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(03)9605388#212</t>
+          <t>(07)6851111</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2029/10/06</t>
+          <t>2028/12/28</t>
         </is>
       </c>
     </row>
@@ -4987,22 +4987,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>夏堤民宿</t>
+          <t>若家民宿</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>屏東縣琉球鄉上福村2鄰杉板路51巷2號</t>
+          <t>臺東縣關山鎮里壠里23鄰水源21號</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>(08)8611155</t>
+          <t>(0921)240981</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2029/02/25</t>
+          <t>2029/10/19</t>
         </is>
       </c>
     </row>
@@ -5024,32 +5024,32 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>夏優旅居</t>
+          <t>香格里拉冬山河旅館</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區新興街67號</t>
+          <t>宜蘭縣五結鄉協和村公園二路15號</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(07)5328885</t>
+          <t>(03)9605388#212</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2028/12/11</t>
+          <t>2029/10/06</t>
         </is>
       </c>
     </row>
@@ -5061,22 +5061,22 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>娜路彎花園酒店</t>
+          <t>香格里拉休閒農場</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>臺東縣台東市新興路77號</t>
+          <t>宜蘭縣冬山鄉大進村梅山路168號</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(089)231111</t>
+          <t>(03)9605388#210</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2029/10/20</t>
         </is>
       </c>
     </row>
@@ -5098,22 +5098,22 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>娜路彎會館</t>
+          <t>夏堤民宿</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>臺東縣台東市中興路2段385號</t>
+          <t>屏東縣琉球鄉上福村2鄰杉板路51巷2號</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(089)235500</t>
+          <t>(08)8611155</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>2029/02/25</t>
         </is>
       </c>
     </row>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>娜路彎銀河行館</t>
+          <t>夏優旅居</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>臺東縣台東市豐興路88號</t>
+          <t>高雄市鹽埕區新興街67號</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(089)383366</t>
+          <t>(07)5328885</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2028/09/16</t>
+          <t>2028/12/11</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>娜路彎銀河酒店</t>
+          <t>娜路彎花園酒店</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5182,22 +5182,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>臺東縣台東市豐興路66號</t>
+          <t>臺東縣台東市新興路77號</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(089)225000#8263</t>
+          <t>(089)231111</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2028/09/03</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -5209,22 +5209,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>悅徠舘</t>
+          <t>娜路彎會館</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>桃園市龜山區興華三街18號2樓之1</t>
+          <t>臺東縣台東市中興路2段385號</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>(03)3280177</t>
+          <t>(089)235500</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2027/08/15</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -5246,22 +5246,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>悅豪大飯店</t>
+          <t>娜路彎銀河行館</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>新竹市東區復興路22號</t>
+          <t>臺東縣台東市豐興路88號</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(03)5267890</t>
+          <t>(089)383366</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2029/07/20</t>
+          <t>2028/09/16</t>
         </is>
       </c>
     </row>
@@ -5283,32 +5283,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>挪威森林頂級汽車旅館</t>
+          <t>娜路彎銀河酒店</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>新北市板橋區和平路14巷3號</t>
+          <t>臺東縣台東市豐興路66號</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(02)29562211</t>
+          <t>(089)225000#8263</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2029/09/30</t>
+          <t>2028/09/03</t>
         </is>
       </c>
     </row>
@@ -5320,22 +5320,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>旅行邦尼</t>
+          <t>悅徠舘</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>新北市淡水區中山路87巷7號</t>
+          <t>桃園市龜山區興華三街18號2樓之1</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>(09)28824850</t>
+          <t>(03)3280177</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2029/01/05</t>
+          <t>2027/08/15</t>
         </is>
       </c>
     </row>
@@ -5357,22 +5357,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>旅悅國際青年旅館</t>
+          <t>悅豪大飯店</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>高雄市前鎮區三多三路211號3樓及4樓</t>
+          <t>新竹市東區復興路22號</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>(07)3359006</t>
+          <t>(03)5267890</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2027/10/13</t>
+          <t>2029/07/20</t>
         </is>
       </c>
     </row>
@@ -5394,32 +5394,32 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>桃園大溪笠復威斯汀度假酒店</t>
+          <t>挪威森林頂級汽車旅館</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>桃園市大溪區日新路166號</t>
+          <t>新北市板橋區和平路14巷3號</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(03)2725035</t>
+          <t>(02)29562211</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2029/09/30</t>
         </is>
       </c>
     </row>
@@ -5431,32 +5431,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>桃園喜來登酒店</t>
+          <t>旅行邦尼</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>桃園市大園區大觀路777號</t>
+          <t>新北市淡水區中山路87巷7號</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>(03)3850000#2605</t>
+          <t>(09)28824850</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026/10/29</t>
+          <t>2029/01/05</t>
         </is>
       </c>
     </row>
@@ -5468,32 +5468,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>泰安觀止溫泉會館</t>
+          <t>旅悅國際青年旅館</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>苗栗縣泰安鄉錦水村圓墩58-7號</t>
+          <t>高雄市前鎮區三多三路211號3樓及4樓</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>(037)941951#527</t>
+          <t>(07)3359006</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2028/06/25</t>
+          <t>2027/10/13</t>
         </is>
       </c>
     </row>
@@ -5505,32 +5505,32 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>海福花園飯店</t>
+          <t>桃園大溪笠復威斯汀度假酒店</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>金門縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>金門縣金沙鎮高陽路1號</t>
+          <t>桃園市大溪區日新路166號</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>(082)353888</t>
+          <t>(03)2725035</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2029/09/01</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -5542,32 +5542,32 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>海霞您的家</t>
+          <t>桃園喜來登酒店</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>新北市貢寮區仁里里14鄰仁愛路38號</t>
+          <t>桃園市大園區大觀路777號</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>(09)35204895</t>
+          <t>(03)3850000#2605</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2026/10/29</t>
         </is>
       </c>
     </row>
@@ -5579,22 +5579,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>海灣假日酒店</t>
+          <t>泰安觀止溫泉會館</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>新北市深坑區北深路3段265號</t>
+          <t>苗栗縣泰安鄉錦水村圓墩58-7號</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>(02)77035880</t>
+          <t>(037)941951#527</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2028/12/17</t>
+          <t>2028/06/25</t>
         </is>
       </c>
     </row>
@@ -5616,22 +5616,22 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>神隱國度民宿</t>
+          <t>海福花園飯店</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>金門縣</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>新北市瑞芳區崙頂路90號</t>
+          <t>金門縣金沙鎮高陽路1號</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>(09)05788650</t>
+          <t>(082)353888</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2029/09/01</t>
         </is>
       </c>
     </row>
@@ -5653,32 +5653,32 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>秧悦美地度假酒店</t>
+          <t>海霞您的家</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>花蓮縣吉安鄉干城村干城二街95-9號</t>
+          <t>新北市貢寮區仁里里14鄰仁愛路38號</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(03)8129168#2701</t>
+          <t>(09)35204895</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -5690,32 +5690,32 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>秘境41</t>
+          <t>海灣假日酒店</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>桃園市大溪區興和里中央路41號</t>
+          <t>新北市深坑區北深路3段265號</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(03)3887111</t>
+          <t>(02)77035880</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2027/12/10</t>
+          <t>2028/12/17</t>
         </is>
       </c>
     </row>
@@ -5727,22 +5727,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>秘境民宿</t>
+          <t>神隱國度民宿</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>屏東縣東港鎮屏東縣東港鎮水源路223號(新和段737-3地號)</t>
+          <t>新北市瑞芳區崙頂路90號</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(08)8333345</t>
+          <t>(09)05788650</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2029/01/18</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -5764,32 +5764,32 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>茶田關舍民宿</t>
+          <t>秧悦美地度假酒店</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>臺東縣關山鎮豐泉里3鄰平等路99號</t>
+          <t>花蓮縣吉安鄉干城村干城二街95-9號</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(089)812098</t>
+          <t>(03)8129168#2701</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2029/10/16</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -5801,32 +5801,32 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>高雄中央公園英迪格酒店</t>
+          <t>秘境41</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>高雄市新興區中山一路4號</t>
+          <t>桃園市大溪區興和里中央路41號</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(07)2721555#301</t>
+          <t>(03)3887111</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2028/02/02</t>
+          <t>2027/12/10</t>
         </is>
       </c>
     </row>
@@ -5838,22 +5838,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>高雄商旅</t>
+          <t>秘境民宿</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>高雄市新興區民族二路33號1、4~10樓；37號1、3~10樓</t>
+          <t>屏東縣東港鎮屏東縣東港鎮水源路223號(新和段737-3地號)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>(09)19546590</t>
+          <t>(08)8333345</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2029/01/18</t>
         </is>
       </c>
     </row>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>高雄富野渡假酒店</t>
+          <t>茶田關舍民宿</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>高雄市前鎮區瑞田街99號</t>
+          <t>臺東縣關山鎮豐泉里3鄰平等路99號</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>(07)8215299#7102</t>
+          <t>(089)812098</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2029/02/09</t>
+          <t>2029/10/16</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>高雄圓山大飯店</t>
+          <t>高雄中央公園英迪格酒店</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>高雄市鳥松區圓山路2號</t>
+          <t>高雄市新興區中山一路4號</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>(07)3706007#519</t>
+          <t>(07)2721555#301</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2028/02/02</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>高雄福華大飯店</t>
+          <t>高雄商旅</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5959,22 +5959,22 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>高雄市新興區七賢一路311號</t>
+          <t>高雄市新興區民族二路33號1、4~10樓；37號1、3~10樓</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(07)2307737</t>
+          <t>(09)19546590</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026/11/16</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -5986,22 +5986,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>國聯大飯店</t>
+          <t>高雄富野渡假酒店</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>臺北市大安區光復南路200號</t>
+          <t>高雄市前鎮區瑞田街99號</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>(02)27731515#184</t>
+          <t>(07)8215299#7102</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2029/09/15</t>
+          <t>2029/02/09</t>
         </is>
       </c>
     </row>
@@ -6023,32 +6023,32 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>基拉耳景觀民宿</t>
+          <t>高雄圓山大飯店</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>桃園市復興區溪口路16巷29號</t>
+          <t>高雄市鳥松區圓山路2號</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(02)23965188#594</t>
+          <t>(07)3706007#519</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2028/06/15</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>將捷金鬱金香酒店</t>
+          <t>高雄福華大飯店</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>新北市淡水區中正路1段2之1號(A區地上3至6層、B區地上1至5層、C區地下3層至地上3層)</t>
+          <t>高雄市新興區七賢一路311號</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(02)26218555#2913</t>
+          <t>(07)2307737</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2027/04/14</t>
+          <t>2026/11/16</t>
         </is>
       </c>
     </row>
@@ -6097,32 +6097,32 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>康橋商旅-六合夜市七賢館</t>
+          <t>國軍退除役官兵輔導委員會福壽山農場</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>高雄市新興區同愛街28號1樓、30號</t>
+          <t>臺中市和平區梨山里福壽路29號</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(07)288-5588</t>
+          <t>(04)25989960#130</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2029/10/23</t>
         </is>
       </c>
     </row>
@@ -6134,22 +6134,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>康橋商旅-六合夜市中正館</t>
+          <t>國聯大飯店</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>高雄市前金區中正四路112號2至8樓</t>
+          <t>臺北市大安區光復南路200號</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(07)2881166</t>
+          <t>(02)27731515#184</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2029/10/13</t>
+          <t>2029/09/15</t>
         </is>
       </c>
     </row>
@@ -6171,22 +6171,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>康橋商旅臺南赤崁樓館</t>
+          <t>基拉耳景觀民宿</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>臺南市中西區赤崁里民權路二段97號1至8樓</t>
+          <t>桃園市復興區溪口路16巷29號</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(06)2253377</t>
+          <t>(02)23965188#594</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2028/06/15</t>
         </is>
       </c>
     </row>
@@ -6208,32 +6208,32 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>康橋商旅-高雄-光榮碼頭館</t>
+          <t>將捷金鬱金香酒店</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>高雄市苓雅區青年二路169號</t>
+          <t>新北市淡水區中正路1段2之1號(A區地上3至6層、B區地上1至5層、C區地下3層至地上3層)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>(07)3343377</t>
+          <t>(02)26218555#2913</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/04/14</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>康橋商旅-高雄站前館</t>
+          <t>康橋商旅-六合夜市七賢館</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>高雄市三民區建國二路295號</t>
+          <t>高雄市新興區同愛街28號1樓、30號</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>(07)2386677</t>
+          <t>(07)288-5588</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -6282,22 +6282,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>康橋慢旅</t>
+          <t>康橋商旅-六合夜市中正館</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>臺南市中西區民生路二段416號</t>
+          <t>高雄市前金區中正四路112號2至8樓</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>(06)2805566</t>
+          <t>(07)2881166</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2029/10/13</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>捷絲旅 臺南虎山館</t>
+          <t>康橋商旅臺南赤崁樓館</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6329,22 +6329,22 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>臺南市仁德區成功里5鄰文華路2段300號1~9樓，地下一、二樓</t>
+          <t>臺南市中西區赤崁里民權路二段97號1至8樓</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>(06)2662218#8321</t>
+          <t>(06)2253377</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2028/02/13</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -6356,32 +6356,32 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>捷絲旅臺北三重館</t>
+          <t>康橋商旅-高雄-光榮碼頭館</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>新北市三重區三和路四段107-1號</t>
+          <t>高雄市苓雅區青年二路169號</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>(02)22806111#8304</t>
+          <t>(07)3343377</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2028/10/12</t>
+          <t>2029/10/15</t>
         </is>
       </c>
     </row>
@@ -6393,22 +6393,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>捷絲旅西門町店</t>
+          <t>康橋商旅-高雄站前館</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>臺北市中正區中華路一段41號5樓至9樓</t>
+          <t>高雄市三民區建國二路295號</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(02)25215000</t>
+          <t>(07)2386677</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2027/05/12</t>
+          <t>2029/10/13</t>
         </is>
       </c>
     </row>
@@ -6430,32 +6430,32 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>捷絲旅花蓮中正館</t>
+          <t>康橋慢旅</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市主睦里14鄰中正路396號</t>
+          <t>臺南市中西區民生路二段416號</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(03)8900069#8104</t>
+          <t>(06)2805566</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2029/09/02</t>
         </is>
       </c>
     </row>
@@ -6467,22 +6467,22 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>捷絲旅高雄中正館</t>
+          <t>捷絲旅 臺南虎山館</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>高雄市苓雅區中正一路134號</t>
+          <t>臺南市仁德區成功里5鄰文華路2段300號1~9樓，地下一、二樓</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(07)9733587#8104</t>
+          <t>(06)2662218#8321</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2028/10/06</t>
+          <t>2028/02/13</t>
         </is>
       </c>
     </row>
@@ -6504,22 +6504,22 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>捷絲旅高雄站前館</t>
+          <t>捷絲旅臺北三重館</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>高雄市新興區中山一路280號1至14樓</t>
+          <t>新北市三重區三和路四段107-1號</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(07)9733587#8104</t>
+          <t>(02)22806111#8304</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2028/09/29</t>
+          <t>2028/10/12</t>
         </is>
       </c>
     </row>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>捷絲旅臺大尊賢館</t>
+          <t>捷絲旅西門町店</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>臺北市大安區羅斯福路四段83號1-10樓</t>
+          <t>臺北市中正區中華路一段41號5樓至9樓</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(02)77355088</t>
+          <t>(02)25215000</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/05/12</t>
         </is>
       </c>
     </row>
@@ -6578,32 +6578,32 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>捷絲旅礁溪館</t>
+          <t>捷絲旅花蓮中正館</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉德陽路24巷8號、10號</t>
+          <t>花蓮縣花蓮市主睦里14鄰中正路396號</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>(03)9102000#8104</t>
+          <t>(03)8900069#8104</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2027/01/07</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -6615,22 +6615,22 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>清新溫泉飯店</t>
+          <t>捷絲旅高雄中正館</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>臺中市烏日區溫泉路2號</t>
+          <t>高雄市苓雅區中正一路134號</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>(04)23831088#7602</t>
+          <t>(07)9733587#8104</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2029/01/29</t>
+          <t>2028/10/06</t>
         </is>
       </c>
     </row>
@@ -6652,32 +6652,32 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>統一谷關渡假村</t>
+          <t>捷絲旅高雄站前館</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>臺中市和平區博愛里東關路一段188號</t>
+          <t>高雄市新興區中山一路280號1至14樓</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>(04)25950000</t>
+          <t>(07)9733587#8104</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2028/01/06</t>
+          <t>2028/09/29</t>
         </is>
       </c>
     </row>
@@ -6689,32 +6689,32 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>統一渡假村</t>
+          <t>捷絲旅臺大尊賢館</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>新竹縣關西鎮金山里34號</t>
+          <t>臺北市大安區羅斯福路四段83號1-10樓</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>(03)5478888</t>
+          <t>(02)77355088</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2027/12/20</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -6726,22 +6726,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>鹿港澄悅酒店</t>
+          <t>捷絲旅礁溪館</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮中正路598號1樓、5至8樓</t>
+          <t>宜蘭縣礁溪鄉德陽路24巷8號、10號</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>(04)7785727</t>
+          <t>(03)9102000#8104</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2029/03/02</t>
+          <t>2027/01/07</t>
         </is>
       </c>
     </row>
@@ -6763,22 +6763,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>凱旋酒店</t>
+          <t>清新溫泉飯店</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>臺北市內湖區江南街55號3樓至9樓</t>
+          <t>臺中市烏日區溫泉路2號</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(02)87527888#6203</t>
+          <t>(04)23831088#7602</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026/12/10</t>
+          <t>2029/01/29</t>
         </is>
       </c>
     </row>
@@ -6800,32 +6800,32 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>凱達大飯店</t>
+          <t>統一谷關渡假村</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>臺北市萬華區艋舺大道167號1-26樓</t>
+          <t>臺中市和平區博愛里東關路一段188號</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>(02)23836789#6321</t>
+          <t>(04)25950000</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2027/06/02</t>
+          <t>2028/01/06</t>
         </is>
       </c>
     </row>
@@ -6837,32 +6837,32 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>凱撒大飯店</t>
+          <t>統一渡假村</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁路6號</t>
+          <t>新竹縣關西鎮金山里34號</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>(08)8861888</t>
+          <t>(03)5478888</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2028/09/16</t>
+          <t>2027/12/20</t>
         </is>
       </c>
     </row>
@@ -6874,22 +6874,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>勝利127民宿</t>
+          <t>鹿港澄悅酒店</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>屏東縣屏東市勝利路127號</t>
+          <t>彰化縣鹿港鎮中正路598號1樓、5至8樓</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>(08)7320099</t>
+          <t>(04)7785727</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026/12/14</t>
+          <t>2029/03/02</t>
         </is>
       </c>
     </row>
@@ -6911,32 +6911,32 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>勝利131民宿</t>
+          <t>凱旋酒店</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>屏東縣屏東市勝利路131號</t>
+          <t>臺北市內湖區江南街55號3樓至9樓</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>(08)7320099</t>
+          <t>(02)87527888#6203</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026/12/14</t>
+          <t>2026/12/10</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>寒居酒店</t>
+          <t>凱達大飯店</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>臺北市中山區松江路116號1樓至9樓</t>
+          <t>臺北市萬華區艋舺大道167號1-26樓</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>(02)66008000#8886</t>
+          <t>(02)23836789#6321</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2028/07/17</t>
+          <t>2027/06/02</t>
         </is>
       </c>
     </row>
@@ -6985,32 +6985,32 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>寒軒國際大飯店</t>
+          <t>凱撒大飯店</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>高雄市苓雅區四維三路三十三號</t>
+          <t>屏東縣恆春鎮墾丁路6號</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>(0980)556224</t>
+          <t>(08)8861888</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2028/12/11</t>
+          <t>2028/09/16</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>富光大旅社</t>
+          <t>勝利127民宿</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公園路19-7號</t>
+          <t>屏東縣屏東市勝利路127號</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>(08)7345656</t>
+          <t>(08)7320099</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2028/05/28</t>
+          <t>2026/12/14</t>
         </is>
       </c>
     </row>
@@ -7059,32 +7059,32 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>富信大飯店</t>
+          <t>勝利131民宿</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>新北市汐止區大同路一段152號</t>
+          <t>屏東縣屏東市勝利路131號</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>(02)26416422#5112</t>
+          <t>(08)7320099</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2028/03/13</t>
+          <t>2026/12/14</t>
         </is>
       </c>
     </row>
@@ -7096,32 +7096,32 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>富翔大飯店</t>
+          <t>寒居酒店</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>宜蘭縣宜蘭市校舍路19號</t>
+          <t>臺北市中山區松江路116號1樓至9樓</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>(03)9388386</t>
+          <t>(02)66008000#8886</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2029/09/28</t>
+          <t>2028/07/17</t>
         </is>
       </c>
     </row>
@@ -7133,32 +7133,32 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>尊爵大飯店</t>
+          <t>寒軒國際大飯店</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>桃園市桃園區莊敬路一段300號</t>
+          <t>高雄市苓雅區四維三路三十三號</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>(03)3169090#8502</t>
+          <t>(0980)556224</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026/12/21</t>
+          <t>2028/12/11</t>
         </is>
       </c>
     </row>
@@ -7170,32 +7170,32 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>尊爵天際大飯店</t>
+          <t>富光大旅社</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>桃園市蘆竹區南崁路一段108號</t>
+          <t>屏東縣屏東市公園路19-7號</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>(03)2228100#6081</t>
+          <t>(08)7345656</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2028/08/31</t>
+          <t>2028/05/28</t>
         </is>
       </c>
     </row>
@@ -7207,32 +7207,32 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>惠來谷關溫泉會館</t>
+          <t>富信大飯店</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>臺中市和平區東關路一段溫泉巷十號</t>
+          <t>新北市汐止區大同路一段152號</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>(04)25951998#621</t>
+          <t>(02)26416422#5112</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2029/08/13</t>
+          <t>2028/03/13</t>
         </is>
       </c>
     </row>
@@ -7244,22 +7244,22 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>提米好旅</t>
+          <t>富翔大飯店</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>彰化縣彰化市成功路277號</t>
+          <t>宜蘭縣宜蘭市校舍路19號</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>(04)7061086#9</t>
+          <t>(03)9388386</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>2029/09/28</t>
         </is>
       </c>
     </row>
@@ -7281,32 +7281,32 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>揚昊民宿</t>
+          <t>尊爵大飯店</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之6號</t>
+          <t>桃園市桃園區莊敬路一段300號</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>(037)747711#9</t>
+          <t>(03)3169090#8502</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2028/09/08</t>
+          <t>2026/12/21</t>
         </is>
       </c>
     </row>
@@ -7318,32 +7318,32 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>晶泉丰旅</t>
+          <t>尊爵天際大飯店</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉溫泉路67號2至10樓</t>
+          <t>桃園市蘆竹區南崁路一段108號</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>(03)9100000#6105</t>
+          <t>(03)2228100#6081</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2027/05/22</t>
+          <t>2028/08/31</t>
         </is>
       </c>
     </row>
@@ -7355,22 +7355,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>智醫康寓</t>
+          <t>惠來谷關溫泉會館</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>桃園市桃園區民生路107號1-3樓及7-20樓</t>
+          <t>臺中市和平區東關路一段溫泉巷十號</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>(03)3362575</t>
+          <t>(04)25951998#621</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026/10/30</t>
+          <t>2029/08/13</t>
         </is>
       </c>
     </row>
@@ -7392,22 +7392,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>湛藍海寓民宿</t>
+          <t>提米好旅</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>嘉義縣東石鄉東石村12鄰東石6之16號</t>
+          <t>彰化縣彰化市成功路277號</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>(05)3730252</t>
+          <t>(04)7061086#9</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2029/10/13</t>
+          <t>2027/11/27</t>
         </is>
       </c>
     </row>
@@ -7429,32 +7429,32 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>渴望會館</t>
+          <t>揚昊民宿</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>桃園市龍潭區渴望路428號3-5樓</t>
+          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之6號</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>(03)4072999#7110</t>
+          <t>(037)747711#9</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2028/11/02</t>
+          <t>2028/09/08</t>
         </is>
       </c>
     </row>
@@ -7466,32 +7466,32 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>然一酒店</t>
+          <t>晶泉丰旅</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>高雄市前鎮區中山二路199號</t>
+          <t>宜蘭縣礁溪鄉溫泉路67號2至10樓</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>(07)9730186#1666</t>
+          <t>(03)9100000#6105</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2027/06/03</t>
+          <t>2027/05/22</t>
         </is>
       </c>
     </row>
@@ -7503,22 +7503,22 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>發現號特色民宿</t>
+          <t>智醫康寓</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>屏東縣林邊鄉崎峰村裕後路90號</t>
+          <t>桃園市桃園區民生路107號1-3樓及7-20樓</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>(08)8750300</t>
+          <t>(03)3362575</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2026/10/30</t>
         </is>
       </c>
     </row>
@@ -7540,32 +7540,32 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>華泰瑞苑</t>
+          <t>湛藍海寓民宿</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮公園路101號</t>
+          <t>嘉義縣東石鄉東石村12鄰東石6之16號</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>(08)8863666</t>
+          <t>(05)3730252</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2027/06/21</t>
+          <t>2029/10/13</t>
         </is>
       </c>
     </row>
@@ -7577,32 +7577,32 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>華園大飯店草衙館</t>
+          <t>渴望會館</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>高雄市前鎮區中安路一號</t>
+          <t>桃園市龍潭區渴望路428號3-5樓</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>(07)2410123#220</t>
+          <t>(03)4072999#7110</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2029/10/06</t>
+          <t>2028/11/02</t>
         </is>
       </c>
     </row>
@@ -7614,32 +7614,32 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>貳十二度行旅</t>
+          <t>然一酒店</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>宜蘭縣蘇澳鎮信義路177號</t>
+          <t>高雄市前鎮區中山二路199號</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>(03)9901888</t>
+          <t>(07)9730186#1666</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2029/05/24</t>
+          <t>2027/06/03</t>
         </is>
       </c>
     </row>
@@ -7651,32 +7651,32 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>陽明山天籟渡假酒店</t>
+          <t>發現號特色民宿</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>新北市金山區名流路1之6號、1之7號、1之9號、1之9號5樓及1之9號5樓之1至之8</t>
+          <t>屏東縣林邊鄉崎峰村裕後路90號</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>(02)24080400#1700</t>
+          <t>(08)8750300</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2029/02/11</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -7688,32 +7688,32 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>雅霖大飯店</t>
+          <t>華泰瑞苑</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市同和路100號</t>
+          <t>屏東縣恆春鎮公園路101號</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>(06)9261366</t>
+          <t>(08)8863666</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2027/06/21</t>
         </is>
       </c>
     </row>
@@ -7725,32 +7725,32 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>雲品溫泉酒店日月潭</t>
+          <t>華園大飯店草衙館</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉水社村中正路23號</t>
+          <t>高雄市前鎮區中安路一號</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>(049)2212959</t>
+          <t>(07)2410123#220</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2029/05/05</t>
+          <t>2029/10/06</t>
         </is>
       </c>
     </row>
@@ -7762,22 +7762,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>雲頂國際商旅</t>
+          <t>貳十二度行旅</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>臺南市南區大同路二段530號</t>
+          <t>宜蘭縣蘇澳鎮信義路177號</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>(06)2687766</t>
+          <t>(03)9901888</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2029/02/25</t>
+          <t>2029/05/24</t>
         </is>
       </c>
     </row>
@@ -7799,22 +7799,22 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>圓山大飯店</t>
+          <t>陽明山天籟渡假酒店</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>臺北市中山區中山北路4段1巷1號</t>
+          <t>新北市金山區名流路1之6號、1之7號、1之9號、1之9號5樓及1之9號5樓之1至之8</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>(02)28861818#1007</t>
+          <t>(02)24080400#1700</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2028/05/14</t>
+          <t>2029/02/11</t>
         </is>
       </c>
     </row>
@@ -7836,22 +7836,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>奧斯卡去旅行民宿</t>
+          <t>雅霖大飯店</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>臺東縣臺東市興安路一段167號</t>
+          <t>澎湖縣馬公市同和路100號</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>(0910)633944</t>
+          <t>(06)9261366</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2027/01/29</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -7873,32 +7873,32 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>奧斯卡民宿</t>
+          <t>雲品溫泉酒店日月潭</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>臺東縣台東市興安路1段175號</t>
+          <t>南投縣魚池鄉水社村中正路23號</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>(0965)329000</t>
+          <t>(049)2212959</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2027/01/18</t>
+          <t>2029/05/05</t>
         </is>
       </c>
     </row>
@@ -7910,22 +7910,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>新竹安捷國際酒店</t>
+          <t>雲頂國際商旅</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>新竹縣竹北市復興三路二段168號14樓-18樓</t>
+          <t>臺南市南區大同路二段530號</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>(03)6209777#660</t>
+          <t>(06)2687766</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2028/07/13</t>
+          <t>2029/02/25</t>
         </is>
       </c>
     </row>
@@ -7947,32 +7947,32 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>新竹老爺大酒店</t>
+          <t>圓山大飯店</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>新竹市東區光復路一段227號</t>
+          <t>臺北市中山區中山北路4段1巷1號</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>(03)5631285#204</t>
+          <t>(02)28861818#1007</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2028/11/10</t>
+          <t>2028/05/14</t>
         </is>
       </c>
     </row>
@@ -7984,32 +7984,32 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>新竹喜來登大飯店</t>
+          <t>奧斯卡去旅行民宿</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>新竹縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>新竹縣竹北市光明六路東一段265號</t>
+          <t>臺東縣臺東市興安路一段167號</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>(03)6206126</t>
+          <t>(0910)633944</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2027/01/29</t>
         </is>
       </c>
     </row>
@@ -8021,22 +8021,22 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>新竹福華大飯店</t>
+          <t>奧斯卡民宿</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>新竹市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>新竹市中正路178號</t>
+          <t>臺東縣台東市興安路1段175號</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>(03)5282323#5303</t>
+          <t>(0965)329000</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2027/01/18</t>
         </is>
       </c>
     </row>
@@ -8058,22 +8058,22 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>新南一二文創商行</t>
+          <t>新竹安捷國際酒店</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>桃園市大溪區中山路１２號</t>
+          <t>新竹縣竹北市復興三路二段168號14樓-18樓</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>(03)3884466</t>
+          <t>(03)6209777#660</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2029/02/05</t>
+          <t>2028/07/13</t>
         </is>
       </c>
     </row>
@@ -8095,32 +8095,32 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>新悦花園酒店</t>
+          <t>新竹老爺大酒店</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>嘉義市東區後湖里6鄰保順路69號</t>
+          <t>新竹市東區光復路一段227號</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>(05)2777266#5801</t>
+          <t>(03)5631285#204</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2027/04/07</t>
+          <t>2028/11/10</t>
         </is>
       </c>
     </row>
@@ -8132,22 +8132,22 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>溪頭福華渡假飯店-溪頭漢光樓</t>
+          <t>新竹喜來登大飯店</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>新竹縣</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>南投縣鹿谷鄉森林巷11、12號</t>
+          <t>新竹縣竹北市光明六路東一段265號</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>(049)2612588#3005</t>
+          <t>(03)6206126</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2028/12/01</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -8169,22 +8169,22 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>溪邊小築民宿</t>
+          <t>新竹福華大飯店</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>新竹市</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>新北市瑞芳區祈堂路133號</t>
+          <t>新竹市中正路178號</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>(02)24961191</t>
+          <t>(03)5282323#5303</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2029/06/21</t>
+          <t>2026/10/26</t>
         </is>
       </c>
     </row>
@@ -8206,32 +8206,32 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>煙波大飯店臺南館</t>
+          <t>新南一二文創商行</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>臺南市中西區永福路1段269號1-12樓及地下一層至三層</t>
+          <t>桃園市大溪區中山路１２號</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>(06)2156000#1171</t>
+          <t>(03)3884466</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2029/06/09</t>
+          <t>2029/02/05</t>
         </is>
       </c>
     </row>
@@ -8243,22 +8243,22 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>煙波大飯店宜蘭館</t>
+          <t>新悦花園酒店</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>宜蘭縣宜蘭市凱旋路135號 、135號2至9樓</t>
+          <t>嘉義市東區後湖里6鄰保順路69號</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>(09)9256899#1171</t>
+          <t>(05)2777266#5801</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2029/05/06</t>
+          <t>2027/04/07</t>
         </is>
       </c>
     </row>
@@ -8280,32 +8280,32 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮太魯閣山闊館</t>
+          <t>溪頭福華渡假飯店-溪頭漢光樓</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村草林10-7號</t>
+          <t>南投縣鹿谷鄉森林巷11、12號</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>(03)8612000#1470</t>
+          <t>(049)2612588#3005</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026/11/05</t>
+          <t>2028/12/01</t>
         </is>
       </c>
     </row>
@@ -8317,32 +8317,32 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮太魯閣沁海館</t>
+          <t>溪邊小築民宿</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村6鄰草林10之6號</t>
+          <t>新北市瑞芳區祈堂路133號</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>(03)8228835#1174</t>
+          <t>(02)24961191</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2029/04/19</t>
+          <t>2029/06/21</t>
         </is>
       </c>
     </row>
@@ -8354,22 +8354,22 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>煙波大飯店花蓮館</t>
+          <t>煙波大飯店臺南館</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市民立里1鄰中美路142號</t>
+          <t>臺南市中西區永福路1段269號1-12樓及地下一層至三層</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>(03)8228835#1174</t>
+          <t>(06)2156000#1171</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2029/04/19</t>
+          <t>2029/06/09</t>
         </is>
       </c>
     </row>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>煙波花時間 宜蘭傳藝</t>
+          <t>煙波大飯店宜蘭館</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉五濱路二段201號</t>
+          <t>宜蘭縣宜蘭市凱旋路135號 、135號2至9樓</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>(03)9256899#1171</t>
+          <t>(09)9256899#1171</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2027/07/09</t>
+          <t>2029/05/06</t>
         </is>
       </c>
     </row>
@@ -8428,7 +8428,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>煙波花時間 花蓮</t>
+          <t>煙波大飯店花蓮太魯閣山闊館</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉順安村草林10-5號2~6樓</t>
+          <t>花蓮縣新城鄉順安村草林10-7號</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026/11/16</t>
+          <t>2026/11/05</t>
         </is>
       </c>
     </row>
@@ -8465,7 +8465,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>瑞穗天合國際觀光酒店</t>
+          <t>煙波大飯店花蓮太魯閣沁海館</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8475,22 +8475,22 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>花蓮縣瑞穗鄉溫泉路二段368號</t>
+          <t>花蓮縣新城鄉順安村6鄰草林10之6號</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>(03)8876000#3260</t>
+          <t>(03)8228835#1174</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2028/01/19</t>
+          <t>2029/04/19</t>
         </is>
       </c>
     </row>
@@ -8502,32 +8502,32 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>裕元花園酒店</t>
+          <t>煙波大飯店花蓮館</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>臺中市西屯區臺灣大道四段610號</t>
+          <t>花蓮縣花蓮市民立里1鄰中美路142號</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>(04)24655660#5030</t>
+          <t>(03)8228835#1174</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2027/11/19</t>
+          <t>2029/04/19</t>
         </is>
       </c>
     </row>
@@ -8539,32 +8539,32 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>遇見民宿</t>
+          <t>煙波花時間 宜蘭傳藝</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>屏東縣東港鎮水源路221號(新和段737-4地號)</t>
+          <t>宜蘭縣五結鄉五濱路二段201號</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>(08)8333345</t>
+          <t>(03)9256899#1171</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2027/07/09</t>
         </is>
       </c>
     </row>
@@ -8576,32 +8576,32 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>頌華私墅肆區民宿</t>
+          <t>煙波花時間 花蓮</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>澎湖縣湖西鄉許家村6鄰港子尾120之5號</t>
+          <t>花蓮縣新城鄉順安村草林10-5號2~6樓</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>(06)9212953</t>
+          <t>(03)8612000#1470</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2029/01/25</t>
+          <t>2026/11/16</t>
         </is>
       </c>
     </row>
@@ -8613,32 +8613,32 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>嘉仕特飯店</t>
+          <t>瑞穗天合國際觀光酒店</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>桃園市桃園區中山路203號</t>
+          <t>花蓮縣瑞穗鄉溫泉路二段368號</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>(03)3343999</t>
+          <t>(03)8876000#3260</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2027/11/27</t>
+          <t>2028/01/19</t>
         </is>
       </c>
     </row>
@@ -8650,32 +8650,32 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>嘉義富野渡假酒店</t>
+          <t>葉綠宿 川閱</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>嘉義縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>嘉義縣民雄鄉三興村升學一街3、5、7、9、11、13、15、17、19、21、23、25、27號</t>
+          <t>臺中市中區綠川西街123號8樓之1至12樓之1</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>(05)2721688</t>
+          <t>(04)22231789#無</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2028/08/12</t>
+          <t>2029/10/24</t>
         </is>
       </c>
     </row>
@@ -8687,32 +8687,32 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>嘉義智選假日酒店</t>
+          <t>裕元花園酒店</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>嘉義市西區中興路69號B2至13層樓</t>
+          <t>臺中市西屯區臺灣大道四段610號</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>(05)2335899#801</t>
+          <t>(04)24655660#5030</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2027/11/24</t>
+          <t>2027/11/19</t>
         </is>
       </c>
     </row>
@@ -8724,32 +8724,32 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>嘉義福容voco酒店</t>
+          <t>遇見民宿</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>嘉義市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>嘉義市西區世賢路一段789號B4-4樓、7樓、16樓-32樓</t>
+          <t>屏東縣東港鎮水源路221號(新和段737-4地號)</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>(05)232338971</t>
+          <t>(08)8333345</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2029/06/15</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -8761,22 +8761,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>夢想森林親子民宿</t>
+          <t>頌華私墅肆區民宿</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉三星鄉大德路二段613號</t>
+          <t>澎湖縣湖西鄉許家村6鄰港子尾120之5號</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>(03)9898113</t>
+          <t>(06)9212953</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2029/01/19</t>
+          <t>2029/01/25</t>
         </is>
       </c>
     </row>
@@ -8798,32 +8798,32 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>榮美金鬱金香酒店</t>
+          <t>嘉仕特飯店</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>臺南市北區海安路三段50號</t>
+          <t>桃園市桃園區中山路203號</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>(06)2200800#6001</t>
+          <t>(03)3343999</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2027/11/04</t>
+          <t>2027/11/27</t>
         </is>
       </c>
     </row>
@@ -8835,32 +8835,32 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>榮興金鬱金香酒店</t>
+          <t>嘉義富野渡假酒店</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>嘉義縣</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>臺南市中西區民族路二段128號</t>
+          <t>嘉義縣民雄鄉三興村升學一街3、5、7、9、11、13、15、17、19、21、23、25、27號</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>(06)2200800#6006</t>
+          <t>(05)2721688</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2027/11/04</t>
+          <t>2028/08/12</t>
         </is>
       </c>
     </row>
@@ -8872,22 +8872,22 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>福美民宿</t>
+          <t>嘉義智選假日酒店</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>臺東縣台東市精誠路241號</t>
+          <t>嘉義市西區中興路69號B2至13層樓</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>(089)328466</t>
+          <t>(05)2335899#801</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2027/01/09</t>
+          <t>2027/11/24</t>
         </is>
       </c>
     </row>
@@ -8909,22 +8909,22 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>福容大飯店 臺北二館</t>
+          <t>嘉義福容voco酒店</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>嘉義市</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>新北市深坑區北深路三段236號</t>
+          <t>嘉義市西區世賢路一段789號B4-4樓、7樓、16樓-32樓</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>(02)26620088#186</t>
+          <t>(05)232338971</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2028/01/05</t>
+          <t>2029/06/15</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>福容大飯店 桃園</t>
+          <t>夢想森林親子民宿</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>桃園市桃園區同安里大興西路一段200號</t>
+          <t>宜蘭縣三星鄉三星鄉大德路二段613號</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>(03)3265800#300</t>
+          <t>(03)9898113</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2027/12/17</t>
+          <t>2029/01/19</t>
         </is>
       </c>
     </row>
@@ -8983,22 +8983,22 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>福容大飯店 桃園機場捷運 A8</t>
+          <t>榮美金鬱金香酒店</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>桃園市龜山區復興一路2號3樓</t>
+          <t>臺南市北區海安路三段50號</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>(03)3285688#8770</t>
+          <t>(06)2200800#6001</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2027/08/12</t>
+          <t>2027/11/04</t>
         </is>
       </c>
     </row>
@@ -9020,32 +9020,32 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>福容大飯店 高雄</t>
+          <t>榮興金鬱金香酒店</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區五福四路45號</t>
+          <t>臺南市中西區民族路二段128號</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>(07)5317777#7782</t>
+          <t>(06)2200800#6006</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2028/08/14</t>
+          <t>2027/11/04</t>
         </is>
       </c>
     </row>
@@ -9057,32 +9057,32 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>福容大飯店 淡水漁人碼頭</t>
+          <t>福美民宿</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>新北市淡水區觀海路83號</t>
+          <t>臺東縣台東市精誠路241號</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>(02)2805 9958#8178</t>
+          <t>(089)328466</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2028/11/16</t>
+          <t>2027/01/09</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>福容大飯店　福隆</t>
+          <t>福容大飯店 臺北二館</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -9104,12 +9104,12 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>新北市貢寮區福隆里福隆街41號</t>
+          <t>新北市深坑區北深路三段236號</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>(02)24992381</t>
+          <t>(02)26620088#186</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2028/01/05</t>
         </is>
       </c>
     </row>
@@ -9131,22 +9131,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>福容大飯店 墾丁</t>
+          <t>福容大飯店 桃園</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮船帆路1000號</t>
+          <t>桃園市桃園區同安里大興西路一段200號</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>(08)8856969#340</t>
+          <t>(03)3265800#300</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2028/05/28</t>
+          <t>2027/12/17</t>
         </is>
       </c>
     </row>
@@ -9168,32 +9168,32 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>福容大飯店 麗寶樂園</t>
+          <t>福容大飯店 桃園機場捷運 A8</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>臺中市后里區福容路88號</t>
+          <t>桃園市龜山區復興一路2號3樓</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>(04)25571366#8343</t>
+          <t>(03)3285688#8770</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2029/03/19</t>
+          <t>2027/08/12</t>
         </is>
       </c>
     </row>
@@ -9205,32 +9205,32 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>福容大飯店花蓮</t>
+          <t>福容大飯店 高雄</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市民生路51號</t>
+          <t>高雄市鹽埕區五福四路45號</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>(03)8239988#7507</t>
+          <t>(07)5317777#7782</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2027/11/10</t>
+          <t>2028/08/14</t>
         </is>
       </c>
     </row>
@@ -9242,22 +9242,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>福容徠旅 水里</t>
+          <t>福容大飯店 淡水漁人碼頭</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>南投縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>南投縣水里鄉東三街51號1樓至6樓</t>
+          <t>新北市淡水區觀海路83號</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>(049)2771888#5560</t>
+          <t>(02)2805 9958#8178</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2029/07/09</t>
+          <t>2028/11/16</t>
         </is>
       </c>
     </row>
@@ -9279,32 +9279,32 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>福容徠旅林口</t>
+          <t>福容大飯店　福隆</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>桃園市龜山區文二一街68號</t>
+          <t>新北市貢寮區福隆里福隆街41號</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>(03)3277388#300</t>
+          <t>(02)24992381</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2027/12/03</t>
+          <t>2027/01/11</t>
         </is>
       </c>
     </row>
@@ -9316,32 +9316,32 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>福容徠旅高雄</t>
+          <t>福容大飯店 墾丁</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>高雄市前金區永恆街3號6-14樓</t>
+          <t>屏東縣恆春鎮船帆路1000號</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>(07)2156688#6309</t>
+          <t>(08)8856969#340</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2029/03/17</t>
+          <t>2028/05/28</t>
         </is>
       </c>
     </row>
@@ -9353,32 +9353,32 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>福華大飯店</t>
+          <t>福容大飯店 麗寶樂園</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>臺北市大安區仁愛路三段160號</t>
+          <t>臺中市后里區福容路88號</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>(02)27002323#2411</t>
+          <t>(04)25571366#8343</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2029/03/19</t>
         </is>
       </c>
     </row>
@@ -9390,22 +9390,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>福華石門水庫渡假飯店</t>
+          <t>福容大飯店花蓮</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>桃園市龍潭區民富街176號</t>
+          <t>花蓮縣花蓮市民生路51號</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>(03)4714888</t>
+          <t>(03)8239988#7507</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -9427,32 +9427,32 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>福華國際文教會館</t>
+          <t>福容徠旅 水里</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>南投縣</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>臺北市大安區新生南路3段30號(住宿棟1樓及5樓至14樓)</t>
+          <t>南投縣水里鄉東三街51號1樓至6樓</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>(02)77122323#2340</t>
+          <t>(049)2771888#5560</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2027/12/11</t>
+          <t>2029/07/09</t>
         </is>
       </c>
     </row>
@@ -9464,32 +9464,32 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>福爾摩沙遊艇酒店</t>
+          <t>福容徠旅林口</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>臺南市安平區王城里13鄰安平路988號1至10樓</t>
+          <t>桃園市龜山區文二一街68號</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>(06)3911313</t>
+          <t>(03)3277388#300</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2027/02/27</t>
+          <t>2027/12/03</t>
         </is>
       </c>
     </row>
@@ -9501,32 +9501,32 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>綠意山莊民宿</t>
+          <t>福容徠旅高雄</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之5號</t>
+          <t>高雄市前金區永恆街3號6-14樓</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>(037)747711#9</t>
+          <t>(07)2156688#6309</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2028/09/08</t>
+          <t>2029/03/17</t>
         </is>
       </c>
     </row>
@@ -9538,32 +9538,32 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>綠藤輕旅</t>
+          <t>福華大飯店</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>桃園市大園區中山南路二段673號</t>
+          <t>臺北市大安區仁愛路三段160號</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>(03)2873043</t>
+          <t>(02)27002323#2411</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2026/10/26</t>
         </is>
       </c>
     </row>
@@ -9575,32 +9575,32 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>維悅酒店</t>
+          <t>福華石門水庫渡假飯店</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>臺南市安平區慶平路539號 1至5樓及地下1樓</t>
+          <t>桃園市龍潭區民富街176號</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>(06)2950888#1125</t>
+          <t>(03)4714888</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2027/09/01</t>
+          <t>2027/11/10</t>
         </is>
       </c>
     </row>
@@ -9612,32 +9612,32 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>臺中逢甲智選假日酒店</t>
+          <t>福華國際文教會館</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>臺中市西屯區福星北三街33巷28號</t>
+          <t>臺北市大安區新生南路3段30號(住宿棟1樓及5樓至14樓)</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>(04)27083911#6101</t>
+          <t>(02)77122323#2340</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/12/11</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>臺邦商旅</t>
+          <t>福爾摩沙遊艇酒店</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9659,22 +9659,22 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>臺南市安平區永華二街199號</t>
+          <t>臺南市安平區王城里13鄰安平路988號1至10樓</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>(06)2931800#8603</t>
+          <t>(06)3911313</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>查無資料</t>
+          <t>2027/02/27</t>
         </is>
       </c>
     </row>
@@ -9686,22 +9686,22 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>遠雄悅來大飯店</t>
+          <t>綠意山莊民宿</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>花蓮縣壽豐鄉鹽寮村山嶺18號</t>
+          <t>苗栗縣苑裡鎮蕉埔里8鄰蕉埔86之5號</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>(03)8123900#8266</t>
+          <t>(037)747711#9</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2028/12/29</t>
+          <t>2028/09/08</t>
         </is>
       </c>
     </row>
@@ -9723,22 +9723,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>鳳山79 背包客</t>
+          <t>綠藤輕旅</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>高雄市鳳山區黃埔新村東一巷79號</t>
+          <t>桃園市大園區中山南路二段673號</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>(07)5524545</t>
+          <t>(03)2873043</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2028/12/03</t>
+          <t>2026/12/07</t>
         </is>
       </c>
     </row>
@@ -9760,32 +9760,32 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>劍湖山渡假大飯店</t>
+          <t>維悅酒店</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>雲林縣古坑鄉永光村大湖口67-8號</t>
+          <t>臺南市安平區慶平路539號 1至5樓及地下1樓</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>(05)5829900#7214</t>
+          <t>(06)2950888#1125</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2027/06/03</t>
+          <t>2027/09/01</t>
         </is>
       </c>
     </row>
@@ -9797,22 +9797,22 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>澄悅商旅</t>
+          <t>臺中逢甲智選假日酒店</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮埔崙里中正路510巷1號</t>
+          <t>臺中市西屯區福星北三街33巷28號</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>(04)7785727</t>
+          <t>(04)27083911#6101</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2029/09/07</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9834,32 +9834,32 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>澎湖福朋喜來登酒店</t>
+          <t>臺邦商旅</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市新店路197號</t>
+          <t>臺南市安平區永華二街199號</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>(06)9279955#3701</t>
+          <t>(06)2931800#8603</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2028/05/27</t>
+          <t>查無資料</t>
         </is>
       </c>
     </row>
@@ -9871,32 +9871,32 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>澎澄飯店</t>
+          <t>遠雄悅來大飯店</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>澎湖縣馬公市同和路168號</t>
+          <t>花蓮縣壽豐鄉鹽寮村山嶺18號</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>(06)9235678#2103</t>
+          <t>(03)8123900#8266</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2029/08/03</t>
+          <t>2028/12/29</t>
         </is>
       </c>
     </row>
@@ -9908,32 +9908,32 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>緻麗伯爵酒店</t>
+          <t>鳳山79 背包客</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>雲林縣斗六市中山路6號</t>
+          <t>高雄市鳳山區黃埔新村東一巷79號</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>(05)5341666#3</t>
+          <t>(07)5524545</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2029/02/10</t>
+          <t>2028/12/03</t>
         </is>
       </c>
     </row>
@@ -9945,32 +9945,32 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>緣羊軒民宿</t>
+          <t>劍湖山渡假大飯店</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>臺東縣台東市南一街96號</t>
+          <t>雲林縣古坑鄉永光村大湖口67-8號</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>089326400</t>
+          <t>(05)5829900#7214</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026/12/05</t>
+          <t>2027/06/03</t>
         </is>
       </c>
     </row>
@@ -9982,32 +9982,32 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺北</t>
+          <t>澄悅商旅</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
+          <t>彰化縣鹿港鎮埔崙里中正路510巷1號</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>(02)29583000#7701</t>
+          <t>(04)7785727</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2028/03/31</t>
+          <t>2029/09/07</t>
         </is>
       </c>
     </row>
@@ -10019,32 +10019,32 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>趣淘漫旅-臺東</t>
+          <t>澎湖福朋喜來登酒店</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>臺東縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>臺東縣台東市新站路260號</t>
+          <t>澎湖縣馬公市新店路197號</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>(089)231188#7187</t>
+          <t>(06)9279955#3701</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2027/12/05</t>
+          <t>2028/05/27</t>
         </is>
       </c>
     </row>
@@ -10056,32 +10056,32 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>墾丁夏都沙灘酒店</t>
+          <t>澎澄飯店</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁路451號</t>
+          <t>澎湖縣馬公市同和路168號</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>(0910)371823</t>
+          <t>(06)9235678#2103</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2028/03/09</t>
+          <t>2029/08/03</t>
         </is>
       </c>
     </row>
@@ -10093,32 +10093,32 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>墾丁福華渡假飯店</t>
+          <t>緻麗伯爵酒店</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
+          <t>雲林縣斗六市中山路6號</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>(08)8862324#2701</t>
+          <t>(05)5341666#3</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2029/04/12</t>
+          <t>2029/02/10</t>
         </is>
       </c>
     </row>
@@ -10130,22 +10130,22 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>橘子民宿</t>
+          <t>緣羊軒民宿</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
+          <t>臺東縣台東市南一街96號</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>(0972)092658</t>
+          <t>089326400</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2027/11/06</t>
+          <t>2026/12/05</t>
         </is>
       </c>
     </row>
@@ -10167,22 +10167,22 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>翰品酒店 高雄</t>
+          <t>趣淘漫旅-臺北</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>高雄市鹽埕區大仁路43號</t>
+          <t>新北市板橋區中山路1段139號(1至2層)、139號4樓至20樓</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>(07)5614688#3110</t>
+          <t>(02)29583000#7701</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2027/02/16</t>
+          <t>2028/03/31</t>
         </is>
       </c>
     </row>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>興源行民宿</t>
+          <t>趣淘漫旅-臺東</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -10214,12 +10214,12 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>臺東縣關山鎮中福里15鄰中山路16號</t>
+          <t>臺東縣台東市新站路260號</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>(0921)578123</t>
+          <t>(089)231188#7187</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2029/10/13</t>
+          <t>2027/12/05</t>
         </is>
       </c>
     </row>
@@ -10241,32 +10241,32 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>礁溪老爺酒店</t>
+          <t>墾丁夏都沙灘酒店</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
+          <t>屏東縣恆春鎮墾丁路451號</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>(03)9885211#8006</t>
+          <t>(0910)371823</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2028/08/24</t>
+          <t>2028/03/09</t>
         </is>
       </c>
     </row>
@@ -10278,32 +10278,32 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>礁溪寒沐酒店</t>
+          <t>墾丁福華渡假飯店</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
+          <t>屏東縣恆春鎮墾丁里墾丁路2號</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>(03)9058007</t>
+          <t>(08)8862324#2701</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>金級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2029/04/12</t>
         </is>
       </c>
     </row>
@@ -10315,32 +10315,32 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>禧榕軒大飯店</t>
+          <t>橘子民宿</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>苗栗縣</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>臺南市北區成功路28號</t>
+          <t>苗栗縣竹南鎮竹南里7鄰民治街12號</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>(06)2222788#2203</t>
+          <t>(0972)092658</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2029/05/10</t>
+          <t>2027/11/06</t>
         </is>
       </c>
     </row>
@@ -10352,32 +10352,32 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>薆悅酒店野柳渡假館一館</t>
+          <t>翰品酒店 高雄</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>新北市萬里區野柳里港東路162號之2</t>
+          <t>高雄市鹽埕區大仁路43號</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>(02)77035770#623</t>
+          <t>(07)5614688#3110</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2028/12/14</t>
+          <t>2027/02/16</t>
         </is>
       </c>
     </row>
@@ -10389,22 +10389,22 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>藍水輕旅</t>
+          <t>興源行民宿</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺東縣</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>桃園市大園區高鐵南路一段126號</t>
+          <t>臺東縣關山鎮中福里15鄰中山路16號</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>(03)2871855</t>
+          <t>(0921)578123</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2029/10/13</t>
         </is>
       </c>
     </row>
@@ -10426,32 +10426,32 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>關子嶺富野溫泉會館</t>
+          <t>礁溪老爺酒店</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>臺南市白河區關子嶺28號</t>
+          <t>宜蘭縣礁溪鄉大忠村五峰路69號、69-1號</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>(06)6822288</t>
+          <t>(03)9885211#8006</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2029/01/07</t>
+          <t>2028/08/24</t>
         </is>
       </c>
     </row>
@@ -10463,32 +10463,32 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>麗格休閒飯店</t>
+          <t>礁溪寒沐酒店</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市商校街258.260.262號</t>
+          <t>宜蘭縣礁溪鄉健康路1號1至14樓</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>(03)8349922</t>
+          <t>(03)9058007</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>金級環保旅宿</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2029/01/11</t>
         </is>
       </c>
     </row>
@@ -10500,32 +10500,32 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>麗軒國際飯店</t>
+          <t>禧榕軒大飯店</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市中美路99之1號</t>
+          <t>臺南市北區成功路28號</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>(03)8246898</t>
+          <t>(06)2222788#2203</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>銅級環保旅宿</t>
+          <t>銀級環保旅宿</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2029/01/08</t>
+          <t>2029/05/10</t>
         </is>
       </c>
     </row>
@@ -10537,22 +10537,22 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>麗翔大飯店</t>
+          <t>薆悅酒店野柳渡假館一館</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
+          <t>新北市萬里區野柳里港東路162號之2</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>(03)8323737</t>
+          <t>(02)77035770#623</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2028/01/12</t>
+          <t>2028/12/14</t>
         </is>
       </c>
     </row>
@@ -10574,22 +10574,22 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>讀好民宿</t>
+          <t>藍水輕旅</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
+          <t>桃園市大園區高鐵南路一段126號</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>(0920)023139</t>
+          <t>(03)2871855</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2029/01/11</t>
+          <t>2026/11/23</t>
         </is>
       </c>
     </row>
@@ -10611,32 +10611,32 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>觀霧山莊</t>
+          <t>關子嶺富野溫泉會館</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>苗栗縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
+          <t>臺南市白河區關子嶺28號</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>(03)3343818</t>
+          <t>(06)6822288</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2029/01/22</t>
+          <t>2029/01/07</t>
         </is>
       </c>
     </row>
@@ -10648,32 +10648,32 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>綉溪安平</t>
+          <t>麗格休閒飯店</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+          <t>花蓮縣花蓮市商校街258.260.262號</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>(06)3910988#3111</t>
+          <t>(03)8349922</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>銀級環保旅宿</t>
+          <t>銅級環保旅宿</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2028/10/12</t>
+          <t>2029/01/08</t>
         </is>
       </c>
     </row>
@@ -10685,30 +10685,215 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
+          <t>麗軒國際飯店</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>花蓮縣</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>花蓮縣花蓮市中美路99之1號</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>(03)8246898</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>2029/01/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>麗翔大飯店</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>花蓮縣</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>花蓮縣花蓮市花崗街2、4、6、8、10號</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>(03)8323737</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>2028/01/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>讀好民宿</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>宜蘭縣</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>宜蘭縣五結鄉五結中路二段241巷7弄16號</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>(0920)023139</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>2029/01/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>觀霧山莊</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>苗栗縣</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>苗栗縣泰安鄉梅園村觀霧8號</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>(03)3343818</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>銀級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>2029/01/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>綉溪安平</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>臺南市</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>臺南市安平區王城里12鄰古堡街136號、138號、138之1號</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>(06)3910988#3111</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>銀級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>2028/10/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>環保標章旅宿</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
           <t>鐡馬騎跡</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
+      <c r="C283" t="inlineStr">
         <is>
           <t>屏東縣</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr">
+      <c r="D283" t="inlineStr">
         <is>
           <t>屏東縣東港鎮新學路50號</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
+      <c r="E283" t="inlineStr">
         <is>
           <t>(0952)848898</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>銅級環保旅宿</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>銅級環保旅宿</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
         <is>
           <t>2029/01/18</t>
         </is>
